--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -803,54 +803,54 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0.8333333333333333</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>-1</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>-10.5</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>10.5</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-7.666666666666666</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AJ2" t="n">
         <v>-0.7333333333333329</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AK2" t="n">
         <v>-0.8333333333333335</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-0.5</v>
       </c>
       <c r="AL2" t="n">
         <v>71.22727272727272</v>
@@ -858,49 +858,49 @@
       <c r="AM2" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="n">
+        <v>-29846130.95238096</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>1.697725122744469</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>1.610714285714284</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>-4.617364768874054</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-6.928968253968279</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-0.6529583972743467</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-20828499.91459402</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-5.53524554758107</v>
+      </c>
+      <c r="AY2" t="n">
         <v>-5.786111111111126</v>
       </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="n">
-        <v>-0.6529583972743467</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-5.53524554758107</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-20828499.91459402</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-29846130.95238096</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>-2.036111111111097</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
         <v>-0.2652031356801094</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BE2" t="n">
         <v>-0.6529761904761904</v>
       </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>-2.036111111111097</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1.610714285714284</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>-6.928968253968279</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="n">
-        <v>-4.617364768874054</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.697725122744469</v>
-      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -984,54 +984,54 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>-4.333333333333336</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>4.333333333333336</v>
       </c>
-      <c r="X3" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.416666666666666</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AJ3" t="n">
         <v>0.5366666666666666</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AK3" t="n">
         <v>0.8383333333333336</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>2.083333333333334</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-0.2</v>
       </c>
       <c r="AL3" t="n">
         <v>78.76801346801348</v>
@@ -1039,49 +1039,49 @@
       <c r="AM3" t="n">
         <v>77.85375573921029</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="n">
+        <v>-52528383.83838384</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-1.702080137329435</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>-3.228484848484843</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-7.193227926985998</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-4.290404040404042</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>4.663911373155372</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-30861818.17709465</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-3.922110422454423</v>
+      </c>
+      <c r="AY3" t="n">
         <v>-7.368484848484854</v>
       </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>4.663911373155372</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-3.922110422454423</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-30861818.17709465</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-52528383.83838384</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>0.7455555555555406</v>
+      </c>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="n">
         <v>-0.6644494615050729</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BE3" t="n">
         <v>-1.394848484848485</v>
       </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>0.7455555555555406</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-3.228484848484843</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>-4.290404040404042</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
-        <v>-7.193227926985998</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-1.702080137329435</v>
-      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1165,54 +1165,54 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>-1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AG4" t="n">
         <v>1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>12</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AI4" t="n">
         <v>-12</v>
       </c>
-      <c r="X4" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AJ4" t="n">
         <v>-0.8949999999999998</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AK4" t="n">
         <v>1.085</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
         <v>77.95454545454545</v>
@@ -1220,49 +1220,49 @@
       <c r="AM4" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="n">
+        <v>-2588798.701298706</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>-1.6851765897053</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>0.4009740259740262</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.4662913277439316</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.9415584415584277</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-3.019159858832978</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-780645.2390500437</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.164141144634812</v>
+      </c>
+      <c r="AY4" t="n">
         <v>0.08279220779220964</v>
       </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>-3.019159858832978</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.164141144634812</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-780645.2390500437</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-2588798.701298706</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>0.7142857142857224</v>
+      </c>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="n">
         <v>-0.07075274904011941</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BE4" t="n">
         <v>-0.2418831168831173</v>
       </c>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>0.7142857142857224</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.4009740259740262</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="n">
-        <v>-0.9415584415584277</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
-        <v>0.4662913277439316</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-1.6851765897053</v>
-      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1346,54 +1346,54 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>12.5</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1</v>
       </c>
       <c r="AB5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>-1</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>0.9299999999999998</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>-1.285</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-2.5</v>
       </c>
       <c r="AL5" t="n">
         <v>77.62272727272727</v>
@@ -1401,49 +1401,49 @@
       <c r="AM5" t="n">
         <v>76.5</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>-7768311.688311685</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>3.697361368789938</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>1.584415584415584</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.06373503947033043</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-1.303896103896093</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-2.482223040731469</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-4560738.276371153</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-1.855779584561105</v>
+      </c>
+      <c r="AY5" t="n">
         <v>-1.028571428571425</v>
       </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>-2.482223040731469</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-1.855779584561105</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>-4560738.276371153</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-7768311.688311685</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>0.7597402597402549</v>
+      </c>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
         <v>0.03935195290237292</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="BE5" t="n">
         <v>-0.02467532467532463</v>
       </c>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>0.7597402597402549</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.584415584415584</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="n">
-        <v>-1.303896103896093</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
-        <v>-0.06373503947033043</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>3.697361368789938</v>
-      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1527,54 +1527,54 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-21.66666666666667</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>-3.166666666666667</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>18.33333333333334</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>-18.33333333333334</v>
       </c>
-      <c r="X6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-21.66666666666667</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AJ6" t="n">
         <v>2.831666666666667</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AK6" t="n">
         <v>-2.891666666666667</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-11.33333333333333</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-3</v>
       </c>
       <c r="AL6" t="n">
         <v>75.97205387205388</v>
@@ -1582,49 +1582,49 @@
       <c r="AM6" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>47881727.43055556</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>0.3440181335692181</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>-1.880208333333332</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.096245041078632</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.868055555555557</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-1.492309818664296</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>28947364.23277445</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5.901018756784993</v>
+      </c>
+      <c r="AY6" t="n">
         <v>7.060763888888886</v>
       </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="n">
-        <v>-1.492309818664296</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5.901018756784993</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>28947364.23277445</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>47881727.43055556</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>0.07986111111111427</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="n">
         <v>0.4727499731950198</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="BE6" t="n">
         <v>0.8263888888888886</v>
       </c>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>0.07986111111111427</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1.880208333333332</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>6.868055555555557</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
-        <v>9.096245041078632</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.3440181335692181</v>
-      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1708,54 +1708,54 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>-2</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>-14.75</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>14.75</v>
       </c>
-      <c r="X7" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD7" t="n">
+      <c r="AJ7" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AK7" t="n">
         <v>-1.1925</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-2</v>
       </c>
       <c r="AL7" t="n">
         <v>77.02146464646464</v>
@@ -1763,49 +1763,49 @@
       <c r="AM7" t="n">
         <v>75.80000000000001</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="n">
+        <v>1775953.282828284</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>1.618717119284788</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>1.663816738816742</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.2109521425847163</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.9375901875902031</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.326102350265018</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-1432068.723799587</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-3.315135535049265</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.171753246753255</v>
       </c>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="n">
-        <v>8.326102350265018</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>-3.315135535049265</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>-1432068.723799587</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1775953.282828284</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>1.620490620490642</v>
+      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="n">
         <v>-0.06534905438147809</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BE7" t="n">
         <v>0.2233766233766232</v>
       </c>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>1.620490620490642</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.663816738816742</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-0.9375901875902031</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
-        <v>-0.2109521425847163</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.618717119284788</v>
-      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1889,54 +1889,54 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>-0.6000000000000001</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>2.5</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AI8" t="n">
         <v>-2.5</v>
       </c>
-      <c r="X8" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.199999999999999</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.800000000000001</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AJ8" t="n">
         <v>1.316</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AK8" t="n">
         <v>0.3799999999999999</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-0.8999999999999999</v>
       </c>
       <c r="AL8" t="n">
         <v>73.29545454545455</v>
@@ -1944,49 +1944,49 @@
       <c r="AM8" t="n">
         <v>72.99111111111111</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="n">
+        <v>14692283.05785124</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>1.409744653790366</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>0.7660123966942081</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.202640962511481</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>4.699896694214871</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.517704458265484</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>10053627.24598238</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.96223784474266</v>
+      </c>
+      <c r="AY8" t="n">
         <v>4.902169421487613</v>
       </c>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="n">
-        <v>2.517704458265484</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2.96223784474266</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>10053627.24598238</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>14692283.05785124</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>5.375206611570235</v>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="n">
         <v>0.4238095238095236</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BE8" t="n">
         <v>0.5102272727272728</v>
       </c>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>5.375206611570235</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0.7660123966942081</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="n">
-        <v>4.699896694214871</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
-        <v>3.202640962511481</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.409744653790366</v>
-      </c>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -2070,54 +2070,54 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
         <v>0.25</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>0.5</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>-8</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>8</v>
       </c>
-      <c r="X9" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD9" t="n">
+      <c r="AJ9" t="n">
         <v>-0.0349999999999997</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AK9" t="n">
         <v>-0.4700000000000002</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0.75</v>
       </c>
       <c r="AL9" t="n">
         <v>81.76666666666667</v>
@@ -2125,49 +2125,49 @@
       <c r="AM9" t="n">
         <v>80.13415404040404</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>-112321.4285714291</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>0.9000830395087078</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>0.9857142857142875</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.9510967786844304</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.2910714285714278</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>2.362852243863756</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-238945.7190112025</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.3619543532862792</v>
+      </c>
+      <c r="AY9" t="n">
         <v>-0.03749999999999432</v>
       </c>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>2.362852243863756</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.3619543532862792</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>-238945.7190112025</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-112321.4285714291</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>3.742857142857105</v>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="n">
         <v>0.1161873589842288</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BE9" t="n">
         <v>0.1089285714285715</v>
       </c>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>3.742857142857105</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.9857142857142875</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="n">
-        <v>-0.2910714285714278</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
-        <v>0.9510967786844304</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.9000830395087078</v>
-      </c>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2247,102 +2247,102 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>-2</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>-4</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>4</v>
       </c>
-      <c r="X10" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AJ10" t="n">
         <v>-0.1925000000000001</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AK10" t="n">
         <v>-1.3675</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-1.25</v>
       </c>
       <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>-45110909.09090909</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>1.938006096158269</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>0.4595959595959549</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-10.60447435012652</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-11.28787878787877</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0.06185875316307943</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-32647976.76558546</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-11.21757821486082</v>
+      </c>
+      <c r="AY10" t="n">
         <v>-12.20606060606062</v>
       </c>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>-0.06185875316307943</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>-11.21757821486082</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>-32647976.76558546</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>-45110909.09090909</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>-0.6909090909090878</v>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="n">
         <v>-0.8513400046008743</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BE10" t="n">
         <v>-1.65050505050505</v>
       </c>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>-0.6909090909090878</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.4595959595959549</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>-11.28787878787877</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
-        <v>-10.60447435012652</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.938006096158269</v>
-      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2426,54 +2426,54 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="U11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="Y11" t="n">
         <v>0.5</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>-0.75</v>
       </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AB11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>0.8125</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AK11" t="n">
         <v>-0.08499999999999996</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0.5</v>
       </c>
       <c r="AL11" t="n">
         <v>78.01627272727274</v>
@@ -2481,49 +2481,49 @@
       <c r="AM11" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="n">
+        <v>17019983.60225633</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-3.654831907610326</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-2.333989243080151</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.02235611336402599</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.466745375836283</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.544944017851492</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>10984469.04336654</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.024274162893079</v>
+      </c>
+      <c r="AY11" t="n">
         <v>2.722746950019683</v>
       </c>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="n">
-        <v>2.544944017851492</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.024274162893079</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10984469.04336654</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>17019983.60225633</v>
-      </c>
-      <c r="AT11" t="n">
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>0.7954742227468898</v>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
         <v>0.5276486675638035</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BE11" t="n">
         <v>0.6762691853600942</v>
       </c>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>0.7954742227468898</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-2.333989243080151</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="n">
-        <v>5.466745375836283</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
-        <v>0.02235611336402599</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-3.654831907610326</v>
-      </c>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2607,54 +2607,54 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" t="n">
         <v>-2.333333333333333</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
         <v>5.666666666666664</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AI12" t="n">
         <v>-5.666666666666664</v>
       </c>
-      <c r="X12" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-7.333333333333333</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD12" t="n">
+      <c r="AJ12" t="n">
         <v>-0.3266666666666667</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AK12" t="n">
         <v>-1.066666666666667</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
       </c>
       <c r="AL12" t="n">
         <v>72.98888888888888</v>
@@ -2662,49 +2662,49 @@
       <c r="AM12" t="n">
         <v>69</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="n">
+        <v>6137873.176206509</v>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>2.571972157433972</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-1.061503928170595</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.331146766698879</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4.746520763187448</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.8657106619825754</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3577584.255148304</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>3.016572387689507</v>
+      </c>
+      <c r="AY12" t="n">
         <v>4.648877665544319</v>
       </c>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="n">
-        <v>0.8657106619825754</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>3.016572387689507</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3577584.255148304</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6137873.176206509</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>2.392087542087609</v>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
         <v>0.04603727455894635</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BE12" t="n">
         <v>0.1550505050505051</v>
       </c>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>2.392087542087609</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-1.061503928170595</v>
-      </c>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="n">
-        <v>4.746520763187448</v>
-      </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
-        <v>7.331146766698879</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.571972157433972</v>
-      </c>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="n">
         <v>0</v>
       </c>
@@ -2788,54 +2788,54 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0.5</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AG13" t="n">
         <v>2.5</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AH13" t="n">
         <v>21.5</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AI13" t="n">
         <v>-21.5</v>
       </c>
-      <c r="X13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD13" t="n">
+      <c r="AJ13" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AK13" t="n">
         <v>0.665</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
       </c>
       <c r="AL13" t="n">
         <v>71.18181818181819</v>
@@ -2843,49 +2843,49 @@
       <c r="AM13" t="n">
         <v>69.5409090909091</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="n">
+        <v>1776341.991341992</v>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>0.0640253202730392</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-2.962770562770565</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.043052003410054</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.493073593073603</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-4.192364047068082</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1651013.664523781</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4.433221114532756</v>
+      </c>
+      <c r="AY13" t="n">
         <v>2.123376623376615</v>
       </c>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>-4.192364047068082</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.433221114532756</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1651013.664523781</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1776341.991341992</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>-3.160173160173173</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="n">
         <v>0.01481295416717421</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BE13" t="n">
         <v>0.09220779220779241</v>
       </c>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="n">
-        <v>-3.160173160173173</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-2.962770562770565</v>
-      </c>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="n">
-        <v>4.493073593073603</v>
-      </c>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="n">
-        <v>4.043052003410054</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0.0640253202730392</v>
-      </c>
+      <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -3401,54 +3401,54 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="U18" t="n">
+        <v>9</v>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
         <v>2</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AH18" t="n">
         <v>-21</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AI18" t="n">
         <v>21</v>
       </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AJ18" t="n">
         <v>-1.04</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AK18" t="n">
         <v>2.73</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>74</v>
@@ -3456,49 +3456,49 @@
       <c r="AM18" t="n">
         <v>69</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="n">
+        <v>-1281253.306878306</v>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>1.216519796764572</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>4.621296296296293</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.4217652273900256</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-5.914153439153438</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.2953982603720817</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-130365.5393059938</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-0.5411850373547225</v>
+      </c>
+      <c r="AY18" t="n">
         <v>0.3376984126984013</v>
       </c>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="n">
-        <v>0.2953982603720817</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>-0.5411850373547225</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>-130365.5393059938</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>-1281253.306878306</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="n">
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
         <v>1.906944444444434</v>
       </c>
-      <c r="AY18" t="n">
-        <v>4.621296296296293</v>
-      </c>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="n">
-        <v>-5.914153439153438</v>
-      </c>
-      <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
       <c r="BE18" t="n">
-        <v>0.4217652273900256</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.216519796764572</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
@@ -5044,54 +5044,54 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-24</v>
+      </c>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
         <v>2</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>21</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AI33" t="n">
         <v>-21</v>
       </c>
-      <c r="X33" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>-24</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AJ33" t="n">
         <v>1.61</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AK33" t="n">
         <v>-1.41</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>-1</v>
       </c>
       <c r="AL33" t="n">
         <v>66.2</v>
@@ -5099,49 +5099,49 @@
       <c r="AM33" t="n">
         <v>70.18181818181819</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="n">
+        <v>-2234641.203703703</v>
+      </c>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="n">
+        <v>1.301905073233439</v>
+      </c>
+      <c r="AR33" t="inlineStr"/>
+      <c r="AS33" t="n">
+        <v>-0.5010416666666657</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>-2.202103660443441</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>-2.82534722222222</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>-0.2023692810457476</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>-1269591.292981506</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>-2.49301163447835</v>
+      </c>
+      <c r="AY33" t="n">
         <v>-2.816666666666649</v>
       </c>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="n">
-        <v>-0.2023692810457476</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>-2.49301163447835</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>-1269591.292981506</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>-2234641.203703703</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="n">
+      <c r="AZ33" t="inlineStr"/>
+      <c r="BA33" t="inlineStr"/>
+      <c r="BB33" t="n">
         <v>-1.420370370370335</v>
       </c>
-      <c r="AY33" t="n">
-        <v>-0.5010416666666657</v>
-      </c>
-      <c r="AZ33" t="inlineStr"/>
-      <c r="BA33" t="n">
-        <v>-2.82534722222222</v>
-      </c>
-      <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
       <c r="BE33" t="n">
-        <v>-2.202103660443441</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.301905073233439</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BF33" t="inlineStr"/>
       <c r="BG33" t="n">
         <v>0</v>
       </c>
@@ -6589,54 +6589,54 @@
         <v>0</v>
       </c>
       <c r="T47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF47" t="n">
         <v>-1</v>
       </c>
-      <c r="U47" t="n">
+      <c r="AG47" t="n">
         <v>1.5</v>
       </c>
-      <c r="V47" t="n">
+      <c r="AH47" t="n">
         <v>-7</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AI47" t="n">
         <v>7</v>
       </c>
-      <c r="X47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AD47" t="n">
+      <c r="AJ47" t="n">
         <v>0.1174999999999999</v>
       </c>
-      <c r="AE47" t="n">
+      <c r="AK47" t="n">
         <v>0.5950000000000002</v>
-      </c>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1</v>
       </c>
       <c r="AL47" t="n">
         <v>76.15625</v>
@@ -6644,49 +6644,49 @@
       <c r="AM47" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="n">
+        <v>-43592483.9302112</v>
+      </c>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="n">
+        <v>-0.6387726578234556</v>
+      </c>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="n">
+        <v>-1.885417814508717</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>-5.74893747653573</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>-3.136501377410468</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>5.572761884128397</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>-27821847.68622385</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>-3.786451794156378</v>
+      </c>
+      <c r="AY47" t="n">
         <v>-5.649201101928398</v>
       </c>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="n">
-        <v>5.572761884128397</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>-3.786451794156378</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>-27821847.68622385</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>-43592483.9302112</v>
-      </c>
-      <c r="AT47" t="n">
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="n">
+        <v>2.633526170798888</v>
+      </c>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="n">
         <v>-0.4920997390452169</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="BE47" t="n">
         <v>-0.9389256198347109</v>
       </c>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="n">
-        <v>2.633526170798888</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>-1.885417814508717</v>
-      </c>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="n">
-        <v>-3.136501377410468</v>
-      </c>
-      <c r="BB47" t="inlineStr"/>
-      <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="inlineStr"/>
-      <c r="BE47" t="n">
-        <v>-5.74893747653573</v>
-      </c>
-      <c r="BF47" t="n">
-        <v>-0.6387726578234556</v>
-      </c>
+      <c r="BF47" t="inlineStr"/>
       <c r="BG47" t="n">
         <v>1</v>
       </c>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG47"/>
+  <dimension ref="A1:BG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AeRSxQrK</t>
+          <t>GdWtpsjm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.66666666666</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,128 +779,128 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
         <v>-3</v>
       </c>
-      <c r="P2" t="n">
+      <c r="V2" t="n">
+        <v>9</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
         <v>-2</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-7.666666666666666</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>-0.7333333333333329</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.8333333333333335</v>
+        <v>-8</v>
       </c>
       <c r="AL2" t="n">
-        <v>71.22727272727272</v>
+        <v>79.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>77.21818181818182</v>
+        <v>75.25</v>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-29846130.95238096</v>
+        <v>0.01082251082251418</v>
       </c>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>1.697725122744469</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>1.610714285714284</v>
+        <v>6.413026113064092</v>
       </c>
       <c r="AT2" t="n">
-        <v>-4.617364768874054</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-6.928968253968279</v>
-      </c>
+        <v>6.572294372294365</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>-0.6529583972743467</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-20828499.91459402</v>
-      </c>
+        <v>2.617380219313731</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-5.53524554758107</v>
+        <v>28975595.05902538</v>
       </c>
       <c r="AY2" t="n">
-        <v>-5.786111111111126</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+        <v>7.0025120294749</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-1.191774891774884</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>37206233.76623376</v>
+      </c>
       <c r="BB2" t="n">
-        <v>-2.036111111111097</v>
+        <v>1.658874458874459</v>
       </c>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-0.2652031356801094</v>
+        <v>-1.400342735619549</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.6529761904761904</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>6.595238095238088</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.8205042937592022</v>
+      </c>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -908,32 +908,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fmqtFMjD</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45522.52083333334</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,128 +960,128 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P3" t="n">
         <v>2</v>
       </c>
-      <c r="P3" t="n">
-        <v>-7</v>
-      </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>6.75</v>
+        <v>-3</v>
       </c>
       <c r="U3" t="n">
-        <v>10</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.166666666666667</v>
+      </c>
       <c r="X3" t="n">
-        <v>0.3999999999999999</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.166666666666666</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.416666666666666</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.083333333333334</v>
+        <v>-0.3516666666666666</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5833333333333335</v>
+        <v>0.5016666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.666666666666667</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-4.333333333333336</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.333333333333336</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5366666666666666</v>
+        <v>-1.833333333333334</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8383333333333336</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.76801346801348</v>
+        <v>74.45454545454545</v>
       </c>
       <c r="AM3" t="n">
-        <v>77.85375573921029</v>
+        <v>76.96801346801347</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-52528383.83838384</v>
+        <v>2.760582010582009</v>
       </c>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
-        <v>-1.702080137329435</v>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-3.228484848484843</v>
+        <v>-1.399630966887983</v>
       </c>
       <c r="AT3" t="n">
-        <v>-7.193227926985998</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-4.290404040404042</v>
-      </c>
+        <v>-1.4704585537919</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>4.663911373155372</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>-30861818.17709465</v>
-      </c>
+        <v>-2.325476828890402</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-3.922110422454423</v>
+        <v>-7470161.574287699</v>
       </c>
       <c r="AY3" t="n">
-        <v>-7.368484848484854</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+        <v>-2.655071549765765</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-0.07208994708992122</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-7764412.47795414</v>
+      </c>
       <c r="BB3" t="n">
-        <v>0.7455555555555406</v>
+        <v>-0.3082010582010584</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-0.6644494615050729</v>
+        <v>1.098301267204988</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.394848484848485</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>-3.587301587301596</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.3595826702576952</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1089,32 +1089,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8WpYGrM0</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45522.41666666666</v>
+        <v>45529.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,128 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="U4" t="n">
+        <v>12.66666666666666</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z4" t="n">
-        <v>-4.5</v>
+        <v>6.333333333333334</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3.5</v>
+        <v>-2</v>
       </c>
       <c r="AB4" t="n">
+        <v>-1.363333333333334</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.2566666666666666</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>12</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>-12</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.8949999999999998</v>
+        <v>-4.666666666666668</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.085</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AL4" t="n">
-        <v>77.95454545454545</v>
+        <v>76.81818181818181</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.54545454545455</v>
+        <v>76.47575757575758</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-2588798.701298706</v>
+        <v>-2.020779220779218</v>
       </c>
       <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
-        <v>-1.6851765897053</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>0.4009740259740262</v>
+        <v>-0.3082283631155747</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.4662913277439316</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-0.9415584415584277</v>
-      </c>
+        <v>-2.816883116883119</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>-3.019159858832978</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>-780645.2390500437</v>
-      </c>
+        <v>1.503422381711886</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>1.164141144634812</v>
+        <v>-2956650.31762306</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.08279220779220964</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+        <v>0.2849678308324997</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-3.857142857142861</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-10421298.7012987</v>
+      </c>
       <c r="BB4" t="n">
-        <v>0.7142857142857224</v>
+        <v>-0.3402597402597405</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>-0.07075274904011941</v>
+        <v>-2.49869316147511</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.2418831168831173</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+        <v>-1.766233766233753</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.1313996571515368</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1270,32 +1270,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>nHdPI4il</t>
+          <t>2g67Vsyf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
-  london </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1322,128 +1322,128 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="R5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA5" t="n">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>4</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>0.9299999999999998</v>
-      </c>
       <c r="AK5" t="n">
-        <v>-1.285</v>
+        <v>3.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>77.62272727272727</v>
+        <v>80.62121212121212</v>
       </c>
       <c r="AM5" t="n">
-        <v>76.5</v>
+        <v>80.78888888888889</v>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>-7768311.688311685</v>
+        <v>1.978896103896108</v>
       </c>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>3.697361368789938</v>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>1.584415584415584</v>
+        <v>-7.683412712506566</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.06373503947033043</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-1.303896103896093</v>
-      </c>
+        <v>-3.585317460317455</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>-2.482223040731469</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-4560738.276371153</v>
-      </c>
+        <v>4.277544956047279</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>-1.855779584561105</v>
+        <v>-23630255.32465113</v>
       </c>
       <c r="AY5" t="n">
-        <v>-1.028571428571425</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+        <v>-5.31768846560422</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-0.9334415584415297</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-33926587.3015873</v>
+      </c>
       <c r="BB5" t="n">
-        <v>0.7597402597402549</v>
+        <v>-0.0912698412698405</v>
       </c>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>0.03935195290237292</v>
+        <v>-1.084584950407592</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.02467532467532463</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>-4.762806637806634</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.1134129821519252</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,32 +1451,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CntkHiGq</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">selhurst park
   london </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,128 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.205</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="AD6" t="n">
         <v>3</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-21.66666666666667</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AE6" t="n">
         <v>-3</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-11.33333333333333</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-3.166666666666667</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.33333333333334</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-18.33333333333334</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>2.831666666666667</v>
+        <v>8.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>-2.891666666666667</v>
+        <v>-19</v>
       </c>
       <c r="AL6" t="n">
-        <v>75.97205387205388</v>
+        <v>78.64090909090909</v>
       </c>
       <c r="AM6" t="n">
-        <v>84.92727272727274</v>
+        <v>81.93939393939394</v>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>47881727.43055556</v>
+        <v>-2.668831168831172</v>
       </c>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>0.3440181335692181</v>
-      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>-1.880208333333332</v>
+        <v>0.1490999430074993</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.096245041078632</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>6.868055555555557</v>
-      </c>
+        <v>-2.369264069264091</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>-1.492309818664296</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>28947364.23277445</v>
-      </c>
+        <v>2.90767185662142</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>5.901018756784993</v>
+        <v>-1592563.45720106</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.060763888888886</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+        <v>-1.224704730377013</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4837662337662607</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-3549740.259740259</v>
+      </c>
       <c r="BB6" t="n">
-        <v>0.07986111111111427</v>
+        <v>-0.8261904761904761</v>
       </c>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>0.4727499731950198</v>
+        <v>-0.008494003662065097</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.8263888888888886</v>
-      </c>
-      <c r="BF6" t="inlineStr"/>
+        <v>-0.1000000000000085</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.5504971685643953</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1632,32 +1632,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,128 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-23</v>
+      </c>
+      <c r="U7" t="n">
+        <v>23</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-2.595</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AE7" t="n">
         <v>2</v>
       </c>
-      <c r="R7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1</v>
       </c>
-      <c r="AG7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-14.75</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>14.75</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>-0.24</v>
+        <v>-14</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.1925</v>
+        <v>10</v>
       </c>
       <c r="AL7" t="n">
-        <v>77.02146464646464</v>
+        <v>81.5409090909091</v>
       </c>
       <c r="AM7" t="n">
-        <v>75.80000000000001</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>1775953.282828284</v>
+        <v>0.4456565656565665</v>
       </c>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
-        <v>1.618717119284788</v>
-      </c>
+      <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>1.663816738816742</v>
+        <v>1.572721783047868</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.2109521425847163</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-0.9375901875902031</v>
-      </c>
+        <v>1.290404040404027</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>8.326102350265018</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>-1432068.723799587</v>
-      </c>
+        <v>0.8322058415627396</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-3.315135535049265</v>
+        <v>1165327.111809983</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.171753246753255</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+        <v>-0.2003483651972573</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.9432323232323654</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3469636.363636361</v>
+      </c>
       <c r="BB7" t="n">
-        <v>1.620490620490642</v>
+        <v>0.1016161616161615</v>
       </c>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>-0.06534905438147809</v>
+        <v>2.113813240086966</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.2233766233766232</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+        <v>0.9821212121212142</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.1609272833327213</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1813,32 +1813,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pjyqwZx3</t>
+          <t>lAUlrLKa</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,128 +1865,124 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lhUKMQZu</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="n">
-        <v>13</v>
-      </c>
-      <c r="R8" t="n">
         <v>2</v>
       </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>7.199999999999999</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="U8" t="n">
-        <v>1.800000000000001</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+        <v>-28.16666666666666</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.333333333333333</v>
+      </c>
       <c r="X8" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.8999999999999999</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="Z8" t="n">
-        <v>-1.800000000000001</v>
+        <v>-8.833333333333332</v>
       </c>
       <c r="AA8" t="n">
-        <v>-2.199999999999999</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.4</v>
+        <v>0.5316666666666663</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.2999999999999998</v>
+        <v>-0.9866666666666666</v>
       </c>
       <c r="AD8" t="n">
-        <v>-2.8</v>
+        <v>-0.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>2.5</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AI8" t="n">
-        <v>-2.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.316</v>
+        <v>4.833333333333332</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.3799999999999999</v>
+        <v>-8.166666666666668</v>
       </c>
       <c r="AL8" t="n">
-        <v>73.29545454545455</v>
+        <v>78.94351851851853</v>
       </c>
       <c r="AM8" t="n">
-        <v>72.99111111111111</v>
+        <v>70.58585858585859</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>14692283.05785124</v>
+        <v>0.5838383838383834</v>
       </c>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
-        <v>1.409744653790366</v>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>0.7660123966942081</v>
+        <v>11.12046768788032</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.202640962511481</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.699896694214871</v>
-      </c>
+        <v>15.04242424242426</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>2.517704458265484</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>10053627.24598238</v>
-      </c>
+        <v>-5.284725436068157</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>2.96223784474266</v>
+        <v>43081331.70498473</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.902169421487613</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+        <v>11.73923745021358</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.4070707070706874</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>71284444.44444445</v>
+      </c>
       <c r="BB8" t="n">
-        <v>5.375206611570235</v>
+        <v>2.192929292929293</v>
       </c>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>0.4238095238095236</v>
+        <v>-0.8048620414349301</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.5102272727272728</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+        <v>13.27979797979798</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.287436794363478</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1994,32 +1990,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.45833333334</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">scott g 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2046,128 +2042,128 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-4</v>
       </c>
-      <c r="P9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-2</v>
-      </c>
       <c r="R9" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>26.5</v>
       </c>
       <c r="U9" t="n">
-        <v>-6</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>-26.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="X9" t="n">
-        <v>-0.75</v>
+        <v>-1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>-2</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>-2.75</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.75</v>
+        <v>0.1500000000000001</v>
       </c>
       <c r="AC9" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>-1</v>
       </c>
-      <c r="AD9" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
       <c r="AK9" t="n">
-        <v>-0.4700000000000002</v>
+        <v>-7</v>
       </c>
       <c r="AL9" t="n">
-        <v>81.76666666666667</v>
+        <v>70.48333333333333</v>
       </c>
       <c r="AM9" t="n">
-        <v>80.13415404040404</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>-112321.4285714291</v>
+        <v>0.231818181818177</v>
       </c>
       <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
-        <v>0.9000830395087078</v>
-      </c>
+      <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>0.9857142857142875</v>
+        <v>-4.110121246566237</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.9510967786844304</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.2910714285714278</v>
-      </c>
+        <v>-2.298484848484861</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>2.362852243863756</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-238945.7190112025</v>
-      </c>
+        <v>-6.631758548830163</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>0.3619543532862792</v>
+        <v>-7216036.076266255</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.03749999999999432</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+        <v>-4.153188473457021</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-5.080808080808083</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-4453484.848484848</v>
+      </c>
       <c r="BB9" t="n">
-        <v>3.742857142857105</v>
+        <v>-0.2833333333333334</v>
       </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>0.1161873589842288</v>
+        <v>0.2864903449302361</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.1089285714285715</v>
-      </c>
-      <c r="BF9" t="inlineStr"/>
+        <v>-2.698484848484838</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.416873706004141</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2175,32 +2171,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4kJMDhM</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45521.35416666666</v>
+        <v>45528.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2227,122 +2223,128 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
       <c r="Q10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>17</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.25</v>
+        <v>18.83333333333334</v>
       </c>
       <c r="U10" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>-18.83333333333334</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.333333333333333</v>
+      </c>
       <c r="X10" t="n">
-        <v>1.75</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.25</v>
+        <v>0.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>-3.25</v>
+        <v>0.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.5</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.25</v>
+        <v>1.053333333333333</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4</v>
+        <v>-0.7083333333333335</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>-4</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1925000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>-1.3675</v>
-      </c>
-      <c r="AL10" t="inlineStr"/>
+        <v>-14</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>80.99621212121212</v>
+      </c>
       <c r="AM10" t="n">
-        <v>78.65909090909091</v>
+        <v>78.03749999999999</v>
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>-45110909.09090909</v>
+        <v>-2.476479076479077</v>
       </c>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
-        <v>1.938006096158269</v>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>0.4595959595959549</v>
+        <v>5.492297330831633</v>
       </c>
       <c r="AT10" t="n">
-        <v>-10.60447435012652</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>-11.28787878787877</v>
-      </c>
+        <v>5.122366522366519</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
-        <v>-0.06185875316307943</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-32647976.76558546</v>
-      </c>
+        <v>-5.151636646267946</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>-11.21757821486082</v>
+        <v>19843329.26238764</v>
       </c>
       <c r="AY10" t="n">
-        <v>-12.20606060606062</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+        <v>4.652590380164241</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.437806637806574</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>28638383.83838384</v>
+      </c>
       <c r="BB10" t="n">
-        <v>-0.6909090909090878</v>
+        <v>0.4965367965367966</v>
       </c>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-0.8513400046008743</v>
+        <v>-0.3894781406078849</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.65050505050505</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+        <v>6.015873015873012</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.3217405612130437</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2350,32 +2352,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Kl1AOZN9</t>
+          <t>8j9FTL56</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.66666666666</v>
+        <v>45528.35416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">donohue m 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2402,128 +2404,128 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
+        <v>-5</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.7433333333333332</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.5866666666666666</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>-0.3999999999999999</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>-1.666666666666666</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.8125</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.08499999999999996</v>
+        <v>-9.333333333333334</v>
       </c>
       <c r="AL11" t="n">
-        <v>78.01627272727274</v>
+        <v>79.23367003367004</v>
       </c>
       <c r="AM11" t="n">
-        <v>74.54545454545453</v>
+        <v>80.72323232323232</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>17019983.60225633</v>
+        <v>1.078843995510663</v>
       </c>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
-        <v>-3.654831907610326</v>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>-2.333989243080151</v>
+        <v>-1.654632899589046</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.02235611336402599</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.466745375836283</v>
-      </c>
+        <v>-4.351346801346793</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>2.544944017851492</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>10984469.04336654</v>
-      </c>
+        <v>-6.154116035037049</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
-        <v>5.024274162893079</v>
+        <v>-9622848.393078659</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.722746950019683</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+        <v>-1.042907036108801</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-2.566778900112212</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-20172056.67789001</v>
+      </c>
       <c r="BB11" t="n">
-        <v>0.7954742227468898</v>
+        <v>-0.8220538720538724</v>
       </c>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>0.5276486675638035</v>
+        <v>-0.7771996278575237</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.6762691853600942</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+        <v>-4.391189674523005</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.3841575740698548</v>
+      </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2531,42 +2533,42 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>697ha3El</t>
+          <t>AeRSxQrK</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45518.66666666666</v>
+        <v>45523.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">bell j 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">elland road
-  leeds </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>tUxUbLR2</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6F0lvLNC</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>48</v>
       </c>
       <c r="H12" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>20242025</v>
@@ -2578,133 +2580,133 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>-3</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.666666666666666</v>
+        <v>-10.5</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.333333333333333</v>
-      </c>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+        <v>10.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-5.333333333333333</v>
+      </c>
       <c r="X12" t="n">
-        <v>-2</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.666666666666668</v>
+        <v>0.1666666666666661</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="AB12" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.7333333333333329</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.333333333333333</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>5.666666666666664</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.666666666666664</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1.066666666666667</v>
+        <v>-7.666666666666666</v>
       </c>
       <c r="AL12" t="n">
-        <v>72.98888888888888</v>
+        <v>71.22727272727272</v>
       </c>
       <c r="AM12" t="n">
-        <v>69</v>
+        <v>77.21818181818182</v>
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>6137873.176206509</v>
+        <v>1.720000000000002</v>
       </c>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="n">
-        <v>2.571972157433972</v>
-      </c>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>-1.061503928170595</v>
+        <v>-4.873920573013891</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.331146766698879</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.746520763187448</v>
-      </c>
+        <v>-5.980952380952374</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
-        <v>0.8657106619825754</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3577584.255148304</v>
-      </c>
+        <v>-0.6626622499078962</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="n">
-        <v>3.016572387689507</v>
+        <v>-20874595.33673916</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.648877665544319</v>
-      </c>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
+        <v>-5.359832369949572</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-2.086666666666645</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-30444730.15873016</v>
+      </c>
       <c r="BB12" t="n">
-        <v>2.392087542087609</v>
+        <v>-0.6431746031746028</v>
       </c>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="n">
-        <v>0.04603727455894635</v>
+        <v>1.501286670968224</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.1550505050505051</v>
-      </c>
-      <c r="BF12" t="inlineStr"/>
+        <v>-7.178730158730161</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0.2608402451889849</v>
+      </c>
       <c r="BG12" t="n">
         <v>0</v>
       </c>
@@ -2712,42 +2714,42 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>634r8bcJ</t>
+          <t>fmqtFMjD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45518.65625</v>
+        <v>45522.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">mkm stadium
-  hull </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S66R0t75</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>llcCvIcG</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>48</v>
       </c>
       <c r="H13" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>20242025</v>
@@ -2759,133 +2761,133 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="Q13" t="n">
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>-4.333333333333336</v>
       </c>
       <c r="U13" t="n">
-        <v>8</v>
-      </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+        <v>4.333333333333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.5833333333333335</v>
+      </c>
       <c r="X13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Z13" t="n">
-        <v>-2.5</v>
+        <v>3.166666666666666</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.5</v>
+        <v>1.416666666666666</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.5</v>
+        <v>0.5366666666666666</v>
       </c>
       <c r="AC13" t="n">
-        <v>8</v>
+        <v>0.8383333333333336</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>21.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AI13" t="n">
-        <v>-21.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.36</v>
+        <v>6.75</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.665</v>
+        <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>71.18181818181819</v>
+        <v>78.76801346801348</v>
       </c>
       <c r="AM13" t="n">
-        <v>69.5409090909091</v>
+        <v>77.36540404040404</v>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>1776341.991341992</v>
+        <v>-3.395286195286193</v>
       </c>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>0.0640253202730392</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
-        <v>-2.962770562770565</v>
+        <v>-6.940612621783259</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.043052003410054</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.493073593073603</v>
-      </c>
+        <v>-7.728170594837266</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
-        <v>-4.192364047068082</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1651013.664523781</v>
-      </c>
+        <v>4.51620916532633</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
       <c r="AX13" t="n">
-        <v>4.433221114532756</v>
+        <v>-29625592.38763808</v>
       </c>
       <c r="AY13" t="n">
-        <v>2.123376623376615</v>
-      </c>
-      <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="inlineStr"/>
+        <v>-3.895102332436878</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.7700336700336265</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-53717283.95061729</v>
+      </c>
       <c r="BB13" t="n">
-        <v>-3.160173160173173</v>
+        <v>-1.452188552188552</v>
       </c>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="n">
-        <v>0.01481295416717421</v>
+        <v>-1.444567859041545</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.09220779220779241</v>
-      </c>
-      <c r="BF13" t="inlineStr"/>
+        <v>-4.439393939393938</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.6232386894151596</v>
+      </c>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -2893,37 +2895,42 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>pbFTwdnB</t>
+          <t>8WpYGrM0</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45518.65625</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>45522.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">home park
-  plymouth </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>WpGM6ELj</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>jizXHcsM</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>48</v>
       </c>
       <c r="H14" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>20242025</v>
@@ -2935,63 +2942,133 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="T14" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-12</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.8949999999999998</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2</v>
+      </c>
       <c r="AL14" t="n">
-        <v>69.63636363636364</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
+        <v>77.95454545454545</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>76.54545454545455</v>
+      </c>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
+      <c r="AO14" t="n">
+        <v>0.5930735930735942</v>
+      </c>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>0.3947107497969995</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.1601731601731586</v>
+      </c>
       <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-2.736316924430582</v>
+      </c>
       <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-806290.1812771903</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.318756332942542</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.7359307359307365</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-2735714.285714291</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0.2510822510822515</v>
+      </c>
       <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>-1.75660047644789</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-1.030303030303031</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.06328256448778324</v>
+      </c>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -2999,37 +3076,42 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>vyoZBtbf</t>
+          <t>nHdPI4il</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45517.66666666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>45521.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">bramall lane
-  sheffield </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MeKPSerA</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IgO7K1ZA</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>48</v>
       </c>
       <c r="H15" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>20242025</v>
@@ -3041,63 +3123,133 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="T15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9299999999999998</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-2.5</v>
+      </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+      <c r="AH15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
       <c r="AL15" t="n">
-        <v>76.57205387205387</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
+        <v>77.62272727272727</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>76.5</v>
+      </c>
       <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
+      <c r="AO15" t="n">
+        <v>1.727272727272723</v>
+      </c>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-0.3468443185355028</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-1.033333333333317</v>
+      </c>
       <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>-2.440900425826896</v>
+      </c>
       <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>-3850457.883279577</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-1.567192584104333</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.7954545454545041</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-7953939.393939391</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.02878787878787881</v>
+      </c>
       <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>3.101948051948046</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-1.354545454545459</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0.03268309849192175</v>
+      </c>
       <c r="BG15" t="n">
         <v>0</v>
       </c>
@@ -3105,37 +3257,42 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>48</v>
       </c>
       <c r="H16" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>20242025</v>
@@ -3147,67 +3304,133 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
       <c r="O16" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>-2</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-2</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AH16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-3</v>
+      </c>
       <c r="AL16" t="n">
-        <v>69.13636363636363</v>
-      </c>
-      <c r="AM16" t="inlineStr"/>
+        <v>77.02146464646464</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75.80000000000001</v>
+      </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
+      <c r="AO16" t="n">
+        <v>1.389442039442034</v>
+      </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-0.3097956459471476</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.153030303030306</v>
+      </c>
       <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>8.527110169010342</v>
+      </c>
       <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>-1365357.45304987</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-3.10573312849165</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.399230399230419</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1998494.468494467</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.201082251082251</v>
+      </c>
       <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BD16" t="n">
+        <v>1.42343180979486</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0.8108465608465707</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0.02094313698019268</v>
+      </c>
       <c r="BG16" t="n">
         <v>0</v>
       </c>
@@ -3215,37 +3438,42 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>pjyqwZx3</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>45521.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>48</v>
       </c>
       <c r="H17" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>20242025</v>
@@ -3257,67 +3485,133 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>5</v>
+      </c>
       <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
+      <c r="AH17" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.1000000000000001</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.800000000000001</v>
+      </c>
       <c r="AL17" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="AM17" t="inlineStr"/>
+        <v>73.29545454545455</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>72.99111111111111</v>
+      </c>
       <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
+      <c r="AO17" t="n">
+        <v>0.5818181818181785</v>
+      </c>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>3.579467100849982</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.965367965367989</v>
+      </c>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>2.66230671012363</v>
+      </c>
       <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>10940136.6259064</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.446755465471227</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.156998556998587</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>14835497.83549783</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.5116883116883117</v>
+      </c>
       <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>1.387282207569015</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.814718614718601</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.4557823129251699</v>
+      </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3325,42 +3619,42 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ward g 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>20242025</v>
@@ -3372,133 +3666,133 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>efl cup</t>
+          <t>premier league</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>nPjMw0nA</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="P18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="W18" t="n">
         <v>-1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="X18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0.0349999999999997</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
         <v>-6</v>
       </c>
-      <c r="U18" t="n">
-        <v>9</v>
-      </c>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.73</v>
-      </c>
       <c r="AL18" t="n">
-        <v>74</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AM18" t="n">
-        <v>69</v>
+        <v>80.13415404040404</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>-1281253.306878306</v>
+        <v>1.207142857142863</v>
       </c>
       <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="n">
-        <v>1.216519796764572</v>
-      </c>
+      <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="inlineStr"/>
       <c r="AS18" t="n">
-        <v>4.621296296296293</v>
+        <v>0.8388825088318299</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.4217652273900256</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>-5.914153439153438</v>
-      </c>
+        <v>0.1499999999999915</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="n">
-        <v>0.2953982603720817</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>-130365.5393059938</v>
-      </c>
+        <v>2.466029456994647</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
       <c r="AX18" t="n">
-        <v>-0.5411850373547225</v>
+        <v>-767450.2320170831</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.3376984126984013</v>
-      </c>
-      <c r="AZ18" t="inlineStr"/>
-      <c r="BA18" t="inlineStr"/>
+        <v>0.4214651771532942</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>3.780952380952357</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>39285.71428571455</v>
+      </c>
       <c r="BB18" t="n">
-        <v>1.906944444444434</v>
+        <v>0.1119047619047622</v>
       </c>
       <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>0.8249206089758587</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="inlineStr"/>
+        <v>-0.3500000000000085</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.09249105023050785</v>
+      </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
@@ -3506,42 +3800,42 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>CntkHiGq</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45521.45833333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">eltringham g 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>48</v>
       </c>
       <c r="H19" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>20242025</v>
@@ -3553,67 +3847,133 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MsDWbjnD</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="P19" t="n">
+        <v>6</v>
+      </c>
       <c r="Q19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3</v>
+      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.831666666666667</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-2.891666666666667</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-3</v>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
+      <c r="AH19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-21.66666666666667</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75.97205387205388</v>
+      </c>
       <c r="AM19" t="n">
-        <v>68.61805555555556</v>
+        <v>84.92727272727274</v>
       </c>
       <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
+      <c r="AO19" t="n">
+        <v>-1.791666666666664</v>
+      </c>
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>9.0118740319094</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>7.105158730158735</v>
+      </c>
       <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-1.40474505591709</v>
+      </c>
       <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>28656762.1306896</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.899660534070094</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.2698412698412653</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>47880505.95238096</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0.8253968253968251</v>
+      </c>
       <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>0.2961711000189524</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>6.855158730158735</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0.478255608463481</v>
+      </c>
       <c r="BG19" t="n">
         <v>0</v>
       </c>
@@ -3621,37 +3981,42 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>t4kJMDhM</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>45521.35416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>48</v>
       </c>
       <c r="H20" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>20242025</v>
@@ -3663,61 +4028,127 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.1925000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1.3675</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
+      <c r="AH20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-9.5</v>
+      </c>
       <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>78.65909090909091</v>
+      </c>
       <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
+      <c r="AO20" t="n">
+        <v>0.2012987012986969</v>
+      </c>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-10.718677905945</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-12.69350649350649</v>
+      </c>
       <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>-0.1266415261756322</v>
+      </c>
       <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="inlineStr"/>
-      <c r="BB20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>-33738368.08636498</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>-11.30040668441291</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.4506493506493712</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-46723506.49350649</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-1.719480519480519</v>
+      </c>
       <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
-      <c r="BF20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>2.003031647441585</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-11.45584415584413</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-0.9088657202011241</v>
+      </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -3725,37 +4156,42 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>Kl1AOZN9</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>45520.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donohue m 
+  eng </t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>48</v>
       </c>
       <c r="H21" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>20242025</v>
@@ -3767,57 +4203,133 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>efl cup</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>22</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>13</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-0.08499999999999996</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>76.15625</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>74.54545454545453</v>
+      </c>
       <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
+      <c r="AO21" t="n">
+        <v>-2.15746352413019</v>
+      </c>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-0.2266699953294165</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.766498316498314</v>
+      </c>
       <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
+      <c r="AV21" t="n">
+        <v>2.609098920639809</v>
+      </c>
       <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>10854144.80867007</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>5.056230519583039</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.8731762065094983</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>16510272.1661055</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.6659932659932661</v>
+      </c>
       <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+      <c r="BD21" t="n">
+        <v>-3.87185395238464</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.382772166105511</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.50512767835871</v>
+      </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
@@ -3825,27 +4337,32 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>697ha3El</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>45518.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bell j 
+  eng </t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">elland road
+  leeds </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>tUxUbLR2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>6F0lvLNC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3870,54 +4387,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>9</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>6</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>5.666666666666664</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-5.666666666666664</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-0.3266666666666667</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2</v>
+      </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
+      <c r="AH22" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>72.98888888888888</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>69</v>
+      </c>
       <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
+      <c r="AO22" t="n">
+        <v>-1.06920634920635</v>
+      </c>
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>6.827767826428826</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.909206349206357</v>
+      </c>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>0.3984636270162696</v>
+      </c>
       <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
+      <c r="AX22" t="n">
+        <v>3593784.842479503</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.033166674227033</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.587619047619086</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6375174.603174603</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0.1485714285714284</v>
+      </c>
       <c r="BC22" t="inlineStr"/>
-      <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
+      <c r="BD22" t="n">
+        <v>2.219128968726494</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.985396825396819</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0.03953449800973008</v>
+      </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
@@ -3925,27 +4518,32 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>634r8bcJ</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45517.65625</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>45518.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">mkm stadium
+  hull </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>S66R0t75</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>llcCvIcG</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3970,58 +4568,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>8tPSZqtA</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>3</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="V23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
+      <c r="AH23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>69.5409090909091</v>
+      </c>
       <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
+      <c r="AO23" t="n">
+        <v>-3.221212121212126</v>
+      </c>
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
+      <c r="AS23" t="n">
+        <v>4.110390955899263</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.169696969696972</v>
+      </c>
       <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
+      <c r="AV23" t="n">
+        <v>-4.961513518450801</v>
+      </c>
       <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="inlineStr"/>
+      <c r="AX23" t="n">
+        <v>1890838.908933138</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>4.420315650414764</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>-2.48333333333332</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1808409.090909091</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0.09242424242424252</v>
+      </c>
       <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
-      <c r="BF23" t="inlineStr"/>
+      <c r="BD23" t="n">
+        <v>-0.1078290978227052</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.842424242424244</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0.02538363171355495</v>
+      </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
@@ -4029,27 +4699,27 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>pbFTwdnB</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45518.65625</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">home park
+  plymouth </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>WpGM6ELj</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>jizXHcsM</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4076,22 +4746,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>8tPSZqtA</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>-1</v>
-      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -4114,7 +4776,7 @@
       <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr"/>
       <c r="AL24" t="n">
-        <v>69.64141414141415</v>
+        <v>69.63636363636364</v>
       </c>
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
@@ -4143,27 +4805,27 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>vyoZBtbf</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45517.65625</v>
+        <v>45517.66666666666</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">bramall lane
+  sheffield </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>MeKPSerA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>IgO7K1ZA</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4188,7 +4850,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>EoQjC3VB</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -4215,7 +4881,9 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
+      <c r="AL25" t="n">
+        <v>76.57205387205387</v>
+      </c>
       <c r="AM25" t="inlineStr"/>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr"/>
@@ -4243,7 +4911,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -4252,18 +4920,18 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4290,12 +4958,8 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
@@ -4347,7 +5011,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -4356,18 +5020,18 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4392,11 +5056,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>tMUvLt7h</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
         <v>0</v>
@@ -4419,7 +5091,9 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
+      <c r="AL27" t="n">
+        <v>69.2</v>
+      </c>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
@@ -4447,7 +5121,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -4456,18 +5130,18 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">dw stadium
+  wigan </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4494,9 +5168,13 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>3</v>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
         <v>0</v>
@@ -4547,7 +5225,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -4556,18 +5234,18 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4592,19 +5270,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>AHNtWa3o</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>0</v>
@@ -4627,9 +5297,7 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="n">
-        <v>70.70833333333333</v>
-      </c>
+      <c r="AL29" t="inlineStr"/>
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
@@ -4657,7 +5325,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -4666,18 +5334,18 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4702,12 +5370,24 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="O30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-1</v>
+      </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
@@ -4729,7 +5409,9 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
+      <c r="AL30" t="n">
+        <v>69.64141414141415</v>
+      </c>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
@@ -4757,32 +5439,27 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4807,15 +5484,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>-2</v>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="n">
+        <v>-1</v>
+      </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
         <v>0</v>
@@ -4838,10 +5519,10 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AL31" t="n">
+        <v>69.13636363636363</v>
+      </c>
+      <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
@@ -4868,7 +5549,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -4877,18 +5558,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4968,32 +5649,27 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5020,127 +5696,61 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+          <t>AHNtWa3o</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>4</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
-        <v>7</v>
-      </c>
-      <c r="U33" t="n">
-        <v>-24</v>
-      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>-1.41</v>
-      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>70.18181818181819</v>
-      </c>
+        <v>70.70833333333333</v>
+      </c>
+      <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="n">
-        <v>-2234641.203703703</v>
-      </c>
+      <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="n">
-        <v>1.301905073233439</v>
-      </c>
+      <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="n">
-        <v>-0.5010416666666657</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>-2.202103660443441</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>-2.82534722222222</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>-0.2023692810457476</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>-1269591.292981506</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>-2.49301163447835</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>-2.816666666666649</v>
-      </c>
+      <c r="AS33" t="inlineStr"/>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr"/>
+      <c r="AX33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="n">
-        <v>-1.420370370370335</v>
-      </c>
+      <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
       <c r="BF33" t="inlineStr"/>
       <c r="BG33" t="n">
         <v>0</v>
@@ -5149,27 +5759,32 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5195,10 +5810,18 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>-2</v>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="n">
+        <v>-1</v>
+      </c>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
         <v>0</v>
@@ -5222,7 +5845,9 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
+      <c r="AM34" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
@@ -5249,7 +5874,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5258,18 +5883,18 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5349,7 +5974,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -5358,18 +5983,18 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5394,14 +6019,14 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
@@ -5425,9 +6050,7 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AL36" t="inlineStr"/>
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
@@ -5455,7 +6078,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -5464,18 +6087,18 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5502,9 +6125,13 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
         <v>0</v>
@@ -5555,32 +6182,27 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5606,18 +6228,10 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>2</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
         <v>0</v>
@@ -5641,9 +6255,7 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
       <c r="AP38" t="inlineStr"/>
@@ -5670,27 +6282,32 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5715,54 +6332,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-21</v>
+      </c>
+      <c r="U39" t="n">
+        <v>21</v>
+      </c>
+      <c r="V39" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>8</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
+      <c r="AH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>69</v>
+      </c>
       <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
+      <c r="AO39" t="n">
+        <v>4.081666666666667</v>
+      </c>
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
+      <c r="AS39" t="n">
+        <v>0.4796834704515049</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.4862499999999983</v>
+      </c>
       <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
+      <c r="AV39" t="n">
+        <v>0.1362195517032205</v>
+      </c>
       <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
-      <c r="BA39" t="inlineStr"/>
-      <c r="BB39" t="inlineStr"/>
+      <c r="AX39" t="n">
+        <v>-200668.3320019464</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>-0.9468219381573988</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.075833333333321</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>-1118180.555555556</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
       <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="inlineStr"/>
-      <c r="BE39" t="inlineStr"/>
-      <c r="BF39" t="inlineStr"/>
+      <c r="BD39" t="n">
+        <v>1.465790161411626</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>-5.248055555555567</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
@@ -5770,7 +6463,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -5779,18 +6472,18 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5870,7 +6563,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -5879,18 +6572,18 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5917,13 +6610,9 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
-      <c r="O41" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="n">
         <v>0</v>
@@ -5974,27 +6663,32 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6019,12 +6713,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -6050,10 +6744,10 @@
       <c r="AI42" t="inlineStr"/>
       <c r="AJ42" t="inlineStr"/>
       <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="n">
-        <v>69.33522727272728</v>
-      </c>
-      <c r="AM42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
       <c r="AP42" t="inlineStr"/>
@@ -6080,32 +6774,27 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6131,11 +6820,7 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -6162,9 +6847,7 @@
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
       <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="n">
-        <v>71.77777777777777</v>
-      </c>
+      <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
       <c r="AP43" t="inlineStr"/>
@@ -6191,32 +6874,27 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>45517.64583333334</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+        <v>45517.65625</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6241,12 +6919,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -6272,10 +6950,10 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AL44" t="n">
+        <v>69.33522727272728</v>
+      </c>
+      <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
       <c r="AP44" t="inlineStr"/>
@@ -6302,32 +6980,32 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6355,12 +7033,16 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>2</v>
+      </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>0</v>
@@ -6385,7 +7067,7 @@
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
       <c r="AM45" t="n">
-        <v>76</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
@@ -6413,27 +7095,27 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>45517.64583333334</v>
+        <v>45517.65625</v>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6513,181 +7195,1323 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
+          <t>SMr3Nz2U</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>hO8wh6aP</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GILi6JC9</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>48</v>
+      </c>
+      <c r="H47" t="n">
+        <v>484</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="n">
+        <v>71.47727272727272</v>
+      </c>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
+      <c r="AQ47" t="inlineStr"/>
+      <c r="AR47" t="inlineStr"/>
+      <c r="AS47" t="inlineStr"/>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr"/>
+      <c r="AX47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr"/>
+      <c r="BA47" t="inlineStr"/>
+      <c r="BB47" t="inlineStr"/>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>bHPacsq1</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>tCZ3D68d</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CCBWpzjj</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>48</v>
+      </c>
+      <c r="H48" t="n">
+        <v>484</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
+        <v>72.22962962962963</v>
+      </c>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
+      <c r="AQ48" t="inlineStr"/>
+      <c r="AR48" t="inlineStr"/>
+      <c r="AS48" t="inlineStr"/>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr"/>
+      <c r="AX48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr"/>
+      <c r="BA48" t="inlineStr"/>
+      <c r="BB48" t="inlineStr"/>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>bw1zAKS6</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Or1bBrWD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>t6G9wMZN</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>48</v>
+      </c>
+      <c r="H49" t="n">
+        <v>484</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr"/>
+      <c r="AX49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr"/>
+      <c r="BA49" t="inlineStr"/>
+      <c r="BB49" t="inlineStr"/>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>CnnJp4ae</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>KKJL7QXd</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>U3lM3y4e</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>48</v>
+      </c>
+      <c r="H50" t="n">
+        <v>484</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
+      <c r="AQ50" t="inlineStr"/>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AS50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr"/>
+      <c r="AX50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr"/>
+      <c r="BA50" t="inlineStr"/>
+      <c r="BB50" t="inlineStr"/>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>GINCsvmn</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MahqU27I</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>GOvB22xg</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>48</v>
+      </c>
+      <c r="H51" t="n">
+        <v>484</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>C2sV0kf7</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>3</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>21</v>
+      </c>
+      <c r="U51" t="n">
+        <v>-21</v>
+      </c>
+      <c r="V51" t="n">
+        <v>4</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>70.18181818181819</v>
+      </c>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="n">
+        <v>-0.6712037037037035</v>
+      </c>
+      <c r="AP51" t="inlineStr"/>
+      <c r="AQ51" t="inlineStr"/>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="n">
+        <v>-2.294259417483119</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>-2.760925925925932</v>
+      </c>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="n">
+        <v>-0.9354549251917206</v>
+      </c>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="n">
+        <v>-1318294.858832687</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>-2.566349016480586</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>-1.005555555555503</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>-2148009.259259259</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="n">
+        <v>1.350305783397889</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>-2.621203703703713</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>6os5wmhS</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>xYu73rNn</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>EmlVDpVP</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>48</v>
+      </c>
+      <c r="H52" t="n">
+        <v>484</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Kl7vhn7L</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45517.65625</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>QVmLl54o</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>xSloasB8</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>48</v>
+      </c>
+      <c r="H53" t="n">
+        <v>484</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>fRe0c20b</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kitchen a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>IX6WjNvr</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>6Nl8nagD</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>484</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="n">
+        <v>76</v>
+      </c>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
+      <c r="AQ54" t="inlineStr"/>
+      <c r="AR54" t="inlineStr"/>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>jXcAnQUr</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisbane road
+  london </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>KKyYcus9</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ChwgcrNJ</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>48</v>
+      </c>
+      <c r="H55" t="n">
+        <v>484</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
+      <c r="AQ55" t="inlineStr"/>
+      <c r="AR55" t="inlineStr"/>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>OMDVg8x9</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45517.64583333334</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>dUzTIwSF</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>hSUajdSS</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>48</v>
+      </c>
+      <c r="H56" t="n">
+        <v>484</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>efl cup</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>UwJevjpg</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
+      <c r="AQ56" t="inlineStr"/>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t>tYjCfe2E</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n">
+      <c r="B57" s="2" t="n">
         <v>45514.45833333334</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t xml:space="preserve">wembley stadium
   london </t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>ppjDR086</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
+      <c r="G57" t="n">
         <v>48</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H57" t="n">
         <v>482</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I57" t="n">
         <v>1</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J57" t="n">
         <v>2024</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>fa community shield</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>hxNijWrJ</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>dpjHQ7zJ</t>
         </is>
       </c>
-      <c r="O47" t="n">
-        <v>6</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="O57" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P57" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R57" t="n">
+        <v>3</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>19.59999999999999</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-19.59999999999999</v>
+      </c>
+      <c r="V57" t="n">
+        <v>5.000000000000001</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="X57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-0.8179999999999997</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>77.36565656565656</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>76.90282828282827</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>1.935241301907965</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR57" t="n">
         <v>-4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3</v>
-      </c>
-      <c r="R47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="U47" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>-7</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.1174999999999999</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0.5950000000000002</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>76.15625</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>77.36540404040404</v>
-      </c>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="n">
-        <v>-43592483.9302112</v>
-      </c>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="n">
-        <v>-0.6387726578234556</v>
-      </c>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="n">
-        <v>-1.885417814508717</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>-5.74893747653573</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>-3.136501377410468</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>5.572761884128397</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>-27821847.68622385</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>-3.786451794156378</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>-5.649201101928398</v>
-      </c>
-      <c r="AZ47" t="inlineStr"/>
-      <c r="BA47" t="inlineStr"/>
-      <c r="BB47" t="n">
-        <v>2.633526170798888</v>
-      </c>
-      <c r="BC47" t="inlineStr"/>
-      <c r="BD47" t="n">
-        <v>-0.4920997390452169</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>-0.9389256198347109</v>
-      </c>
-      <c r="BF47" t="inlineStr"/>
-      <c r="BG47" t="n">
+      <c r="AS57" t="n">
+        <v>5.818247068993031</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>5.84410774410776</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>-5.593070794413478</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>-8500000</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>27404062.88584091</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>3.733329160971948</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>-2.559034792368095</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>44633869.24803592</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0.9875420875420873</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>0.6996112630383706</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>3.316722783389451</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>0.5104847340780838</v>
+      </c>
+      <c r="BG57" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -803,55 +803,55 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>-3</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="X2" t="n">
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Z2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2</v>
       </c>
-      <c r="AA2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.56</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AI2" t="n">
         <v>0.1499999999999999</v>
       </c>
-      <c r="AD2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-8</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>79.5</v>
       </c>
@@ -860,47 +860,47 @@
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>0.01082251082251418</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>1.569421487603305</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.527412323919933</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>25630810.58734082</v>
+      </c>
       <c r="AS2" t="n">
-        <v>6.413026113064092</v>
+        <v>35034231.40495867</v>
       </c>
       <c r="AT2" t="n">
-        <v>6.572294372294365</v>
+        <v>-0.2683471074380144</v>
       </c>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>2.617380219313731</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
+        <v>-1.387272727272745</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.861012030774461</v>
+      </c>
       <c r="AX2" t="n">
-        <v>28975595.05902538</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.0025120294749</v>
-      </c>
+        <v>0.6897535476294401</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>-1.191774891774884</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>37206233.76623376</v>
-      </c>
+        <v>6.536694214876022</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>1.658874458874459</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>-1.55662180814355</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.293471074380165</v>
+      </c>
       <c r="BD2" t="n">
-        <v>-1.400342735619549</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.595238095238088</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.8205042937592022</v>
-      </c>
+        <v>3.470118133239026</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -984,55 +984,55 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AD3" t="n">
         <v>-3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AE3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AF3" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AG3" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AH3" t="n">
         <v>-0.3516666666666666</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AI3" t="n">
         <v>0.5016666666666667</v>
       </c>
-      <c r="AD3" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-1.833333333333334</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-2.666666666666666</v>
-      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
         <v>74.45454545454545</v>
       </c>
@@ -1041,47 +1041,47 @@
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>2.760582010582009</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-0.2936091686091686</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-1.861768873802802</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>-7009472.251331244</v>
+      </c>
       <c r="AS3" t="n">
-        <v>-1.399630966887983</v>
+        <v>-9093658.945221439</v>
       </c>
       <c r="AT3" t="n">
-        <v>-1.4704585537919</v>
+        <v>3.08627622377622</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-2.325476828890402</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>0.03674242424244767</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-2.761978734970938</v>
+      </c>
       <c r="AX3" t="n">
-        <v>-7470161.574287699</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-2.655071549765765</v>
-      </c>
+        <v>-0.4348348877797352</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-0.07208994708992122</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-7764412.47795414</v>
-      </c>
+        <v>-3.740860528360528</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-0.3082010582010584</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>0.8130711560941961</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-1.619803807303811</v>
+      </c>
       <c r="BD3" t="n">
-        <v>1.098301267204988</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-3.587301587301596</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-0.3595826702576952</v>
-      </c>
+        <v>-1.627174064665326</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1165,55 +1165,55 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD4" t="n">
         <v>-12.66666666666666</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AE4" t="n">
         <v>12.66666666666666</v>
       </c>
-      <c r="V4" t="n">
-        <v>-3.666666666666666</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X4" t="n">
+      <c r="AF4" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AG4" t="n">
         <v>-1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AH4" t="n">
         <v>-1.363333333333334</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AI4" t="n">
         <v>-0.2566666666666666</v>
       </c>
-      <c r="AD4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-2.666666666666666</v>
-      </c>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
         <v>76.81818181818181</v>
       </c>
@@ -1222,47 +1222,47 @@
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-2.020779220779218</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>-0.3812672176308536</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.269527213650363</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>112762.8293770142</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-0.3082283631155747</v>
+        <v>-10959954.08631772</v>
       </c>
       <c r="AT4" t="n">
-        <v>-2.816883116883119</v>
+        <v>-2.134802571166208</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>1.503422381711886</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>-3.950688705234171</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.361197039790753</v>
+      </c>
       <c r="AX4" t="n">
-        <v>-2956650.31762306</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.2849678308324997</v>
-      </c>
+        <v>-0.05763281571998036</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-3.857142857142861</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-10421298.7012987</v>
-      </c>
+        <v>-1.863269054178133</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>-0.3402597402597405</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
+        <v>-2.160385287689216</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-3.02745638200183</v>
+      </c>
       <c r="BD4" t="n">
-        <v>-2.49869316147511</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-1.766233766233753</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-0.1313996571515368</v>
-      </c>
+        <v>1.298764296806212</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1346,55 +1346,55 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD5" t="n">
         <v>-7.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AE5" t="n">
         <v>7.5</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AF5" t="n">
         <v>0.5</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="AG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AH5" t="n">
         <v>0.8400000000000001</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
         <v>0.105</v>
       </c>
-      <c r="AD5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
         <v>80.62121212121212</v>
       </c>
@@ -1403,47 +1403,47 @@
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>1.978896103896108</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>-0.1052020202020199</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-7.167656031936374</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>-22916982.21220653</v>
+      </c>
       <c r="AS5" t="n">
-        <v>-7.683412712506566</v>
+        <v>-32423924.24242425</v>
       </c>
       <c r="AT5" t="n">
-        <v>-3.585317460317455</v>
+        <v>1.56219696969697</v>
       </c>
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>4.277544956047279</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>-0.2730555555555156</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-5.112415908114855</v>
+      </c>
       <c r="AX5" t="n">
-        <v>-23630255.32465113</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-5.31768846560422</v>
-      </c>
+        <v>-0.05674125905129435</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-0.9334415584415297</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-33926587.3015873</v>
-      </c>
+        <v>-4.525606060606052</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-0.0912698412698405</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
+        <v>-1.032944191059684</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-3.762348484848474</v>
+      </c>
       <c r="BD5" t="n">
-        <v>-1.084584950407592</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-4.762806637806634</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-0.1134129821519252</v>
-      </c>
+        <v>3.586695921729074</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1527,55 +1527,55 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AD6" t="n">
         <v>17.5</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AE6" t="n">
         <v>-17.5</v>
       </c>
-      <c r="V6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-11</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AF6" t="n">
         <v>4</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AG6" t="n">
         <v>-4</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AH6" t="n">
         <v>1.205</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AI6" t="n">
         <v>-2.49</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-19</v>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
         <v>78.64090909090909</v>
       </c>
@@ -1584,47 +1584,47 @@
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>-2.668831168831172</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>-0.8372727272727274</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-0.8868432728822881</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-1483116.268641843</v>
+      </c>
       <c r="AS6" t="n">
-        <v>0.1490999430074993</v>
+        <v>-4979454.545454549</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.369264069264091</v>
+        <v>-2.036363636363639</v>
       </c>
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="n">
-        <v>2.90767185662142</v>
-      </c>
-      <c r="AW6" t="inlineStr"/>
+        <v>0.5500000000000114</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-1.104214906647769</v>
+      </c>
       <c r="AX6" t="n">
-        <v>-1592563.45720106</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-1.224704730377013</v>
-      </c>
+        <v>-0.5538933913486344</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>0.4837662337662607</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-3549740.259740259</v>
-      </c>
+        <v>-0.5690909090909173</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-0.8261904761904761</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
+        <v>-0.9342014500134717</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-2.51636363636365</v>
+      </c>
       <c r="BD6" t="n">
-        <v>-0.008494003662065097</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.1000000000000085</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.5504971685643953</v>
-      </c>
+        <v>2.920346237309133</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1708,55 +1708,55 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-14</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD7" t="n">
         <v>-23</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AE7" t="n">
         <v>23</v>
       </c>
-      <c r="V7" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="AF7" t="n">
         <v>-2.5</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AG7" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AH7" t="n">
         <v>-2.595</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AI7" t="n">
         <v>1.61</v>
       </c>
-      <c r="AD7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>10</v>
-      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
         <v>81.5409090909091</v>
       </c>
@@ -1765,47 +1765,47 @@
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>0.4456565656565665</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>0.1506060606060606</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.490039820972314</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>876508.1615898339</v>
+      </c>
       <c r="AS7" t="n">
-        <v>1.572721783047868</v>
+        <v>3256969.696969695</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.290404040404027</v>
+        <v>0.5854545454545459</v>
       </c>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="n">
-        <v>0.8322058415627396</v>
-      </c>
-      <c r="AW7" t="inlineStr"/>
+        <v>1.111616161616183</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.0645759396075789</v>
+      </c>
       <c r="AX7" t="n">
-        <v>1165327.111809983</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-0.2003483651972573</v>
-      </c>
+        <v>-0.1382801957095268</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>0.9432323232323654</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>3469636.363636361</v>
-      </c>
+        <v>1.091212121212109</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>0.1016161616161615</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
+        <v>2.198315014504956</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.273232323232307</v>
+      </c>
       <c r="BD7" t="n">
-        <v>2.113813240086966</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.9821212121212142</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.1609272833327213</v>
-      </c>
+        <v>0.6708701780787294</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1885,104 +1885,104 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>4.833333333333333</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.833333333333332</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-8.166666666666668</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-8.833333333333332</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.6666666666666661</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AD8" t="n">
         <v>28.16666666666667</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AE8" t="n">
         <v>-28.16666666666666</v>
       </c>
-      <c r="V8" t="n">
-        <v>-0.6666666666666661</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AF8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AG8" t="n">
         <v>-0.6666666666666667</v>
       </c>
-      <c r="Z8" t="n">
-        <v>-8.833333333333332</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.833333333333334</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AH8" t="n">
         <v>0.5316666666666663</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AI8" t="n">
         <v>-0.9866666666666666</v>
       </c>
-      <c r="AD8" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>3.833333333333333</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>4.833333333333332</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>-8.166666666666668</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
-        <v>78.94351851851853</v>
+        <v>78.94405594405595</v>
       </c>
       <c r="AM8" t="n">
         <v>70.58585858585859</v>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>0.5838383838383834</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>2.121678321678321</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.19733209151367</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>42145361.24669117</v>
+      </c>
       <c r="AS8" t="n">
-        <v>11.12046768788032</v>
+        <v>70308624.70862469</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.04242424242426</v>
+        <v>0.002874902874903995</v>
       </c>
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="n">
-        <v>-5.284725436068157</v>
-      </c>
-      <c r="AW8" t="inlineStr"/>
+        <v>-0.6117327117326852</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11.60342130163103</v>
+      </c>
       <c r="AX8" t="n">
-        <v>43081331.70498473</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>11.73923745021358</v>
-      </c>
+        <v>1.240149627297965</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>-0.4070707070706874</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>71284444.44444445</v>
-      </c>
+        <v>13.13504273504273</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>2.192929292929293</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
+        <v>-0.5474322021636588</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.35881895881897</v>
+      </c>
       <c r="BD8" t="n">
-        <v>-0.8048620414349301</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>13.27979797979798</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.287436794363478</v>
-      </c>
+        <v>-5.050249717129475</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -2066,55 +2066,55 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>26.5</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>-26.5</v>
+        <v>-1</v>
       </c>
       <c r="V9" t="n">
         <v>-1</v>
       </c>
       <c r="W9" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA9" t="n">
         <v>1.5</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AB9" t="n">
         <v>-1</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
         <v>0.1500000000000001</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AI9" t="n">
         <v>-0.5899999999999999</v>
       </c>
-      <c r="AD9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-7</v>
-      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
         <v>70.48333333333333</v>
       </c>
@@ -2123,47 +2123,47 @@
       </c>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>0.231818181818177</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>-0.2963636363636364</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-4.211557572861921</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-7624331.600198607</v>
+      </c>
       <c r="AS9" t="n">
-        <v>-4.110121246566237</v>
+        <v>-4295867.132867132</v>
       </c>
       <c r="AT9" t="n">
-        <v>-2.298484848484861</v>
+        <v>0.2301787101787092</v>
       </c>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="n">
-        <v>-6.631758548830163</v>
-      </c>
-      <c r="AW9" t="inlineStr"/>
+        <v>-5.551111111111084</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-3.951833422332143</v>
+      </c>
       <c r="AX9" t="n">
-        <v>-7216036.076266255</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-4.153188473457021</v>
-      </c>
+        <v>-0.4371781756180735</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>-5.080808080808083</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-4453484.848484848</v>
-      </c>
+        <v>-2.599456099456106</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-0.2833333333333334</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
+        <v>0.2416428243538249</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2.113947163947174</v>
+      </c>
       <c r="BD9" t="n">
-        <v>0.2864903449302361</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-2.698484848484838</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-0.416873706004141</v>
-      </c>
+        <v>-5.974788557563471</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2247,55 +2247,55 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>18.83333333333334</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="U10" t="n">
-        <v>-18.83333333333334</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="V10" t="n">
-        <v>2.833333333333333</v>
+        <v>7.5</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.333333333333333</v>
+        <v>-14</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="Z10" t="n">
         <v>0.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>18.83333333333334</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-18.83333333333334</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.053333333333333</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AI10" t="n">
         <v>-0.7083333333333335</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.166666666666667</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-14</v>
-      </c>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="n">
         <v>80.99621212121212</v>
       </c>
@@ -2304,47 +2304,47 @@
       </c>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>-2.476479076479077</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
+        <v>0.5454545454545456</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5.500652816093634</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>20552139.51903879</v>
+      </c>
       <c r="AS10" t="n">
-        <v>5.492297330831633</v>
+        <v>28696590.90909091</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.122366522366519</v>
+        <v>-2.261363636363637</v>
       </c>
       <c r="AU10" t="inlineStr"/>
       <c r="AV10" t="n">
-        <v>-5.151636646267946</v>
-      </c>
-      <c r="AW10" t="inlineStr"/>
+        <v>0.726515151515116</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.883776750218217</v>
+      </c>
       <c r="AX10" t="n">
-        <v>19843329.26238764</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.652590380164241</v>
-      </c>
+        <v>0.4003064243644767</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="n">
-        <v>1.437806637806574</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>28638383.83838384</v>
-      </c>
+        <v>5.89015151515153</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>0.4965367965367966</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
+        <v>-0.6863371627373311</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.13459595959597</v>
+      </c>
       <c r="BD10" t="n">
-        <v>-0.3894781406078849</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.015873015873012</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.3217405612130437</v>
-      </c>
+        <v>-4.184758908404802</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2428,104 +2428,104 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-9.333333333333334</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.666666666666666</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>11</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AE11" t="n">
         <v>-11</v>
       </c>
-      <c r="V11" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AF11" t="n">
         <v>-0.6666666666666666</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AG11" t="n">
         <v>-0.3333333333333335</v>
       </c>
-      <c r="Z11" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AH11" t="n">
         <v>0.7433333333333332</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AI11" t="n">
         <v>-0.5866666666666666</v>
       </c>
-      <c r="AD11" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
-        <v>-1.666666666666666</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.333333333333333</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-9.333333333333334</v>
-      </c>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
         <v>79.23367003367004</v>
       </c>
       <c r="AM11" t="n">
-        <v>80.72323232323232</v>
+        <v>80.62556332556332</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>1.078843995510663</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
+        <v>-0.8355434688768022</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-2.249542429030427</v>
+      </c>
       <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>-10623383.50646303</v>
+      </c>
       <c r="AS11" t="n">
-        <v>-1.654632899589046</v>
+        <v>-20324584.7362514</v>
       </c>
       <c r="AT11" t="n">
-        <v>-4.351346801346793</v>
+        <v>0.9760597427264059</v>
       </c>
       <c r="AU11" t="inlineStr"/>
       <c r="AV11" t="n">
-        <v>-6.154116035037049</v>
-      </c>
-      <c r="AW11" t="inlineStr"/>
+        <v>-2.97611154277817</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-1.198670460292306</v>
+      </c>
       <c r="AX11" t="n">
-        <v>-9622848.393078659</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-1.042907036108801</v>
-      </c>
+        <v>-0.4859644290365113</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="n">
-        <v>-2.566778900112212</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>-20172056.67789001</v>
-      </c>
+        <v>-4.307519640852973</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>-0.8220538720538724</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
+        <v>-1.061381178254749</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-4.370948804282136</v>
+      </c>
       <c r="BD11" t="n">
-        <v>-0.7771996278575237</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-4.391189674523005</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-0.3841575740698548</v>
-      </c>
+        <v>-6.132733766678257</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2609,55 +2609,55 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-7.666666666666666</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-5.333333333333333</v>
+      </c>
+      <c r="AD12" t="n">
         <v>-10.5</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AE12" t="n">
         <v>10.5</v>
       </c>
-      <c r="V12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AF12" t="n">
         <v>0.8333333333333333</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AG12" t="n">
         <v>-1</v>
       </c>
-      <c r="Z12" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AH12" t="n">
         <v>-0.7333333333333329</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AI12" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-7.666666666666666</v>
-      </c>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
         <v>71.22727272727272</v>
       </c>
@@ -2666,47 +2666,47 @@
       </c>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="n">
-        <v>1.720000000000002</v>
-      </c>
-      <c r="AP12" t="inlineStr"/>
+        <v>-0.7506060606060605</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-5.152669862738819</v>
+      </c>
       <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>-21623315.76815349</v>
+      </c>
       <c r="AS12" t="n">
-        <v>-4.873920573013891</v>
+        <v>-30325924.24242424</v>
       </c>
       <c r="AT12" t="n">
-        <v>-5.980952380952374</v>
+        <v>1.331363636363637</v>
       </c>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="n">
-        <v>-0.6626622499078962</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
+        <v>-1.469949494949503</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-5.835632629715093</v>
+      </c>
       <c r="AX12" t="n">
-        <v>-20874595.33673916</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-5.359832369949572</v>
-      </c>
+        <v>-0.3442275439636824</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="n">
-        <v>-2.086666666666645</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>-30444730.15873016</v>
-      </c>
+        <v>-6.998636363636365</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>-0.6431746031746028</v>
-      </c>
-      <c r="BC12" t="inlineStr"/>
+        <v>1.450330433865471</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-5.975101010101014</v>
+      </c>
       <c r="BD12" t="n">
-        <v>1.501286670968224</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-7.178730158730161</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-0.2608402451889849</v>
-      </c>
+        <v>-1.285564543737195</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="n">
         <v>0</v>
       </c>
@@ -2790,55 +2790,55 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.166666666666666</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.416666666666666</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AD13" t="n">
         <v>-4.333333333333336</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AE13" t="n">
         <v>4.333333333333336</v>
       </c>
-      <c r="V13" t="n">
-        <v>2.083333333333334</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.5833333333333335</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.166666666666666</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.416666666666666</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AH13" t="n">
         <v>0.5366666666666666</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AI13" t="n">
         <v>0.8383333333333336</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>10</v>
-      </c>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
         <v>78.76801346801348</v>
       </c>
@@ -2847,47 +2847,47 @@
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="n">
-        <v>-3.395286195286193</v>
-      </c>
-      <c r="AP13" t="inlineStr"/>
+        <v>-1.375291375291375</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-6.590519421351274</v>
+      </c>
       <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>-29581965.33174726</v>
+      </c>
       <c r="AS13" t="n">
-        <v>-6.940612621783259</v>
+        <v>-51794716.39471639</v>
       </c>
       <c r="AT13" t="n">
-        <v>-7.728170594837266</v>
+        <v>-3.143822843822843</v>
       </c>
       <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
-        <v>4.51620916532633</v>
-      </c>
-      <c r="AW13" t="inlineStr"/>
+        <v>0.8218337218336842</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-3.5921210880324</v>
+      </c>
       <c r="AX13" t="n">
-        <v>-29625592.38763808</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-3.895102332436878</v>
-      </c>
+        <v>-0.5517358888101922</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="n">
-        <v>0.7700336700336265</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>-53717283.95061729</v>
-      </c>
+        <v>-4.146076146076155</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="n">
-        <v>-1.452188552188552</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
+        <v>-1.445227330289253</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-7.169696969696972</v>
+      </c>
       <c r="BD13" t="n">
-        <v>-1.444567859041545</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>-4.439393939393938</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-0.6232386894151596</v>
-      </c>
+        <v>4.817381170675645</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -2971,55 +2971,55 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
         <v>12</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AE14" t="n">
         <v>-12</v>
       </c>
-      <c r="V14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AF14" t="n">
         <v>-1</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AG14" t="n">
         <v>1</v>
       </c>
-      <c r="Z14" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
         <v>-0.8949999999999998</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AI14" t="n">
         <v>1.085</v>
       </c>
-      <c r="AD14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2</v>
-      </c>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
         <v>77.95454545454545</v>
       </c>
@@ -3028,47 +3028,47 @@
       </c>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="n">
-        <v>0.5930735930735942</v>
-      </c>
-      <c r="AP14" t="inlineStr"/>
+        <v>-0.2545454545454549</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.8000808900982292</v>
+      </c>
       <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>615215.1131238164</v>
+      </c>
       <c r="AS14" t="n">
-        <v>0.3947107497969995</v>
+        <v>-2663818.181818182</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.1601731601731586</v>
+        <v>0.3154545454545428</v>
       </c>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="n">
-        <v>-2.736316924430582</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
+        <v>1.114545454545436</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.266714102498341</v>
+      </c>
       <c r="AX14" t="n">
-        <v>-806290.1812771903</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.318756332942542</v>
-      </c>
+        <v>-0.06403315407017129</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="n">
-        <v>0.7359307359307365</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>-2735714.285714291</v>
-      </c>
+        <v>-0.9945454545454453</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="n">
-        <v>-0.2510822510822515</v>
-      </c>
-      <c r="BC14" t="inlineStr"/>
+        <v>-1.897480919904194</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
       <c r="BD14" t="n">
-        <v>-1.75660047644789</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>-1.030303030303031</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-0.06328256448778324</v>
-      </c>
+        <v>-4.000341032675465</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3152,55 +3152,55 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC15" t="n">
         <v>-4</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AD15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE15" t="n">
         <v>4</v>
       </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AF15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AG15" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AH15" t="n">
         <v>0.9299999999999998</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AI15" t="n">
         <v>-1.285</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1</v>
-      </c>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
         <v>77.62272727272727</v>
       </c>
@@ -3209,47 +3209,47 @@
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="n">
-        <v>1.727272727272723</v>
-      </c>
-      <c r="AP15" t="inlineStr"/>
+        <v>0.006363636363636793</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.2661949279052891</v>
+      </c>
       <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>-5772490.741009841</v>
+      </c>
       <c r="AS15" t="n">
-        <v>-0.3468443185355028</v>
+        <v>-6850636.36363636</v>
       </c>
       <c r="AT15" t="n">
-        <v>-1.033333333333317</v>
+        <v>1.72909090909091</v>
       </c>
       <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="n">
-        <v>-2.440900425826896</v>
-      </c>
-      <c r="AW15" t="inlineStr"/>
+        <v>0.4572727272727093</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-2.063036392422575</v>
+      </c>
       <c r="AX15" t="n">
-        <v>-3850457.883279577</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>-1.567192584104333</v>
-      </c>
+        <v>-0.001038864162265396</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="n">
-        <v>0.7954545454545041</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>-7953939.393939391</v>
-      </c>
+        <v>-1.222727272727269</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="n">
-        <v>-0.02878787878787881</v>
-      </c>
-      <c r="BC15" t="inlineStr"/>
+        <v>3.999191605495959</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.5618181818181824</v>
+      </c>
       <c r="BD15" t="n">
-        <v>3.101948051948046</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>-1.354545454545459</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0.03268309849192175</v>
-      </c>
+        <v>-2.417804575716985</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="n">
         <v>0</v>
       </c>
@@ -3333,55 +3333,55 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AD16" t="n">
         <v>-14.75</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AE16" t="n">
         <v>14.75</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AF16" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AG16" t="n">
         <v>-2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AH16" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AI16" t="n">
         <v>-1.1925</v>
       </c>
-      <c r="AD16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>-3</v>
-      </c>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
         <v>77.02146464646464</v>
       </c>
@@ -3390,47 +3390,47 @@
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="n">
-        <v>1.389442039442034</v>
-      </c>
-      <c r="AP16" t="inlineStr"/>
+        <v>0.2061728395061724</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-0.003630135120403111</v>
+      </c>
       <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>-1243673.984887624</v>
+      </c>
       <c r="AS16" t="n">
-        <v>-0.3097956459471476</v>
+        <v>1861301.907968573</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.153030303030306</v>
+        <v>1.552300785634117</v>
       </c>
       <c r="AU16" t="inlineStr"/>
       <c r="AV16" t="n">
-        <v>8.527110169010342</v>
-      </c>
-      <c r="AW16" t="inlineStr"/>
+        <v>1.802918069584734</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-3.187342346168066</v>
+      </c>
       <c r="AX16" t="n">
-        <v>-1365357.45304987</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>-3.10573312849165</v>
-      </c>
+        <v>-0.0007441557858842707</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="n">
-        <v>1.399230399230419</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1998494.468494467</v>
-      </c>
+        <v>-0.9500561167227914</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="n">
-        <v>0.201082251082251</v>
-      </c>
-      <c r="BC16" t="inlineStr"/>
+        <v>1.850529250983385</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.206846240179587</v>
+      </c>
       <c r="BD16" t="n">
-        <v>1.42343180979486</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>-0.8108465608465707</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>-0.02094313698019268</v>
-      </c>
+        <v>8.059273693077529</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
       <c r="BG16" t="n">
         <v>0</v>
       </c>
@@ -3514,55 +3514,55 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.800000000000001</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.5</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AE17" t="n">
         <v>-2.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.2999999999999998</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AF17" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AG17" t="n">
         <v>-0.6000000000000001</v>
       </c>
-      <c r="Z17" t="n">
-        <v>-1.800000000000001</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-2.199999999999999</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AH17" t="n">
         <v>1.316</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
         <v>0.3799999999999999</v>
       </c>
-      <c r="AD17" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>-0.1000000000000001</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>7.199999999999999</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.800000000000001</v>
-      </c>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
         <v>73.29545454545455</v>
       </c>
@@ -3571,47 +3571,47 @@
       </c>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="n">
-        <v>0.5818181818181785</v>
-      </c>
-      <c r="AP17" t="inlineStr"/>
+        <v>0.5449035812672174</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.34440858103379</v>
+      </c>
       <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>8243721.972391321</v>
+      </c>
       <c r="AS17" t="n">
-        <v>3.579467100849982</v>
+        <v>15066457.58282122</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.965367965367989</v>
+        <v>1.006442042805681</v>
       </c>
       <c r="AU17" t="inlineStr"/>
       <c r="AV17" t="n">
-        <v>2.66230671012363</v>
-      </c>
-      <c r="AW17" t="inlineStr"/>
+        <v>5.816345270890736</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.561599790970874</v>
+      </c>
       <c r="AX17" t="n">
-        <v>10940136.6259064</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.446755465471227</v>
-      </c>
+        <v>0.3767063634652568</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="n">
-        <v>5.156998556998587</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>14835497.83549783</v>
-      </c>
+        <v>4.671816062725142</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="n">
-        <v>0.5116883116883117</v>
-      </c>
-      <c r="BC17" t="inlineStr"/>
+        <v>1.019644226578656</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.145949000494468</v>
+      </c>
       <c r="BD17" t="n">
-        <v>1.387282207569015</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>4.814718614718601</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0.4557823129251699</v>
-      </c>
+        <v>2.642024949784741</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3695,55 +3695,55 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD18" t="n">
         <v>-8</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AE18" t="n">
         <v>8</v>
       </c>
-      <c r="V18" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AF18" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AG18" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z18" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AH18" t="n">
         <v>-0.0349999999999997</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AI18" t="n">
         <v>-0.4700000000000002</v>
       </c>
-      <c r="AD18" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>-6</v>
-      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
         <v>81.76666666666667</v>
       </c>
@@ -3752,47 +3752,47 @@
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="n">
-        <v>1.207142857142863</v>
-      </c>
-      <c r="AP18" t="inlineStr"/>
+        <v>0.1327272727272726</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.5976217781777677</v>
+      </c>
       <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>-732153.2015697286</v>
+      </c>
       <c r="AS18" t="n">
-        <v>0.8388825088318299</v>
+        <v>189363.6363636367</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.1499999999999915</v>
+        <v>0.8981818181818184</v>
       </c>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="n">
-        <v>2.466029456994647</v>
-      </c>
-      <c r="AW18" t="inlineStr"/>
+        <v>3.685454545454519</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.02903659157051663</v>
+      </c>
       <c r="AX18" t="n">
-        <v>-767450.2320170831</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0.4214651771532942</v>
-      </c>
+        <v>0.1181046278727971</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="n">
-        <v>3.780952380952357</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>39285.71428571455</v>
-      </c>
+        <v>-0.2090909090909037</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="n">
-        <v>0.1119047619047622</v>
-      </c>
-      <c r="BC18" t="inlineStr"/>
+        <v>0.8990982367567355</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0.004545454545464622</v>
+      </c>
       <c r="BD18" t="n">
-        <v>0.8249206089758587</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>-0.3500000000000085</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0.09249105023050785</v>
-      </c>
+        <v>2.033999310972519</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
@@ -3876,55 +3876,55 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-21.66666666666667</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AD19" t="n">
         <v>18.33333333333334</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AE19" t="n">
         <v>-18.33333333333334</v>
       </c>
-      <c r="V19" t="n">
-        <v>6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-11.33333333333333</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="AF19" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AG19" t="n">
         <v>-3.166666666666667</v>
       </c>
-      <c r="Z19" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AH19" t="n">
         <v>2.831666666666667</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AI19" t="n">
         <v>-2.891666666666667</v>
       </c>
-      <c r="AD19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>-21.66666666666667</v>
-      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
         <v>75.97205387205388</v>
       </c>
@@ -3933,47 +3933,47 @@
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="n">
-        <v>-1.791666666666664</v>
-      </c>
-      <c r="AP19" t="inlineStr"/>
+        <v>0.783333333333333</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.526123463739552</v>
+      </c>
       <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>29706898.9663431</v>
+      </c>
       <c r="AS19" t="n">
-        <v>9.0118740319094</v>
+        <v>46183159.72222222</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.105158730158735</v>
+        <v>-1.874999999999993</v>
       </c>
       <c r="AU19" t="inlineStr"/>
       <c r="AV19" t="n">
-        <v>-1.40474505591709</v>
-      </c>
-      <c r="AW19" t="inlineStr"/>
+        <v>-0.03055555555556566</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.932920780317346</v>
+      </c>
       <c r="AX19" t="n">
-        <v>28656762.1306896</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.899660534070094</v>
-      </c>
+        <v>0.5191367618527765</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="n">
-        <v>0.2698412698412653</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>47880505.95238096</v>
-      </c>
+        <v>6.67638888888888</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="n">
-        <v>0.8253968253968251</v>
-      </c>
-      <c r="BC19" t="inlineStr"/>
+        <v>0.6386943558052494</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6.905555555555566</v>
+      </c>
       <c r="BD19" t="n">
-        <v>0.2961711000189524</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.855158730158735</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0.478255608463481</v>
-      </c>
+        <v>-1.750258349243694</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="n">
         <v>0</v>
       </c>
@@ -4053,102 +4053,102 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AC20" t="n">
         <v>-4</v>
       </c>
-      <c r="U20" t="n">
+      <c r="AD20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AE20" t="n">
         <v>4</v>
       </c>
-      <c r="V20" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
         <v>-2</v>
       </c>
-      <c r="Z20" t="n">
-        <v>-3.25</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AH20" t="n">
         <v>-0.1925000000000001</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AI20" t="n">
         <v>-1.3675</v>
       </c>
-      <c r="AD20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>-9.5</v>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
         <v>78.65909090909091</v>
       </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="n">
-        <v>0.2012987012986969</v>
-      </c>
-      <c r="AP20" t="inlineStr"/>
+        <v>-1.614876033057851</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-10.27796624139336</v>
+      </c>
       <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>-31334259.10856218</v>
+      </c>
       <c r="AS20" t="n">
-        <v>-10.718677905945</v>
+        <v>-43719807.16253443</v>
       </c>
       <c r="AT20" t="n">
-        <v>-12.69350649350649</v>
+        <v>0.6276400367309414</v>
       </c>
       <c r="AU20" t="inlineStr"/>
       <c r="AV20" t="n">
-        <v>-0.1266415261756322</v>
-      </c>
-      <c r="AW20" t="inlineStr"/>
+        <v>-0.6777777777777771</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-11.03030118503264</v>
+      </c>
       <c r="AX20" t="n">
-        <v>-33738368.08636498</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>-11.30040668441291</v>
-      </c>
+        <v>-0.7867624915578886</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="n">
-        <v>-0.4506493506493712</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>-46723506.49350649</v>
-      </c>
+        <v>-11.14921946740127</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="n">
-        <v>-1.719480519480519</v>
-      </c>
-      <c r="BC20" t="inlineStr"/>
+        <v>1.962950784178407</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-11.81781450872361</v>
+      </c>
       <c r="BD20" t="n">
-        <v>2.003031647441585</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>-11.45584415584413</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>-0.9088657202011241</v>
-      </c>
+        <v>0.05128627647806638</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -4235,52 +4235,52 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="V21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.75</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AC21" t="n">
         <v>1.5</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AH21" t="n">
         <v>0.8125</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AI21" t="n">
         <v>-0.08499999999999996</v>
       </c>
-      <c r="AD21" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
         <v>76.15625</v>
       </c>
@@ -4289,47 +4289,47 @@
       </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="n">
-        <v>-2.15746352413019</v>
-      </c>
-      <c r="AP21" t="inlineStr"/>
+        <v>0.683916083916084</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.4151497898237011</v>
+      </c>
       <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>12061725.57887552</v>
+      </c>
       <c r="AS21" t="n">
-        <v>-0.2266699953294165</v>
+        <v>16835646.46464647</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.766498316498314</v>
+        <v>-2.183815073815069</v>
       </c>
       <c r="AU21" t="inlineStr"/>
       <c r="AV21" t="n">
-        <v>2.609098920639809</v>
-      </c>
-      <c r="AW21" t="inlineStr"/>
+        <v>0.80501165501164</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.402444625564826</v>
+      </c>
       <c r="AX21" t="n">
-        <v>10854144.80867007</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>5.056230519583039</v>
-      </c>
+        <v>0.568909900131128</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="n">
-        <v>0.8731762065094983</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>16510272.1661055</v>
-      </c>
+        <v>5.274848484848491</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="n">
-        <v>0.6659932659932661</v>
-      </c>
-      <c r="BC21" t="inlineStr"/>
+        <v>-3.751456358361732</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.731375291375286</v>
+      </c>
       <c r="BD21" t="n">
-        <v>-3.87185395238464</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.382772166105511</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0.50512767835871</v>
-      </c>
+        <v>2.872913347663996</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
@@ -4413,55 +4413,55 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-7.333333333333333</v>
+      </c>
+      <c r="X22" t="n">
+        <v>6.666666666666668</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AD22" t="n">
         <v>5.666666666666664</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AE22" t="n">
         <v>-5.666666666666664</v>
       </c>
-      <c r="V22" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="AF22" t="n">
         <v>-2.333333333333333</v>
       </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.666666666666668</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
         <v>-0.3266666666666667</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AI22" t="n">
         <v>-1.066666666666667</v>
       </c>
-      <c r="AD22" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>-7.333333333333333</v>
-      </c>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
       <c r="AL22" t="n">
         <v>72.98888888888888</v>
       </c>
@@ -4470,47 +4470,47 @@
       </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="n">
-        <v>-1.06920634920635</v>
-      </c>
-      <c r="AP22" t="inlineStr"/>
+        <v>0.1565656565656564</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7.164334327785696</v>
+      </c>
       <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>3541222.416324455</v>
+      </c>
       <c r="AS22" t="n">
-        <v>6.827767826428826</v>
+        <v>5977710.437710438</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.909206349206357</v>
+        <v>-1.254461279461278</v>
       </c>
       <c r="AU22" t="inlineStr"/>
       <c r="AV22" t="n">
-        <v>0.3984636270162696</v>
-      </c>
-      <c r="AW22" t="inlineStr"/>
+        <v>2.451010101010098</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3.092468129852037</v>
+      </c>
       <c r="AX22" t="n">
-        <v>3593784.842479503</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.033166674227033</v>
-      </c>
+        <v>0.06047824831687043</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="n">
-        <v>2.587619047619086</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6375174.603174603</v>
-      </c>
+        <v>4.716835016835034</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="n">
-        <v>0.1485714285714284</v>
-      </c>
-      <c r="BC22" t="inlineStr"/>
+        <v>2.498082208779447</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.279713804713793</v>
+      </c>
       <c r="BD22" t="n">
-        <v>2.219128968726494</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.985396825396819</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0.03953449800973008</v>
-      </c>
+        <v>1.282963061142851</v>
+      </c>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
@@ -4594,55 +4594,55 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>21.5</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>-21.5</v>
+        <v>-1</v>
       </c>
       <c r="V23" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="W23" t="n">
         <v>8</v>
       </c>
       <c r="X23" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="AF23" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AG23" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AI23" t="n">
         <v>0.665</v>
       </c>
-      <c r="AD23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>8</v>
-      </c>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
       <c r="AL23" t="n">
         <v>71.18181818181819</v>
       </c>
@@ -4651,47 +4651,47 @@
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="n">
-        <v>-3.221212121212126</v>
-      </c>
-      <c r="AP23" t="inlineStr"/>
+        <v>0.09393939393939421</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>3.635794575479167</v>
+      </c>
       <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>1354569.911297852</v>
+      </c>
       <c r="AS23" t="n">
-        <v>4.110390955899263</v>
+        <v>1884015.151515152</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.169696969696972</v>
+        <v>-2.392929292929296</v>
       </c>
       <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="n">
-        <v>-4.961513518450801</v>
-      </c>
-      <c r="AW23" t="inlineStr"/>
+        <v>-3.19595959595955</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.210217098111386</v>
+      </c>
       <c r="AX23" t="n">
-        <v>1890838.908933138</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>4.420315650414764</v>
-      </c>
+        <v>0.00766316188311067</v>
+      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="n">
-        <v>-2.48333333333332</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1808409.090909091</v>
-      </c>
+        <v>4.343434343434367</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="n">
-        <v>0.09242424242424252</v>
-      </c>
-      <c r="BC23" t="inlineStr"/>
+        <v>-0.1003201441607224</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.598989898989913</v>
+      </c>
       <c r="BD23" t="n">
-        <v>-0.1078290978227052</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.842424242424244</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0.02538363171355495</v>
-      </c>
+        <v>-4.196248257757162</v>
+      </c>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
@@ -4911,27 +4911,32 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eltringham g 
+  eng </t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4957,10 +4962,18 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>MsDWbjnD</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>-2</v>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="n">
+        <v>-1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
       <c r="S26" t="n">
         <v>0</v>
@@ -4984,7 +4997,9 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
+      <c r="AM26" t="n">
+        <v>68.61805555555556</v>
+      </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
@@ -5011,7 +5026,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -5020,18 +5035,18 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">dw stadium
+  wigan </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5056,18 +5071,14 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
@@ -5091,9 +5102,7 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="n">
-        <v>69.2</v>
-      </c>
+      <c r="AL27" t="inlineStr"/>
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
@@ -5121,7 +5130,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -5130,18 +5139,18 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5168,13 +5177,9 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="n">
-        <v>3</v>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
         <v>0</v>
@@ -5225,27 +5230,32 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ward g 
+  eng </t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5270,52 +5280,128 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Y39YvFx6</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W29" t="n">
+        <v>9</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>-21</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.73</v>
+      </c>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
+      <c r="AL29" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>69</v>
+      </c>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.6380053976449886</v>
+      </c>
       <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>-77314.16185897798</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>-1275463.734567902</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.831882716049385</v>
+      </c>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
+      <c r="AV29" t="n">
+        <v>2.113919753086407</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>-0.5262976278543618</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
       <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
+      <c r="AZ29" t="n">
+        <v>-5.979506172839507</v>
+      </c>
       <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="inlineStr"/>
+      <c r="BB29" t="n">
+        <v>1.389894695561338</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0.4389197530864237</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0.2003976659411819</v>
+      </c>
       <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="inlineStr"/>
       <c r="BG29" t="n">
@@ -5325,7 +5411,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -5334,18 +5420,18 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5372,22 +5458,18 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>phM8NElP</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P30" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>0</v>
       </c>
@@ -5410,7 +5492,7 @@
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
       <c r="AL30" t="n">
-        <v>69.64141414141415</v>
+        <v>69.2</v>
       </c>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
@@ -5439,7 +5521,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -5448,18 +5530,18 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5486,16 +5568,16 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
@@ -5520,7 +5602,7 @@
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
       <c r="AL31" t="n">
-        <v>69.13636363636363</v>
+        <v>70.70833333333333</v>
       </c>
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
@@ -5549,7 +5631,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -5558,18 +5640,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5649,7 +5731,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -5658,18 +5740,18 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5696,16 +5778,16 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>zNcAe8Sa</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
@@ -5730,7 +5812,7 @@
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
       <c r="AL33" t="n">
-        <v>70.70833333333333</v>
+        <v>69.13636363636363</v>
       </c>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
@@ -5759,32 +5841,27 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5810,18 +5887,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>MsDWbjnD</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
         <v>0</v>
@@ -5845,9 +5918,7 @@
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
       <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
       <c r="AP34" t="inlineStr"/>
@@ -5874,7 +5945,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5883,18 +5954,18 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5921,9 +5992,13 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
         <v>0</v>
@@ -5974,7 +6049,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -5983,18 +6058,18 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6021,12 +6096,8 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1</v>
-      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
@@ -6078,7 +6149,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -6087,18 +6158,18 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6125,13 +6196,9 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
       <c r="S37" t="n">
         <v>0</v>
@@ -6182,7 +6249,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -6191,18 +6258,18 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6227,12 +6294,24 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="O38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-1</v>
+      </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
@@ -6254,7 +6333,9 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
+      <c r="AL38" t="n">
+        <v>69.64141414141415</v>
+      </c>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
@@ -6282,32 +6363,27 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6332,130 +6408,54 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>0</v>
       </c>
-      <c r="T39" t="n">
-        <v>-21</v>
-      </c>
-      <c r="U39" t="n">
-        <v>21</v>
-      </c>
-      <c r="V39" t="n">
-        <v>-5</v>
-      </c>
-      <c r="W39" t="n">
-        <v>8</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>74</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>69</v>
-      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="n">
-        <v>4.081666666666667</v>
-      </c>
+      <c r="AO39" t="inlineStr"/>
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr"/>
       <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="n">
-        <v>0.4796834704515049</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0.4862499999999983</v>
-      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="inlineStr"/>
       <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="n">
-        <v>0.1362195517032205</v>
-      </c>
+      <c r="AV39" t="inlineStr"/>
       <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="n">
-        <v>-200668.3320019464</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>-0.9468219381573988</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.075833333333321</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>-1118180.555555556</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr"/>
+      <c r="BA39" t="inlineStr"/>
+      <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
-      <c r="BD39" t="n">
-        <v>1.465790161411626</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>-5.248055555555567</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
@@ -6463,7 +6463,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -6472,18 +6472,18 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6510,9 +6510,13 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="O40" t="n">
+        <v>-2</v>
+      </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="n">
+        <v>-1</v>
+      </c>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
         <v>0</v>
@@ -6663,7 +6667,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6671,24 +6675,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6716,12 +6720,16 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
         <v>0</v>
@@ -6746,7 +6754,7 @@
       <c r="AK42" t="inlineStr"/>
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="n">
-        <v>71.77777777777777</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
@@ -6774,7 +6782,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -6783,18 +6791,18 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6819,7 +6827,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
@@ -6846,7 +6858,9 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
+      <c r="AL43" t="n">
+        <v>71.47727272727272</v>
+      </c>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
@@ -6874,7 +6888,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -6883,18 +6897,18 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6919,11 +6933,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
@@ -6950,9 +6960,7 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr"/>
       <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="n">
-        <v>69.33522727272728</v>
-      </c>
+      <c r="AL44" t="inlineStr"/>
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
@@ -6980,32 +6988,27 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">langford o 
-  eng </t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7031,18 +7034,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>OS3AwgCU</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>2</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>0</v>
@@ -7066,9 +7061,7 @@
       <c r="AJ45" t="inlineStr"/>
       <c r="AK45" t="inlineStr"/>
       <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="n">
-        <v>67.40000000000001</v>
-      </c>
+      <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
       <c r="AP45" t="inlineStr"/>
@@ -7195,7 +7188,7 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
@@ -7204,18 +7197,18 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7242,7 +7235,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>zNcAe8Sa</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -7272,7 +7265,7 @@
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
       <c r="AL47" t="n">
-        <v>71.47727272727272</v>
+        <v>69.33522727272728</v>
       </c>
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
@@ -7412,7 +7405,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -7421,18 +7414,18 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7512,27 +7505,32 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7558,7 +7556,11 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>U3POrPvM</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -7585,7 +7587,9 @@
       <c r="AJ50" t="inlineStr"/>
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
+      <c r="AM50" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
       <c r="AP50" t="inlineStr"/>
@@ -7688,55 +7692,55 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>7</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-24</v>
+      </c>
+      <c r="X51" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD51" t="n">
         <v>21</v>
       </c>
-      <c r="U51" t="n">
+      <c r="AE51" t="n">
         <v>-21</v>
       </c>
-      <c r="V51" t="n">
-        <v>4</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X51" t="n">
+      <c r="AF51" t="n">
         <v>2</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
         <v>1.61</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AI51" t="n">
         <v>-1.41</v>
       </c>
-      <c r="AD51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>-24</v>
-      </c>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="n">
         <v>66.2</v>
       </c>
@@ -7745,47 +7749,47 @@
       </c>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="n">
-        <v>-0.6712037037037035</v>
-      </c>
-      <c r="AP51" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>-2.18276958464368</v>
+      </c>
       <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
+      <c r="AR51" t="n">
+        <v>-1392917.724649544</v>
+      </c>
       <c r="AS51" t="n">
-        <v>-2.294259417483119</v>
+        <v>-2190757.575757575</v>
       </c>
       <c r="AT51" t="n">
-        <v>-2.760925925925932</v>
+        <v>-0.5365881032547684</v>
       </c>
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="n">
-        <v>-0.9354549251917206</v>
-      </c>
-      <c r="AW51" t="inlineStr"/>
+        <v>-1.629854096520717</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>-2.909130516126041</v>
+      </c>
       <c r="AX51" t="n">
-        <v>-1318294.858832687</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>-2.566349016480586</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="n">
-        <v>-1.005555555555503</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>-2148009.259259259</v>
-      </c>
+        <v>-2.624326599326608</v>
+      </c>
+      <c r="BA51" t="inlineStr"/>
       <c r="BB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC51" t="inlineStr"/>
+        <v>1.460704946544887</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>-2.885493827160488</v>
+      </c>
       <c r="BD51" t="n">
-        <v>1.350305783397889</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>-2.621203703703713</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
-      </c>
+        <v>0.3684150332076115</v>
+      </c>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
@@ -7793,7 +7797,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -7802,18 +7806,18 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7840,13 +7844,9 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
         <v>0</v>
@@ -7897,7 +7897,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -7906,18 +7906,18 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7997,7 +7997,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
@@ -8005,24 +8005,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8050,7 +8050,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>UwJevjpg</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -8080,7 +8080,7 @@
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
       <c r="AM54" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
@@ -8208,7 +8208,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -8216,24 +8216,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8261,7 +8261,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>UwJevjpg</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -8291,7 +8291,7 @@
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="n">
-        <v>71.2</v>
+        <v>76</v>
       </c>
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
@@ -8395,58 +8395,58 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V57" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="X57" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>5.000000000000001</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AD57" t="n">
         <v>19.59999999999999</v>
       </c>
-      <c r="U57" t="n">
+      <c r="AE57" t="n">
         <v>-19.59999999999999</v>
       </c>
-      <c r="V57" t="n">
-        <v>5.000000000000001</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="X57" t="n">
+      <c r="AF57" t="n">
         <v>1</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AG57" t="n">
         <v>-1</v>
       </c>
-      <c r="Z57" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB57" t="n">
+      <c r="AH57" t="n">
         <v>0.724</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AI57" t="n">
         <v>-0.8179999999999997</v>
       </c>
-      <c r="AD57" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>-0.2000000000000001</v>
-      </c>
-      <c r="AF57" t="n">
+      <c r="AJ57" t="n">
         <v>-3</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AK57" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>-12.4</v>
       </c>
       <c r="AL57" t="n">
         <v>77.36565656565656</v>
@@ -8455,61 +8455,61 @@
         <v>76.90282828282827</v>
       </c>
       <c r="AN57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>1.935241301907965</v>
+        <v>0.9104895104895103</v>
       </c>
       <c r="AP57" t="n">
-        <v>-1</v>
+        <v>4.713604546916557</v>
       </c>
       <c r="AQ57" t="n">
         <v>11</v>
       </c>
       <c r="AR57" t="n">
+        <v>25360675.28269542</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>43287766.12276611</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1.715073815073808</v>
+      </c>
+      <c r="AU57" t="n">
         <v>-4</v>
       </c>
-      <c r="AS57" t="n">
-        <v>5.818247068993031</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>5.84410774410776</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0</v>
-      </c>
       <c r="AV57" t="n">
-        <v>-5.593070794413478</v>
+        <v>-2.962703962703927</v>
       </c>
       <c r="AW57" t="n">
+        <v>3.408590649191694</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>0.3623117646774934</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>3.079487179487188</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>0.1590587304142304</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>5.451282051282064</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>-5.886652726358591</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF57" t="n">
         <v>-8500000</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>27404062.88584091</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>3.733329160971948</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>-2.559034792368095</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>44633869.24803592</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>0.9875420875420873</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>0.6996112630383706</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>3.316722783389451</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0.5104847340780838</v>
       </c>
       <c r="BG57" t="n">
         <v>1</v>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG57"/>
+  <dimension ref="A1:BG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -802,105 +802,105 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
         <v>2</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.5</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>20</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>-8</v>
       </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2</v>
-      </c>
       <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AB2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2</v>
-      </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="AF2" t="n">
         <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
       <c r="AL2" t="n">
         <v>79.5</v>
       </c>
       <c r="AM2" t="n">
         <v>75.25</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>6.861012030774461</v>
+      </c>
       <c r="AO2" t="n">
+        <v>-1.387272727272745</v>
+      </c>
+      <c r="AP2" t="n">
         <v>1.569421487603305</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5.527412323919933</v>
       </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>25630810.58734082</v>
+        <v>0.6897535476294401</v>
       </c>
       <c r="AS2" t="n">
-        <v>35034231.40495867</v>
+        <v>5.527412323919933</v>
       </c>
       <c r="AT2" t="n">
+        <v>3.470118133239026</v>
+      </c>
+      <c r="AU2" t="n">
         <v>-0.2683471074380144</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>-1.387272727272745</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>6.861012030774461</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.6897535476294401</v>
-      </c>
+        <v>6.536694214876022</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>6.536694214876022</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
+        <v>25630810.58734082</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>35034231.40495867</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="n">
+        <v>6.293471074380165</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
         <v>-1.55662180814355</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.293471074380165</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.470118133239026</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -908,7 +908,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>61T7bt5t</t>
+          <t>6RCbX36s</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,128 +960,128 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>x6CvOHH9</t>
+          <t>zuJM7XDg</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>12.66666666666666</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-1.363333333333334</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-0.2566666666666666</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>-1.333333333333333</v>
       </c>
-      <c r="U3" t="n">
-        <v>-0.1666666666666665</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-1.833333333333334</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.3516666666666666</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.5016666666666667</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
+      <c r="AK3" t="n">
+        <v>-1</v>
+      </c>
       <c r="AL3" t="n">
-        <v>74.45454545454545</v>
+        <v>76.81818181818181</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.96801346801347</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>76.47575757575758</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.361197039790753</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-0.2936091686091686</v>
+        <v>-3.950688705234171</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.861768873802802</v>
+        <v>-0.3812672176308536</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>-7009472.251331244</v>
+        <v>-0.05763281571998036</v>
       </c>
       <c r="AS3" t="n">
-        <v>-9093658.945221439</v>
+        <v>1.269527213650363</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.08627622377622</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>0.03674242424244767</v>
-      </c>
+        <v>1.298764296806212</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-2.134802571166208</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-2.761978734970938</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-0.4348348877797352</v>
-      </c>
+        <v>-1.863269054178133</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-3.740860528360528</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>0.8130711560941961</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-1.619803807303811</v>
-      </c>
+        <v>112762.8293770142</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-10959954.08631772</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-1.627174064665326</v>
+        <v>-3.02745638200183</v>
       </c>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>-2.160385287689216</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1089,7 +1089,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6RCbX36s</t>
+          <t>61T7bt5t</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1097,24 +1097,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,128 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>zuJM7XDg</t>
+          <t>x6CvOHH9</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.666666666666667</v>
-      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-4.666666666666668</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="W4" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="Y4" t="n">
         <v>-2.666666666666666</v>
       </c>
-      <c r="X4" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-2</v>
-      </c>
       <c r="Z4" t="n">
-        <v>-0.5</v>
+        <v>-3</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>-3.666666666666666</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AC4" t="n">
-        <v>-3</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AD4" t="n">
-        <v>-12.66666666666666</v>
+        <v>-0.3516666666666666</v>
       </c>
       <c r="AE4" t="n">
-        <v>12.66666666666666</v>
+        <v>0.5016666666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="AH4" t="n">
-        <v>-1.363333333333334</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.2566666666666666</v>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AL4" t="n">
-        <v>76.81818181818181</v>
+        <v>74.45454545454545</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.47575757575758</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
+        <v>76.96801346801347</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-2.761978734970938</v>
+      </c>
       <c r="AO4" t="n">
-        <v>-0.3812672176308536</v>
+        <v>0.03674242424244767</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.269527213650363</v>
+        <v>-0.2936091686091686</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>112762.8293770142</v>
+        <v>-0.4348348877797352</v>
       </c>
       <c r="AS4" t="n">
-        <v>-10959954.08631772</v>
+        <v>-1.861768873802802</v>
       </c>
       <c r="AT4" t="n">
-        <v>-2.134802571166208</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>-3.950688705234171</v>
-      </c>
+        <v>-1.627174064665326</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.08627622377622</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>1.361197039790753</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-0.05763281571998036</v>
-      </c>
+        <v>-3.740860528360528</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-1.863269054178133</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>-2.160385287689216</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-3.02745638200183</v>
-      </c>
+        <v>-7009472.251331244</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-9093658.945221439</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>1.298764296806212</v>
+        <v>-1.619803807303811</v>
       </c>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>0.8130711560941961</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1345,105 +1345,105 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
         <v>-1</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>1</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>4</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>3.5</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AD5" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
         <v>6</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AH5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
         <v>4</v>
       </c>
-      <c r="AD5" t="n">
-        <v>-7.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AK5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0.8400000000000001</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
         <v>80.62121212121212</v>
       </c>
       <c r="AM5" t="n">
         <v>80.78888888888889</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AN5" t="n">
+        <v>-5.112415908114855</v>
+      </c>
       <c r="AO5" t="n">
+        <v>-0.2730555555555156</v>
+      </c>
+      <c r="AP5" t="n">
         <v>-0.1052020202020199</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-7.167656031936374</v>
       </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-22916982.21220653</v>
+        <v>-0.05674125905129435</v>
       </c>
       <c r="AS5" t="n">
-        <v>-32423924.24242425</v>
+        <v>-7.167656031936374</v>
       </c>
       <c r="AT5" t="n">
+        <v>3.586695921729074</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1.56219696969697</v>
       </c>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>-0.2730555555555156</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-5.112415908114855</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>-0.05674125905129435</v>
-      </c>
+        <v>-4.525606060606052</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-4.525606060606052</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
+        <v>-22916982.21220653</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-32423924.24242425</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
+        <v>-3.762348484848474</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
         <v>-1.032944191059684</v>
       </c>
-      <c r="BC5" t="n">
-        <v>-3.762348484848474</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.586695921729074</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,7 +1451,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>2m3cvwKO</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
+          <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,128 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>EoQjC3VB</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>hUGEt9yf</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-1.5</v>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>8.5</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="W6" t="n">
-        <v>-19</v>
+        <v>-0.166666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Y6" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>18.83333333333334</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-18.83333333333334</v>
+      </c>
+      <c r="AB6" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AC6" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>1.053333333333333</v>
       </c>
       <c r="AE6" t="n">
-        <v>-17.5</v>
+        <v>-0.7083333333333335</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>-4</v>
+        <v>2.666666666666666</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.205</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AL6" t="n">
-        <v>78.64090909090909</v>
+        <v>80.99621212121212</v>
       </c>
       <c r="AM6" t="n">
-        <v>81.93939393939394</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>78.03749999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>4.883776750218217</v>
+      </c>
       <c r="AO6" t="n">
-        <v>-0.8372727272727274</v>
+        <v>0.726515151515116</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.8868432728822881</v>
+        <v>0.5454545454545456</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>-1483116.268641843</v>
+        <v>0.4003064243644767</v>
       </c>
       <c r="AS6" t="n">
-        <v>-4979454.545454549</v>
+        <v>5.500652816093634</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.036363636363639</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>0.5500000000000114</v>
-      </c>
+        <v>-4.184758908404802</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-2.261363636363637</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>-1.104214906647769</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.5538933913486344</v>
-      </c>
+        <v>5.89015151515153</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>-0.5690909090909173</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>-0.9342014500134717</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-2.51636363636365</v>
-      </c>
+        <v>20552139.51903879</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>28696590.90909091</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>2.920346237309133</v>
+        <v>5.13459595959597</v>
       </c>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>-0.6863371627373311</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>fNaktakC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">scott g 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,128 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>MBpIn2MH</t>
+          <t>AHNtWa3o</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="X7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-7</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.5899999999999999</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AH7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI7" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>-2.595</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
+      <c r="AJ7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
       <c r="AL7" t="n">
-        <v>81.5409090909091</v>
+        <v>70.48333333333333</v>
       </c>
       <c r="AM7" t="n">
-        <v>69.88888888888889</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>71.84999999999999</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-3.951833422332143</v>
+      </c>
       <c r="AO7" t="n">
-        <v>0.1506060606060606</v>
+        <v>-5.551111111111084</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.490039820972314</v>
+        <v>-0.2963636363636364</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>876508.1615898339</v>
+        <v>-0.4371781756180735</v>
       </c>
       <c r="AS7" t="n">
-        <v>3256969.696969695</v>
+        <v>-4.211557572861921</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.5854545454545459</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>1.111616161616183</v>
-      </c>
+        <v>-5.974788557563471</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.2301787101787092</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>-0.0645759396075789</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>-0.1382801957095268</v>
-      </c>
+        <v>-2.599456099456106</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>1.091212121212109</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>2.198315014504956</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.273232323232307</v>
-      </c>
+        <v>-7624331.600198607</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-4295867.132867132</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>0.6708701780787294</v>
+        <v>-2.113947163947174</v>
       </c>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>0.2416428243538249</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1884,105 +1884,105 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
         <v>4.833333333333333</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>2.166666666666667</v>
       </c>
-      <c r="V8" t="n">
-        <v>4.833333333333332</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-8.166666666666668</v>
-      </c>
       <c r="X8" t="n">
-        <v>-8.833333333333332</v>
+        <v>1.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.833333333333334</v>
+        <v>-7.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0.25</v>
+        <v>26</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5</v>
+        <v>-26</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.6666666666666661</v>
+        <v>0.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>-2.333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>28.16666666666667</v>
+        <v>0.165</v>
       </c>
       <c r="AE8" t="n">
-        <v>-28.16666666666666</v>
+        <v>-0.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.5</v>
+        <v>-7.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.6666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.5316666666666663</v>
+        <v>-2.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.9866666666666666</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.75</v>
+      </c>
       <c r="AL8" t="n">
-        <v>78.94405594405595</v>
+        <v>79.29040404040406</v>
       </c>
       <c r="AM8" t="n">
         <v>70.58585858585859</v>
       </c>
-      <c r="AN8" t="inlineStr"/>
+      <c r="AN8" t="n">
+        <v>11.53098304539206</v>
+      </c>
       <c r="AO8" t="n">
-        <v>2.121678321678321</v>
+        <v>-0.577417027416999</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.19733209151367</v>
+        <v>2.074025974025974</v>
       </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>42145361.24669117</v>
+        <v>1.242837352332237</v>
       </c>
       <c r="AS8" t="n">
-        <v>70308624.70862469</v>
+        <v>11.14067269419846</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.002874902874903995</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>-0.6117327117326852</v>
-      </c>
+        <v>-4.895914041945247</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0.258513708513707</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>11.60342130163103</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.240149627297965</v>
-      </c>
+        <v>12.99408369408368</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>13.13504273504273</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-0.5474322021636588</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>14.35881895881897</v>
-      </c>
+        <v>42088758.53481489</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>68494751.08225107</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>-5.050249717129475</v>
+        <v>13.89668109668111</v>
       </c>
       <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>-0.4531050342842455</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1990,7 +1990,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>dCkAk3SP</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1998,24 +1998,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">scott g 
+          <t xml:space="preserve">kitchen a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2042,128 +2042,128 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AHNtWa3o</t>
+          <t>MBpIn2MH</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>fcpIzd9s</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-2.595</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="X9" t="n">
+      <c r="AH9" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.5</v>
       </c>
-      <c r="Y9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.1500000000000001</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.5899999999999999</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="n">
-        <v>70.48333333333333</v>
+        <v>81.5409090909091</v>
       </c>
       <c r="AM9" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>69.88888888888889</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.0645759396075789</v>
+      </c>
       <c r="AO9" t="n">
-        <v>-0.2963636363636364</v>
+        <v>1.111616161616183</v>
       </c>
       <c r="AP9" t="n">
-        <v>-4.211557572861921</v>
+        <v>0.1506060606060606</v>
       </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>-7624331.600198607</v>
+        <v>-0.1382801957095268</v>
       </c>
       <c r="AS9" t="n">
-        <v>-4295867.132867132</v>
+        <v>1.490039820972314</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.2301787101787092</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="n">
-        <v>-5.551111111111084</v>
-      </c>
+        <v>0.6708701780787294</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.5854545454545459</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-3.951833422332143</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.4371781756180735</v>
-      </c>
+        <v>1.091212121212109</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>-2.599456099456106</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>0.2416428243538249</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>-2.113947163947174</v>
-      </c>
+        <v>876508.1615898339</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3256969.696969695</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-5.974788557563471</v>
+        <v>1.273232323232307</v>
       </c>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>2.198315014504956</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2171,7 +2171,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U5cORazJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2179,24 +2179,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
+          <t xml:space="preserve">selhurst park
   london </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2223,128 +2223,128 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>hUGEt9yf</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-19</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-17.5</v>
+      </c>
+      <c r="AB10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>17</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="U10" t="n">
-        <v>-0.166666666666667</v>
-      </c>
-      <c r="V10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.666666666666666</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.833333333333333</v>
-      </c>
       <c r="AC10" t="n">
-        <v>-1.333333333333333</v>
+        <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>18.83333333333334</v>
+        <v>1.205</v>
       </c>
       <c r="AE10" t="n">
-        <v>-18.83333333333334</v>
+        <v>-2.49</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.053333333333333</v>
+        <v>7.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.7083333333333335</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
+        <v>-11</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-4</v>
+      </c>
       <c r="AL10" t="n">
-        <v>80.99621212121212</v>
+        <v>78.64090909090909</v>
       </c>
       <c r="AM10" t="n">
-        <v>78.03749999999999</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>81.93939393939394</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1.104214906647769</v>
+      </c>
       <c r="AO10" t="n">
-        <v>0.5454545454545456</v>
+        <v>0.5500000000000114</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.500652816093634</v>
+        <v>-0.8372727272727274</v>
       </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>20552139.51903879</v>
+        <v>-0.5538933913486344</v>
       </c>
       <c r="AS10" t="n">
-        <v>28696590.90909091</v>
+        <v>-0.8868432728822881</v>
       </c>
       <c r="AT10" t="n">
-        <v>-2.261363636363637</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="n">
-        <v>0.726515151515116</v>
-      </c>
+        <v>2.920346237309133</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-2.036363636363639</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>4.883776750218217</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0.4003064243644767</v>
-      </c>
+        <v>-0.5690909090909173</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="n">
-        <v>5.89015151515153</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
-        <v>-0.6863371627373311</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.13459595959597</v>
-      </c>
+        <v>-1483116.268641843</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-4979454.545454549</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-4.184758908404802</v>
+        <v>-2.51636363636365</v>
       </c>
       <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>-0.9342014500134717</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2360,8 +2360,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2427,105 +2427,105 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
         <v>-1.666666666666666</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>-0.333333333333333</v>
       </c>
-      <c r="V11" t="n">
-        <v>5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-9.333333333333334</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.666666666666666</v>
+        <v>5.416666666666666</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.333333333333334</v>
+        <v>-6.833333333333334</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.75</v>
+        <v>11.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>-11.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.6666666666666665</v>
+        <v>-0.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>-2</v>
+        <v>0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="AE11" t="n">
-        <v>-11</v>
+        <v>-0.3925</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.6666666666666666</v>
+        <v>3.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.3333333333333335</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.7433333333333332</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.5866666666666666</v>
-      </c>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.5833333333333334</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
       <c r="AL11" t="n">
         <v>79.23367003367004</v>
       </c>
       <c r="AM11" t="n">
-        <v>80.62556332556332</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
+        <v>79.00808080808081</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1.204028361535308</v>
+      </c>
       <c r="AO11" t="n">
-        <v>-0.8355434688768022</v>
+        <v>-2.886828603495218</v>
       </c>
       <c r="AP11" t="n">
-        <v>-2.249542429030427</v>
+        <v>-0.8680776014109348</v>
       </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
-        <v>-10623383.50646303</v>
+        <v>-0.4902260102779061</v>
       </c>
       <c r="AS11" t="n">
-        <v>-20324584.7362514</v>
+        <v>-2.220045261256857</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.9760597427264059</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="n">
-        <v>-2.97611154277817</v>
-      </c>
+        <v>-6.070959326487667</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.8573673240339943</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>-1.198670460292306</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-0.4859644290365113</v>
-      </c>
+        <v>-4.284070867404196</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="n">
-        <v>-4.307519640852973</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>-1.061381178254749</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-4.370948804282136</v>
-      </c>
+        <v>-10696243.71160468</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-20726413.74058041</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>-6.132733766678257</v>
+        <v>-4.469905403238755</v>
       </c>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>-0.9165736522748631</v>
+      </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
@@ -2608,105 +2608,105 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
         <v>-0.6666666666666665</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>-1.666666666666667</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>-0.5</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>-7.666666666666666</v>
       </c>
-      <c r="X12" t="n">
-        <v>0.1666666666666661</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>-5.333333333333334</v>
-      </c>
       <c r="Z12" t="n">
-        <v>0.5</v>
+        <v>-10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.5</v>
+        <v>10.5</v>
       </c>
       <c r="AB12" t="n">
         <v>0.5</v>
       </c>
       <c r="AC12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.7333333333333329</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1666666666666661</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI12" t="n">
         <v>-5.333333333333333</v>
       </c>
-      <c r="AD12" t="n">
-        <v>-10.5</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AF12" t="n">
+      <c r="AJ12" t="n">
         <v>0.8333333333333333</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AK12" t="n">
         <v>-1</v>
       </c>
-      <c r="AH12" t="n">
-        <v>-0.7333333333333329</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="n">
         <v>71.22727272727272</v>
       </c>
       <c r="AM12" t="n">
         <v>77.21818181818182</v>
       </c>
-      <c r="AN12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>-5.835632629715093</v>
+      </c>
       <c r="AO12" t="n">
+        <v>-1.469949494949503</v>
+      </c>
+      <c r="AP12" t="n">
         <v>-0.7506060606060605</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>-5.152669862738819</v>
       </c>
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
-        <v>-21623315.76815349</v>
+        <v>-0.3442275439636824</v>
       </c>
       <c r="AS12" t="n">
-        <v>-30325924.24242424</v>
+        <v>-5.152669862738819</v>
       </c>
       <c r="AT12" t="n">
+        <v>-1.285564543737195</v>
+      </c>
+      <c r="AU12" t="n">
         <v>1.331363636363637</v>
       </c>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="n">
-        <v>-1.469949494949503</v>
-      </c>
+      <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="n">
-        <v>-5.835632629715093</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>-0.3442275439636824</v>
-      </c>
+        <v>-6.998636363636365</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="n">
-        <v>-6.998636363636365</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
+        <v>-21623315.76815349</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-30325924.24242424</v>
+      </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="n">
+        <v>-5.975101010101014</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="n">
         <v>1.450330433865471</v>
       </c>
-      <c r="BC12" t="n">
-        <v>-5.975101010101014</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>-1.285564543737195</v>
-      </c>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="n">
         <v>0</v>
       </c>
@@ -2722,8 +2722,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2789,105 +2789,105 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="U13" t="n">
+      <c r="W13" t="n">
         <v>0.6666666666666665</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>6.75</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>10</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.5366666666666666</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.8383333333333336</v>
+      </c>
+      <c r="AF13" t="n">
         <v>3.166666666666666</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AG13" t="n">
         <v>1.416666666666666</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AH13" t="n">
         <v>2.083333333333334</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AI13" t="n">
         <v>0.5833333333333335</v>
       </c>
-      <c r="AD13" t="n">
-        <v>-4.333333333333336</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>4.333333333333336</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0.5366666666666666</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0.8383333333333336</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
       <c r="AL13" t="n">
         <v>78.76801346801348</v>
       </c>
       <c r="AM13" t="n">
         <v>77.36540404040404</v>
       </c>
-      <c r="AN13" t="inlineStr"/>
+      <c r="AN13" t="n">
+        <v>-3.519682831793432</v>
+      </c>
       <c r="AO13" t="n">
-        <v>-1.375291375291375</v>
+        <v>0.787518037517998</v>
       </c>
       <c r="AP13" t="n">
-        <v>-6.590519421351274</v>
+        <v>-1.327639027639028</v>
       </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
-        <v>-29581965.33174726</v>
+        <v>-0.5544236138444647</v>
       </c>
       <c r="AS13" t="n">
-        <v>-51794716.39471639</v>
+        <v>-6.533860024036059</v>
       </c>
       <c r="AT13" t="n">
-        <v>-3.143822843822843</v>
-      </c>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
-        <v>0.8218337218336842</v>
-      </c>
+        <v>4.663045495491417</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-2.882434232434232</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="n">
-        <v>-3.5921210880324</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-0.5517358888101922</v>
-      </c>
+        <v>-4.005117105117108</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="n">
-        <v>-4.146076146076155</v>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="n">
-        <v>-1.445227330289253</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-7.169696969696972</v>
-      </c>
+        <v>-29525362.61987098</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-49980842.76834277</v>
+      </c>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="n">
-        <v>4.817381170675645</v>
+        <v>-6.707559107559106</v>
       </c>
       <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+      <c r="BF13" t="n">
+        <v>-1.539554498168666</v>
+      </c>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
@@ -2970,105 +2970,105 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>-5</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>2</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0.8949999999999998</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.085</v>
+      </c>
+      <c r="AF14" t="n">
         <v>-4.5</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AG14" t="n">
         <v>-3.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
         <v>0.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>-12</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>-1</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AK14" t="n">
         <v>1</v>
       </c>
-      <c r="AH14" t="n">
-        <v>-0.8949999999999998</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.085</v>
-      </c>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
       <c r="AL14" t="n">
         <v>77.95454545454545</v>
       </c>
       <c r="AM14" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AN14" t="n">
+        <v>1.266714102498341</v>
+      </c>
       <c r="AO14" t="n">
+        <v>1.114545454545436</v>
+      </c>
+      <c r="AP14" t="n">
         <v>-0.2545454545454549</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.8000808900982292</v>
       </c>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
-        <v>615215.1131238164</v>
+        <v>-0.06403315407017129</v>
       </c>
       <c r="AS14" t="n">
-        <v>-2663818.181818182</v>
+        <v>0.8000808900982292</v>
       </c>
       <c r="AT14" t="n">
+        <v>-4.000341032675465</v>
+      </c>
+      <c r="AU14" t="n">
         <v>0.3154545454545428</v>
       </c>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="n">
-        <v>1.114545454545436</v>
-      </c>
+      <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="n">
-        <v>1.266714102498341</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>-0.06403315407017129</v>
-      </c>
+        <v>-0.9945454545454453</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="n">
-        <v>-0.9945454545454453</v>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="n">
+        <v>615215.1131238164</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-2663818.181818182</v>
+      </c>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
         <v>-1.897480919904194</v>
       </c>
-      <c r="BC14" t="n">
-        <v>-0.1099999999999994</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-4.000341032675465</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
       <c r="BG14" t="n">
         <v>0</v>
       </c>
@@ -3151,105 +3151,105 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
         <v>-1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>-1</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>12.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.5</v>
       </c>
       <c r="Y15" t="n">
         <v>1</v>
       </c>
       <c r="Z15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
         <v>2</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AD15" t="n">
+        <v>0.9299999999999998</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
         <v>6.5</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AI15" t="n">
         <v>-4</v>
       </c>
-      <c r="AD15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AJ15" t="n">
         <v>2.5</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AK15" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AH15" t="n">
-        <v>0.9299999999999998</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>-1.285</v>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
         <v>77.62272727272727</v>
       </c>
       <c r="AM15" t="n">
         <v>76.5</v>
       </c>
-      <c r="AN15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>-2.063036392422575</v>
+      </c>
       <c r="AO15" t="n">
+        <v>0.4572727272727093</v>
+      </c>
+      <c r="AP15" t="n">
         <v>0.006363636363636793</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>-0.2661949279052891</v>
       </c>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="n">
-        <v>-5772490.741009841</v>
+        <v>-0.001038864162265396</v>
       </c>
       <c r="AS15" t="n">
-        <v>-6850636.36363636</v>
+        <v>-0.2661949279052891</v>
       </c>
       <c r="AT15" t="n">
+        <v>-2.417804575716985</v>
+      </c>
+      <c r="AU15" t="n">
         <v>1.72909090909091</v>
       </c>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="n">
-        <v>0.4572727272727093</v>
-      </c>
+      <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="n">
-        <v>-2.063036392422575</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>-0.001038864162265396</v>
-      </c>
+        <v>-1.222727272727269</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="n">
-        <v>-1.222727272727269</v>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="n">
+        <v>-5772490.741009841</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-6850636.36363636</v>
+      </c>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="n">
+        <v>-0.5618181818181824</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
         <v>3.999191605495959</v>
       </c>
-      <c r="BC15" t="n">
-        <v>-0.5618181818181824</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>-2.417804575716985</v>
-      </c>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="n">
         <v>0</v>
       </c>
@@ -3257,7 +3257,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hdlcFVpd</t>
+          <t>tIUiyD7F</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -3265,24 +3265,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3309,22 +3309,22 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="R16" t="n">
         <v>-2</v>
@@ -3332,105 +3332,105 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
         <v>-0.25</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>-0.0349999999999997</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.4700000000000002</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AI16" t="n">
         <v>-1</v>
       </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>-14.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>-1.1925</v>
-      </c>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
+      <c r="AJ16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AL16" t="n">
-        <v>77.02146464646464</v>
+        <v>81.76666666666667</v>
       </c>
       <c r="AM16" t="n">
-        <v>75.80000000000001</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
+        <v>80.13415404040404</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0.02903659157051663</v>
+      </c>
       <c r="AO16" t="n">
-        <v>0.2061728395061724</v>
+        <v>3.685454545454519</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.003630135120403111</v>
+        <v>0.1327272727272726</v>
       </c>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="n">
-        <v>-1243673.984887624</v>
+        <v>0.1181046278727971</v>
       </c>
       <c r="AS16" t="n">
-        <v>1861301.907968573</v>
+        <v>0.5976217781777677</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.552300785634117</v>
-      </c>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="n">
-        <v>1.802918069584734</v>
-      </c>
+        <v>2.033999310972519</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.8981818181818184</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="n">
-        <v>-3.187342346168066</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>-0.0007441557858842707</v>
-      </c>
+        <v>-0.2090909090909037</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="n">
-        <v>-0.9500561167227914</v>
-      </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="n">
-        <v>1.850529250983385</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.206846240179587</v>
-      </c>
+        <v>-732153.2015697286</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>189363.6363636367</v>
+      </c>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="n">
-        <v>8.059273693077529</v>
+        <v>-0.004545454545464622</v>
       </c>
       <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>0.8990982367567355</v>
+      </c>
       <c r="BG16" t="n">
         <v>0</v>
       </c>
@@ -3513,105 +3513,105 @@
       <c r="S17" t="n">
         <v>0</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
         <v>-1.8</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="V17" t="n">
+      <c r="X17" t="n">
         <v>7.199999999999999</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Y17" t="n">
         <v>1.800000000000001</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="AF17" t="n">
         <v>-1.800000000000001</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AG17" t="n">
         <v>-2.199999999999999</v>
       </c>
-      <c r="Z17" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AH17" t="n">
         <v>3.4</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AI17" t="n">
         <v>0.2999999999999998</v>
       </c>
-      <c r="AD17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AJ17" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AK17" t="n">
         <v>-0.6000000000000001</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.316</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0.3799999999999999</v>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
       <c r="AL17" t="n">
         <v>73.29545454545455</v>
       </c>
       <c r="AM17" t="n">
         <v>72.99111111111111</v>
       </c>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>2.561599790970874</v>
+      </c>
       <c r="AO17" t="n">
+        <v>5.816345270890736</v>
+      </c>
+      <c r="AP17" t="n">
         <v>0.5449035812672174</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.34440858103379</v>
       </c>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="n">
-        <v>8243721.972391321</v>
+        <v>0.3767063634652568</v>
       </c>
       <c r="AS17" t="n">
-        <v>15066457.58282122</v>
+        <v>2.34440858103379</v>
       </c>
       <c r="AT17" t="n">
+        <v>2.642024949784741</v>
+      </c>
+      <c r="AU17" t="n">
         <v>1.006442042805681</v>
       </c>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="n">
-        <v>5.816345270890736</v>
-      </c>
+      <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="n">
-        <v>2.561599790970874</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.3767063634652568</v>
-      </c>
+        <v>4.671816062725142</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="n">
-        <v>4.671816062725142</v>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="n">
+        <v>8243721.972391321</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>15066457.58282122</v>
+      </c>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="n">
+        <v>5.145949000494468</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
         <v>1.019644226578656</v>
       </c>
-      <c r="BC17" t="n">
-        <v>5.145949000494468</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.642024949784741</v>
-      </c>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3619,7 +3619,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tIUiyD7F</t>
+          <t>hdlcFVpd</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3627,24 +3627,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>-2</v>
@@ -3694,105 +3694,105 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>-0.25</v>
       </c>
-      <c r="U18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-14.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-1.1925</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>1</v>
       </c>
-      <c r="W18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AK18" t="n">
         <v>-2</v>
       </c>
-      <c r="Y18" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>-0.0349999999999997</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>-0.4700000000000002</v>
-      </c>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="n">
-        <v>81.76666666666667</v>
+        <v>77.02146464646464</v>
       </c>
       <c r="AM18" t="n">
-        <v>80.13415404040404</v>
-      </c>
-      <c r="AN18" t="inlineStr"/>
+        <v>75.80000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-3.187342346168066</v>
+      </c>
       <c r="AO18" t="n">
-        <v>0.1327272727272726</v>
+        <v>1.802918069584734</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.5976217781777677</v>
+        <v>0.2061728395061724</v>
       </c>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="n">
-        <v>-732153.2015697286</v>
+        <v>-0.0007441557858842707</v>
       </c>
       <c r="AS18" t="n">
-        <v>189363.6363636367</v>
+        <v>-0.003630135120403111</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.8981818181818184</v>
-      </c>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="n">
-        <v>3.685454545454519</v>
-      </c>
+        <v>8.059273693077529</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.552300785634117</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
       <c r="AW18" t="n">
-        <v>0.02903659157051663</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0.1181046278727971</v>
-      </c>
+        <v>-0.9500561167227914</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="n">
-        <v>-0.2090909090909037</v>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="n">
-        <v>0.8990982367567355</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>-0.004545454545464622</v>
-      </c>
+        <v>-1243673.984887624</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1861301.907968573</v>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="n">
-        <v>2.033999310972519</v>
+        <v>1.206846240179587</v>
       </c>
       <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>1.850529250983385</v>
+      </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
@@ -3875,105 +3875,105 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
         <v>-1</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>-1</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>22.66666666666667</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>-21.66666666666667</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
+        <v>18.33333333333334</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-18.33333333333334</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.831666666666667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-2.891666666666667</v>
+      </c>
+      <c r="AF19" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AG19" t="n">
         <v>2.333333333333334</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AH19" t="n">
         <v>6</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AI19" t="n">
         <v>-11.33333333333333</v>
       </c>
-      <c r="AD19" t="n">
-        <v>18.33333333333334</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>-18.33333333333334</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AJ19" t="n">
         <v>2.833333333333333</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AK19" t="n">
         <v>-3.166666666666667</v>
       </c>
-      <c r="AH19" t="n">
-        <v>2.831666666666667</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>-2.891666666666667</v>
-      </c>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
       <c r="AL19" t="n">
         <v>75.97205387205388</v>
       </c>
       <c r="AM19" t="n">
         <v>84.92727272727274</v>
       </c>
-      <c r="AN19" t="inlineStr"/>
+      <c r="AN19" t="n">
+        <v>5.932920780317346</v>
+      </c>
       <c r="AO19" t="n">
+        <v>-0.03055555555556566</v>
+      </c>
+      <c r="AP19" t="n">
         <v>0.783333333333333</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.526123463739552</v>
       </c>
       <c r="AQ19" t="inlineStr"/>
       <c r="AR19" t="n">
-        <v>29706898.9663431</v>
+        <v>0.5191367618527765</v>
       </c>
       <c r="AS19" t="n">
-        <v>46183159.72222222</v>
+        <v>9.526123463739552</v>
       </c>
       <c r="AT19" t="n">
+        <v>-1.750258349243694</v>
+      </c>
+      <c r="AU19" t="n">
         <v>-1.874999999999993</v>
       </c>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="n">
-        <v>-0.03055555555556566</v>
-      </c>
+      <c r="AV19" t="inlineStr"/>
       <c r="AW19" t="n">
-        <v>5.932920780317346</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0.5191367618527765</v>
-      </c>
+        <v>6.67638888888888</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="n">
-        <v>6.67638888888888</v>
-      </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="n">
+        <v>29706898.9663431</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>46183159.72222222</v>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="n">
+        <v>6.905555555555566</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
         <v>0.6386943558052494</v>
       </c>
-      <c r="BC19" t="n">
-        <v>6.905555555555566</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>-1.750258349243694</v>
-      </c>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="n">
         <v>0</v>
       </c>
@@ -4052,103 +4052,103 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
         <v>0.25</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.75</v>
       </c>
-      <c r="V20" t="n">
+      <c r="X20" t="n">
         <v>4.25</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Y20" t="n">
         <v>-9.5</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-0.1925000000000001</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-1.3675</v>
+      </c>
+      <c r="AF20" t="n">
         <v>-3.25</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AG20" t="n">
         <v>4.5</v>
       </c>
-      <c r="Z20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AH20" t="n">
         <v>-2.25</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AI20" t="n">
         <v>-4</v>
       </c>
-      <c r="AD20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
         <v>-2</v>
       </c>
-      <c r="AH20" t="n">
-        <v>-0.1925000000000001</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>-1.3675</v>
-      </c>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
         <v>78.65909090909091</v>
       </c>
-      <c r="AN20" t="inlineStr"/>
+      <c r="AN20" t="n">
+        <v>-11.03030118503264</v>
+      </c>
       <c r="AO20" t="n">
+        <v>-0.6777777777777771</v>
+      </c>
+      <c r="AP20" t="n">
         <v>-1.614876033057851</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>-10.27796624139336</v>
       </c>
       <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="n">
-        <v>-31334259.10856218</v>
+        <v>-0.7867624915578886</v>
       </c>
       <c r="AS20" t="n">
-        <v>-43719807.16253443</v>
+        <v>-10.27796624139336</v>
       </c>
       <c r="AT20" t="n">
+        <v>0.05128627647806638</v>
+      </c>
+      <c r="AU20" t="n">
         <v>0.6276400367309414</v>
       </c>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="n">
-        <v>-0.6777777777777771</v>
-      </c>
+      <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="n">
-        <v>-11.03030118503264</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>-0.7867624915578886</v>
-      </c>
+        <v>-11.14921946740127</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="n">
-        <v>-11.14921946740127</v>
-      </c>
-      <c r="BA20" t="inlineStr"/>
-      <c r="BB20" t="n">
+        <v>-31334259.10856218</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-43719807.16253443</v>
+      </c>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="n">
+        <v>-11.81781450872361</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="n">
         <v>1.962950784178407</v>
       </c>
-      <c r="BC20" t="n">
-        <v>-11.81781450872361</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0.05128627647806638</v>
-      </c>
-      <c r="BE20" t="inlineStr"/>
-      <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
@@ -4231,105 +4231,105 @@
       <c r="S21" t="n">
         <v>0</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>5.25</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>3.5</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.08499999999999996</v>
+      </c>
+      <c r="AF21" t="n">
         <v>-4.25</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AG21" t="n">
         <v>-0.75</v>
       </c>
-      <c r="Z21" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AA21" t="n">
+      <c r="AH21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>-0.08499999999999996</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="n">
         <v>76.15625</v>
       </c>
       <c r="AM21" t="n">
         <v>74.54545454545453</v>
       </c>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AN21" t="n">
+        <v>5.407802526807828</v>
+      </c>
       <c r="AO21" t="n">
-        <v>0.683916083916084</v>
+        <v>0.7157287157286873</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.4151497898237011</v>
+        <v>0.7164502164502167</v>
       </c>
       <c r="AQ21" t="inlineStr"/>
       <c r="AR21" t="n">
-        <v>12061725.57887552</v>
+        <v>0.5731714813725228</v>
       </c>
       <c r="AS21" t="n">
-        <v>16835646.46464647</v>
+        <v>0.3856526220501308</v>
       </c>
       <c r="AT21" t="n">
-        <v>-2.183815073815069</v>
-      </c>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="n">
-        <v>0.80501165501164</v>
-      </c>
+        <v>2.811138907473406</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-2.065122655122657</v>
+      </c>
+      <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="n">
-        <v>5.402444625564826</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0.568909900131128</v>
-      </c>
+        <v>5.251399711399714</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="n">
-        <v>5.274848484848491</v>
-      </c>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="n">
-        <v>-3.751456358361732</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.731375291375286</v>
-      </c>
+        <v>12134585.78401716</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>17237475.46897547</v>
+      </c>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
       <c r="BD21" t="n">
-        <v>2.872913347663996</v>
+        <v>2.830331890331905</v>
       </c>
       <c r="BE21" t="inlineStr"/>
-      <c r="BF21" t="inlineStr"/>
+      <c r="BF21" t="n">
+        <v>-3.896263884341618</v>
+      </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">bell j 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>n94TZqsm</t>
+          <t>tMUvLt7h</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -4412,105 +4412,105 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>4</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-7.333333333333333</v>
-      </c>
       <c r="X22" t="n">
-        <v>6.666666666666668</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>-7.75</v>
       </c>
       <c r="Z22" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="AB22" t="n">
         <v>-2</v>
       </c>
-      <c r="AA22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>-1.333333333333333</v>
-      </c>
       <c r="AC22" t="n">
-        <v>-1.333333333333333</v>
+        <v>1.75</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.666666666666664</v>
+        <v>-0.3266666666666667</v>
       </c>
       <c r="AE22" t="n">
-        <v>-5.666666666666664</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="AF22" t="n">
-        <v>-2.333333333333333</v>
+        <v>7.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AH22" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-0.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>-1.066666666666667</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AL22" t="n">
         <v>72.98888888888888</v>
       </c>
       <c r="AM22" t="n">
         <v>69</v>
       </c>
-      <c r="AN22" t="inlineStr"/>
+      <c r="AN22" t="n">
+        <v>2.922519483242283</v>
+      </c>
       <c r="AO22" t="n">
-        <v>0.1565656565656564</v>
+        <v>2.421188811188813</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.164334327785696</v>
+        <v>0.1536674436674434</v>
       </c>
       <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="n">
-        <v>3541222.416324455</v>
+        <v>0.07371250742589153</v>
       </c>
       <c r="AS22" t="n">
-        <v>5977710.437710438</v>
+        <v>6.998578267806636</v>
       </c>
       <c r="AT22" t="n">
-        <v>-1.254461279461278</v>
-      </c>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="n">
-        <v>2.451010101010098</v>
-      </c>
+        <v>0.9011872383127297</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>-1.219246309246305</v>
+      </c>
+      <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="n">
-        <v>3.092468129852037</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0.06047824831687043</v>
-      </c>
+        <v>4.55793317793318</v>
+      </c>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="n">
-        <v>4.716835016835034</v>
-      </c>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="n">
-        <v>2.498082208779447</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.279713804713793</v>
-      </c>
+        <v>3453610.899162427</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5881553.224553224</v>
+      </c>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="n">
-        <v>1.282963061142851</v>
+        <v>4.234864024864024</v>
       </c>
       <c r="BE22" t="inlineStr"/>
-      <c r="BF22" t="inlineStr"/>
+      <c r="BF22" t="n">
+        <v>2.575982293882983</v>
+      </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8tPSZqtA</t>
+          <t>IPNnvzM7</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -4593,105 +4593,105 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>-1</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH23" t="n">
         <v>2.5</v>
       </c>
-      <c r="W23" t="n">
-        <v>8</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>-21.5</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI23" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.5</v>
+      </c>
       <c r="AL23" t="n">
-        <v>71.18181818181819</v>
+        <v>69.84090909090909</v>
       </c>
       <c r="AM23" t="n">
         <v>69.5409090909091</v>
       </c>
-      <c r="AN23" t="inlineStr"/>
+      <c r="AN23" t="n">
+        <v>3.992829556064848</v>
+      </c>
       <c r="AO23" t="n">
-        <v>0.09393939393939421</v>
+        <v>-2.9931313131313</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.635794575479167</v>
+        <v>0.08454545454545448</v>
       </c>
       <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="n">
-        <v>1354569.911297852</v>
+        <v>0.005507956805910652</v>
       </c>
       <c r="AS23" t="n">
-        <v>1884015.151515152</v>
+        <v>2.98891655256746</v>
       </c>
       <c r="AT23" t="n">
-        <v>-2.392929292929296</v>
-      </c>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="n">
-        <v>-3.19595959595955</v>
-      </c>
+        <v>-4.440773995588529</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>-2.457878787878784</v>
+      </c>
+      <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="n">
-        <v>4.210217098111386</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0.00766316188311067</v>
-      </c>
+        <v>4.320909090909112</v>
+      </c>
+      <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="n">
-        <v>4.343434343434367</v>
-      </c>
-      <c r="BA23" t="inlineStr"/>
-      <c r="BB23" t="n">
-        <v>-0.1003201441607224</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.598989898989913</v>
-      </c>
+        <v>1247666.865417665</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1822368.686868687</v>
+      </c>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="n">
-        <v>-4.196248257757162</v>
+        <v>2.485757575757589</v>
       </c>
       <c r="BE23" t="inlineStr"/>
-      <c r="BF23" t="inlineStr"/>
+      <c r="BF23" t="n">
+        <v>-0.527797279210322</v>
+      </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>EoQjC3VB</t>
+          <t>6wEAqBAE</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -4911,32 +4911,27 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>GbaVU03t</t>
+          <t>vaX1LmWq</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eltringham g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">fratton park
-  portsmouth </t>
+          <t xml:space="preserve">vicarage road
+  watford </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>zckREQFJ</t>
+          <t>UmMRoGzp</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>6uz2cJBL</t>
+          <t>f9KDxtkU</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4961,20 +4956,24 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>MsDWbjnD</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q26" t="n">
         <v>-1</v>
       </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>-1</v>
+      </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
@@ -4996,10 +4995,10 @@
       <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="n">
-        <v>68.61805555555556</v>
-      </c>
+      <c r="AL26" t="n">
+        <v>69.64141414141415</v>
+      </c>
+      <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
@@ -5026,27 +5025,32 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>n1hhaOVo</t>
+          <t>tOTmlbNp</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">dw stadium
-  wigan </t>
+          <t xml:space="preserve">deepdale
+  preston </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MgHlK2Na</t>
+          <t>x8IDVcbi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UNGEKMx6</t>
+          <t>WSzc94ws</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5071,58 +5075,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6wEAqBAE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
       <c r="O27" t="n">
-        <v>3</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>74</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>-0.3320019228240199</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>2.322095959595941</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.01136363636363646</v>
+      </c>
       <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0.8307266109812019</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0.2878791043202966</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.756818181818183</v>
+      </c>
       <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
+      <c r="AW27" t="n">
+        <v>-5.693434343434348</v>
+      </c>
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
-      <c r="BA27" t="inlineStr"/>
+      <c r="AZ27" t="n">
+        <v>-15598.00324832229</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-840901.5151515151</v>
+      </c>
       <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="inlineStr"/>
+      <c r="BD27" t="n">
+        <v>0.6388888888888857</v>
+      </c>
       <c r="BE27" t="inlineStr"/>
-      <c r="BF27" t="inlineStr"/>
+      <c r="BF27" t="n">
+        <v>1.348370217841715</v>
+      </c>
       <c r="BG27" t="n">
         <v>0</v>
       </c>
@@ -5130,7 +5206,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>KWD8eLDD</t>
+          <t>2FcwTvYh</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -5139,18 +5215,18 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">lner stadium
-  lincoln </t>
+          <t xml:space="preserve">swansea com stadium
+  swansea </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>hrHTRs5B</t>
+          <t>K6xezbY7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CQv5qrFt</t>
+          <t>WvZyDeKk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5175,11 +5251,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>phM8NElP</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
         <v>0</v>
@@ -5202,7 +5286,9 @@
       <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
+      <c r="AL28" t="n">
+        <v>69.2</v>
+      </c>
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
@@ -5230,32 +5316,27 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>tOTmlbNp</t>
+          <t>pWhdu9NF</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ward g 
-  eng </t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">deepdale
-  preston </t>
+          <t xml:space="preserve">peninsula stadium
+  salford </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>x8IDVcbi</t>
+          <t>W4AadhN3</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSzc94ws</t>
+          <t>hlzYDy5q</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5280,128 +5361,52 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Y39YvFx6</t>
-        </is>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>0</v>
       </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>-6</v>
-      </c>
-      <c r="W29" t="n">
-        <v>9</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2.73</v>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="n">
-        <v>74</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>69</v>
-      </c>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.6380053976449886</v>
-      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="n">
-        <v>-77314.16185897798</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>-1275463.734567902</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>4.831882716049385</v>
-      </c>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
       <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="n">
-        <v>2.113919753086407</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>-0.5262976278543618</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
       <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="n">
-        <v>-5.979506172839507</v>
-      </c>
+      <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="inlineStr"/>
-      <c r="BB29" t="n">
-        <v>1.389894695561338</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0.4389197530864237</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0.2003976659411819</v>
-      </c>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
       <c r="BE29" t="inlineStr"/>
       <c r="BF29" t="inlineStr"/>
       <c r="BG29" t="n">
@@ -5411,7 +5416,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>2FcwTvYh</t>
+          <t>EBSD6oME</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -5420,18 +5425,18 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">swansea com stadium
-  swansea </t>
+          <t xml:space="preserve">prenton park
+  birkenhead </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>K6xezbY7</t>
+          <t>jVhkb1QE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WvZyDeKk</t>
+          <t>6ZvdGuYf</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5456,19 +5461,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>tMUvLt7h</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
         <v>0</v>
@@ -5491,9 +5488,7 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="n">
-        <v>69.2</v>
-      </c>
+      <c r="AL30" t="inlineStr"/>
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
@@ -5521,27 +5516,32 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>CCV9JR0d</t>
+          <t>GbaVU03t</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">carrow road
-  norwich </t>
+          <t xml:space="preserve">fratton park
+  portsmouth </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qo6off6p</t>
+          <t>zckREQFJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ANwyQM2M</t>
+          <t>6uz2cJBL</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5571,13 +5571,17 @@
           <t>AHNtWa3o</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
@@ -5601,29 +5605,41 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="n">
-        <v>70.70833333333333</v>
-      </c>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>68.61805555555556</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-1.693333333333342</v>
+      </c>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.635238095238094</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>-4.520595238095211</v>
+      </c>
       <c r="AU31" t="inlineStr"/>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr"/>
       <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
+      <c r="AZ31" t="n">
+        <v>-232866.0714285714</v>
+      </c>
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
       <c r="BE31" t="inlineStr"/>
-      <c r="BF31" t="inlineStr"/>
+      <c r="BF31" t="n">
+        <v>4.146547619047617</v>
+      </c>
       <c r="BG31" t="n">
         <v>0</v>
       </c>
@@ -5631,7 +5647,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>xUXzYQFk</t>
+          <t>n1hhaOVo</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -5640,18 +5656,18 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">sixfields stadium
-  northampton </t>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>l4P6dwRR</t>
+          <t>MgHlK2Na</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>hl2V5JIl</t>
+          <t>UNGEKMx6</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5678,9 +5694,13 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
       <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
         <v>0</v>
@@ -5731,7 +5751,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>nPQL4PjR</t>
+          <t>xUXzYQFk</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -5740,18 +5760,18 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">aesseal new york stadium
-  rotherham </t>
+          <t xml:space="preserve">sixfields stadium
+  northampton </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>KMfM7P4b</t>
+          <t>l4P6dwRR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>YacqHHdS</t>
+          <t>hl2V5JIl</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5776,19 +5796,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
-      <c r="O33" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
         <v>0</v>
@@ -5811,9 +5823,7 @@
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="n">
-        <v>69.13636363636363</v>
-      </c>
+      <c r="AL33" t="inlineStr"/>
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
@@ -5841,7 +5851,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6NnRD2Ts</t>
+          <t>CCV9JR0d</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -5850,18 +5860,18 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">the croud meadow
-  shrewsbury </t>
+          <t xml:space="preserve">carrow road
+  norwich </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EqfQ6qK4</t>
+          <t>Qo6off6p</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EwJVdqzn</t>
+          <t>ANwyQM2M</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5886,15 +5896,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
         <v>0</v>
@@ -5917,7 +5931,9 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
+      <c r="AL34" t="n">
+        <v>70.70833333333333</v>
+      </c>
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
@@ -5945,7 +5961,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bsinRI25</t>
+          <t>WSQqW4p2</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -5954,18 +5970,18 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">kassam stadium
-  oxford </t>
+          <t xml:space="preserve">bescot stadium
+  walsall </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>vgOBT43c</t>
+          <t>YgrfcLuL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>tWeI85kh</t>
+          <t>ve14a3l4</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5992,13 +6008,9 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
         <v>0</v>
@@ -6049,7 +6061,7 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>EBSD6oME</t>
+          <t>bsinRI25</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -6058,18 +6070,18 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">prenton park
-  birkenhead </t>
+          <t xml:space="preserve">kassam stadium
+  oxford </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>jVhkb1QE</t>
+          <t>vgOBT43c</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6ZvdGuYf</t>
+          <t>tWeI85kh</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6094,11 +6106,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>IuMTL627</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
         <v>0</v>
@@ -6149,7 +6169,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>WSQqW4p2</t>
+          <t>Kl7vhn7L</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -6158,18 +6178,18 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">bescot stadium
-  walsall </t>
+          <t xml:space="preserve">the broadfield stadium
+  crawley </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>YgrfcLuL</t>
+          <t>QVmLl54o</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ve14a3l4</t>
+          <t>xSloasB8</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6249,7 +6269,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>vaX1LmWq</t>
+          <t>6NnRD2Ts</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -6258,18 +6278,18 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">vicarage road
-  watford </t>
+          <t xml:space="preserve">the croud meadow
+  shrewsbury </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UmMRoGzp</t>
+          <t>EqfQ6qK4</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>f9KDxtkU</t>
+          <t>EwJVdqzn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6294,24 +6314,16 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>phM8NElP</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
         <v>0</v>
       </c>
@@ -6333,9 +6345,7 @@
       <c r="AI38" t="inlineStr"/>
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="n">
-        <v>69.64141414141415</v>
-      </c>
+      <c r="AL38" t="inlineStr"/>
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
@@ -6363,7 +6373,7 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>pWhdu9NF</t>
+          <t>nPQL4PjR</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -6372,18 +6382,18 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">peninsula stadium
-  salford </t>
+          <t xml:space="preserve">aesseal new york stadium
+  rotherham </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>W4AadhN3</t>
+          <t>KMfM7P4b</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>hlzYDy5q</t>
+          <t>YacqHHdS</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6408,11 +6418,19 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>zNcAe8Sa</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>-2</v>
+      </c>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="n">
+        <v>-1</v>
+      </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
         <v>0</v>
@@ -6435,7 +6453,9 @@
       <c r="AI39" t="inlineStr"/>
       <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
+      <c r="AL39" t="n">
+        <v>69.13636363636363</v>
+      </c>
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
@@ -6463,7 +6483,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>6os5wmhS</t>
+          <t>CnnJp4ae</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -6472,18 +6492,18 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">colchester community stadium
-  colchester </t>
+          <t xml:space="preserve">holker street
+  barrow in furness </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>xYu73rNn</t>
+          <t>KKJL7QXd</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>EmlVDpVP</t>
+          <t>U3lM3y4e</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6510,13 +6530,9 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
-      <c r="O40" t="n">
-        <v>-2</v>
-      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
-        <v>-1</v>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="n">
         <v>0</v>
@@ -6567,7 +6583,7 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>x6klsVh3</t>
+          <t>b3pRrrU7</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -6576,18 +6592,18 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">hayes lane
-  london </t>
+          <t xml:space="preserve">pirelli stadium
+  burton upon trent </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Opdcd08Q</t>
+          <t>nwCtJaJT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4KREuF43</t>
+          <t>8EFIJthC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6667,7 +6683,7 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>xYBLuIHb</t>
+          <t>GINCsvmn</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -6675,24 +6691,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">langford o 
+          <t xml:space="preserve">ward g 
   eng </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">the valley
-  london </t>
+          <t xml:space="preserve">ashton gate stadium
+  bristol </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>fXf5mQ7t</t>
+          <t>MahqU27I</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SWk4muv7</t>
+          <t>GOvB22xg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6717,64 +6733,130 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>OS3AwgCU</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
-      </c>
-      <c r="P42" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
       <c r="S42" t="n">
         <v>0</v>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>66.2</v>
+      </c>
       <c r="AM42" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
+        <v>69.59090909090909</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-2.854501304434322</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>-1.42083333333332</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>-2.089385353694496</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0.1954230809050159</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>-0.4792129629629649</v>
+      </c>
       <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
+      <c r="AW42" t="n">
+        <v>-2.558101851851873</v>
+      </c>
       <c r="AX42" t="inlineStr"/>
       <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
-      <c r="BA42" t="inlineStr"/>
+      <c r="AZ42" t="n">
+        <v>-1381022.967690681</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>-2150032.407407408</v>
+      </c>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr"/>
-      <c r="BD42" t="inlineStr"/>
+      <c r="BD42" t="n">
+        <v>-2.790740740740731</v>
+      </c>
       <c r="BE42" t="inlineStr"/>
-      <c r="BF42" t="inlineStr"/>
+      <c r="BF42" t="n">
+        <v>1.593950738009909</v>
+      </c>
       <c r="BG42" t="n">
         <v>0</v>
       </c>
@@ -6782,7 +6864,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>SMr3Nz2U</t>
+          <t>x6klsVh3</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -6791,18 +6873,18 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">cardiff city stadium
-  cardiff </t>
+          <t xml:space="preserve">hayes lane
+  london </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>hO8wh6aP</t>
+          <t>Opdcd08Q</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>GILi6JC9</t>
+          <t>4KREuF43</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6827,11 +6909,7 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>zNcAe8Sa</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
@@ -6858,9 +6936,7 @@
       <c r="AI43" t="inlineStr"/>
       <c r="AJ43" t="inlineStr"/>
       <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="n">
-        <v>71.47727272727272</v>
-      </c>
+      <c r="AL43" t="inlineStr"/>
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
@@ -6888,7 +6964,7 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>MwmHgKaN</t>
+          <t>KWD8eLDD</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -6897,18 +6973,18 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">blundell park
-  cleethorpes </t>
+          <t xml:space="preserve">lner stadium
+  lincoln </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OEaiS3za</t>
+          <t>hrHTRs5B</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>bsc3EJ27</t>
+          <t>CQv5qrFt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6988,7 +7064,7 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Kl7vhn7L</t>
+          <t>6os5wmhS</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -6997,18 +7073,18 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">the broadfield stadium
-  crawley </t>
+          <t xml:space="preserve">colchester community stadium
+  colchester </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>QVmLl54o</t>
+          <t>xYu73rNn</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>xSloasB8</t>
+          <t>EmlVDpVP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7035,9 +7111,13 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>-2</v>
+      </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="n">
+        <v>-1</v>
+      </c>
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>0</v>
@@ -7088,7 +7168,7 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>nw6fJO5K</t>
+          <t>bw1zAKS6</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
@@ -7097,18 +7177,18 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">pride park
-  derby </t>
+          <t xml:space="preserve">toughsheet community stadium
+  bolton </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Iug0YO0Q</t>
+          <t>Or1bBrWD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>dQIMIN5n</t>
+          <t>t6G9wMZN</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7188,27 +7268,32 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>lQl9etVA</t>
+          <t>bHPacsq1</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">john smith s stadium
-  huddersfield </t>
+          <t xml:space="preserve">highbury stadium
+  fleetwood </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>xxxpBZl2</t>
+          <t>tCZ3D68d</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>zmKRcPKu</t>
+          <t>CCBWpzjj</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7233,12 +7318,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -7264,10 +7349,10 @@
       <c r="AI47" t="inlineStr"/>
       <c r="AJ47" t="inlineStr"/>
       <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="n">
-        <v>69.33522727272728</v>
-      </c>
-      <c r="AM47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="n">
+        <v>71.26597222222222</v>
+      </c>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
       <c r="AP47" t="inlineStr"/>
@@ -7294,32 +7379,27 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bHPacsq1</t>
+          <t>SMr3Nz2U</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">robinson t 
-  eng </t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">highbury stadium
-  fleetwood </t>
+          <t xml:space="preserve">cardiff city stadium
+  cardiff </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>tCZ3D68d</t>
+          <t>hO8wh6aP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CCBWpzjj</t>
+          <t>GILi6JC9</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7344,12 +7424,12 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>nPjMw0nA</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>OEy2L7Zo</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -7375,10 +7455,10 @@
       <c r="AI48" t="inlineStr"/>
       <c r="AJ48" t="inlineStr"/>
       <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="n">
-        <v>72.22962962962963</v>
-      </c>
+      <c r="AL48" t="n">
+        <v>70.50336700336699</v>
+      </c>
+      <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="inlineStr"/>
@@ -7405,7 +7485,7 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>b3pRrrU7</t>
+          <t>MwmHgKaN</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
@@ -7414,18 +7494,18 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">pirelli stadium
-  burton upon trent </t>
+          <t xml:space="preserve">blundell park
+  cleethorpes </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>nwCtJaJT</t>
+          <t>OEaiS3za</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>8EFIJthC</t>
+          <t>bsc3EJ27</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7505,7 +7585,7 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>WfkfPdXH</t>
+          <t>xYBLuIHb</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -7513,24 +7593,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">langford o 
   eng </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">abbey stadium
-  cambridge </t>
+          <t xml:space="preserve">the valley
+  london </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>lnb8EJRp</t>
+          <t>fXf5mQ7t</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>lrMHUHDc</t>
+          <t>SWk4muv7</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7558,12 +7638,16 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>OS3AwgCU</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="n">
         <v>0</v>
@@ -7588,7 +7672,7 @@
       <c r="AK50" t="inlineStr"/>
       <c r="AL50" t="inlineStr"/>
       <c r="AM50" t="n">
-        <v>71.77777777777777</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
@@ -7616,32 +7700,27 @@
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>GINCsvmn</t>
+          <t>nw6fJO5K</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">smith j 
-  eng </t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">ashton gate stadium
-  bristol </t>
+          <t xml:space="preserve">pride park
+  derby </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MahqU27I</t>
+          <t>Iug0YO0Q</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GOvB22xg</t>
+          <t>dQIMIN5n</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7668,126 +7747,54 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>C2sV0kf7</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>U3POrPvM</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>4</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
+          <t>fcpIzd9s</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
         <v>0</v>
       </c>
-      <c r="T51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>7</v>
-      </c>
-      <c r="W51" t="n">
-        <v>-24</v>
-      </c>
-      <c r="X51" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>-21</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>-1.41</v>
-      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>70.18181818181819</v>
-      </c>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>-2.18276958464368</v>
-      </c>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="n">
-        <v>-1392917.724649544</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>-2190757.575757575</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>-0.5365881032547684</v>
-      </c>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AS51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
       <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="n">
-        <v>-1.629854096520717</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>-2.909130516126041</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0</v>
-      </c>
+      <c r="AV51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr"/>
+      <c r="AX51" t="inlineStr"/>
       <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="n">
-        <v>-2.624326599326608</v>
-      </c>
+      <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="inlineStr"/>
-      <c r="BB51" t="n">
-        <v>1.460704946544887</v>
-      </c>
-      <c r="BC51" t="n">
-        <v>-2.885493827160488</v>
-      </c>
-      <c r="BD51" t="n">
-        <v>0.3684150332076115</v>
-      </c>
+      <c r="BB51" t="inlineStr"/>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
       <c r="BE51" t="inlineStr"/>
       <c r="BF51" t="inlineStr"/>
       <c r="BG51" t="n">
@@ -7797,27 +7804,32 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bw1zAKS6</t>
+          <t>WfkfPdXH</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
         <v>45517.65625</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">toughsheet community stadium
-  bolton </t>
+          <t xml:space="preserve">abbey stadium
+  cambridge </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Or1bBrWD</t>
+          <t>lnb8EJRp</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>t6G9wMZN</t>
+          <t>lrMHUHDc</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7843,7 +7855,11 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>nPjMw0nA</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -7870,7 +7886,9 @@
       <c r="AJ52" t="inlineStr"/>
       <c r="AK52" t="inlineStr"/>
       <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
+      <c r="AM52" t="n">
+        <v>71.77777777777777</v>
+      </c>
       <c r="AN52" t="inlineStr"/>
       <c r="AO52" t="inlineStr"/>
       <c r="AP52" t="inlineStr"/>
@@ -7897,7 +7915,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>CnnJp4ae</t>
+          <t>lQl9etVA</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
@@ -7906,18 +7924,18 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">holker street
-  barrow in furness </t>
+          <t xml:space="preserve">john smith s stadium
+  huddersfield </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>KKJL7QXd</t>
+          <t>xxxpBZl2</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>U3lM3y4e</t>
+          <t>zmKRcPKu</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7942,7 +7960,11 @@
           <t>efl cup</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
@@ -7969,7 +7991,9 @@
       <c r="AI53" t="inlineStr"/>
       <c r="AJ53" t="inlineStr"/>
       <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
+      <c r="AL53" t="n">
+        <v>69.33522727272728</v>
+      </c>
       <c r="AM53" t="inlineStr"/>
       <c r="AN53" t="inlineStr"/>
       <c r="AO53" t="inlineStr"/>
@@ -7997,32 +8021,27 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>OMDVg8x9</t>
+          <t>jXcAnQUr</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">brunton park
-  carlisle </t>
+          <t xml:space="preserve">brisbane road
+  london </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>dUzTIwSF</t>
+          <t>KKyYcus9</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>hSUajdSS</t>
+          <t>ChwgcrNJ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8048,11 +8067,7 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>UwJevjpg</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
@@ -8079,9 +8094,7 @@
       <c r="AJ54" t="inlineStr"/>
       <c r="AK54" t="inlineStr"/>
       <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="n">
-        <v>71.2</v>
-      </c>
+      <c r="AM54" t="inlineStr"/>
       <c r="AN54" t="inlineStr"/>
       <c r="AO54" t="inlineStr"/>
       <c r="AP54" t="inlineStr"/>
@@ -8108,27 +8121,32 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>jXcAnQUr</t>
+          <t>fRe0c20b</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
         <v>45517.64583333334</v>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisbane road
-  london </t>
+          <t xml:space="preserve">edgeley park
+  stockport </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KKyYcus9</t>
+          <t>IX6WjNvr</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ChwgcrNJ</t>
+          <t>6Nl8nagD</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -8154,7 +8172,11 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>pA2vPxeA</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
@@ -8181,7 +8203,9 @@
       <c r="AJ55" t="inlineStr"/>
       <c r="AK55" t="inlineStr"/>
       <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
+      <c r="AM55" t="n">
+        <v>76</v>
+      </c>
       <c r="AN55" t="inlineStr"/>
       <c r="AO55" t="inlineStr"/>
       <c r="AP55" t="inlineStr"/>
@@ -8208,7 +8232,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>fRe0c20b</t>
+          <t>OMDVg8x9</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
@@ -8216,24 +8240,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">kitchen a 
+          <t xml:space="preserve">ward g 
   eng </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">edgeley park
-  stockport </t>
+          <t xml:space="preserve">brunton park
+  carlisle </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IX6WjNvr</t>
+          <t>dUzTIwSF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>6Nl8nagD</t>
+          <t>hSUajdSS</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -8261,7 +8285,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>fcpIzd9s</t>
+          <t>lYgfxNV9</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -8291,7 +8315,7 @@
       <c r="AK56" t="inlineStr"/>
       <c r="AL56" t="inlineStr"/>
       <c r="AM56" t="n">
-        <v>76</v>
+        <v>71.2</v>
       </c>
       <c r="AN56" t="inlineStr"/>
       <c r="AO56" t="inlineStr"/>
@@ -8316,205 +8340,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>tYjCfe2E</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45514.45833333334</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wembley stadium
-  london </t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>48</v>
-      </c>
-      <c r="H57" t="n">
-        <v>482</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>fa community shield</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>dpjHQ7zJ</t>
-        </is>
-      </c>
-      <c r="O57" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P57" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>-3</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="V57" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W57" t="n">
-        <v>-12.4</v>
-      </c>
-      <c r="X57" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>-0.2000000000000001</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>5.000000000000001</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>19.59999999999999</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>-19.59999999999999</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>-0.8179999999999997</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>77.36565656565656</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>76.90282828282827</v>
-      </c>
-      <c r="AN57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO57" t="n">
-        <v>0.9104895104895103</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>4.713604546916557</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>25360675.28269542</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>43287766.12276611</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.715073815073808</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>-2.962703962703927</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>3.408590649191694</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0.3623117646774934</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ57" t="n">
-        <v>3.079487179487188</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB57" t="n">
-        <v>0.1590587304142304</v>
-      </c>
-      <c r="BC57" t="n">
-        <v>5.451282051282064</v>
-      </c>
-      <c r="BD57" t="n">
-        <v>-5.886652726358591</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>-8500000</v>
-      </c>
-      <c r="BG57" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG8"/>
+  <dimension ref="A1:BG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -630,92 +630,92 @@
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2g67Vsyf</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45536.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,154 +779,140 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-18</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V2" t="n">
         <v>-1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.8400000000000001</v>
-      </c>
       <c r="W2" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>4</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>-7.5</v>
+        <v>-0.5183333333333331</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.5</v>
+        <v>-0.5916666666666666</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2</v>
+        <v>-9.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
+        <v>79.09318181818182</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.004301772159831</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.07726340605496551</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.3317539026629932</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>-16138402.50994796</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>-0.8618059381695709</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>-1.15228037955309</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-15215313.98585075</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-2.705662687480881</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>0.572857724353895</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.231539638812365</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-4.097630876275389</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-2.971635293758055</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
         <v>1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>80.62121212121212</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>80.78888888888889</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-1.189119741749732</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-7.303507108339133</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.1187373737373734</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-0.2614141414140931</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.679848484848488</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-33162712.12121212</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-23441608.96686664</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-5.074968199148699</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.1359099695977135</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-4.63030303030304</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.533810216337713</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-3.746515151515155</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5cORazJ</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,18 +922,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>AovF1Mia</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -974,128 +960,128 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="U3" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="V3" t="n">
-        <v>1.205</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-11</v>
-      </c>
+        <v>-2.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>-0.08666666666666689</v>
       </c>
       <c r="AC3" t="n">
-        <v>-17.5</v>
+        <v>0.02333333333333343</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-19</v>
+        <v>-0.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="AI3" t="n">
-        <v>-4</v>
+        <v>-0.1666666666666661</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5</v>
+        <v>3.833333333333334</v>
       </c>
       <c r="AL3" t="n">
-        <v>78.64090909090909</v>
+        <v>79.92727272727274</v>
       </c>
       <c r="AM3" t="n">
-        <v>81.93939393939394</v>
+        <v>76.13636363636363</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.7664036823730278</v>
+        <v>-3.589258656198442</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.7707852589409754</v>
+        <v>0.473685847382483</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.8302020202020197</v>
+        <v>0.4477272727272721</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>0.70711662075297</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-2.146280991735541</v>
-      </c>
+        <v>7544613.442113435</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>-4910225.895316804</v>
+        <v>-2.355594405594413</v>
       </c>
       <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>-1716954.175744911</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>-1.118400547792803</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+        <v>3.35759518259519</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8090252.662097747</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.522377622377604</v>
+      </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-0.5213958513854189</v>
+        <v>-0.8196324150947873</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.4753351698806227</v>
+        <v>-0.7328865578865873</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.002386751143149</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="n">
-        <v>-2.480734618916443</v>
-      </c>
+        <v>0.5168985077285271</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.95964127522025</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1103,11 +1089,11 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2m3cvwKO</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1117,18 +1103,18 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>UDg08Ohm</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1155,142 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>-1</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="V4" t="n">
-        <v>1.053333333333333</v>
+        <v>-3</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7083333333333335</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="n">
-        <v>2.833333333333333</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.333333333333333</v>
-      </c>
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>18.83333333333334</v>
+        <v>-0.5516666666666667</v>
       </c>
       <c r="AC4" t="n">
-        <v>-18.83333333333334</v>
+        <v>-0.5766666666666669</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5</v>
+        <v>-29.66666666666667</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.5</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AG4" t="n">
-        <v>-14</v>
+        <v>-0.8333333333333333</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.5</v>
+        <v>-4.166666666666666</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.666666666666666</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AL4" t="n">
-        <v>80.99621212121212</v>
+        <v>74.30555555555556</v>
       </c>
       <c r="AM4" t="n">
-        <v>78.03749999999999</v>
+        <v>76.88484848484848</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.8732980149260356</v>
+        <v>1.906390994365946</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.294460303073038</v>
+        <v>-0.3748366558817238</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5190312213039485</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3</v>
-      </c>
+        <v>-0.5611780685644321</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>1.026882460973326</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-2.341666666666665</v>
-      </c>
+        <v>-20035862.41199878</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>28607552.80073462</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>20080363.76021909</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.3333333333333321</v>
-      </c>
+        <v>1.435539103152742</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>5.089356675085511</v>
+        <v>-4.118065120906039</v>
       </c>
       <c r="AY4" t="n">
-        <v>-361</v>
+        <v>-14894675.70262512</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-394</v>
-      </c>
+        <v>-3.685127793082344</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>0.4010196875021763</v>
+        <v>-0.3343830465708209</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.95466023875116</v>
+        <v>0.6740262473217342</v>
       </c>
       <c r="BD4" t="n">
-        <v>-4.124674434894359</v>
+        <v>-4.629863305091988</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1125000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.129981634527098</v>
-      </c>
+        <v>-4.151222284259504</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1298,32 +1270,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lAUlrLKa</t>
+          <t>INsZAAf3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">salisbury m 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1350,138 +1322,128 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>-24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-4</v>
+      </c>
       <c r="Q5" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.333333333333333</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0.165</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-2.5</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>26</v>
+        <v>-0.04666666666666663</v>
       </c>
       <c r="AC5" t="n">
-        <v>-26</v>
+        <v>0.4083333333333333</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.25</v>
+        <v>-0.1666666666666643</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.25</v>
+        <v>0.1666666666666643</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>-7.5</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.25</v>
+        <v>4.833333333333334</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.75</v>
+        <v>1.333333333333334</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-7.5</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>79.29040404040406</v>
+        <v>76.21363636363637</v>
       </c>
       <c r="AM5" t="n">
-        <v>70.58585858585859</v>
+        <v>79.17508417508417</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.3359470599834147</v>
+        <v>2.585834908052345</v>
       </c>
       <c r="AO5" t="n">
-        <v>11.18834843115989</v>
+        <v>-0.5270262005616082</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.081818181818182</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-7.166666666666657</v>
-      </c>
+        <v>-0.9612304866850319</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>-0.4738816738816638</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-0.1230880230880196</v>
-      </c>
+        <v>-52072438.01652893</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>68390530.30303031</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>42499553.13043092</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>-6.833333333333332</v>
-      </c>
+        <v>1.668374655647387</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>11.55127782997256</v>
+        <v>-6.887860422405865</v>
       </c>
       <c r="AY5" t="n">
-        <v>-358</v>
+        <v>-34725580.90765035</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-359</v>
-      </c>
+        <v>-5.735684113865929</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>1.254893285816742</v>
+        <v>1.815677715707238</v>
       </c>
       <c r="BC5" t="n">
-        <v>12.82900432900432</v>
+        <v>1.007456382001806</v>
       </c>
       <c r="BD5" t="n">
-        <v>-4.459878516624002</v>
+        <v>-5.949425257885082</v>
       </c>
       <c r="BE5" t="n">
-        <v>-18900000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>13.87453102453102</v>
-      </c>
+        <v>-7.119658062273857</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1489,32 +1451,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fNaktakC</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1541,136 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-4</v>
-      </c>
       <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="U6" t="n">
         <v>-1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.1500000000000001</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.5899999999999999</v>
-      </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>0.9266666666666666</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG6" t="n">
         <v>-1</v>
       </c>
-      <c r="AA6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-26.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>-7</v>
-      </c>
       <c r="AH6" t="n">
-        <v>-1</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-3.166666666666666</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>-11.16666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>70.48333333333333</v>
+        <v>76.55555555555554</v>
       </c>
       <c r="AM6" t="n">
-        <v>71.84999999999999</v>
+        <v>84.70151515151515</v>
       </c>
       <c r="AN6" t="n">
-        <v>3.772259892187435e-05</v>
+        <v>0.4897854263087602</v>
       </c>
       <c r="AO6" t="n">
-        <v>-4.359121015995328</v>
+        <v>0.07594744701721035</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.3</v>
+        <v>-0.138439955106622</v>
       </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>-5.332741702741714</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0.3021212121212109</v>
-      </c>
+        <v>-3233804.012345679</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
-        <v>-4343375.18037518</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>-7390887.657434516</v>
-      </c>
+        <v>-1.361447811447814</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-3.643842129737266</v>
+        <v>-0.6723625140291887</v>
       </c>
       <c r="AY6" t="n">
-        <v>72</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="n">
-        <v>82</v>
-      </c>
+        <v>2354586.580678123</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-1.613860830527486</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>-0.3993210327609304</v>
+        <v>4.159125495108555</v>
       </c>
       <c r="BC6" t="n">
-        <v>-2.609422799422788</v>
+        <v>2.131846240179584</v>
       </c>
       <c r="BD6" t="n">
-        <v>-6.041171994489503</v>
+        <v>3.188118957324392</v>
       </c>
       <c r="BE6" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-2.090533910533907</v>
-      </c>
+        <v>0.7621914136231567</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1678,11 +1632,11 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dCkAk3SP</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.45833333334</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1692,18 +1646,18 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>69ZiU2Om</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1730,132 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
       <c r="V7" t="n">
-        <v>-2.595</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.5</v>
-      </c>
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="n">
-        <v>-23</v>
+        <v>0.08500000000000008</v>
       </c>
       <c r="AC7" t="n">
-        <v>23</v>
+        <v>-0.246666666666667</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-14</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AG7" t="n">
-        <v>10</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AH7" t="n">
-        <v>-2.5</v>
+        <v>-3</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>81.5409090909091</v>
+        <v>84</v>
       </c>
       <c r="AM7" t="n">
-        <v>69.88888888888889</v>
+        <v>77.03030303030302</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.017129533319469</v>
+        <v>-2.819158373015039</v>
       </c>
       <c r="AO7" t="n">
-        <v>1.279113247545752</v>
+        <v>-0.2978447829005839</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.1171717171717168</v>
+        <v>-0.5024793388429749</v>
       </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>1.335555555555601</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.4260606060606058</v>
-      </c>
+        <v>-9694661.157024793</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
-        <v>3197949.494949492</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>868967.7332681548</v>
-      </c>
+        <v>-0.634297520661157</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-0.1671712609528981</v>
+        <v>-4.17462809917356</v>
       </c>
       <c r="AY7" t="n">
-        <v>-138</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="n">
-        <v>-148</v>
-      </c>
+        <v>-4502556.331911132</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-5.849338842975214</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-0.1539561863855172</v>
+        <v>1.532534641596499</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.8635353535353545</v>
+        <v>-1.631818181818176</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.8897866782452581</v>
+        <v>-5.686038533271713</v>
       </c>
       <c r="BE7" t="n">
-        <v>-7000000</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.11949494949495</v>
-      </c>
+        <v>-2.837689123439546</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1863,195 +1813,1297 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8j9FTL56</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.35416666666</v>
+        <v>45535.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>0.07166666666666655</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.6383333333333332</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.166666666666666</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75.66666666666666</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>77.4074074074074</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>2.506421558606483</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.1998773603723192</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.7395775941230489</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>-16440945.82185491</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0.2573002754820948</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>-3.508172635445362</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-7851854.423149318</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-3.926813590449953</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>-2.391073777759544</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.04141414141420796</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.409208156379421</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-3.064254834921854</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-4.666666666666667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>-0.2033333333333336</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>73.04861111111111</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>79.27129629629628</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.487616580684289</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.0800470549399046</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.4232323232323232</v>
+      </c>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>2354633.838383839</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>3.092676767676775</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>-0.1212121212121247</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-3745213.319923004</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.583838383838398</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>3.065100910897627</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.364646464646455</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1.315439681178447</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-2.448946598631338</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>0.3358333333333333</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.219166666666667</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-4.583333333333336</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>4.583333333333336</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.083333333333334</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-3.833333333333334</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>77.56969696969696</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>74.68888888888888</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.2019147331632212</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.1235878912968698</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.04545454545454541</v>
+      </c>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>6920094.276094276</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0.5164983164983141</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>2.859393939393939</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4720269.565758023</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.546666666666667</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>0.8138196608185524</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.839730639730647</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.023684852162432</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.949627402032164</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.35416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>2XrRecc3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ppjDR086</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="G11" t="n">
         <v>48</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H11" t="n">
         <v>481</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>20242025</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>vBIoDoo1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>1.243333333333334</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.8416666666666666</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.833333333333336</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AG11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>10.16666666666667</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75.51363636363637</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>76.44090909090909</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.330697831365406</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.4396177609799903</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.8335418579736757</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>50299240.70247935</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>-1.848433195592285</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>6.635158402203857</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>28644315.15090087</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>8.002978650137749</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>1.327260581266046</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.8175026782981263</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.977066650025264</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.079671563601522</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>GdWtpsjm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45529.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1.378361978728115</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.6748346793124023</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.601652892561984</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>36145355.37190082</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>-0.2084297520661167</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-160</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>6.611404958677667</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>26098827.98384592</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6.461487603305784</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>3.758933402637808</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-1.287768595041342</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.802180370518641</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.687439116274788</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-153</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6RCbX36s</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.666666666666667</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-3.666666666666666</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="Y13" t="n">
         <v>-0.3333333333333335</v>
       </c>
-      <c r="V8" t="n">
-        <v>0.8166666666666667</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.3925</v>
-      </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>1.083333333333333</v>
-      </c>
-      <c r="AA8" t="n">
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>-1.363333333333334</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.2566666666666666</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>12.66666666666666</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>76.81818181818181</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.47575757575758</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-2.373576987293958</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.1075340014907311</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.3711662075298441</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-138375000</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-10907731.8640955</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-2.141873278236922</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-339</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>-5.761904761904759</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-1.778420569329654</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-631925.9058008529</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-2.956749311294757</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.1428571428571423</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.186807775067052</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-4.091092745638207</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.823529189934959</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.360851189988381</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-308</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>61T7bt5t</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45529.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="AB8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-11.25</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="U14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Y14" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>5.416666666666666</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-6.833333333333334</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>-0.5833333333333334</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.4166666666666667</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>79.23367003367004</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>79.00808080808081</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-0.9354330604105883</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-2.247488848371503</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.8712265512265516</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>-2.576569264069235</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.117272727272731</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>-21433497.83549784</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>-0.3516666666666666</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5016666666666667</v>
+      </c>
+      <c r="AD14" t="n">
         <v>-3</v>
       </c>
-      <c r="AV8" t="n">
-        <v>-10318131.93960474</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-1.155646765061618</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-241</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-248</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>-0.4872894293150096</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-4.511056998556981</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>-6.117584565283977</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-81500000</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-4.571850649350665</v>
-      </c>
-      <c r="BG8" t="n">
+      <c r="AE14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.3333333333333339</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>74.45454545454545</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>76.96801346801347</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.101759975147388</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.3422805685047681</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.2918630751964084</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>13500000</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-9403157.914616246</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>3.227648277648282</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>79</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-3.928414486747812</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-7280454.768384793</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-1.529728913062243</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>-1.751099254103963</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.0830505913838806</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-1.671008176601163</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-2.720958985081111</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>77</v>
+      </c>
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG14"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
@@ -784,7 +784,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -803,54 +803,54 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>-1.166666666666667</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AE2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AF2" t="n">
         <v>-1</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>-0.5183333333333331</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AI2" t="n">
         <v>-0.5916666666666666</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AJ2" t="n">
         <v>-9.5</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AK2" t="n">
         <v>9.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
       </c>
       <c r="AL2" t="n">
         <v>79.09318181818182</v>
@@ -859,48 +859,48 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.004301772159831</v>
+        <v>-0.9009932659932609</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07726340605496551</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-0.3317539026629932</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>-16138402.50994796</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>0.07133485215646318</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>-17129304.71380471</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-2.887962962962973</v>
+      </c>
       <c r="AT2" t="n">
-        <v>-0.8618059381695709</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>0.7296165115315034</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.140286195286194</v>
+      </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>-1.15228037955309</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-15215313.98585075</v>
-      </c>
+        <v>-2.946957639428859</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>-2.705662687480881</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>0.572857724353895</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.231539638812365</v>
-      </c>
+        <v>-4.100489453830249</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-15032471.45984167</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-4.097630876275389</v>
+        <v>-1.269360269360263</v>
       </c>
       <c r="BE2" t="n">
-        <v>-2.971635293758055</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>0.9561994712921837</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-0.3611616161616165</v>
+      </c>
       <c r="BG2" t="n">
         <v>1</v>
       </c>
@@ -908,7 +908,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>U11vkTXq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,128 +960,128 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>-1</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3333333333333335</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V3" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="W3" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
         <v>-2.5</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Y3" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
       <c r="AB3" t="n">
-        <v>-0.08666666666666689</v>
+        <v>-3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02333333333333343</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>-1</v>
       </c>
       <c r="AE3" t="n">
-        <v>-14</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>-4.166666666666666</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.5</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AH3" t="n">
-        <v>-3.833333333333334</v>
+        <v>-0.5516666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.1666666666666661</v>
+        <v>-0.5766666666666669</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.5</v>
+        <v>-29.66666666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.833333333333334</v>
+        <v>29.66666666666667</v>
       </c>
       <c r="AL3" t="n">
-        <v>79.92727272727274</v>
+        <v>74.30555555555556</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.13636363636363</v>
+        <v>76.88484848484848</v>
       </c>
       <c r="AN3" t="n">
-        <v>-3.589258656198442</v>
+        <v>1.434911616161614</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.473685847382483</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.4477272727272721</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>7544613.442113435</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-0.367619793132564</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-19809116.16161617</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>-3.608627946127939</v>
+      </c>
       <c r="AT3" t="n">
-        <v>-2.355594405594413</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>-0.4466180072507768</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.834196127946143</v>
+      </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>3.35759518259519</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8090252.662097747</v>
-      </c>
+        <v>-3.959850928010752</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>1.522377622377604</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
-        <v>-0.8196324150947873</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>-0.7328865578865873</v>
-      </c>
+        <v>-4.411779592884471</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-14486552.70163953</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>0.5168985077285271</v>
+        <v>-4.127882996633005</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.95964127522025</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>1.891513343109708</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.5641624579124578</v>
+      </c>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1089,7 +1089,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1097,24 +1097,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,128 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>-3.833333333333334</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
       <c r="AB4" t="n">
-        <v>-0.5516666666666667</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5766666666666669</v>
+        <v>-2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>-29.66666666666667</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="AE4" t="n">
-        <v>29.66666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.6666666666666667</v>
+        <v>3.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.8333333333333333</v>
+        <v>3.833333333333334</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>-0.08666666666666689</v>
       </c>
       <c r="AI4" t="n">
-        <v>4</v>
+        <v>0.02333333333333343</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-4.166666666666666</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>4.333333333333334</v>
+        <v>-14</v>
       </c>
       <c r="AL4" t="n">
-        <v>74.30555555555556</v>
+        <v>79.92727272727274</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.88484848484848</v>
+        <v>76.13636363636363</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.906390994365946</v>
+        <v>-2.445021645021647</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.3748366558817238</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.5611780685644321</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="n">
-        <v>-20035862.41199878</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>0.4678853967278431</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>7717687.590187585</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>1.520562770562748</v>
+      </c>
       <c r="AT4" t="n">
-        <v>1.435539103152742</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>-1.020454848325983</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.7196608946608762</v>
+      </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>-4.118065120906039</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-14894675.70262512</v>
-      </c>
+        <v>5.111238717999683</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>-3.685127793082344</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
-        <v>-0.3343830465708209</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0.6740262473217342</v>
-      </c>
+        <v>0.9069109447269739</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9117255.802554879</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>-4.629863305091988</v>
+        <v>3.408189033189046</v>
       </c>
       <c r="BE4" t="n">
-        <v>-4.151222284259504</v>
-      </c>
-      <c r="BF4" t="inlineStr"/>
+        <v>-3.578898649520781</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.4234848484848477</v>
+      </c>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1346,54 +1346,54 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6666666666666665</v>
+        <v>-1.5</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-0.833333333333333</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
         <v>-1</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.04666666666666663</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
         <v>0.4083333333333333</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AJ5" t="n">
         <v>-0.1666666666666643</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>0.1666666666666643</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>4.833333333333334</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7.333333333333334</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
         <v>76.21363636363637</v>
@@ -1402,48 +1402,48 @@
         <v>79.17508417508417</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.585834908052345</v>
+        <v>1.668374655647387</v>
       </c>
       <c r="AO5" t="n">
         <v>-0.5270262005616082</v>
       </c>
-      <c r="AP5" t="n">
-        <v>-0.9612304866850319</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
         <v>-52072438.01652893</v>
       </c>
-      <c r="AS5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-5.735684113865929</v>
+      </c>
       <c r="AT5" t="n">
-        <v>1.668374655647387</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>1.815677715707238</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.007456382001806</v>
+      </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
+        <v>-7.119658062273857</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>-5.949425257885082</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-34725580.90765035</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="n">
         <v>-6.887860422405865</v>
       </c>
-      <c r="AY5" t="n">
-        <v>-34725580.90765035</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-5.735684113865929</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
-        <v>1.815677715707238</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.007456382001806</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>-5.949425257885082</v>
-      </c>
       <c r="BE5" t="n">
-        <v>-7.119658062273857</v>
-      </c>
-      <c r="BF5" t="inlineStr"/>
+        <v>2.585834908052345</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.9612304866850319</v>
+      </c>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,7 +1451,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>8QPOfb45</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1459,24 +1459,24 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">barrott s 
+  eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,128 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.166666666666667</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="U6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-5.666666666666666</v>
-      </c>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-4.083333333333334</v>
+      </c>
       <c r="AB6" t="n">
-        <v>0.9266666666666666</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.28</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AE6" t="n">
-        <v>-1.5</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.5</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.333333333333334</v>
+        <v>0.3358333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3.166666666666666</v>
+        <v>1.219166666666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>-4.583333333333336</v>
       </c>
       <c r="AK6" t="n">
-        <v>-11.16666666666667</v>
+        <v>4.583333333333336</v>
       </c>
       <c r="AL6" t="n">
-        <v>76.55555555555554</v>
+        <v>77.56969696969696</v>
       </c>
       <c r="AM6" t="n">
-        <v>84.70151515151515</v>
+        <v>74.68888888888888</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.4897854263087602</v>
+        <v>0.4973247627793072</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.07594744701721035</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-0.138439955106622</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="n">
-        <v>-3233804.012345679</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+        <v>0.136595052694124</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>6870490.970309153</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>3.530468319559219</v>
+      </c>
       <c r="AT6" t="n">
-        <v>-1.361447811447814</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
+        <v>0.6970477622664646</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.826342209978577</v>
+      </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="n">
-        <v>-0.6723625140291887</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2354586.580678123</v>
-      </c>
+        <v>2.199693543321217</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>-1.613860830527486</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
-        <v>4.159125495108555</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.131846240179584</v>
-      </c>
+        <v>3.011981753059956</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4754117.417338846</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>3.188118957324392</v>
+        <v>2.860055096418733</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.7621914136231567</v>
-      </c>
-      <c r="BF6" t="inlineStr"/>
+        <v>0.0278985652925634</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.04132231404958664</v>
+      </c>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1632,7 +1632,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>2Fanm72d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1640,24 +1640,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,128 +1684,128 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-2</v>
       </c>
       <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U7" t="n">
         <v>-1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-1.166666666666667</v>
-      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.6666666666666667</v>
-      </c>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-3.166666666666666</v>
+      </c>
       <c r="AB7" t="n">
-        <v>0.08500000000000008</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.246666666666667</v>
+        <v>-5.666666666666666</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.5</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1666666666666667</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.1666666666666667</v>
+        <v>-11.16666666666667</v>
       </c>
       <c r="AH7" t="n">
-        <v>-3</v>
+        <v>0.9266666666666666</v>
       </c>
       <c r="AI7" t="n">
-        <v>5</v>
+        <v>-1.28</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.833333333333334</v>
+        <v>2</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.5</v>
+        <v>-1.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>84</v>
+        <v>76.55555555555554</v>
       </c>
       <c r="AM7" t="n">
-        <v>77.03030303030302</v>
+        <v>84.70151515151515</v>
       </c>
       <c r="AN7" t="n">
-        <v>-2.819158373015039</v>
+        <v>-1.373484848484846</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.2978447829005839</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-0.5024793388429749</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="n">
-        <v>-9694661.157024793</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+        <v>0.05694861168006926</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-3325173.611111112</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-1.666792929292924</v>
+      </c>
       <c r="AT7" t="n">
-        <v>-0.634297520661157</v>
-      </c>
-      <c r="AU7" t="inlineStr"/>
+        <v>4.355336533291137</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.202525252525248</v>
+      </c>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="n">
-        <v>-4.17462809917356</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-4502556.331911132</v>
-      </c>
+        <v>0.8169144816237264</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>-5.849338842975214</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
-        <v>1.532534641596499</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>-1.631818181818176</v>
-      </c>
+        <v>2.840177295521215</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2240428.597877445</v>
+      </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>-5.686038533271713</v>
+        <v>-0.6785353535353522</v>
       </c>
       <c r="BE7" t="n">
-        <v>-2.837689123439546</v>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+        <v>0.1886910046823935</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.1436868686868689</v>
+      </c>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1813,7 +1813,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>SUdkBJln</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1821,24 +1821,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">portman road
+  ipswich </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P8" t="n">
         <v>-1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="R8" t="n">
         <v>-1</v>
@@ -1889,104 +1889,100 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1666666666666666</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>5</v>
+      </c>
       <c r="AB8" t="n">
-        <v>0.07166666666666655</v>
+        <v>-0.833333333333333</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6383333333333332</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AE8" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="AG8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
       <c r="AH8" t="n">
-        <v>-1.666666666666666</v>
+        <v>0.08500000000000008</v>
       </c>
       <c r="AI8" t="n">
-        <v>-4.166666666666666</v>
+        <v>-0.246666666666667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.166666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>-2.666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>75.66666666666666</v>
+        <v>84</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.4074074074074</v>
+        <v>77.03030303030302</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.506421558606483</v>
+        <v>-0.634297520661157</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.1998773603723192</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-0.7395775941230489</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="n">
-        <v>-16440945.82185491</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+        <v>-0.2978447829005839</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>-9694661.157024793</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-5.849338842975214</v>
+      </c>
       <c r="AT8" t="n">
-        <v>0.2573002754820948</v>
-      </c>
-      <c r="AU8" t="inlineStr"/>
+        <v>1.532534641596499</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-1.631818181818176</v>
+      </c>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="n">
-        <v>-3.508172635445362</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-7851854.423149318</v>
-      </c>
+        <v>-2.837689123439546</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>-3.926813590449953</v>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
-        <v>-2.391073777759544</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>-0.04141414141420796</v>
-      </c>
+        <v>-5.686038533271713</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-4502556.331911132</v>
+      </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>-0.409208156379421</v>
+        <v>-4.17462809917356</v>
       </c>
       <c r="BE8" t="n">
-        <v>-3.064254834921854</v>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+        <v>-2.819158373015039</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.5024793388429749</v>
+      </c>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1994,7 +1990,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>lpob9cJb</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2008,18 +2004,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2046,128 +2042,124 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AD9" t="n">
         <v>-0.1666666666666666</v>
       </c>
-      <c r="U9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-4.666666666666667</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="n">
-        <v>-0.2033333333333336</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.916666666666667</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.333333333333336</v>
-      </c>
       <c r="AE9" t="n">
-        <v>-4.666666666666664</v>
+        <v>-0.8333333333333335</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.166666666666667</v>
+        <v>2.166666666666666</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.8333333333333335</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AH9" t="n">
+        <v>0.07166666666666655</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.6383333333333332</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK9" t="n">
         <v>-3</v>
       </c>
-      <c r="AI9" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-6.5</v>
-      </c>
       <c r="AL9" t="n">
-        <v>73.04861111111111</v>
+        <v>75.66666666666666</v>
       </c>
       <c r="AM9" t="n">
-        <v>79.27129629629628</v>
+        <v>77.4074074074074</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.487616580684289</v>
+        <v>0.2573002754820948</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.0800470549399046</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.4232323232323232</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>2354633.838383839</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+        <v>-0.1998773603723192</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>-16440945.82185491</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>-3.926813590449953</v>
+      </c>
       <c r="AT9" t="n">
-        <v>3.092676767676775</v>
-      </c>
-      <c r="AU9" t="inlineStr"/>
+        <v>-2.391073777759544</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0.04141414141420796</v>
+      </c>
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr"/>
       <c r="AX9" t="n">
-        <v>-0.1212121212121247</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-3745213.319923004</v>
-      </c>
+        <v>-3.064254834921854</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>1.583838383838398</v>
-      </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
-        <v>3.065100910897627</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.364646464646455</v>
-      </c>
+        <v>-0.409208156379421</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-7851854.423149318</v>
+      </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-1.315439681178447</v>
+        <v>-3.508172635445362</v>
       </c>
       <c r="BE9" t="n">
-        <v>-2.448946598631338</v>
-      </c>
-      <c r="BF9" t="inlineStr"/>
+        <v>2.506421558606483</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.7395775941230489</v>
+      </c>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2175,7 +2167,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>x6HuiG3U</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2183,24 +2175,24 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2227,22 +2219,22 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
@@ -2251,104 +2243,104 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5833333333333333</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="U10" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.083333333333333</v>
-      </c>
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
-        <v>-0.3333333333333335</v>
+        <v>-1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
+        <v>-1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="AB10" t="n">
-        <v>0.3358333333333333</v>
+        <v>-0.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.219166666666667</v>
+        <v>-4.666666666666667</v>
       </c>
       <c r="AD10" t="n">
-        <v>-4.583333333333336</v>
+        <v>-0.1666666666666666</v>
       </c>
       <c r="AE10" t="n">
-        <v>4.583333333333336</v>
+        <v>-0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.4166666666666667</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.3333333333333333</v>
+        <v>-6.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>-5.75</v>
+        <v>-0.2033333333333336</v>
       </c>
       <c r="AI10" t="n">
-        <v>-4.083333333333334</v>
+        <v>-0.916666666666667</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-3.833333333333334</v>
+        <v>4.333333333333336</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.666666666666666</v>
+        <v>-4.666666666666664</v>
       </c>
       <c r="AL10" t="n">
-        <v>77.56969696969696</v>
+        <v>73.04861111111111</v>
       </c>
       <c r="AM10" t="n">
-        <v>74.68888888888888</v>
+        <v>79.27129629629628</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.2019147331632212</v>
+        <v>3.041666666666668</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1235878912968698</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.04545454545454541</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>6920094.276094276</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>0.1033427096103772</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>2393632.154882155</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>1.558164983165</v>
+      </c>
       <c r="AT10" t="n">
-        <v>0.5164983164983141</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
+        <v>3.311080574080734</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.481144781144764</v>
+      </c>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr"/>
       <c r="AX10" t="n">
-        <v>2.859393939393939</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4720269.565758023</v>
-      </c>
+        <v>-2.523989712439544</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="n">
-        <v>3.546666666666667</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
-        <v>0.8138196608185524</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.839730639730647</v>
-      </c>
+        <v>-1.15154313438066</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-3467877.904676599</v>
+      </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>3.023684852162432</v>
+        <v>-0.1003367003366975</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.949627402032164</v>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+        <v>1.647532406975973</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.4184343434343432</v>
+      </c>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2432,54 +2424,54 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AD11" t="n">
         <v>0.3333333333333335</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AE11" t="n">
         <v>-0.1666666666666667</v>
       </c>
-      <c r="V11" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="n">
+      <c r="AF11" t="n">
+        <v>10.16666666666667</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.243333333333334</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AI11" t="n">
         <v>-0.8416666666666666</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AJ11" t="n">
         <v>5.833333333333336</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AK11" t="n">
         <v>-5.833333333333336</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>3.833333333333334</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>10.16666666666667</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-6.5</v>
       </c>
       <c r="AL11" t="n">
         <v>75.51363636363637</v>
@@ -2488,622 +2480,49 @@
         <v>76.44090909090909</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.330697831365406</v>
+        <v>-1.848433195592285</v>
       </c>
       <c r="AO11" t="n">
         <v>0.4396177609799903</v>
       </c>
-      <c r="AP11" t="n">
-        <v>0.8335418579736757</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
         <v>50299240.70247935</v>
       </c>
-      <c r="AS11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>8.002978650137749</v>
+      </c>
       <c r="AT11" t="n">
-        <v>-1.848433195592285</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
+        <v>1.327260581266046</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.8175026782981263</v>
+      </c>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr"/>
       <c r="AX11" t="n">
+        <v>4.079671563601522</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>7.977066650025264</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>28644315.15090087</v>
+      </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="n">
         <v>6.635158402203857</v>
       </c>
-      <c r="AY11" t="n">
-        <v>28644315.15090087</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>8.002978650137749</v>
-      </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
-        <v>1.327260581266046</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0.8175026782981263</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.977066650025264</v>
-      </c>
       <c r="BE11" t="n">
-        <v>4.079671563601522</v>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+        <v>1.330697831365406</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.8335418579736757</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>GdWtpsjm</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45529.52083333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">attwell s 
-  eng </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>xYe7DwID</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>48</v>
-      </c>
-      <c r="H12" t="n">
-        <v>481</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>pdaUMZYd</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>75.25</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>-1.378361978728115</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.6748346793124023</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.601652892561984</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>-23000000</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>36145355.37190082</v>
-      </c>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="n">
-        <v>-0.2084297520661167</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>-160</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="n">
-        <v>6.611404958677667</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>26098827.98384592</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6.461487603305784</v>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
-        <v>3.758933402637808</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>-1.287768595041342</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.802180370518641</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>6.687439116274788</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>-153</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6RCbX36s</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">coote d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>OtpNdwrc</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>p6ahwuwJ</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>48</v>
-      </c>
-      <c r="H13" t="n">
-        <v>481</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>IoJ2QpOs</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1.333333333333333</v>
-      </c>
-      <c r="U13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V13" t="n">
-        <v>-3.666666666666666</v>
-      </c>
-      <c r="W13" t="n">
-        <v>-3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="n">
-        <v>-1.363333333333334</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>-0.2566666666666666</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>-12.66666666666666</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>12.66666666666666</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>6.333333333333334</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>76.81818181818181</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>76.47575757575758</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-2.373576987293958</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-0.1075340014907311</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-0.3711662075298441</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>-138375000</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>-10907731.8640955</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>-2.141873278236922</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>-339</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-5.761904761904759</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-1.778420569329654</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>-631925.9058008529</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>-2.956749311294757</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0.1428571428571423</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.186807775067052</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-4.091092745638207</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0.823529189934959</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.360851189988381</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-308</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>61T7bt5t</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45529.41666666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">england d 
-  eng </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>48</v>
-      </c>
-      <c r="H14" t="n">
-        <v>481</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>premier league</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lAbHYaQM</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>hxNijWrJ</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>-6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="n">
-        <v>-0.3516666666666666</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0.5016666666666667</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>-0.3333333333333339</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>-1.833333333333334</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>74.45454545454545</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>76.96801346801347</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.101759975147388</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>-0.3422805685047681</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>-0.2918630751964084</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>13500000</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>-9403157.914616246</v>
-      </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="n">
-        <v>3.227648277648282</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>79</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="n">
-        <v>-3.928414486747812</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>-7280454.768384793</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>-1.529728913062243</v>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="n">
-        <v>-1.751099254103963</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>-0.0830505913838806</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>-1.671008176601163</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>-2.720958985081111</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>77</v>
-      </c>
-      <c r="BG14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -803,54 +803,54 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-9.5</v>
       </c>
       <c r="U2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.5</v>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
+        <v>-0.5183333333333331</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.5916666666666666</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD2" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AE2" t="n">
         <v>1</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>-5.5</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AK2" t="n">
         <v>-2.333333333333333</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.5183333333333331</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-0.5916666666666666</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>9.5</v>
       </c>
       <c r="AL2" t="n">
         <v>79.09318181818182</v>
@@ -859,48 +859,48 @@
         <v>76.54545454545455</v>
       </c>
       <c r="AN2" t="n">
+        <v>0.9561994712921837</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>-0.3611616161616165</v>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
         <v>-0.9009932659932609</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AS2" t="n">
+        <v>1.140286195286194</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>-15032471.45984167</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-1.269360269360263</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-2.887962962962973</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>0.07133485215646318</v>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
+      <c r="BA2" t="n">
+        <v>-2.946957639428859</v>
+      </c>
+      <c r="BB2" t="n">
         <v>-17129304.71380471</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-2.887962962962973</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.7296165115315034</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.140286195286194</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>-2.946957639428859</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="n">
-        <v>-4.100489453830249</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-15032471.45984167</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>-1.269360269360263</v>
+        <v>0.7296165115315034</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.9561994712921837</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-0.3611616161616165</v>
-      </c>
+        <v>-4.100489453830249</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>1</v>
       </c>
@@ -984,54 +984,54 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>-29.66666666666667</v>
+      </c>
+      <c r="U3" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>-0.8333333333333333</v>
       </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>-2.5</v>
+        <v>-0.5516666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.5766666666666669</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>-4.166666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AB3" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="AC3" t="n">
         <v>-1.166666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>-2.5</v>
       </c>
       <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI3" t="n">
         <v>-1.166666666666667</v>
       </c>
-      <c r="AF3" t="n">
-        <v>-4.166666666666666</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.5516666666666667</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.5766666666666669</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>-29.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>29.66666666666667</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="n">
         <v>74.30555555555556</v>
@@ -1040,48 +1040,48 @@
         <v>76.88484848484848</v>
       </c>
       <c r="AN3" t="n">
+        <v>1.891513343109708</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.5641624579124578</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
         <v>1.434911616161614</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AS3" t="n">
+        <v>0.834196127946143</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>-14486552.70163953</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-4.127882996633005</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-3.608627946127939</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>-0.367619793132564</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="n">
+      <c r="BA3" t="n">
+        <v>-3.959850928010752</v>
+      </c>
+      <c r="BB3" t="n">
         <v>-19809116.16161617</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>-3.608627946127939</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>-0.4466180072507768</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.834196127946143</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="n">
-        <v>-3.959850928010752</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
-        <v>-4.411779592884471</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-14486552.70163953</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>-4.127882996633005</v>
+        <v>-0.4466180072507768</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.891513343109708</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-0.5641624579124578</v>
-      </c>
+        <v>-4.411779592884471</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
       </c>
@@ -1165,54 +1165,54 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-14</v>
+      </c>
+      <c r="V4" t="n">
         <v>0.5</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
+        <v>-0.08666666666666689</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.02333333333333343</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>-3.833333333333334</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AK4" t="n">
         <v>-0.1666666666666661</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>3.833333333333334</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.08666666666666689</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.02333333333333343</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-14</v>
       </c>
       <c r="AL4" t="n">
         <v>79.92727272727274</v>
@@ -1221,48 +1221,48 @@
         <v>76.13636363636363</v>
       </c>
       <c r="AN4" t="n">
+        <v>-3.578898649520781</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.4234848484848477</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
         <v>-2.445021645021647</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AS4" t="n">
+        <v>-0.7196608946608762</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>9117255.802554879</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3.408189033189046</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.520562770562748</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>0.4678853967278431</v>
       </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="n">
+      <c r="BA4" t="n">
+        <v>5.111238717999683</v>
+      </c>
+      <c r="BB4" t="n">
         <v>7717687.590187585</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>1.520562770562748</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>-1.020454848325983</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-0.7196608946608762</v>
-      </c>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="n">
-        <v>5.111238717999683</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="n">
-        <v>0.9069109447269739</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>9117255.802554879</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>3.408189033189046</v>
+        <v>-1.020454848325983</v>
       </c>
       <c r="BE4" t="n">
-        <v>-3.578898649520781</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.4234848484848477</v>
-      </c>
+        <v>0.9069109447269739</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1346,54 +1346,54 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>-0.1666666666666643</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1666666666666643</v>
+      </c>
+      <c r="V5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>1.5</v>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
+        <v>-0.04666666666666663</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4083333333333333</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
         <v>-1</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AE5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>4.833333333333334</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AK5" t="n">
         <v>1.333333333333334</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>7.333333333333334</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.04666666666666663</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.4083333333333333</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-0.1666666666666643</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.1666666666666643</v>
       </c>
       <c r="AL5" t="n">
         <v>76.21363636363637</v>
@@ -1402,48 +1402,48 @@
         <v>79.17508417508417</v>
       </c>
       <c r="AN5" t="n">
+        <v>2.585834908052345</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.9612304866850319</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
         <v>1.668374655647387</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AS5" t="n">
+        <v>1.007456382001806</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="n">
+        <v>-34725580.90765035</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>-6.887860422405865</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-5.735684113865929</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>-0.5270262005616082</v>
       </c>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
+      <c r="BA5" t="n">
+        <v>-7.119658062273857</v>
+      </c>
+      <c r="BB5" t="n">
         <v>-52072438.01652893</v>
       </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-5.735684113865929</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1.815677715707238</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.007456382001806</v>
-      </c>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="n">
-        <v>-7.119658062273857</v>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="n">
-        <v>-5.949425257885082</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-34725580.90765035</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="n">
-        <v>-6.887860422405865</v>
+        <v>1.815677715707238</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.585834908052345</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-0.9612304866850319</v>
-      </c>
+        <v>-5.949425257885082</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1527,54 +1527,54 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>-4.583333333333336</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4.583333333333336</v>
+      </c>
+      <c r="V6" t="n">
         <v>-0.4166666666666667</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3358333333333333</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.219166666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-3.833333333333334</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>-5.75</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AK6" t="n">
         <v>-4.083333333333334</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.083333333333333</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.5833333333333333</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-3.833333333333334</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.666666666666666</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.3358333333333333</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.219166666666667</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-4.583333333333336</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>4.583333333333336</v>
       </c>
       <c r="AL6" t="n">
         <v>77.56969696969696</v>
@@ -1583,48 +1583,48 @@
         <v>74.68888888888888</v>
       </c>
       <c r="AN6" t="n">
+        <v>0.0278985652925634</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.04132231404958664</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
         <v>0.4973247627793072</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AS6" t="n">
+        <v>4.826342209978577</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>4754117.417338846</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2.860055096418733</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3.530468319559219</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>0.136595052694124</v>
       </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
+      <c r="BA6" t="n">
+        <v>2.199693543321217</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6870490.970309153</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="n">
-        <v>3.530468319559219</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.6970477622664646</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>4.826342209978577</v>
-      </c>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="n">
-        <v>2.199693543321217</v>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="n">
-        <v>3.011981753059956</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4754117.417338846</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="n">
-        <v>2.860055096418733</v>
+        <v>0.6970477622664646</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0278985652925634</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.04132231404958664</v>
-      </c>
+        <v>3.011981753059956</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1708,54 +1708,54 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="V7" t="n">
         <v>0.5</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>-1</v>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.9266666666666666</v>
       </c>
       <c r="Y7" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-11.16666666666667</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.333333333333334</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AK7" t="n">
         <v>-3.166666666666666</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>-11.16666666666667</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.9266666666666666</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-1.5</v>
       </c>
       <c r="AL7" t="n">
         <v>76.55555555555554</v>
@@ -1764,48 +1764,48 @@
         <v>84.70151515151515</v>
       </c>
       <c r="AN7" t="n">
+        <v>0.1886910046823935</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.1436868686868689</v>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
         <v>-1.373484848484846</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AS7" t="n">
+        <v>2.202525252525248</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>2240428.597877445</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.6785353535353522</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-1.666792929292924</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>0.05694861168006926</v>
       </c>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="n">
+      <c r="BA7" t="n">
+        <v>0.8169144816237264</v>
+      </c>
+      <c r="BB7" t="n">
         <v>-3325173.611111112</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="n">
-        <v>-1.666792929292924</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.355336533291137</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.202525252525248</v>
-      </c>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="n">
-        <v>0.8169144816237264</v>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="n">
-        <v>2.840177295521215</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2240428.597877445</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="n">
-        <v>-0.6785353535353522</v>
+        <v>4.355336533291137</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.1886910046823935</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>-0.1436868686868689</v>
-      </c>
+        <v>2.840177295521215</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1889,50 +1889,50 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>0.08500000000000008</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0.246666666666667</v>
+      </c>
       <c r="Z8" t="n">
+        <v>1.833333333333334</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>-3</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AK8" t="n">
         <v>5</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.833333333333334</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.08500000000000008</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.246666666666667</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.5</v>
       </c>
       <c r="AL8" t="n">
         <v>84</v>
@@ -1941,48 +1941,48 @@
         <v>77.03030303030302</v>
       </c>
       <c r="AN8" t="n">
+        <v>-2.819158373015039</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.5024793388429749</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
         <v>-0.634297520661157</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AS8" t="n">
+        <v>-1.631818181818176</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="n">
+        <v>-4502556.331911132</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-4.17462809917356</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-5.849338842975214</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>-0.2978447829005839</v>
       </c>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="n">
+      <c r="BA8" t="n">
+        <v>-2.837689123439546</v>
+      </c>
+      <c r="BB8" t="n">
         <v>-9694661.157024793</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="n">
-        <v>-5.849338842975214</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.532534641596499</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>-1.631818181818176</v>
-      </c>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="n">
-        <v>-2.837689123439546</v>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="n">
-        <v>-5.686038533271713</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-4502556.331911132</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="n">
-        <v>-4.17462809917356</v>
+        <v>1.532534641596499</v>
       </c>
       <c r="BE8" t="n">
-        <v>-2.819158373015039</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-0.5024793388429749</v>
-      </c>
+        <v>-5.686038533271713</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -2066,50 +2066,50 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.07166666666666655</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.6383333333333332</v>
+      </c>
       <c r="Z9" t="n">
+        <v>2.166666666666666</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>-1.666666666666666</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AK9" t="n">
         <v>-4.166666666666666</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-2.666666666666667</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>-0.1666666666666666</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.166666666666666</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.07166666666666655</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>-0.6383333333333332</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>-3</v>
       </c>
       <c r="AL9" t="n">
         <v>75.66666666666666</v>
@@ -2118,48 +2118,48 @@
         <v>77.4074074074074</v>
       </c>
       <c r="AN9" t="n">
+        <v>2.506421558606483</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.7395775941230489</v>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
         <v>0.2573002754820948</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AS9" t="n">
+        <v>-0.04141414141420796</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
+        <v>-7851854.423149318</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-3.508172635445362</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-3.926813590449953</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>-0.1998773603723192</v>
       </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="n">
+      <c r="BA9" t="n">
+        <v>-3.064254834921854</v>
+      </c>
+      <c r="BB9" t="n">
         <v>-16440945.82185491</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="n">
-        <v>-3.926813590449953</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>-2.391073777759544</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>-0.04141414141420796</v>
-      </c>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="n">
-        <v>-3.064254834921854</v>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="n">
-        <v>-0.409208156379421</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-7851854.423149318</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
-        <v>-3.508172635445362</v>
+        <v>-2.391073777759544</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.506421558606483</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-0.7395775941230489</v>
-      </c>
+        <v>-0.409208156379421</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2243,54 +2243,54 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-4.666666666666664</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.166666666666667</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
+        <v>-0.2033333333333336</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD10" t="n">
         <v>-1</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AE10" t="n">
         <v>-1.5</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.666666666666667</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>-3</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AK10" t="n">
         <v>-3.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-4.666666666666667</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-0.1666666666666666</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-0.2033333333333336</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-0.916666666666667</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>4.333333333333336</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-4.666666666666664</v>
       </c>
       <c r="AL10" t="n">
         <v>73.04861111111111</v>
@@ -2299,48 +2299,48 @@
         <v>79.27129629629628</v>
       </c>
       <c r="AN10" t="n">
+        <v>1.647532406975973</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.4184343434343432</v>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
         <v>3.041666666666668</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AS10" t="n">
+        <v>2.481144781144764</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>-3467877.904676599</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1003367003366975</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.558164983165</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>0.1033427096103772</v>
       </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="n">
+      <c r="BA10" t="n">
+        <v>-2.523989712439544</v>
+      </c>
+      <c r="BB10" t="n">
         <v>2393632.154882155</v>
       </c>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="n">
-        <v>1.558164983165</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.311080574080734</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.481144781144764</v>
-      </c>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="n">
-        <v>-2.523989712439544</v>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="n">
-        <v>-1.15154313438066</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-3467877.904676599</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
-        <v>-0.1003367003366975</v>
+        <v>3.311080574080734</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.647532406975973</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.4184343434343432</v>
-      </c>
+        <v>-1.15154313438066</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2424,54 +2424,54 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>5.833333333333336</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="V11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>-0.5</v>
       </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.243333333333334</v>
       </c>
       <c r="Y11" t="n">
+        <v>-0.8416666666666666</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.16666666666667</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.666666666666666</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AK11" t="n">
         <v>3.833333333333334</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>10.16666666666667</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.243333333333334</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-0.8416666666666666</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>5.833333333333336</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-5.833333333333336</v>
       </c>
       <c r="AL11" t="n">
         <v>75.51363636363637</v>
@@ -2480,48 +2480,48 @@
         <v>76.44090909090909</v>
       </c>
       <c r="AN11" t="n">
+        <v>1.330697831365406</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.8335418579736757</v>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
         <v>-1.848433195592285</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AS11" t="n">
+        <v>0.8175026782981263</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="n">
+        <v>28644315.15090087</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>6.635158402203857</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.002978650137749</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>0.4396177609799903</v>
       </c>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="n">
+      <c r="BA11" t="n">
+        <v>4.079671563601522</v>
+      </c>
+      <c r="BB11" t="n">
         <v>50299240.70247935</v>
       </c>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
-        <v>8.002978650137749</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.327260581266046</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0.8175026782981263</v>
-      </c>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="n">
-        <v>4.079671563601522</v>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="n">
-        <v>7.977066650025264</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>28644315.15090087</v>
-      </c>
-      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="n">
-        <v>6.635158402203857</v>
+        <v>1.327260581266046</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.330697831365406</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0.8335418579736757</v>
-      </c>
+        <v>7.977066650025264</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
         <v>0</v>
       </c>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -535,84 +535,84 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,92 +625,92 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -808,49 +808,49 @@
       <c r="U2" t="n">
         <v>9.5</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.5</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AB2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>-0.5183333333333331</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AI2" t="n">
         <v>-0.5916666666666666</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AJ2" t="n">
         <v>-1</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AK2" t="n">
         <v>1</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2.333333333333333</v>
       </c>
       <c r="AL2" t="n">
         <v>79.09318181818182</v>
@@ -858,48 +858,48 @@
       <c r="AM2" t="n">
         <v>76.54545454545455</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0.9561994712921837</v>
-      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>-0.3611616161616165</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>-4.100489453830249</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.07133485215646318</v>
+      </c>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
         <v>-0.9009932659932609</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0.9561994712921837</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>-1.269360269360263</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-2.887962962962973</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-2.946957639428859</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-17129304.71380471</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.3611616161616165</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-15032471.45984167</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
         <v>1.140286195286194</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>-15032471.45984167</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-1.269360269360263</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-2.887962962962973</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.07133485215646318</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-2.946957639428859</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-17129304.71380471</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="n">
+      <c r="BC2" t="n">
         <v>0.7296165115315034</v>
       </c>
-      <c r="BE2" t="n">
-        <v>-4.100489453830249</v>
-      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>1</v>
@@ -989,49 +989,49 @@
       <c r="U3" t="n">
         <v>29.66666666666667</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.6666666666666667</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AA3" t="n">
         <v>-0.8333333333333333</v>
       </c>
-      <c r="X3" t="n">
-        <v>-0.5516666666666667</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-0.5766666666666669</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-4.166666666666666</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.333333333333334</v>
-      </c>
       <c r="AB3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AC3" t="n">
         <v>-1.166666666666667</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2.5</v>
+        <v>-1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-1</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-3</v>
+        <v>-0.5516666666666667</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1.166666666666667</v>
+        <v>-0.5766666666666669</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>-4.166666666666666</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>4.333333333333334</v>
       </c>
       <c r="AL3" t="n">
         <v>74.30555555555556</v>
@@ -1039,48 +1039,48 @@
       <c r="AM3" t="n">
         <v>76.88484848484848</v>
       </c>
-      <c r="AN3" t="n">
-        <v>1.891513343109708</v>
-      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>-0.5641624579124578</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>-4.246734762485531</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.3514529974669298</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>1.434911616161614</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.834196127946143</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
+        <v>1.367125803489436</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>2.042807944549427</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>-4.130670339761267</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>-3.651331496786028</v>
+      </c>
       <c r="AW3" t="n">
-        <v>-14486552.70163953</v>
+        <v>-3.873556384276185</v>
       </c>
       <c r="AX3" t="n">
-        <v>-4.127882996633005</v>
+        <v>-19684692.37832875</v>
       </c>
       <c r="AY3" t="n">
-        <v>-3.608627946127939</v>
+        <v>-0.5510560146923782</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.367619793132564</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-3.959850928010752</v>
-      </c>
+        <v>-13826652.53401999</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>-19809116.16161617</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>-0.4466180072507768</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-4.411779592884471</v>
-      </c>
+        <v>0.633516988062496</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-0.2640791484057843</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1170,49 +1170,49 @@
       <c r="U4" t="n">
         <v>-14</v>
       </c>
-      <c r="V4" t="n">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-3.833333333333334</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-0.1666666666666661</v>
+      </c>
+      <c r="Z4" t="n">
         <v>0.5</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AA4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AB4" t="n">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH4" t="n">
         <v>-0.08666666666666689</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AI4" t="n">
         <v>0.02333333333333343</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AJ4" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AK4" t="n">
         <v>3.833333333333334</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-3.833333333333334</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-0.1666666666666661</v>
       </c>
       <c r="AL4" t="n">
         <v>79.92727272727274</v>
@@ -1220,48 +1220,48 @@
       <c r="AM4" t="n">
         <v>76.13636363636363</v>
       </c>
-      <c r="AN4" t="n">
-        <v>-3.578898649520781</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>0.4234848484848477</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>0.8923741410345514</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.447302868339321</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>-2.445021645021647</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>-0.7196608946608762</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
+        <v>-2.317376562831107</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>-3.518690613447909</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.320039556403202</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.501758847213395</v>
+      </c>
       <c r="AW4" t="n">
-        <v>9117255.802554879</v>
+        <v>4.994443970670829</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.408189033189046</v>
+        <v>7332867.839231472</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.520562770562748</v>
+        <v>0.4229285865649497</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.4678853967278431</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.111238717999683</v>
-      </c>
+        <v>8992198.521931197</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>7717687.590187585</v>
-      </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>-1.020454848325983</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.9069109447269739</v>
-      </c>
+        <v>-0.631058840149791</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-1.078183194026025</v>
+      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1351,49 +1351,49 @@
       <c r="U5" t="n">
         <v>0.1666666666666643</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>4.833333333333334</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AA5" t="n">
         <v>1.5</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AB5" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH5" t="n">
         <v>-0.04666666666666663</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AI5" t="n">
         <v>0.4083333333333333</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AJ5" t="n">
         <v>7.333333333333334</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AK5" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4.833333333333334</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.333333333333334</v>
       </c>
       <c r="AL5" t="n">
         <v>76.21363636363637</v>
@@ -1401,48 +1401,48 @@
       <c r="AM5" t="n">
         <v>79.17508417508417</v>
       </c>
-      <c r="AN5" t="n">
-        <v>2.585834908052345</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>-0.9612304866850319</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>-6.059816536986247</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.526263666898005</v>
+      </c>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>1.668374655647387</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.007456382001806</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
+        <v>1.718787878787882</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>2.35667932433126</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-6.89434343434344</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-5.745858585858585</v>
+      </c>
       <c r="AW5" t="n">
-        <v>-34725580.90765035</v>
+        <v>-7.090902265189186</v>
       </c>
       <c r="AX5" t="n">
-        <v>-6.887860422405865</v>
+        <v>-52132212.12121212</v>
       </c>
       <c r="AY5" t="n">
-        <v>-5.735684113865929</v>
+        <v>-0.9574747474747469</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.5270262005616082</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-7.119658062273857</v>
-      </c>
+        <v>-34450128.72443547</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>-52072438.01652893</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>1.815677715707238</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-5.949425257885082</v>
-      </c>
+        <v>1.016868686868662</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.735629535278036</v>
+      </c>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1532,49 +1532,49 @@
       <c r="U6" t="n">
         <v>4.583333333333336</v>
       </c>
-      <c r="V6" t="n">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-5.75</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-4.083333333333334</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.4166666666666667</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AA6" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AB6" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0.3358333333333333</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AI6" t="n">
         <v>1.219166666666667</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AJ6" t="n">
         <v>-3.833333333333334</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AK6" t="n">
         <v>3.666666666666666</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.5833333333333333</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>3.083333333333333</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>-4.083333333333334</v>
       </c>
       <c r="AL6" t="n">
         <v>77.56969696969696</v>
@@ -1582,48 +1582,48 @@
       <c r="AM6" t="n">
         <v>74.68888888888888</v>
       </c>
-      <c r="AN6" t="n">
-        <v>0.0278985652925634</v>
-      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
-        <v>0.04132231404958664</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
+        <v>3.092055875814026</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.136595052694124</v>
+      </c>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
-        <v>0.4973247627793072</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.826342209978577</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+        <v>0.4513314967860396</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0.06584250439653161</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.907529843893485</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3.521435130526044</v>
+      </c>
       <c r="AW6" t="n">
-        <v>4754117.417338846</v>
+        <v>2.202306889054753</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.860055096418733</v>
+        <v>6881653.54847173</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.530468319559219</v>
+        <v>0.04132231404958664</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.136595052694124</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.199693543321217</v>
-      </c>
+        <v>4777020.232439416</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>6870490.970309153</v>
-      </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>0.6970477622664646</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.011981753059956</v>
-      </c>
+        <v>4.73366784730419</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.6812337721996755</v>
+      </c>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1713,49 +1713,49 @@
       <c r="U7" t="n">
         <v>-1.5</v>
       </c>
-      <c r="V7" t="n">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3.166666666666666</v>
+      </c>
+      <c r="Z7" t="n">
         <v>0.5</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AA7" t="n">
         <v>-1</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AB7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0.9266666666666666</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AI7" t="n">
         <v>-1.28</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AJ7" t="n">
         <v>12</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AK7" t="n">
         <v>-11.16666666666667</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.333333333333334</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>-3.166666666666666</v>
       </c>
       <c r="AL7" t="n">
         <v>76.55555555555554</v>
@@ -1763,48 +1763,48 @@
       <c r="AM7" t="n">
         <v>84.70151515151515</v>
       </c>
-      <c r="AN7" t="n">
-        <v>0.1886910046823935</v>
-      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
-        <v>-0.1436868686868689</v>
-      </c>
-      <c r="AP7" t="inlineStr"/>
+        <v>2.551432944454518</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.03531281094240724</v>
+      </c>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="n">
-        <v>-1.373484848484846</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.202525252525248</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
+        <v>-1.40166666666666</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0.1217762720194848</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0.6594444444444463</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-1.708611111111111</v>
+      </c>
       <c r="AW7" t="n">
-        <v>2240428.597877445</v>
+        <v>0.7687841189391094</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.6785353535353522</v>
+        <v>-3442173.611111112</v>
       </c>
       <c r="AY7" t="n">
-        <v>-1.666792929292924</v>
+        <v>-0.1627777777777779</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.05694861168006926</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0.8169144816237264</v>
-      </c>
+        <v>1888823.633241331</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>-3325173.611111112</v>
-      </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>4.355336533291137</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.840177295521215</v>
-      </c>
+        <v>2.098888888888894</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.631822247063582</v>
+      </c>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1894,45 +1894,45 @@
       <c r="U8" t="n">
         <v>0.5</v>
       </c>
-      <c r="V8" t="n">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AA8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="X8" t="n">
-        <v>0.08500000000000008</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>-0.246666666666667</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.833333333333334</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="AB8" t="n">
+        <v>-0.833333333333333</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AD8" t="n">
         <v>-0.3333333333333333</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>-0.833333333333333</v>
+        <v>0.08500000000000008</v>
       </c>
       <c r="AI8" t="n">
-        <v>-1.166666666666667</v>
+        <v>-0.246666666666667</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-3</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>-0.5</v>
       </c>
       <c r="AL8" t="n">
         <v>84</v>
@@ -1940,48 +1940,48 @@
       <c r="AM8" t="n">
         <v>77.03030303030302</v>
       </c>
-      <c r="AN8" t="n">
-        <v>-2.819158373015039</v>
-      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
-        <v>-0.5024793388429749</v>
-      </c>
-      <c r="AP8" t="inlineStr"/>
+        <v>-5.533637670702873</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.2942430178043989</v>
+      </c>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
-        <v>-0.634297520661157</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>-1.631818181818176</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
+        <v>-0.6651515151515142</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>-2.615349285080747</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-4.11727272727272</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-5.865656565656579</v>
+      </c>
       <c r="AW8" t="n">
-        <v>-4502556.331911132</v>
+        <v>-2.930371366816374</v>
       </c>
       <c r="AX8" t="n">
-        <v>-4.17462809917356</v>
+        <v>-9659737.373737372</v>
       </c>
       <c r="AY8" t="n">
-        <v>-5.849338842975214</v>
+        <v>-0.4981818181818181</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.2978447829005839</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-2.837689123439546</v>
-      </c>
+        <v>-4571138.972233602</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-9694661.157024793</v>
-      </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>1.532534641596499</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-5.686038533271713</v>
-      </c>
+        <v>-1.536868686868672</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1.553277178679991</v>
+      </c>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2071,45 +2071,45 @@
       <c r="U9" t="n">
         <v>-3</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>-1.666666666666666</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.07166666666666655</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>-0.6383333333333332</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.166666666666666</v>
-      </c>
       <c r="AA9" t="n">
-        <v>-2.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AD9" t="n">
         <v>-0.1666666666666666</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>0.07166666666666655</v>
       </c>
       <c r="AI9" t="n">
-        <v>-2.666666666666667</v>
+        <v>-0.6383333333333332</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-1.666666666666666</v>
+        <v>2.166666666666666</v>
       </c>
       <c r="AK9" t="n">
-        <v>-4.166666666666666</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AL9" t="n">
         <v>75.66666666666666</v>
@@ -2117,48 +2117,48 @@
       <c r="AM9" t="n">
         <v>77.4074074074074</v>
       </c>
-      <c r="AN9" t="n">
-        <v>2.506421558606483</v>
-      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="n">
-        <v>-0.7395775941230489</v>
-      </c>
-      <c r="AP9" t="inlineStr"/>
+        <v>-0.4998184130111412</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.2347719287076873</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
       <c r="AR9" t="n">
-        <v>0.2573002754820948</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>-0.04141414141420796</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
+        <v>0.2030303030302996</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>2.393088559187628</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-3.358989898989904</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-3.829494949494944</v>
+      </c>
       <c r="AW9" t="n">
-        <v>-7851854.423149318</v>
+        <v>-3.030618206612814</v>
       </c>
       <c r="AX9" t="n">
-        <v>-3.508172635445362</v>
+        <v>-15873040.4040404</v>
       </c>
       <c r="AY9" t="n">
-        <v>-3.926813590449953</v>
+        <v>-0.7135353535353537</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.1998773603723192</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>-3.064254834921854</v>
-      </c>
+        <v>-8154796.076644374</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-16440945.82185491</v>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>-2.391073777759544</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-0.409208156379421</v>
-      </c>
+        <v>-0.1355555555555839</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2.341361279759127</v>
+      </c>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2248,49 +2248,49 @@
       <c r="U10" t="n">
         <v>-4.666666666666664</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.166666666666667</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AA10" t="n">
         <v>-0.8333333333333335</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AB10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-4.666666666666667</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH10" t="n">
         <v>-0.2033333333333336</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AI10" t="n">
         <v>-0.916666666666667</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AJ10" t="n">
         <v>-2.666666666666666</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AK10" t="n">
         <v>-6.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>-0.1666666666666666</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>-4.666666666666667</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>-3.5</v>
       </c>
       <c r="AL10" t="n">
         <v>73.04861111111111</v>
@@ -2298,48 +2298,48 @@
       <c r="AM10" t="n">
         <v>79.27129629629628</v>
       </c>
-      <c r="AN10" t="n">
-        <v>1.647532406975973</v>
-      </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
-        <v>0.4184343434343432</v>
-      </c>
-      <c r="AP10" t="inlineStr"/>
+        <v>-1.174410692051623</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.08546477412041131</v>
+      </c>
       <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
-        <v>3.041666666666668</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.481144781144764</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
+        <v>3.155371900826445</v>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>1.44680302983237</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.1507805325987164</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.570064279155204</v>
+      </c>
       <c r="AW10" t="n">
-        <v>-3467877.904676599</v>
+        <v>-2.46606958528757</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1003367003366975</v>
+        <v>2349334.251606982</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.558164983165</v>
+        <v>0.4341597796143246</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1033427096103772</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>-2.523989712439544</v>
-      </c>
+        <v>-3351902.158637099</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>2393632.154882155</v>
-      </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>3.311080574080734</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-1.15154313438066</v>
-      </c>
+        <v>2.376124885215802</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.612592949502215</v>
+      </c>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2429,49 +2429,49 @@
       <c r="U11" t="n">
         <v>-5.833333333333336</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AA11" t="n">
         <v>-0.5</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AB11" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.243333333333334</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AI11" t="n">
         <v>-0.8416666666666666</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AJ11" t="n">
         <v>10.16666666666667</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AK11" t="n">
         <v>-6.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.666666666666666</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>3.833333333333334</v>
       </c>
       <c r="AL11" t="n">
         <v>75.51363636363637</v>
@@ -2479,48 +2479,48 @@
       <c r="AM11" t="n">
         <v>76.44090909090909</v>
       </c>
-      <c r="AN11" t="n">
-        <v>1.330697831365406</v>
-      </c>
+      <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="n">
-        <v>0.8335418579736757</v>
-      </c>
-      <c r="AP11" t="inlineStr"/>
+        <v>7.977066650025264</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.4396177609799903</v>
+      </c>
       <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
         <v>-1.848433195592285</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>1.330697831365406</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.635158402203857</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8.002978650137749</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.079671563601522</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>50299240.70247935</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.8335418579736757</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>28644315.15090087</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
         <v>0.8175026782981263</v>
       </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>28644315.15090087</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.635158402203857</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8.002978650137749</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.4396177609799903</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.079671563601522</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>50299240.70247935</v>
-      </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
+      <c r="BC11" t="n">
         <v>1.327260581266046</v>
       </c>
-      <c r="BE11" t="n">
-        <v>7.977066650025264</v>
-      </c>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
         <v>0</v>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,161 +779,161 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>-6</v>
       </c>
       <c r="P2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R2" t="n">
         <v>-1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>13</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-23</v>
+      </c>
+      <c r="W2" t="n">
+        <v>23</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-9.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-1.166666666666667</v>
+        <v>-0.6400000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.5</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3333333333333333</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5183333333333331</v>
+        <v>-4</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.5916666666666666</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="AL2" t="n">
-        <v>79.09318181818182</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>76.54545454545455</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>-4.100489453830249</v>
-      </c>
+        <v>77.125</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.1744463335920443</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="n">
-        <v>0.07133485215646318</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
+        <v>-4.322610722610733</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-2.242265525016421</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-0.9009932659932609</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
+        <v>-3.214063714063712</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.5476301476301477</v>
+      </c>
       <c r="AT2" t="n">
-        <v>0.9561994712921837</v>
+        <v>-0.3759591524199866</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.269360269360263</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-2.887962962962973</v>
-      </c>
+        <v>1.006449106449104</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>-2.946957639428859</v>
+        <v>0.4253378188247545</v>
       </c>
       <c r="AX2" t="n">
-        <v>-17129304.71380471</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.3611616161616165</v>
-      </c>
+        <v>-0.3697696641097536</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>-15032471.45984167</v>
+        <v>-12997257.18725719</v>
       </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>1.140286195286194</v>
+        <v>-2.043045843045803</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.7296165115315034</v>
+        <v>-6493375.233911039</v>
       </c>
       <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>Wplk7SgS</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">bell j 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,124 +960,124 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>pSZhI8SM</t>
         </is>
       </c>
       <c r="O3" t="n">
+        <v>12</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U3" t="n">
         <v>-1</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-29.66666666666667</v>
-      </c>
-      <c r="U3" t="n">
-        <v>29.66666666666667</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-13</v>
+      </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-0.8333333333333333</v>
-      </c>
+        <v>-0.5</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-1</v>
+        <v>1.47</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.166666666666667</v>
+        <v>-1.51</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1</v>
+        <v>-10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.5516666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.5766666666666669</v>
+        <v>-2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-4.166666666666666</v>
+        <v>-6</v>
       </c>
       <c r="AK3" t="n">
-        <v>4.333333333333334</v>
+        <v>3.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>74.30555555555556</v>
+        <v>84</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.88484848484848</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
-        <v>-4.246734762485531</v>
-      </c>
+        <v>82.02083333333334</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.9668604956424645</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>-0.3514529974669298</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
+        <v>2.777961432506899</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.774518578182281</v>
+      </c>
       <c r="AR3" t="n">
-        <v>1.367125803489436</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>3.230945821854903</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0.5265381083562906</v>
+      </c>
       <c r="AT3" t="n">
-        <v>2.042807944549427</v>
+        <v>0.3064421487151665</v>
       </c>
       <c r="AU3" t="n">
-        <v>-4.130670339761267</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-3.651331496786028</v>
-      </c>
+        <v>-1.151147842056933</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-3.873556384276185</v>
+        <v>-1.821037194547426</v>
       </c>
       <c r="AX3" t="n">
-        <v>-19684692.37832875</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-0.5510560146923782</v>
-      </c>
+        <v>-2.813475361310992</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>-13826652.53401999</v>
+        <v>14578934.80257116</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>0.633516988062496</v>
+        <v>-0.849219467401241</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.2640791484057843</v>
+        <v>6979185.715384007</v>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
@@ -1089,32 +1089,32 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>tzSnG5Wr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">howard p 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,124 +1141,124 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>hxNijWrJ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH4" t="n">
         <v>3</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="n">
-        <v>-3.833333333333334</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.1666666666666661</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3.166666666666667</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.08666666666666689</v>
-      </c>
       <c r="AI4" t="n">
-        <v>0.02333333333333343</v>
+        <v>-2.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3.5</v>
+        <v>-2</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.833333333333334</v>
+        <v>-0.25</v>
       </c>
       <c r="AL4" t="n">
-        <v>79.92727272727274</v>
+        <v>78.19873737373739</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.13636363636363</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="n">
-        <v>0.8923741410345514</v>
-      </c>
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.664594378768101</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>0.447302868339321</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
+        <v>8.309480519480502</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.799782893880121</v>
+      </c>
       <c r="AR4" t="n">
-        <v>-2.317376562831107</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>8.23298701298701</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.029220779220779</v>
+      </c>
       <c r="AT4" t="n">
-        <v>-3.518690613447909</v>
+        <v>1.143728713661458</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.320039556403202</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.501758847213395</v>
-      </c>
+        <v>0.08220779220779306</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>4.994443970670829</v>
+        <v>0.560696844787433</v>
       </c>
       <c r="AX4" t="n">
-        <v>7332867.839231472</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.4229285865649497</v>
-      </c>
+        <v>-1.151832778392532</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>8992198.521931197</v>
+        <v>58806759.74025975</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>-0.631058840149791</v>
+        <v>-2.677532467532444</v>
       </c>
       <c r="BC4" t="n">
-        <v>-1.078183194026025</v>
+        <v>37397308.9579081</v>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
@@ -1270,32 +1270,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>INsZAAf3</t>
+          <t>beYTapn2</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">allison s 
+          <t xml:space="preserve">smith l 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
+          <t xml:space="preserve">selhurst park
   london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1327,119 +1327,119 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>2L1wFbM5</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-24</v>
+        <v>-1</v>
       </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.666666666666664</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-6.666666666666664</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3849999999999999</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-6.666666666666666</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-3.333333333333333</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-2.333333333333334</v>
+      </c>
+      <c r="AK5" t="n">
         <v>-4</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.1666666666666643</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1666666666666643</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="n">
-        <v>4.833333333333334</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.333333333333334</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-0.6666666666666665</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.04666666666666663</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.4083333333333333</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7.333333333333334</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AL5" t="n">
-        <v>76.21363636363637</v>
+        <v>78.70202020202021</v>
       </c>
       <c r="AM5" t="n">
-        <v>79.17508417508417</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>-6.059816536986247</v>
-      </c>
+        <v>76.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.5220611228334207</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>-0.526263666898005</v>
-      </c>
-      <c r="AQ5" t="inlineStr"/>
+        <v>2.135941230486679</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1634408035803006</v>
+      </c>
       <c r="AR5" t="n">
-        <v>1.718787878787882</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>1.054517906336088</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.1033241505968776</v>
+      </c>
       <c r="AT5" t="n">
-        <v>2.35667932433126</v>
+        <v>-0.2239645838225726</v>
       </c>
       <c r="AU5" t="n">
-        <v>-6.89434343434344</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>-5.745858585858585</v>
-      </c>
+        <v>-0.9206611570247922</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-7.090902265189186</v>
+        <v>1.034667874638927</v>
       </c>
       <c r="AX5" t="n">
-        <v>-52132212.12121212</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-0.9574747474747469</v>
-      </c>
+        <v>3.312877081246484</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>-34450128.72443547</v>
+        <v>5346485.996326908</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>1.016868686868662</v>
+        <v>1.150835629017479</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.735629535278036</v>
+        <v>2220487.435608561</v>
       </c>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
@@ -1451,32 +1451,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8QPOfb45</t>
+          <t>2TvL16Hk</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrott s 
+          <t xml:space="preserve">linington j 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brentford community stadium
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,124 +1503,120 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
-      </c>
-      <c r="P6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1.833333333333336</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.833333333333336</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-4.583333333333336</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4.583333333333336</v>
-      </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="n">
-        <v>-5.75</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>-4.083333333333334</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.4166666666666667</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.583333333333333</v>
-      </c>
       <c r="AC6" t="n">
-        <v>3.083333333333333</v>
+        <v>-2</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.5833333333333333</v>
+        <v>1.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.166666666666667</v>
+        <v>-1.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3358333333333333</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.219166666666667</v>
+        <v>0.1666666666666665</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-3.833333333333334</v>
+        <v>-2.833333333333334</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.666666666666666</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="AL6" t="n">
-        <v>77.56969696969696</v>
+        <v>81.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>74.68888888888888</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>3.092055875814026</v>
-      </c>
+        <v>84.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3.274310931726532</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="n">
-        <v>0.136595052694124</v>
-      </c>
-      <c r="AQ6" t="inlineStr"/>
+        <v>5.033103764921947</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6.603833815296909</v>
+      </c>
       <c r="AR6" t="n">
-        <v>0.4513314967860396</v>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+        <v>4.044237832874202</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.3891873278236915</v>
+      </c>
       <c r="AT6" t="n">
-        <v>0.06584250439653161</v>
+        <v>0.3253143907749172</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.907529843893485</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3.521435130526044</v>
-      </c>
+        <v>-0.1338613406795233</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>2.202306889054753</v>
+        <v>-2.04845666056335</v>
       </c>
       <c r="AX6" t="n">
-        <v>6881653.54847173</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0.04132231404958664</v>
-      </c>
+        <v>-5.217530792423503</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="n">
-        <v>4777020.232439416</v>
+        <v>5982439.164370982</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="n">
-        <v>4.73366784730419</v>
+        <v>-0.9179292929292728</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.6812337721996755</v>
+        <v>5783473.359714064</v>
       </c>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
@@ -1632,32 +1628,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2Fanm72d</t>
+          <t>AiyHLR8L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">england d 
+          <t xml:space="preserve">allison s 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1684,124 +1680,124 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-31</v>
+      </c>
       <c r="X7" t="n">
-        <v>2.333333333333334</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-3.166666666666666</v>
-      </c>
-      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.09500000000000008</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-5.666666666666666</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.9266666666666666</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>-1.28</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>-11.16666666666667</v>
+        <v>-4</v>
       </c>
       <c r="AL7" t="n">
-        <v>76.55555555555554</v>
+        <v>76.96969696969697</v>
       </c>
       <c r="AM7" t="n">
-        <v>84.70151515151515</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="n">
-        <v>2.551432944454518</v>
-      </c>
+        <v>73.00555555555556</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>4.408840245376282</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="n">
-        <v>0.03531281094240724</v>
-      </c>
-      <c r="AQ7" t="inlineStr"/>
+        <v>7.007897153351692</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4.864877621425123</v>
+      </c>
       <c r="AR7" t="n">
-        <v>-1.40166666666666</v>
-      </c>
-      <c r="AS7" t="inlineStr"/>
+        <v>8.243526170798901</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.404958677685951</v>
+      </c>
       <c r="AT7" t="n">
-        <v>0.1217762720194848</v>
+        <v>0.4510077689282497</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.6594444444444463</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>-1.708611111111111</v>
-      </c>
+        <v>0.7445362718089967</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>0.7687841189391094</v>
+        <v>-1.167344931003402</v>
       </c>
       <c r="AX7" t="n">
-        <v>-3442173.611111112</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-0.1627777777777779</v>
-      </c>
+        <v>-1.920630764163377</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="n">
-        <v>1888823.633241331</v>
+        <v>40534573.00275481</v>
       </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>2.098888888888894</v>
+        <v>-1.39972451790635</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.631822247063582</v>
+        <v>23498404.12543216</v>
       </c>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
@@ -1813,32 +1809,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SUdkBJln</t>
+          <t>jkLFNmv9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45549.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1865,120 +1861,124 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>Uu6L6Igl</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y8" t="n">
         <v>-1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.03000000000000014</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-1.315</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>-0.5</v>
       </c>
-      <c r="U8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>-0.833333333333333</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-1.166666666666667</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>0.08500000000000008</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>-0.246666666666667</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.833333333333334</v>
-      </c>
       <c r="AK8" t="n">
-        <v>-0.5</v>
+        <v>7</v>
       </c>
       <c r="AL8" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AM8" t="n">
-        <v>77.03030303030302</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="n">
-        <v>-5.533637670702873</v>
-      </c>
+        <v>81.17272727272727</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.3854778927381375</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="n">
-        <v>-0.2942430178043989</v>
-      </c>
-      <c r="AQ8" t="inlineStr"/>
+        <v>-1.831868686868688</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-1.998515000203</v>
+      </c>
       <c r="AR8" t="n">
-        <v>-0.6651515151515142</v>
-      </c>
-      <c r="AS8" t="inlineStr"/>
+        <v>-2.514217171717178</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0.6349494949494945</v>
+      </c>
       <c r="AT8" t="n">
-        <v>-2.615349285080747</v>
+        <v>-0.5095074419754726</v>
       </c>
       <c r="AU8" t="n">
-        <v>-4.11727272727272</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-5.865656565656579</v>
-      </c>
+        <v>-1.007954545454549</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>-2.930371366816374</v>
+        <v>0.3484155078368651</v>
       </c>
       <c r="AX8" t="n">
-        <v>-9659737.373737372</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-0.4981818181818181</v>
-      </c>
+        <v>1.110515840723679</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="n">
-        <v>-4571138.972233602</v>
+        <v>-7181712.121212123</v>
       </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>-1.536868686868672</v>
+        <v>1.267601010101004</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.553277178679991</v>
+        <v>-4936184.098936018</v>
       </c>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
@@ -1990,32 +1990,32 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>lpob9cJb</t>
+          <t>2kGeEq1e</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45549.35416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2042,22 +2042,22 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>OEy2L7Zo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>-29</v>
       </c>
       <c r="P9" t="n">
         <v>-1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="R9" t="n">
         <v>-1</v>
@@ -2066,96 +2066,100 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>-0.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-24.5</v>
+      </c>
       <c r="X9" t="n">
-        <v>-1.666666666666666</v>
+        <v>-1.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>-4.166666666666666</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.1666666666666666</v>
+        <v>-0.4450000000000001</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+        <v>-0.1674999999999998</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
       <c r="AH9" t="n">
-        <v>0.07166666666666655</v>
+        <v>-1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.6383333333333332</v>
+        <v>2.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.166666666666666</v>
+        <v>3.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>-2.666666666666666</v>
+        <v>3.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>75.66666666666666</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="AM9" t="n">
-        <v>77.4074074074074</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="n">
-        <v>-0.4998184130111412</v>
-      </c>
+        <v>78.76565656565657</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-4.730099787457306</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="n">
-        <v>-0.2347719287076873</v>
-      </c>
-      <c r="AQ9" t="inlineStr"/>
+        <v>-8.370485070485088</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-5.429286281757058</v>
+      </c>
       <c r="AR9" t="n">
-        <v>0.2030303030302996</v>
-      </c>
-      <c r="AS9" t="inlineStr"/>
+        <v>-7.29951159951159</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-1.324891774891775</v>
+      </c>
       <c r="AT9" t="n">
-        <v>2.393088559187628</v>
+        <v>-0.8225451093075318</v>
       </c>
       <c r="AU9" t="n">
-        <v>-3.358989898989904</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-3.829494949494944</v>
-      </c>
+        <v>0.5665168165168168</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-3.030618206612814</v>
+        <v>0.2266046088547959</v>
       </c>
       <c r="AX9" t="n">
-        <v>-15873040.4040404</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-0.7135353535353537</v>
-      </c>
+        <v>-5.177602045176059</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="n">
-        <v>-8154796.076644374</v>
+        <v>-27048782.05128205</v>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>-0.1355555555555839</v>
+        <v>-4.560350760350758</v>
       </c>
       <c r="BC9" t="n">
-        <v>-2.341361279759127</v>
+        <v>-14889880.18397031</v>
       </c>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
@@ -2167,32 +2171,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x6HuiG3U</t>
+          <t>z1q67ylB</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.45833333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
-  liverpool </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2219,161 +2223,169 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P10" t="n">
         <v>-1</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.333333333333336</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.666666666666664</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+        <v>-0.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9.5</v>
+      </c>
       <c r="X10" t="n">
-        <v>-3</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>-0.8333333333333335</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.1666666666666666</v>
+        <v>-0.5183333333333331</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.5</v>
+        <v>-0.5916666666666666</v>
       </c>
       <c r="AF10" t="n">
         <v>-1</v>
       </c>
       <c r="AG10" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.2033333333333336</v>
+        <v>-1</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.916666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-2.666666666666666</v>
+        <v>-5.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>-6.5</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="AL10" t="n">
-        <v>73.04861111111111</v>
+        <v>79.09318181818182</v>
       </c>
       <c r="AM10" t="n">
-        <v>79.27129629629628</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="n">
-        <v>-1.174410692051623</v>
-      </c>
+        <v>76.54545454545455</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-4.62252177601556</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="n">
-        <v>0.08546477412041131</v>
-      </c>
-      <c r="AQ10" t="inlineStr"/>
+        <v>-1.350465695920221</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-3.10781636410519</v>
+      </c>
       <c r="AR10" t="n">
-        <v>3.155371900826445</v>
-      </c>
-      <c r="AS10" t="inlineStr"/>
+        <v>-3.055358782631529</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.3800669027941761</v>
+      </c>
       <c r="AT10" t="n">
-        <v>1.44680302983237</v>
+        <v>0.004335420445668925</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.1507805325987164</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.570064279155204</v>
-      </c>
+        <v>-0.9313328086055321</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>-2.46606958528757</v>
+        <v>0.6799099063462428</v>
       </c>
       <c r="AX10" t="n">
-        <v>2349334.251606982</v>
+        <v>0.7245517939617514</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.4341597796143246</v>
+        <v>416</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-3351902.158637099</v>
-      </c>
-      <c r="BA10" t="inlineStr"/>
+        <v>-17949699.26538108</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>396</v>
+      </c>
       <c r="BB10" t="n">
-        <v>2.376124885215802</v>
+        <v>1.065669683851496</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.612592949502215</v>
+        <v>-16104178.08446729</v>
       </c>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>120500000</v>
+      </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ERWFdKZh</t>
+          <t>tvOWhxZH</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.35416666666</v>
+        <v>45536.39583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2400,129 +2412,1667 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>thRJMAq0</t>
         </is>
       </c>
       <c r="O11" t="n">
+        <v>22</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>14</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-14</v>
+      </c>
+      <c r="X11" t="n">
         <v>2</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5.833333333333336</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-5.833333333333336</v>
-      </c>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="n">
-        <v>1.666666666666666</v>
-      </c>
       <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.08666666666666689</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.02333333333333343</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG11" t="n">
         <v>3.833333333333334</v>
       </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-1.666666666666667</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.3333333333333335</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.243333333333334</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.8416666666666666</v>
+        <v>-2.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.16666666666667</v>
+        <v>-3.833333333333334</v>
       </c>
       <c r="AK11" t="n">
-        <v>-6.5</v>
+        <v>-0.1666666666666661</v>
       </c>
       <c r="AL11" t="n">
-        <v>75.51363636363637</v>
+        <v>79.92727272727274</v>
       </c>
       <c r="AM11" t="n">
-        <v>76.44090909090909</v>
-      </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="n">
-        <v>7.977066650025264</v>
-      </c>
+        <v>76.13636363636363</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.4719195955800046</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="n">
-        <v>0.4396177609799903</v>
-      </c>
-      <c r="AQ11" t="inlineStr"/>
+        <v>3.245659391113961</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.768666458709106</v>
+      </c>
       <c r="AR11" t="n">
-        <v>-1.848433195592285</v>
-      </c>
-      <c r="AS11" t="inlineStr"/>
+        <v>1.452172070353882</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.4174189446916716</v>
+      </c>
       <c r="AT11" t="n">
-        <v>1.330697831365406</v>
+        <v>0.453881815707742</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.635158402203857</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.002978650137749</v>
-      </c>
+        <v>-2.239323302959669</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>4.079671563601522</v>
+        <v>-3.530951378998143</v>
       </c>
       <c r="AX11" t="n">
-        <v>50299240.70247935</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.8335418579736757</v>
-      </c>
+        <v>-1.019570753834643</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="n">
-        <v>28644315.15090087</v>
+        <v>7060324.221233308</v>
       </c>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>0.8175026782981263</v>
+        <v>-0.445567563749421</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.327260581266046</v>
+        <v>8570316.045854641</v>
       </c>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>U11vkTXq</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.39583333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-29.66666666666667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>29.66666666666667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0.5516666666666667</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.5766666666666669</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-4.166666666666666</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>74.30555555555556</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>76.88484848484848</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-2.975139441741618</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-3.99724517906337</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-3.203162820151988</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-3.392084481175388</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>-0.5037741046831958</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0.2984586298634289</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.478071625344349</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.176284740371429</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.2276504261992329</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>326</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-18585082.6446281</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>312</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.5763636363636806</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-11157231.53485876</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>INsZAAf3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-24</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.04666666666666663</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.4083333333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>6.000000000000002</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>75.29057239057239</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>79.17508417508417</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-5.342292450819869</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-6.856702741702733</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-6.491312654109549</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-5.657860750360754</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.9515440115440121</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.4786454060162308</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.724837662337666</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.162323948059214</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.568716559815755</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-51316865.80086581</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.9699314574314428</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-33281546.54385157</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SUdkBJln</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>zHJOSLsG</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.08500000000000008</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-0.246666666666667</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>77.03030303030302</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-5.42107033063553</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="n">
+        <v>-3.848838383838384</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-2.970118841563846</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-5.505555555555546</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>-0.4742929292929294</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.2725258460872273</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-0.8161616161616188</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-2.282428409659872</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.182014552417343</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>363</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-8834762.626262626</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>349</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-1.447777777777787</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-4735851.093445722</v>
+      </c>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>10800000</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>x6HuiG3U</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>5.166666666666664</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-5.416666666666664</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.2033333333333336</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.9166666666666661</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-6.916666666666666</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-3.833333333333334</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>73.04861111111111</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>79.23472222222222</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1.045667376543619</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9.333333333333343</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-0.3001836547291248</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-2.514910940011291</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.500367309458227</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.4138659320477502</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.1146314407870781</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.079430670339761</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.763180035179968</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.246884393352445</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2127024.79338843</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>2.715886134067915</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-3107873.08109699</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-18900000</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2Fanm72d</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>YuNX1zGT</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9266666666666666</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10.66666666666667</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-10.66666666666667</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-4.999999999999999</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-3.999999999999999</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>77.60370370370369</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>84.70151515151515</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.202462674528363</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="n">
+        <v>-0.5333333333333314</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.119380948580044</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-1.377777777777794</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0.1277777777777778</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.02237513587237916</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-1.238888888888887</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>-0.4487371606263046</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>5.012989486686735</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>-79</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-2951006.944444446</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-77</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.218055555555566</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1985187.587914111</v>
+      </c>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>lpob9cJb</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10.66666666666666</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-10.66666666666666</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.07166666666666655</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-0.6383333333333332</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>6.666666666666666</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-5.666666666666666</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>75.66666666666666</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>77.4074074074074</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-0.7407275039202261</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.1666666666666572</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-3.536767676767681</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-2.949449375443976</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-4.023939393939386</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>-0.7068686868686871</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.2750316689674275</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0.2252525252525288</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.128802844901919</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-2.356945695343541</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-96</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-16115512.62626262</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-102</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-0.5288888888889289</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>-8168740.881839179</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-64000000</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8QPOfb45</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>MiVxbVgA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.2666666666666668</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-7.933333333333337</v>
+      </c>
+      <c r="W18" t="n">
+        <v>7.933333333333337</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.5333333333333332</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.3358333333333333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.219166666666667</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-3.933333333333334</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.666666666666666</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.2666666666666666</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2.733333333333333</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-3.800000000000001</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-3.533333333333333</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>77.56969696969696</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>74.68888888888888</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.333509743583676</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-7.833333333333343</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.934669774669786</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.213168542021677</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.576192696192706</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.04545454545454541</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0.1108079742754666</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.4434110334110315</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.8333333333333321</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.01147593739560193</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.247990699482955</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>85</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6996878.01087801</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>89</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>4.615011655011671</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4775431.952298503</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>38600000</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ERWFdKZh</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.35416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>COqtASrJ</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.833333333333336</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.243333333333334</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-0.8416666666666666</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10.16666666666667</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>75.51363636363637</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>76.44090909090909</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>8.406853278320185</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="n">
+        <v>6.574724517906333</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.387538723804738</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.433792470156092</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.8709136822773185</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.475197100371249</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.488613406795221</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>1.429206649493199</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.46089474592938</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>249</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>50847510.33057851</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>241</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.093434343434325</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>28712177.40294973</v>
+      </c>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>87500000</v>
+      </c>
+      <c r="BG19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG4"/>
+  <dimension ref="A1:BG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,84 +535,84 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1q67ylB</t>
+          <t>Of1jzRNE</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
+        <v>45550.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,22 +779,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="P2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -805,139 +805,135 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-4</v>
+        <v>0.2000000000000002</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-6</v>
+      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>-6</v>
+        <v>6.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.2</v>
+        <v>74.21666666666667</v>
       </c>
       <c r="AM2" t="n">
-        <v>71.45454545454545</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="AN2" t="n">
-        <v>-3.10781636410519</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.6799099063462428</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-3.055358782631529</v>
-      </c>
+        <v>-0.0274671052631581</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>396</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-17949699.26538108</v>
-      </c>
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>120500000</v>
-      </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>-0.3800669027941761</v>
+        <v>-2.405772703818371</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.004335420445668925</v>
+        <v>-1.143263028895774</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.065669683851496</v>
+        <v>1.735384416924667</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>-10251101.32868937</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.9313328086055321</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>416</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-4.62252177601556</v>
-      </c>
+        <v>-2.916666666666671</v>
+      </c>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>-16104178.08446729</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
+        <v>-4.724999999999994</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-13383333.33333333</v>
+      </c>
       <c r="BD2" t="n">
-        <v>-1.350465695920221</v>
+        <v>0.3583333333333307</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.7245517939617514</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>-2.391666666666666</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-2.31161635706917</v>
+      </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tvOWhxZH</t>
+          <t>AFJ3CNV7</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45550.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
+          <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -964,25 +960,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>thRJMAq0</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>-13</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -990,131 +986,135 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-4</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF3" t="n">
         <v>2</v>
       </c>
-      <c r="X3" t="n">
-        <v>-6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.4400000000000001</v>
-      </c>
       <c r="AG3" t="n">
-        <v>-0.7000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>84.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.27272727272727</v>
+        <v>79.72727272727273</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.768666458709106</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>-3.530951378998143</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.452172070353882</v>
-      </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="n">
-        <v>7060324.221233308</v>
-      </c>
+        <v>-0.1714519140989728</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="n">
+        <v>-0.4537037037037037</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>0.4174189446916716</v>
+        <v>-1.397124661830532</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.453881815707742</v>
+        <v>-1.983097512509275</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.445567563749421</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>-0.6762521247815343</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>-12689359.03421198</v>
+      </c>
       <c r="AY3" t="n">
-        <v>-2.239323302959669</v>
+        <v>-3.083333333333329</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="n">
-        <v>0.4719195955800046</v>
-      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>8570316.045854641</v>
-      </c>
-      <c r="BC3" t="inlineStr"/>
+        <v>1.560185185185162</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-26624537.03703704</v>
+      </c>
       <c r="BD3" t="n">
-        <v>3.245659391113961</v>
+        <v>0.7129629629629619</v>
       </c>
       <c r="BE3" t="n">
-        <v>-1.019570753834643</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>-2.370370370370367</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6.417302604802586</v>
+      </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>U11vkTXq</t>
+          <t>AVat9lPF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.39583333334</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,25 +1141,25 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R4" t="n">
         <v>-1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1167,113 +1167,1366 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>-0.6400000000000001</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>77.125</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0.46784188034188</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>-0.2783459595959594</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>-3.687267471091005</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-5.142879587732537</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.4856083459024667</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-19571278.28054299</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-3.615656565656565</v>
+      </c>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>-3.204356060606102</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-16966256.31313131</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.973358585858584</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-4.951010101010098</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0.1940610859728906</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.05329840116024354</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="n">
+        <v>0.4904040404040404</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>4.209415584415595</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.8149496702128118</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-3.239995658581186</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>4967824.525164163</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.382828282828271</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>0.6017676767676505</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>14896729.7979798</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-1.556565656565656</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3.645454545454541</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-3.995516453575675</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>82</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.1087662337662341</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>0.4668560606060608</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>6.123762469414643</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.002780914737428</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-2.219033502729154</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>5807556.582909844</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2.582512626262641</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>-1.230113636363626</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4738235.479797979</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.086174242424242</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>3.274494949494965</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-4.145863918689997</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4899999999999999</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>79.22222222222223</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.1177318295739349</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="n">
+        <v>-0.07777777777777772</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>-0.4463979551150459</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.500946969696969</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.987129756208706</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1954346.537508545</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.63055555555556</v>
+      </c>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>1.963888888888903</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5716180.555555556</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.9805555555555578</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2.230555555555569</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3.944269053315082</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.4899999999999999</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.9000000000000001</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.6291345358960447</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>-0.7361111111111107</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>-3.874938644759609</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-3.788419279108226</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.4408234357642904</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-9958842.824020255</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-3.759027777777789</v>
+      </c>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>1.51875000000004</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-10496527.77777778</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-1.059027777777779</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-2.779166666666654</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.937609389935147</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>6</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-27</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>76.27272727272727</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>73.11111111111111</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.518089721586575</v>
+      </c>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>4.121731979405027</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3.945587814645293</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.6669789282990095</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>20368790.5225019</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.633333333333326</v>
+      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>0.03333333333333144</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>47936666.66666667</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.566666666666666</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.433333333333323</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-2.60040760869569</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-1.735</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC10" t="n">
         <v>-12</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>76.76111111111112</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.037573099415204</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="n">
+        <v>1.978787878787879</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="n">
+        <v>5.102192982456131</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>7.052046783625727</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>2.612573099415204</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>35040617.69005848</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6.872727272727275</v>
+      </c>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>-3.606060606060566</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>53793750</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.9106060606060637</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.778787878787881</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.276169590643292</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-29</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.9549999999999998</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6150000000000002</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="AA11" t="n">
         <v>12</v>
       </c>
-      <c r="X4" t="n">
-        <v>-51</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AB11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF11" t="n">
         <v>-1</v>
       </c>
-      <c r="AD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AG11" t="n">
         <v>-1</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>73.11111111111111</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
         <v>75</v>
       </c>
-      <c r="AN4" t="n">
-        <v>-3.203162820151988</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>2.176284740371429</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-3.392084481175388</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>313</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>-18585082.6446281</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>-0.5037741046831958</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-0.2984586298634289</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.5763636363636806</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.478071625344349</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>328</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-2.975139441741618</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-11157231.53485876</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-0.1666666666666667</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-3.99724517906337</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.2276504261992329</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG4" t="n">
+      <c r="AM11" t="n">
+        <v>77.24242424242425</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.8457060708898942</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="n">
+        <v>-1.62962962962963</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>-3.257811428767312</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-6.518213812331467</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-1.787228763883174</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-13171656.21429224</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-8.125</v>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>-2.091435185185247</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-32016087.96296296</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.1053240740740691</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-7.979166666666671</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-5.382916266739784</v>
+      </c>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG11"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,94 +525,94 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_interceptions</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_interceptions_against</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goal_attempts</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goal_attempts_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>UwFBuMaf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45557.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,22 +779,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -802,105 +802,105 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-1.083333333333333</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.2000000000000002</v>
+        <v>0.04083333333333328</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6400000000000001</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Y2" t="n">
+        <v>-0.7725</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
       <c r="AA2" t="n">
-        <v>-6</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="AB2" t="n">
-        <v>-15.5</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.5</v>
+        <v>-0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>6.5</v>
+        <v>1.583333333333334</v>
       </c>
       <c r="AE2" t="n">
-        <v>-3.5</v>
+        <v>-6.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AG2" t="n">
-        <v>2</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.5</v>
+        <v>-8.166666666666666</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>1.833333333333334</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5</v>
+        <v>-13</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.21666666666667</v>
+        <v>77.38518939393938</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.33333333333333</v>
+        <v>78.02047558922558</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.0274671052631581</v>
+        <v>2.372996728335579</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>-0.1499999999999999</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>10229076.39488602</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-1699431.81818182</v>
+      </c>
       <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AT2" t="n">
+        <v>0.3574092680550478</v>
+      </c>
       <c r="AU2" t="n">
-        <v>-2.405772703818371</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-1.143263028895774</v>
-      </c>
+        <v>-1.439393939393938</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>1.735384416924667</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-10251101.32868937</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-2.916666666666671</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
+        <v>0.4507575757575757</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>0.7424242424242422</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.9772727272727337</v>
+      </c>
       <c r="BB2" t="n">
-        <v>-4.724999999999994</v>
+        <v>1.645268680594754</v>
       </c>
       <c r="BC2" t="n">
-        <v>-13383333.33333333</v>
+        <v>2.089743110683013</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3583333333333307</v>
+        <v>0.3307896281042133</v>
       </c>
       <c r="BE2" t="n">
-        <v>-2.391666666666666</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-2.31161635706917</v>
-      </c>
+        <v>-0.1515151515151416</v>
+      </c>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="n">
         <v>0</v>
       </c>
@@ -908,32 +908,32 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>GhtVSrGl</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
-  london </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -960,161 +960,161 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>-13</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>0.06333333333333324</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>-2</v>
-      </c>
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>-14</v>
+        <v>-0.7999999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2</v>
+        <v>-0.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>-1.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AL3" t="n">
-        <v>76.40000000000001</v>
+        <v>78.24513888888889</v>
       </c>
       <c r="AM3" t="n">
-        <v>79.72727272727273</v>
+        <v>77.54707070707072</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.1714519140989728</v>
+        <v>-8.051050420168053</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-0.4537037037037037</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
+        <v>-1605886.650114592</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-1728156.565656565</v>
+      </c>
       <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
+      <c r="AT3" t="n">
+        <v>-0.09731028775146378</v>
+      </c>
       <c r="AU3" t="n">
-        <v>-1.397124661830532</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-1.983097512509275</v>
-      </c>
+        <v>-3.196022727272748</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>-0.6762521247815343</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-12689359.03421198</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-3.083333333333329</v>
-      </c>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
+        <v>0.1799242424242422</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>1.475378787878785</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>-0.5044191919191832</v>
+      </c>
       <c r="BB3" t="n">
-        <v>1.560185185185162</v>
+        <v>-3.153558696205764</v>
       </c>
       <c r="BC3" t="n">
-        <v>-26624537.03703704</v>
+        <v>-1.623284313725485</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.7129629629629619</v>
+        <v>0.2383212375859358</v>
       </c>
       <c r="BE3" t="n">
-        <v>-2.370370370370367</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>6.417302604802586</v>
-      </c>
+        <v>-0.08175505050505194</v>
+      </c>
+      <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AVat9lPF</t>
+          <t>OIqwRMp1</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.66666666666</v>
+        <v>45556.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">taylor a 
+  eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1141,128 +1141,128 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="P4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="R4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.75</v>
+      </c>
       <c r="V4" t="n">
-        <v>-0.6400000000000001</v>
+        <v>-0.3216666666666665</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2000000000000002</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Y4" t="n">
+        <v>0.5966666666666667</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-5</v>
-      </c>
       <c r="AF4" t="n">
-        <v>-5</v>
+        <v>0.75</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>-2</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-2.75</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL4" t="n">
-        <v>78.90000000000001</v>
+        <v>77.34494949494949</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.125</v>
+        <v>77.94626262626262</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.46784188034188</v>
+        <v>-0.6082341269841152</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>-0.2783459595959594</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>-12150526.4202172</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-21256818.18181818</v>
+      </c>
       <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+      <c r="AT4" t="n">
+        <v>-0.6912698412698413</v>
+      </c>
       <c r="AU4" t="n">
-        <v>-3.687267471091005</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>-5.142879587732537</v>
-      </c>
+        <v>0.2931818181818642</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>-0.4856083459024667</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>-19571278.28054299</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-3.615656565656565</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
+        <v>-1.147727272727272</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>-0.0477272727272755</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-4.402272727272717</v>
+      </c>
       <c r="BB4" t="n">
-        <v>-3.204356060606102</v>
+        <v>-1.031490183792812</v>
       </c>
       <c r="BC4" t="n">
-        <v>-16966256.31313131</v>
+        <v>2.365726817042606</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.973358585858584</v>
+        <v>-4.522044695071003</v>
       </c>
       <c r="BE4" t="n">
-        <v>-4.951010101010098</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-0.1940610859728906</v>
-      </c>
+        <v>-4.309090909090912</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
         <v>0</v>
       </c>
@@ -1270,32 +1270,32 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Wplk7SgS</t>
+          <t>pYXoP0FD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.5625</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1322,128 +1322,128 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="V5" t="n">
-        <v>1.48</v>
+        <v>-0.5233333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-3</v>
-      </c>
+        <v>-0.49</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="AA5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-8</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>-4.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-4.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>84</v>
+        <v>77.19898989898991</v>
       </c>
       <c r="AM5" t="n">
-        <v>80.66666666666667</v>
+        <v>75.69819444444445</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.05329840116024354</v>
+        <v>1.026343712542229</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>0.4904040404040404</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>-12742070.01879699</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-14224772.72727273</v>
+      </c>
       <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+      <c r="AT5" t="n">
+        <v>-0.1890667565653268</v>
+      </c>
       <c r="AU5" t="n">
-        <v>4.209415584415595</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.8149496702128118</v>
-      </c>
+        <v>-2.390909090909105</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>-3.239995658581186</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4967824.525164163</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.382828282828271</v>
-      </c>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
+        <v>-0.2818181818181817</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>-0.5022727272727323</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-3.390909090909091</v>
+      </c>
       <c r="BB5" t="n">
-        <v>0.6017676767676505</v>
+        <v>-2.608198144818573</v>
       </c>
       <c r="BC5" t="n">
-        <v>14896729.7979798</v>
+        <v>0.826641331589844</v>
       </c>
       <c r="BD5" t="n">
-        <v>-1.556565656565656</v>
+        <v>-3.378492426718964</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.645454545454541</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>-3.995516453575675</v>
-      </c>
+        <v>-2.897727272727266</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
         <v>0</v>
       </c>
@@ -1451,32 +1451,32 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2TvL16Hk</t>
+          <t>d8abY4hR</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.45833333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith l 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1503,124 +1503,128 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1.416666666666667</v>
+      </c>
       <c r="V6" t="n">
-        <v>1.97</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.8633333333333333</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>-0.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>-0.08333333333333348</v>
       </c>
       <c r="AB6" t="n">
-        <v>-5</v>
+        <v>0.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>5</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>-3</v>
+        <v>-0.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>-2.083333333333334</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.5</v>
+        <v>0.08333333333333326</v>
       </c>
       <c r="AG6" t="n">
-        <v>-3</v>
+        <v>-0.9166666666666667</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>-1.416666666666666</v>
       </c>
       <c r="AI6" t="n">
-        <v>-3</v>
+        <v>1.083333333333334</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>-2.583333333333336</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.583333333333336</v>
       </c>
       <c r="AL6" t="n">
-        <v>82</v>
+        <v>78.80176767676768</v>
       </c>
       <c r="AM6" t="n">
-        <v>84.7</v>
+        <v>77.35272727272726</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.1087662337662341</v>
+        <v>0.8967653863165026</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
-        <v>0.4668560606060608</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+        <v>3277614.695675842</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>14012834.59595959</v>
+      </c>
       <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>-0.01763505672174337</v>
+      </c>
       <c r="AU6" t="n">
-        <v>6.123762469414643</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.002780914737428</v>
-      </c>
+        <v>0.7511994949494749</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="n">
-        <v>-2.219033502729154</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5807556.582909844</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.582512626262641</v>
-      </c>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
+        <v>0.6647727272727273</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>-0.5301767676767675</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.531755050505055</v>
+      </c>
       <c r="BB6" t="n">
-        <v>-1.230113636363626</v>
+        <v>-1.019749127721269</v>
       </c>
       <c r="BC6" t="n">
-        <v>4738235.479797979</v>
+        <v>-3.97641771283412</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.086174242424242</v>
+        <v>2.403510378510376</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.274494949494965</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-4.145863918689997</v>
-      </c>
+        <v>2.542676767676767</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
         <v>0</v>
       </c>
@@ -1628,32 +1632,32 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>beYTapn2</t>
+          <t>W2BSyvaJ</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.45833333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">smith j 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
+          <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1680,22 +1684,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1703,105 +1707,105 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>2.416666666666667</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-3.416666666666667</v>
+      </c>
       <c r="V7" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.2233333333333336</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4899999999999999</v>
-      </c>
-      <c r="X7" t="n">
+        <v>-0.6166666666666665</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
         <v>-0.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AA7" t="n">
-        <v>-5</v>
+        <v>0.08333333333333348</v>
       </c>
       <c r="AB7" t="n">
-        <v>6</v>
+        <v>-0.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>-6</v>
+        <v>0.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>-2</v>
+        <v>4.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>-3</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>-1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.5</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.5</v>
+        <v>-20.83333333333333</v>
       </c>
       <c r="AL7" t="n">
-        <v>79.22222222222223</v>
+        <v>78.67500000000001</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.2</v>
+        <v>79.93497474747475</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1177318295739349</v>
+        <v>2.905962823725986</v>
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
-        <v>-0.07777777777777772</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
+        <v>15174850.99467418</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>30495240.42508418</v>
+      </c>
       <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>0.6668859649122802</v>
+      </c>
       <c r="AU7" t="n">
-        <v>-0.4463979551150459</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.500946969696969</v>
-      </c>
+        <v>-1.028240740740671</v>
+      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="n">
-        <v>1.987129756208706</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1954346.537508545</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.63055555555556</v>
-      </c>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
+        <v>0.9981060606060608</v>
+      </c>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-0.3795454545454575</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.925652356902361</v>
+      </c>
       <c r="BB7" t="n">
-        <v>1.963888888888903</v>
+        <v>4.180855785296572</v>
       </c>
       <c r="BC7" t="n">
-        <v>5716180.555555556</v>
+        <v>0.6642256683375081</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.9805555555555578</v>
+        <v>3.433275898078534</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.230555555555569</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.944269053315082</v>
-      </c>
+        <v>5.508712121212127</v>
+      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="n">
         <v>0</v>
       </c>
@@ -1809,32 +1813,32 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jkLFNmv9</t>
+          <t>Q58Kw0U6</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.45833333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">smith l 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1861,128 +1865,128 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>-0.4899999999999999</v>
+        <v>0.3366666666666664</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.9000000000000001</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2</v>
-      </c>
+        <v>-0.4600000000000004</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>-4</v>
+        <v>0.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>14</v>
+        <v>0.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>-14</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="AD8" t="n">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-22.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>75</v>
+        <v>78.01193181818181</v>
       </c>
       <c r="AM8" t="n">
-        <v>76.8</v>
+        <v>79.8598327020202</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.6291345358960447</v>
+        <v>-3.275586102232495</v>
       </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
-        <v>-0.7361111111111107</v>
-      </c>
-      <c r="AR8" t="inlineStr"/>
+        <v>144845.4163767467</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2151835.016835018</v>
+      </c>
       <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
+      <c r="AT8" t="n">
+        <v>0.06432974527603674</v>
+      </c>
       <c r="AU8" t="n">
-        <v>-3.874938644759609</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>-3.788419279108226</v>
-      </c>
+        <v>-1.668771043771102</v>
+      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>-0.4408234357642904</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>-9958842.824020255</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-3.759027777777789</v>
-      </c>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
+        <v>-0.01346801346801341</v>
+      </c>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>0.3766835016835053</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.606818181818184</v>
+      </c>
       <c r="BB8" t="n">
-        <v>1.51875000000004</v>
+        <v>-1.430984146217526</v>
       </c>
       <c r="BC8" t="n">
-        <v>-10496527.77777778</v>
+        <v>-1.592152945094121</v>
       </c>
       <c r="BD8" t="n">
-        <v>-1.059027777777779</v>
+        <v>2.812470111942631</v>
       </c>
       <c r="BE8" t="n">
-        <v>-2.779166666666654</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.937609389935147</v>
-      </c>
+        <v>0.6078282828282795</v>
+      </c>
+      <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="n">
         <v>0</v>
       </c>
@@ -1990,15 +1994,15 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>AiyHLR8L</t>
+          <t>dQG3srVs</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.45833333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
@@ -2015,7 +2019,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2047,17 +2051,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
         <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
         <v>2</v>
@@ -2065,105 +2069,105 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-3.916666666666667</v>
+      </c>
       <c r="V9" t="n">
-        <v>0.1699999999999999</v>
+        <v>0.0900000000000003</v>
       </c>
       <c r="W9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1</v>
-      </c>
+        <v>-0.9633333333333333</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>-4</v>
+        <v>-0.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>0.4166666666666665</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-27</v>
+        <v>-0.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>-3</v>
+        <v>0.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>-7</v>
+        <v>-7.583333333333333</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-1.333333333333334</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-4.083333333333333</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="AL9" t="n">
-        <v>76.27272727272727</v>
+        <v>76.04048295454545</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.11111111111111</v>
+        <v>77.69272727272728</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.518089721586575</v>
+        <v>2.515665976535587</v>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="n">
-        <v>1.566666666666667</v>
-      </c>
-      <c r="AR9" t="inlineStr"/>
+        <v>24370618.80244088</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>50531313.13131315</v>
+      </c>
       <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AT9" t="n">
+        <v>0.770572263993317</v>
+      </c>
       <c r="AU9" t="n">
-        <v>4.121731979405027</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.945587814645293</v>
-      </c>
+        <v>4.204545454545439</v>
+      </c>
+      <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="n">
-        <v>-0.6669789282990095</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>20368790.5225019</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.633333333333326</v>
-      </c>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
+        <v>1.795454545454546</v>
+      </c>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>3.393939393939398</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>10.81313131313131</v>
+      </c>
       <c r="BB9" t="n">
-        <v>0.03333333333333144</v>
+        <v>6.459968308452289</v>
       </c>
       <c r="BC9" t="n">
-        <v>47936666.66666667</v>
+        <v>1.707437070938212</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.566666666666666</v>
+        <v>3.735666158148987</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.433333333333323</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-2.60040760869569</v>
-      </c>
+        <v>6.904040404040416</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
       <c r="BG9" t="n">
         <v>0</v>
       </c>
@@ -2171,32 +2175,32 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tzSnG5Wr</t>
+          <t>xtzXn47K</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.45833333334</v>
+        <v>45556.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith j 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2223,128 +2227,128 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="T10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-1</v>
+      </c>
       <c r="V10" t="n">
-        <v>1.135</v>
+        <v>-0.2766666666666666</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.735</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>-1.2</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-7</v>
+        <v>-0.3333333333333335</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>0.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-12</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>-1</v>
+        <v>-0.75</v>
       </c>
       <c r="AE10" t="n">
         <v>-0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>-1.5</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>76.76111111111112</v>
+        <v>78.37222222222222</v>
       </c>
       <c r="AM10" t="n">
-        <v>85.09999999999999</v>
+        <v>77.70915404040403</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.037573099415204</v>
+        <v>-3.94175554837318</v>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="n">
-        <v>1.978787878787879</v>
-      </c>
-      <c r="AR10" t="inlineStr"/>
+        <v>-2538103.946706888</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1724772.727272728</v>
+      </c>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>-0.1538533362062771</v>
+      </c>
       <c r="AU10" t="n">
-        <v>5.102192982456131</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>7.052046783625727</v>
-      </c>
+        <v>-1.554545454545462</v>
+      </c>
+      <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="n">
-        <v>2.612573099415204</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>35040617.69005848</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>6.872727272727275</v>
-      </c>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
+        <v>-0.2181818181818183</v>
+      </c>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>-1.086363636363636</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-1</v>
+      </c>
       <c r="BB10" t="n">
-        <v>-3.606060606060566</v>
+        <v>-1.599962292609348</v>
       </c>
       <c r="BC10" t="n">
-        <v>53793750</v>
+        <v>-1.36709940386411</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.9106060606060637</v>
+        <v>0.3531171442936198</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.778787878787881</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.276169590643292</v>
-      </c>
+        <v>-0.02954545454544188</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
       <c r="BG10" t="n">
         <v>0</v>
       </c>
@@ -2352,32 +2356,32 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2kGeEq1e</t>
+          <t>C0axT3Xo</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.35416666666</v>
+        <v>45556.35416666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
-  eng </t>
+          <t xml:space="preserve">gillett j 
+  aus </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2404,129 +2408,1935 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>-29</v>
+        <v>-14</v>
       </c>
       <c r="P11" t="n">
         <v>-1</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="T11" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="V11" t="n">
-        <v>-0.9549999999999998</v>
+        <v>-0.6799999999999997</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6150000000000002</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5</v>
-      </c>
+        <v>0.5166666666666668</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="n">
-        <v>-4.5</v>
+        <v>0.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>12</v>
+        <v>0.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.5</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>-18.5</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>1.916666666666666</v>
       </c>
       <c r="AE11" t="n">
-        <v>3.5</v>
+        <v>5.583333333333334</v>
       </c>
       <c r="AF11" t="n">
-        <v>-1</v>
+        <v>-1.083333333333333</v>
       </c>
       <c r="AG11" t="n">
-        <v>-1</v>
+        <v>-0.4166666666666667</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3.666666666666666</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-2.666666666666666</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-1</v>
+        <v>-15.16666666666666</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>15.16666666666666</v>
       </c>
       <c r="AL11" t="n">
-        <v>75</v>
+        <v>77.74757575757576</v>
       </c>
       <c r="AM11" t="n">
-        <v>77.24242424242425</v>
+        <v>77.76338383838385</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.8457060708898942</v>
+        <v>1.642078608712751</v>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="n">
-        <v>-1.62962962962963</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
+        <v>-5712919.300061744</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-2373964.646464646</v>
+      </c>
       <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
+      <c r="AT11" t="n">
+        <v>0.3597632989122421</v>
+      </c>
       <c r="AU11" t="n">
-        <v>-3.257811428767312</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-6.518213812331467</v>
-      </c>
+        <v>0.2871212121212068</v>
+      </c>
+      <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="n">
-        <v>-1.787228763883174</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>-13171656.21429224</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>-8.125</v>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
+        <v>0.6626262626262625</v>
+      </c>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>5.274747474747475</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.62323232323233</v>
+      </c>
       <c r="BB11" t="n">
-        <v>-2.091435185185247</v>
+        <v>1.537729393817003</v>
       </c>
       <c r="BC11" t="n">
-        <v>-32016087.96296296</v>
+        <v>4.815177329513041</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.1053240740740691</v>
+        <v>-2.255103872212487</v>
       </c>
       <c r="BE11" t="n">
-        <v>-7.979166666666671</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-5.382916266739784</v>
-      </c>
+        <v>-2.762121212121215</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
       <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Of1jzRNE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.03333333333333344</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>76.87840909090909</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75.6875</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-2.022444166600536</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="n">
+        <v>-10178083.31514117</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-14157152.77777778</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="n">
+        <v>-0.04538969265168991</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-3.611805555555577</v>
+      </c>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="n">
+        <v>-0.2541666666666667</v>
+      </c>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>-0.2402777777777771</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-3.509027777777789</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-1.187015178878582</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.529686300971132</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-2.215556117858739</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-2.263888888888886</v>
+      </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AFJ3CNV7</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.3099999999999998</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.2933333333333332</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.333333333333334</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-5.333333333333334</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-2.666666666666666</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-19.33333333333333</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.90909090909092</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>4.561041083099866</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>-9416271.591970123</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-24897870.37037037</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0.03014705882352953</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.2425925925926435</v>
+      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>0.9083333333333314</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-2.645370370370372</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-1.503618113912239</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.04785247432306505</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-1.470716619981317</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-2.216666666666669</v>
+      </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AVat9lPF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.1233333333333333</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5033333333333332</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.08333333333333326</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.916666666666666</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>4.583333333333334</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.083333333333333</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.666666666666666</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.08333333333333393</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-9.416666666666664</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>9.666666666666664</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>77.55227272727274</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>79.03636363636365</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-0.9694474891405491</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="n">
+        <v>-17980837.05640914</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-16929797.97979798</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="n">
+        <v>-0.5742020492407491</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-3.637878787878833</v>
+      </c>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>-0.365151515151515</v>
+      </c>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>0.7303030303030269</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-4.310101010100993</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-4.173787169329984</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0.2872690037113195</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-3.222127409316116</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-4.36767676767677</v>
+      </c>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Wplk7SgS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>12</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1666666666666665</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-2.166666666666667</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6433333333333334</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.08333333333333326</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.083333333333334</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.333333333333334</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.9166666666666643</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.9166666666666643</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>79.76296296296296</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>77.18796296296296</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-3.025620234598534</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="n">
+        <v>4271627.704725616</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>14775340.90909091</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>0.02679681859248495</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.8712121212120962</v>
+      </c>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="n">
+        <v>0.5015151515151515</v>
+      </c>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>-1.343181818181815</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>3.354545454545445</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.4090467496040162</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-2.603284228671225</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.163201177907069</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3.460606060606068</v>
+      </c>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>2TvL16Hk</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.113333333333333</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.9000000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>80.34393939393939</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>81.65454545454544</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-4.623022815845673</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="n">
+        <v>5703771.506626368</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4714277.146464646</v>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="n">
+        <v>0.1124115654166804</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-1.334280303030312</v>
+      </c>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="n">
+        <v>0.4703282828282831</v>
+      </c>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>1.169507575757574</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.526957070707084</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.806268960153233</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-2.091392920804683</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.803970768149156</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>3.125189393939408</v>
+      </c>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tzSnG5Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-0.04583333333333295</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1.095833333333333</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>77.87424242424242</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>78.90572390572392</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.7179184689616989</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>34820198.98153032</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>53693678.97727273</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>0.9941481741437985</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-2.710227272727252</v>
+      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="n">
+        <v>1.823863636363636</v>
+      </c>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>-0.5454545454545467</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.59375</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.329742579803565</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.706116304697456</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.234782146164065</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7.573863636363654</v>
+      </c>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>beYTapn2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3633333333333334</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>78.15387205387205</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>78.95084175084175</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.852888655462209</v>
+      </c>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="n">
+        <v>3799975.49019608</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>6520568.181818184</v>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="n">
+        <v>-0.05842670401493932</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.690909090909116</v>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="n">
+        <v>-0.02272727272727249</v>
+      </c>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>-0.9159090909090928</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.718181818181819</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.214256535947712</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.647315592903826</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.1123366013071916</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2.179545454545448</v>
+      </c>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AiyHLR8L</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.666666666666667</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.3900000000000001</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.3433333333333334</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-3.833333333333333</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>-3.083333333333334</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-4.083333333333333</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-12</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>76.39393939393939</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>75.74444444444444</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-2.611692555810123</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="n">
+        <v>22039854.69187675</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>48225899.62121213</v>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="n">
+        <v>0.5365280960869203</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-1.001893939393995</v>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="n">
+        <v>1.537878787878788</v>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="n">
+        <v>1.483901515151516</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9.777462121212125</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.829630336983271</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.318305958747132</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.203617052881754</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.138257575757578</v>
+      </c>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jkLFNmv9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>-10</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.3900000000000002</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.6000000000000003</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>76.3060606060606</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>78.21969696969697</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.1663336329955314</v>
+      </c>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="n">
+        <v>-12923935.85866841</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-12262550.5050505</v>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>-0.664643946823581</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.9007575757575523</v>
+      </c>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="n">
+        <v>-0.7429292929292926</v>
+      </c>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>-1.488383838383843</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-4.018686868686871</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-4.373011332679511</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.7440258254331482</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-4.246216764737923</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-2.847727272727269</v>
+      </c>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>2kGeEq1e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45549.35416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-29</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.3250000000000001</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5433333333333332</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>-18.75</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>77.0030303030303</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>79.0439393939394</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-5.747079880903414</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="n">
+        <v>-19160402.1857915</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-29636195.28619529</v>
+      </c>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="n">
+        <v>-0.7589043309631545</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-1.652104377104394</v>
+      </c>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="n">
+        <v>-1.428872053872054</v>
+      </c>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>0.4160774410774444</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-7.4830808080808</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-7.737150577320861</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-0.7011226733362932</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-5.108007833240023</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-7.766161616161625</v>
+      </c>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG3"/>
+  <dimension ref="A1:BG21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,84 +535,84 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_interceptions_against</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_interceptions_against</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -625,97 +625,97 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -727,32 +727,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>KQ2pRs2b</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">attwell s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,154 +779,140 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>-4</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="R2" t="n">
         <v>-1</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.0125</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="V2" t="n">
+        <v>3.800000000000001</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.6000000000000014</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0.6000000000000005</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.7999999999999998</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-19.39999999999999</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>78.86018518518519</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>76.76452525252526</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1.381532113509493</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>3.594653168431591</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1978518.518518518</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-2.370370370370377</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>2.600000000000009</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4.285002441509377</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>0.05185185185185204</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>0.5555555555555571</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>-1.592592592592553</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>1.595636173999395</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-0.09689567398545762</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="n">
+        <v>5584630.678731835</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.03333333333333344</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.3166666666666667</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-4.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>76.87840909090909</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>75.6875</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-251</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-10178083.31514117</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.529686300971132</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-14157152.77777778</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-3.611805555555577</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>-1.187015178878582</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-69100000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.2402777777777771</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-234</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-0.2541666666666667</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.04538969265168991</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-2.215556117858739</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-2.022444166600536</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-3.509027777777789</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>-2.263888888888886</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>SCsTyaGG</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45564.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -936,182 +922,3422 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>48</v>
+      </c>
+      <c r="H3" t="n">
+        <v>481</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>30</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.02350000000000008</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1779999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-3.949999999999999</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>78.5689696969697</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>77.83090909090909</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.6466149749373429</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.3014019423558949</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-4930006.31313131</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1160227272727248</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>-0.2106818181818113</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-0.1636669799498662</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="n">
+        <v>0.3647727272727272</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="n">
+        <v>-0.514608585858582</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="n">
+        <v>-0.3130808080808265</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>1.007509920634902</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.08579365079365076</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>1832656.999269009</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H4" t="n">
+        <v>481</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-1.699999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-7.200000000000003</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7.200000000000003</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>78.42383838383839</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>78.23855555555556</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.612880154350073</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-5.977449153574483</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-19741333.33333333</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.4803030303030305</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>-5.097373737373744</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-4.43597596933509</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="n">
+        <v>-0.9414141414141415</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>-6.868282828282844</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="n">
+        <v>-1.23030303030302</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>0.8587281182495303</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.3851024620374466</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>-9587705.02663308</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>-13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.4549999999999998</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.2175</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-3.300000000000001</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.699999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-13.45</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>77.59469696969695</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>75.85858585858587</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3.380498366013075</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-5.753440170940181</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-48162287.87878788</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.03646464646464054</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-7.439696969696982</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-3.606202416864193</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>-1.436363636363636</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>-8.937020202020221</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="n">
+        <v>-0.4454040404040143</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>-2.832831465919753</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.3728340695252463</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>-22011225.93011564</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4575000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.03249999999999997</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-2.799999999999999</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-7.399999999999999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>7.600000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>77.0615404040404</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>77.62763636363636</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2.420553747190571</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2.772523278085941</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-264113.6363636386</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.093181818181815</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0.8609090909090895</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.2731720751541644</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>-0.08727272727272695</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>-0.943181818181813</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>0.2118181818181881</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>1.581559825511221</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.02626100242468565</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>2814964.9859944</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5375000000000001</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-2.199999999999999</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.7999999999999989</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>76.91786868686867</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>78.17850505050505</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.8559911330499546</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.06737556561088809</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-5063636.363636365</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.154545454545456</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="n">
+        <v>-2.36545454545454</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-0.855980849216138</v>
+      </c>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="n">
+        <v>0.2218181818181815</v>
+      </c>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>-0.7345454545454544</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="n">
+        <v>-0.1872727272727843</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>0.5238207870560814</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.2025513049042458</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>-1320860.87115499</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.1374999999999997</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.3275000000000001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-5.050000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.550000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="n">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0.3999999999999999</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>78.35781818181817</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>77.77045454545456</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.1038566335625148</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>3.250971479500905</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>15211876.26262626</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-3.550505050505048</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>4.204646464646459</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5.475586007130133</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="n">
+        <v>-0.09696969696969737</v>
+      </c>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="n">
+        <v>3.918131313131312</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="n">
+        <v>1.699797979797978</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>3.869897822765466</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.5581065380697734</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>18205715.09740259</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>17</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>13</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.5175000000000002</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02249999999999996</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.3000000000000007</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.050000000000001</v>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="n">
+        <v>0.6500000000000004</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0.6500000000000004</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-1.100000000000001</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1.100000000000001</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>79.18727272727273</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>77.91741414141413</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1.500397090654445</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7.038482938630011</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>53325204.54545455</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-1.753749999999997</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>8.520340909090905</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.077371880570411</v>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="n">
+        <v>1.029545454545455</v>
+      </c>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="n">
+        <v>8.693295454545449</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>0.9464772727272646</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>-1.884663069773325</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.6277226572447157</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>25531894.92217341</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.3274999999999997</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2049999999999998</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-2.799999999999999</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-2.399999999999999</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.1999999999999997</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>4.799999999999997</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>80.53253787878789</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>78.04957912457913</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-4.430162114773097</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1.560790315710221</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-12386832.07070707</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-2.183030303030304</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-1.868787878787884</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-5.874133910203696</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="n">
+        <v>-1.046969696969696</v>
+      </c>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="n">
+        <v>-4.322676767676768</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="n">
+        <v>0.567575757575753</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>-1.813958356035045</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.7407528207871454</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>-12344902.22798432</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>-24</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.1819999999999999</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8304999999999998</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="n">
+        <v>-0.7999999999999998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.799999999999999</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.333333333333333</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>75.90547138047138</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>78.56625631313132</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.4538224950891561</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-4.351159050264599</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-38489000</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.25272727272727</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>-5.370909090909095</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-3.100439844962338</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>-1.250909090909091</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>-4.089090909090899</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>5.141818181818167</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>1.271070404446363</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.6713398425731849</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>-22366912.89240889</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwFBuMaf</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.3569999999999998</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.5829999999999997</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-6.65</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>-0.04999999999999982</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.9500000000000002</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>77.53575757575757</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>78.15681818181818</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.026495118798508</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.6811933271332151</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1526250</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.021022727272729</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>0.05965909090909349</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.784203389853971</v>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>0.5159090909090911</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>-0.409659090909102</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="n">
+        <v>-0.9755681818181756</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="n">
+        <v>3.075752074545221</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.344777204360005</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>13079517.8998724</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GhtVSrGl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.3699999999999997</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.0774999999999999</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-2.800000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.5999999999999996</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-16</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>78.41704545454546</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>77.61373737373738</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1.544215686274509</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5046275783040386</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1573707.07070707</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.8166666666666629</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0.2400505050505046</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-2.725052839317541</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>0.1893939393939392</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>-0.8835353535353647</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>-2.704090909090922</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="n">
+        <v>-6.651134453781509</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.1006423478482299</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="n">
+        <v>-1360665.202444615</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>OIqwRMp1</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>-16</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.286</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.4420000000000002</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="n">
+        <v>-0.7999999999999998</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>77.4790404040404</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>79.0439393939394</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.131470342522974</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-4.810969089390156</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-21096181.81818182</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.009090909090911481</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>-4.147272727272735</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-1.448525480367593</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>-1.092727272727273</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>-4.307272727272718</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="n">
+        <v>-0.03272727272724296</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="n">
+        <v>-0.666587301587299</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.735238095238095</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>-13078754.4695071</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>W2BSyvaJ</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>UDg08Ohm</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>48</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H15" t="n">
         <v>481</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
         <v>20242025</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1575000000000002</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.8175000000000001</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.949999999999999</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-6.300000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.08333333333333348</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>78.39375000000001</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>80.2929292929293</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0.7040491854636564</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>3.140499686716794</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>30399040.4040404</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.3323863636363633</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>5.407954545454544</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.992353279030908</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0.9761363636363636</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>5.911426767676758</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="n">
+        <v>-1.071464646464619</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="n">
+        <v>2.753887322472877</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.6535087719298243</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>14080509.01994569</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>d8abY4hR</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>hbOpz9hE</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>QHesBmSQ</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>-13</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3824999999999998</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.9074999999999998</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.050000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.08333333333333348</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>4.200000000000003</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-4.200000000000003</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>78.82222222222222</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>77.32272727272728</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-3.94466353436875</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.087420502203116</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>13075924.24242424</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.7589898989899027</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>2.416969696969701</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-1.393058643395165</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>3.050656565656595</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="n">
+        <v>0.5817676767676403</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="n">
+        <v>0.4467099120350326</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.01262308009514923</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>2548445.677854549</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Q58Kw0U6</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
         <v>-3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="P17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.3099999999999998</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.2933333333333332</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="R17" t="n">
         <v>-1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.1325000000000001</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.799999999999999</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.1999999999999997</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>77.93409090909091</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>79.64090909090909</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1.167358719711665</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.532703362281381</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1991501.683501685</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.4441077441077468</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.3448484848484838</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-0.8856964078831169</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>-0.02154882154882154</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>1.469292929292934</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="n">
+        <v>-1.464983164983209</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="n">
+        <v>-2.553196154513302</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0.1060092507662842</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>425103.6058286708</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pYXoP0FD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.5099999999999999</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.5149999999999999</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="n">
+        <v>-0.6000000000000005</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.5999999999999996</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4.200000000000001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>-1</v>
       </c>
-      <c r="AH3" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>19.33333333333333</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-19.33333333333333</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>76.90909090909092</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-345</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-9416271.591970123</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.04785247432306505</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-24897870.37037037</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.2425925925926435</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-1.503618113912239</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-257000000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9083333333333314</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-335</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.03014705882352953</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-1.470716619981317</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.561041083099866</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-2.645370370370372</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-2.216666666666669</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1</v>
+      <c r="AK18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>77.22954545454544</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>75.86111111111111</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.6021025389560783</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-3.655425520322524</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-13643818.18181818</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.2618181818181853</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>-2.958181818181814</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-3.277347989539066</v>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>-0.2254545454545454</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>-3.092727272727274</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="n">
+        <v>-2.412727272727267</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="n">
+        <v>0.9438819875776403</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.2968674403399802</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>-15377647.24310777</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xtzXn47K</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.1125</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.9150000000000003</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.399999999999999</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-0.7999999999999998</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>78.4131313131313</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>77.39097222222222</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.6391340685458324</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>-0.2356881027469484</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-1505727.272727273</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.250909090909097</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>0.1218181818181847</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-1.398151652269291</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>-0.2109090909090907</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>-0.9090909090909065</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="n">
+        <v>-1.189090909090879</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="n">
+        <v>-4.34431352960766</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-0.1230826689650215</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
+        <v>-2597301.339183692</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dQG3srVs</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45556.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>13</v>
+      </c>
+      <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.2500000000000002</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.8225</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-7.199999999999999</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="n">
+        <v>-0.1500000000000004</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.4166666666666665</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-3.949999999999999</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-15.25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>76.29545454545453</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>77.66404040404041</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.50017584722676</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.516112291598574</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>50857676.76767677</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3.202020202020204</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>7.175252525252532</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.035930995968187</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="n">
+        <v>1.797474747474747</v>
+      </c>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="n">
+        <v>10.72979797979798</v>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="n">
+        <v>4.151515151515156</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="n">
+        <v>2.484953416149096</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.7361998746867171</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="n">
+        <v>23040750.99433366</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>C0axT3Xo</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45556.35416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>-14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5625</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.1775000000000002</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.449999999999999</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-0.3499999999999996</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-2.550000000000001</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.3500000000000001</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>78.01575757575759</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>77.97171717171716</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>4.722042551158179</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-2.54023983319145</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1509348.484848484</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.055505050505054</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-2.4940909090909</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.240612914085943</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="n">
+        <v>0.7136363636363634</v>
+      </c>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="n">
+        <v>1.683535353535362</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>0.318535353535367</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="n">
+        <v>0.3332765657750656</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0.2217240908741278</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="n">
+        <v>-7098214.678866137</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG3"/>
+  <dimension ref="A1:DP21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,225 +500,530 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35</t>
+          <t>result</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>h2h_35_segun_loc</t>
+          <t>dif_mean_last_60_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>h2h_3_segun_loc</t>
+          <t>dif_mean_last_270_matches_expected_goals_(xg)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>result</t>
+          <t>dif_mean_last_270_matches_expected_goals_(xg)_against</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
+          <t>dif_mean_last_60_matches_expected_points</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+          <t>dif_mean_last_60_matches_expected_points_against</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals</t>
+          <t>dif_mean_last_270_matches_expected_points</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goals_against</t>
+          <t>dif_mean_last_270_matches_expected_points_against</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
+          <t>dif_mean_last_60_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
+          <t>dif_mean_last_60_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls</t>
+          <t>dif_mean_last_270_matches_shots_on_goal</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_fouls_against</t>
+          <t>dif_mean_last_270_matches_shots_on_goal_against</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_interceptions</t>
+          <t>dif_mean_last_60_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_interceptions_against</t>
+          <t>dif_mean_last_60_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points</t>
+          <t>dif_mean_last_270_matches_goal_attempts</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_points_against</t>
+          <t>dif_mean_last_270_matches_goal_attempts_against</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
+          <t>dif_mean_last_60_matches_goals</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
+          <t>dif_mean_last_60_matches_goals_against</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts</t>
+          <t>dif_mean_last_270_matches_goals</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
+          <t>dif_mean_last_270_matches_goals_against</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession</t>
+          <t>dif_mean_last_60_matches_points</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
+          <t>dif_mean_last_60_matches_points_against</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>dif_mean_last_270_matches_points</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_last_270_matches_points_against</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_miss</t>
+          <t>dif_mean_last_60_matches_goal_ratio</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_60_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_ratio</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_goal_ratio_against</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPS</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPS_against</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacks</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacks_against</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dangerous_attacks_against</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dead_balls</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_dead_balls_against</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_ball_possession</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_total_passes</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_total_passes_against</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacking_efficiency</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_attacking_efficiency_against</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacking_efficiency</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_attacking_efficiency_against</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_yellow_cards</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_yellow_cards_against</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_red_cards</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_red_cards_against</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_actions</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_actions_against</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPDA</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_PPDA_against</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_KGP</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_KGP_against</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_clean_sheet</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_clean_sheet_against</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_efficiency</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_defensive_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_efficiency</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_defensive_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_efficiency</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_60_matches_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_efficiency</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_270_matches_efficiency_against</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_270_matches_mean_rat_player_start_home_against</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_last_270_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_start</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>is_rival_match</t>
         </is>
@@ -727,32 +1032,32 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Of1jzRNE</t>
+          <t>fsjksfhd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -779,175 +1084,346 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-2</v>
+        <v>-0.4420000000000002</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1</v>
+        <v>0.01600000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>-0.399616666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0.05719999999999992</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03333333333333344</v>
+        <v>-0.3214285714285714</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3166666666666667</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.25</v>
+        <v>-0.2472527472527473</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>0.1071428571428572</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-1.071428571428571</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6666666666666667</v>
+        <v>-0.2380952380952381</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>-0.6933333333333334</v>
       </c>
       <c r="AA2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>-0.01777777777777789</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-0.2619047619047628</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-0.9047619047619051</v>
+      </c>
       <c r="AD2" t="n">
-        <v>-1.5</v>
+        <v>0.08444444444444521</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>0.336296296296295</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.25</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="AH2" t="n">
-        <v>2</v>
+        <v>-0.3496296296296295</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4.25</v>
+        <v>-0.1525925925925926</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2</v>
+        <v>-0.6428571428571428</v>
       </c>
       <c r="AL2" t="n">
-        <v>76.87840909090909</v>
+        <v>-0.1758241758241756</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.6875</v>
+        <v>0.04670329670329654</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.25</v>
+        <v>2.510173839475995</v>
       </c>
       <c r="AO2" t="n">
-        <v>12.5</v>
+        <v>-1.058351370851371</v>
       </c>
       <c r="AP2" t="n">
-        <v>-251</v>
+        <v>-0.7539986875412685</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-10178083.31514117</v>
+        <v>-0.1251977179199404</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.529686300971132</v>
+        <v>23.39743912735341</v>
       </c>
       <c r="AS2" t="n">
-        <v>-14157152.77777778</v>
+        <v>1.796310332875066</v>
       </c>
       <c r="AT2" t="n">
-        <v>-3.611805555555577</v>
+        <v>-44.73922527731349</v>
       </c>
       <c r="AU2" t="n">
-        <v>-1.187015178878582</v>
+        <v>-4.9814467394894</v>
       </c>
       <c r="AV2" t="n">
-        <v>-69100000</v>
+        <v>-19.06666666666668</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.2402777777777771</v>
+        <v>16.7</v>
       </c>
       <c r="AX2" t="n">
-        <v>-234</v>
+        <v>-11.82051282051283</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0.2541666666666667</v>
+        <v>7.339743589743591</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.04538969265168991</v>
+        <v>-25.26666666666666</v>
       </c>
       <c r="BA2" t="n">
-        <v>-2.215556117858739</v>
+        <v>1.766666666666666</v>
       </c>
       <c r="BB2" t="n">
-        <v>-2.022444166600536</v>
+        <v>-20.01602564102564</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-1.698717948717949</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3.509027777777789</v>
+        <v>-6.767857142857146</v>
       </c>
       <c r="BE2" t="n">
-        <v>-2.263888888888886</v>
+        <v>-5.553571428571427</v>
       </c>
       <c r="BF2" t="n">
-        <v>-3</v>
+        <v>-7.565934065934062</v>
       </c>
       <c r="BG2" t="n">
+        <v>-4.552197802197806</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-5.119047619047613</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>5.11904761904762</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-3.988148148148149</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>3.988148148148149</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>-14.20000000000005</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>34.60000000000002</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>8.703333333333376</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>61.18166666666667</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.2420000000000001</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.1087166666666667</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>-0.08613333333333335</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>-0.2285714285714282</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.5428571428571427</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.01388888888888884</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.2314814814814814</v>
+      </c>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>-5.410714285714285</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>-0.7527472527472554</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>-2.895604395604398</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>2.27187435247418</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>-0.820008626639062</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.930425893392014</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>3.281485754479075</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>-0.008788898800612503</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.02563007280167453</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.0001892527506210245</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.008998372598941658</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0.2321428571428572</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>-0.01785714285714285</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>0.1703296703296703</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.1263736263736264</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>-0.2420000000000001</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.08613333333333335</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.1087166666666667</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.4580000000000001</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.4580000000000001</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>-0.02258333333333323</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.02258333333333323</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>77.46744172494172</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>77.75743561993562</v>
+      </c>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="n">
+        <v>-4.129585546339769</v>
+      </c>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="n">
+        <v>-1.176625119744863</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-25609.74836904459</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-1.565937950937951</v>
+      </c>
+      <c r="DI2" t="inlineStr"/>
+      <c r="DJ2" t="inlineStr"/>
+      <c r="DK2" t="inlineStr"/>
+      <c r="DL2" t="n">
+        <v>0.3561038961038925</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-45717.8354978355</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-5.051117189299958</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-7.229668109668111</v>
+      </c>
+      <c r="DP2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AFJ3CNV7</t>
+          <t>nywy5cp3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gillett j 
-  aus </t>
+          <t xml:space="preserve">jones r 
+  eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -974,144 +1450,6915 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.4280000000000002</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4959487179487179</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2714615384615382</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1457174638487209</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1657397107897663</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.2000000000000002</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.557142857142857</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.8666666666666654</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.449999999999999</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.335714285714287</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.033333333333333</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.011904761904762</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4047619047619047</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.7652947719688543</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>-0.7130144605116796</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.4528479853479856</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>2.659573934837092</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.8629306039738931</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.5577179227031461</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-132.2063002476713</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-28.38331856198417</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>-59.45111461716425</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>51.49801790216182</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>11.43295019157088</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>-23.22605363984674</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>-1.649999999999999</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.180076628352495</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-4.305236270753511</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.119047619047617</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-5.714285714285715</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-0.7708565072302562</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-4.651835372636263</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-17.76666666666667</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>14.57619047619048</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-14.61190476190476</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>182.1999999999999</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-113.8</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>163.5357142857143</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>-126.3983516483516</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.5720000000000001</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.5296923076923077</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>-0.2714615384615385</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>-0.06666666666666643</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>0.03333333333333366</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>0.1296296296296298</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>-0.007407407407407529</v>
+      </c>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="n">
+        <v>0.08333333333333331</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>-6.785714285714285</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.1666666666666679</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>-2.942157953281423</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>4.219132369299224</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>-0.8082691382691394</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>7.351193771486326</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>-3.770117395929445</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>3.898138846898107</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.01129626370241869</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.01612470250029908</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>0.008051379504342801</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>0.01406333978342941</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>0.0878754171301446</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>-0.04560622914349277</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>-0.5720000000000001</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>0.2714615384615385</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>-0.5296923076923077</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>-0.732</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>0.8011538461538463</v>
+      </c>
+      <c r="CY3" t="n">
+        <v>-0.8011538461538463</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>78.19688590978915</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>77.0481949598021</v>
+      </c>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="n">
+        <v>-2.182287370626369</v>
+      </c>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="n">
+        <v>-1.245324791382473</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>28309.75672877846</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>-0.02358585858587503</v>
+      </c>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="n">
+        <v>-2.697904040404044</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>27458.78787878787</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>3.491338590298241</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>3.27457070707068</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ltBAlx0M</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H4" t="n">
+        <v>481</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1270000000000002</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.1986666666666664</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-0.2009285714285716</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0.04575714285714283</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0.3486352357320099</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.2692307692307692</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1.542857142857144</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4857142857142858</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-1.453333333333334</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0.5466666666666669</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-1.885714285714286</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.742857142857142</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-3.386666666666667</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-4.353333333333333</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.3400000000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1933333333333334</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.7916666666666665</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.7083333333333334</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.2357320099255582</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.414765323378768</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.8734693877551023</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.573007907158757</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.29562483156539</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>192.807408277344</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-59.8045028711187</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>60.15013204881657</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-29.14102265051338</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>24.83333333333333</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>-10.98419540229885</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>-9.646551724137936</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-3.329022988505749</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-12.0948275862069</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.166666666666668</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-2.375</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.939205955334984</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-6.388337468982627</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-4.742857142857147</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4.742857142857147</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.7666666666666728</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>-0.7666666666666728</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-106.4</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-7.200000000000045</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-34.29000000000002</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-36.63999999999999</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.8730000000000001</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.4319999999999998</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.03235714285714278</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.1986142857142857</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.2200000000000002</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>7.458333333333332</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>-4.892059553349874</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>4.770471464019852</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.2864887312591744</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>-15.51459975056749</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>2.224561024758524</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-4.961061276940466</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.01126100961899273</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.001372118802053561</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.01630103912171238</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0.004835832189953412</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>-0.08333333333333334</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>-0.06575682382133993</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.1017369727047147</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.4319999999999998</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>-0.8730000000000001</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0.1986142857142857</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0.03235714285714278</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>-0.441</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0.1662571428571427</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.1662571428571427</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>77.91508754208753</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>78.10608044733044</v>
+      </c>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="n">
+        <v>-3.804337448175289</v>
+      </c>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="n">
+        <v>-0.8193122557947703</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>-26428.70737921409</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.9292207792207705</v>
+      </c>
+      <c r="DI4" t="inlineStr"/>
+      <c r="DJ4" t="inlineStr"/>
+      <c r="DK4" t="inlineStr"/>
+      <c r="DL4" t="n">
+        <v>0.6422077922077918</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>-26987.33766233767</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-2.962813866965561</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>-1.298376623376612</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>l0Zi1FqS</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>hbOpz9hE</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.5620000000000001</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2219999999999998</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.732948717948718</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.003942307692307745</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.1071428571428571</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2142857142857142</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.4285714285714286</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.7619047619047614</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0.5238095238095237</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.666666666666667</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0.5555555555555554</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.333333333333334</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-4.285714285714286</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0.8518518518518512</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0.518518518518519</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.2142857142857142</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.119047619047619</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.185185185185185</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.07407407407407396</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.410714285714286</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4.212301587301587</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.007812857077562</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.538200648266868</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.5004598071244919</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>137.7998599558861</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>33.98569479662461</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>100.6625799187521</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-37.48528751264772</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.933333333333323</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-7.266666666666666</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.03846153846154721</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>-3.230769230769226</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-5.066666666666663</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-18.73333333333334</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-1.653846153846153</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>-3.115384615384613</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-2.035714285714285</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.1428571428571459</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-2.464285714285715</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3.071428571428569</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-10.30952380952381</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>10.30952380952381</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-7.259259259259252</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>7.259259259259252</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-69.80000000000001</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>90.80000000000007</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-83.58974358974359</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>47.37820512820508</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0.5426923076923078</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.01355769230769229</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-1.192307692307692</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3.928571428571427</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-7.785714285714285</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>1.892857142857146</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-7.892857142857142</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.3352613553700472</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0.2123744615237886</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>-0.2099596284425509</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.3832902390823385</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.03604999730677993</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>-0.002125646015674561</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.0004526099122899863</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>-0.02301838824316574</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0.01785714285714285</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>-1.378</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0.162</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>-0.01355769230769229</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.5426923076923078</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>-1.216</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>-0.55625</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.55625</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>77.35648281759393</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>77.33874458874459</v>
+      </c>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="n">
+        <v>1.813610409198645</v>
+      </c>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="n">
+        <v>-0.01090123326965653</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-57894.5220006172</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-3.45122655122654</v>
+      </c>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="n">
+        <v>0.3310966810966853</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-65745.16594516594</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-3.554396332511672</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-3.694733044733056</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>tbEWgXy2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5743333333333334</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.398</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7720769230769229</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.5392820512820511</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.017857142857143</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.6964285714285714</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.064516129032258</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.6907675194660734</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.023809523809524</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.261904761904762</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-1.614285714285714</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.142857142857142</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-4.833333333333333</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4.669047619047619</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-6.254761904761905</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.173809523809524</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.5904761904761905</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9285714285714284</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.8392857142857143</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.339265850945495</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1.190211345939933</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.5946196660482368</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.88584570191713</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.7234177111565945</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>3.759990384746301</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-97.21088754338544</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>82.19844399394449</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-86.19762770752763</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>91.39755930487854</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-9.799999999999997</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-26.53333333333333</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>27.08939974457215</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-42.40102171136653</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>33.66666666666666</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-6.166666666666664</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>32.76756066411239</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-21.7037037037037</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-9.125</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.181312569521687</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-10.0622914349277</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>15.31904761904762</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-15.31904761904762</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>244.4</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-89.80000000000001</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>230.9784482758621</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-108.7830459770115</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.5256666666666666</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.409974358974359</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0.07866666666666663</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0.5476190476190479</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.3214285714285714</v>
+      </c>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>-6.232142857142858</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-3.089285714285715</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>-5.057842046718577</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>5.321468298109011</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>-0.5123780677433647</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>9.209958194433998</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.4619955246284491</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>4.120347241154001</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.02075156808526011</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>-0.01011376346908414</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.02429663061997738</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0.007148861537300877</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.01785714285714285</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.1802002224694104</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0.2091212458286986</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0.398</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>-0.5256666666666666</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.07866666666666663</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0.409974358974359</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.1276666666666667</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0.1276666666666667</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.4886410256410257</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>-0.4886410256410257</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>77.78721081785598</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>77.45160082972583</v>
+      </c>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="n">
+        <v>-2.675782646461272</v>
+      </c>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="n">
+        <v>-0.7837599078186166</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>78933.44076969255</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-2.528787878787909</v>
+      </c>
+      <c r="DI6" t="inlineStr"/>
+      <c r="DJ6" t="inlineStr"/>
+      <c r="DK6" t="inlineStr"/>
+      <c r="DL6" t="n">
+        <v>-0.8779220779220758</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>109519.4805194805</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>6.193350063831105</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>7.584632034632051</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>YXAOeg7k</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.062</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.4300000000000002</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-0.1776373626373624</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.1754120879120877</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.4285714285714287</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.4285714285714287</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.07380952380952377</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.09761904761904761</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0.06641123882503219</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>-1.444444444444445</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-4.666666666666666</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-1.333333333333334</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>-2.344827586206897</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-1.200510855683268</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.4252873563218391</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-0.3486590038314177</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>-0.2857142857142856</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-0.2714285714285714</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>7.11755082149819</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-2.722786131996658</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.279320470386353</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.1430859532521103</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>86.59043630470964</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>-58.40957976137381</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>-49.71493861826957</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>31.68737095677238</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-20.40000000000001</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3.939560439560452</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-12.17582417582418</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-17</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>-0.4000000000000057</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>-4.063186813186817</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>-6.843406593406591</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.4285714285714306</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-4.314285714285717</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-6.952380952380949</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.833333333333336</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10.6360153256705</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>-10.67305236270754</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>35.60000000000002</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.399999999999977</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>57.83653846153845</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>26.29807692307691</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1.262</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.4715934065934066</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-0.151510989010989</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0.8222811671087533</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.06763925729442954</v>
+      </c>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3.571428571428569</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-11.54047619047619</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-9.726190476190474</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-1.106836511836512</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>-1.891752510627111</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0.6475355925487261</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0.5554168276119551</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.006481427804024088</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.04907358842695685</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.009274839157153179</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.01801773637138934</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.08809523809523809</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0.1166666666666667</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-1.262</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.151510989010989</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0.4715934065934066</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.832</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.6231043956043957</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>-0.6231043956043957</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>72.36747648902821</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>77.03023756079313</v>
+      </c>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="n">
+        <v>-0.8243734313427353</v>
+      </c>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="n">
+        <v>2.399730595005867</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-435.0949165998318</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>2.207912457912471</v>
+      </c>
+      <c r="DI7" t="inlineStr"/>
+      <c r="DJ7" t="inlineStr"/>
+      <c r="DK7" t="inlineStr"/>
+      <c r="DL7" t="n">
+        <v>2.850000000000001</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>1981.313131313127</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0.7517992297706968</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.9786195286195181</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bFdtqGNq</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1959999999999997</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3560000000000001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2645192307692308</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.1416666666666666</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.1619047619047619</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.002380952380952372</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.8571428571428568</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.5836526181353765</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0.4636015325670497</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.142857142857144</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0.3716475095785441</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.4329501915708818</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.9999999999999998</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3167305236270752</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0.1902937420178801</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0.875</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.111904761904762</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0.1595238095238094</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.035412626589097</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-2.343039003965777</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.546999312446578</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.7271621925251583</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-38.19725638718739</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-23.19809647693123</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.656968069332265</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-29.43666321805995</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.666666666666671</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-3.241758241758248</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.027472527472526</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-1.166666666666664</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.833333333333329</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.304945054945051</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8.021978021978022</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.3452380952380949</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-3.026190476190475</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>4.285714285714285</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-4.285714285714285</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-5.436781609195407</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.436781609195407</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>35.39999999999998</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>93.20000000000005</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-85.85897435897436</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>44.49358974358972</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>-1.356</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0.123301282051282</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0.0282051282051282</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0.3690932311621964</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0.07662835249042144</v>
+      </c>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-7.264285714285716</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-2.821428571428573</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>13.80427168610836</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.1037810337810328</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>7.402301069201204</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>-1.547946031947275</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0.02090137337162307</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.006117904789034255</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0.01239859799929777</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0.0002501011809557391</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.01190476190476192</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0.08809523809523809</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.356</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0.204</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0.0282051282051282</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>-0.123301282051282</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0.1515064102564102</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>-0.1515064102564102</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>78.79742294742294</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>77.46436026936026</v>
+      </c>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="n">
+        <v>-0.1316102756892121</v>
+      </c>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="n">
+        <v>-4.399925672023201</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-13239.8372675656</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0.6333874458874504</v>
+      </c>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="n">
+        <v>-1.555471380471381</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-3149.873737373739</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>-4.088160729878979</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-1.089015151515142</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SQM1jbV9</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.002000000000000224</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.1739999999999997</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4864492753623189</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.3211884057971016</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.08333333333333337</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.6274509803921569</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.3210784313725489</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.371428571428571</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0.5142857142857142</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.8880105401844531</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.845849802371541</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1.800000000000001</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.760210803689066</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-1.7167325428195</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-1.257142857142857</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.9380764163372859</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0.9934123847167325</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.9534313725490196</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0.9436274509803921</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.334199134199134</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.8223160173160178</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.8041558173155474</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.6261059234495643</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>51.60831252419663</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>100.4073490156608</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>91.66500904403009</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-6.23858555379141</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>14.33333333333333</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-4.625</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2.88636363636364</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-5.833333333333336</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>9.431818181818187</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.153409090909093</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.458333333333332</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.629901960784316</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>5.867647058823529</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-22.97142857142857</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>22.97142857142857</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-11.22529644268775</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>11.22529644268774</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-242</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>91.40000000000003</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-90.24844720496895</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>36.45341614906835</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>-1.026</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.6092028985507246</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0.6904057971014492</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1.371428571428571</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0.2571428571428571</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2878787878787881</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0.4242424242424243</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>10.55637254901961</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>7.389705882352942</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>1.471289360650815</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>-7.867197406739843</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>2.602952563913323</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2.317113905199307</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0.05822425738785356</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.007710962382776521</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0.02767218511828428</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.004806116353445709</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.3480392156862746</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0.1519607843137255</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-1.198</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.6904057971014492</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0.6092028985507246</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>2.224</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-2.224</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>1.299608695652174</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>-1.299608695652174</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>77.86026570048308</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>71.61772937710438</v>
+      </c>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="n">
+        <v>-1.242460227251229</v>
+      </c>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="n">
+        <v>-0.9651595695326414</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>64946.52295159262</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>1.941666666666691</v>
+      </c>
+      <c r="DI9" t="inlineStr"/>
+      <c r="DJ9" t="inlineStr"/>
+      <c r="DK9" t="inlineStr"/>
+      <c r="DL9" t="n">
+        <v>-1.963888888888892</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>81491.66666666667</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>7.724089399592501</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>10.15277777777777</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>d6dJHzU8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45570.45833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0.1899999999999999</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.3599358974358975</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.8189743589743588</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.2857142857142858</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-0.618131868131868</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.7252747252747251</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-1.974814814814815</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.754074074074074</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.833333333333334</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.833333333333332</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-2.416296296296295</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5.980740740740739</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.5318518518518518</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.7896296296296297</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.2857142857142858</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.6071428571428572</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.6208791208791209</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.703030303030303</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-5.236652236652237</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.7698752665367739</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-2.697305491303152</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>39.20949454723572</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-112.3999968338449</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-43.04077642857845</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-67.28634128583028</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10.39999999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-8.942307692307693</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13.67948717948717</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>2.800000000000004</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-7.028846153846153</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>14.32371794871795</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-1.571428571428569</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.989010989010989</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.285714285714285</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-9.333333333333336</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>9.333333333333336</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>63.59999999999997</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-56.80000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.958333333333314</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>41.83333333333331</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-0.002000000000000002</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.3899999999999999</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0.1528846153846154</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.1233333333333334</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-0.166666666666667</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.07384615384615367</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.5092307692307694</v>
+      </c>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>2.285714285714285</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>8.271978021978022</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>13.39835164835165</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0.8977787132222623</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.87450105698426</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>2.903027486357768</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.001152022485285897</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-0.07601920519600348</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0.01889591417927143</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0.01897107966012356</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0.003859945116844052</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0.1730769230769231</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.1263736263736264</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>-0.3899999999999999</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.002000000000000002</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0.1233333333333334</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.1528846153846154</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>-0.3919999999999998</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.3919999999999998</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0.2762179487179486</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.2762179487179486</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>77.45004856254856</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>72.1736531986532</v>
+      </c>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="n">
+        <v>0.6692412243311026</v>
+      </c>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="n">
+        <v>2.521302188212271</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>39552.09609281154</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1.043434343434342</v>
+      </c>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="n">
+        <v>2.116329966329968</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>42801.01010101011</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>8.304021000374803</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>7.819696969696977</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>r3Wq3yFF</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45570.35416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0.5980000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.9259999999999999</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.7564285714285715</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1880434782608698</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.5416666666666667</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.4583333333333334</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.5074074074074073</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.4925925925925926</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.085714285714285</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-3.315649867374006</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.316976127320955</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-3.77142857142857</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.742857142857142</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-9.148541114058357</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.6419098143236077</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.5714285714285714</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0.6140583554376655</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.3580901856763925</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-0.9166666666666665</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.6925925925925926</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.5962962962962963</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.9859093704958362</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.3363553113553115</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3.76261255390656</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.3318783108169536</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>42.60042266173781</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-58.99827409598001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>98.20212808130481</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-62.65991753424964</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0.5833333333333286</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11.83333333333333</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-31.68428571428572</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>26.06285714285714</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-15.83333333333334</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-27.77285714285714</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.432857142857145</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-6.166666666666664</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-2.916666666666668</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-6.474074074074075</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.3629629629629605</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-10.28571428571428</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>10.28571428571428</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-17.80106100795756</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>17.80106100795756</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-109.8</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>86</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-194.5602006688964</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>179.3327759197325</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-0.6020000000000001</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.2740000000000001</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.09493788819875776</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.3057453416149069</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.4857142857142855</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-1.457142857142857</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.2942857142857143</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0.6471428571428572</v>
+      </c>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0.3592592592592609</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.8555555555555578</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>9.642087711708205</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-6.841509708929063</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>7.226815160508263</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-7.542344336251983</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.03691533931809513</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.01246066916717892</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-5.453262099230222e-05</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.01753102153155087</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.4166666666666666</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.08333333333333334</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.04074074074074074</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.08518518518518517</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0.2740000000000001</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.6020000000000001</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0.3057453416149069</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0.09493788819875776</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0.8760000000000002</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.8760000000000002</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0.2108074534161491</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.2108074534161491</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>77.27159451659452</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>76.99335437710438</v>
+      </c>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="n">
+        <v>0.2734126984126419</v>
+      </c>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="n">
+        <v>2.867063492063494</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-65655.55555555556</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0.6493506493506231</v>
+      </c>
+      <c r="DI11" t="inlineStr"/>
+      <c r="DJ11" t="inlineStr"/>
+      <c r="DK11" t="inlineStr"/>
+      <c r="DL11" t="n">
+        <v>-1.294805194805193</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-116949.3506493506</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-4.459523809523802</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-7.707792207792195</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>KQ2pRs2b</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.1179999999999997</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.185740740740741</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2249629629629628</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.619047619047619</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.738095238095238</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.2584033613445378</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1008403361344536</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.071428571428571</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.119047619047619</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.1869747899159666</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.016806722689076</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.2857142857142865</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.031512605042016</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.184873949579831</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.4523809523809524</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.3571428571428572</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.430672268907563</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.1008403361344536</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0.02380952380952395</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-0.4327731092436975</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.3298319327731094</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-2.239225905673274</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3.148182957393483</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.2921638678699265</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.01650533333376369</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.41546067019485</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>53.40755004885105</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>170.1658453645524</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-45.96406446361991</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-4.799999999999997</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>37.73333333333333</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-3.454545454545453</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>22.9057239057239</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-1.533333333333339</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.1582491582491627</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>12.32996632996633</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.333333333333336</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9.809523809523807</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.991596638655462</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>14.98319327731092</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-20.07142857142857</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>20.23809523809523</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-18.71848739495798</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>18.75420168067227</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-217.6</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-205.5238095238096</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>71.52910052910056</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.108</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.08200000000000005</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.3412962962962963</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0.1657037037037037</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0.5714285714285716</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0.02380952380952372</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.6296296296296298</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0.05664488017429203</v>
+      </c>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>-2.80952380952381</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>16.35924369747899</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>11.73739495798319</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>4.533218779271408</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-2.338303892996365</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>1.60065767027354</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-3.409718746686726</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0.0437517702453652</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>-0.003816438702714364</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0.017404526876991</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>-0.006552827299115341</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.07142857142857145</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0.0861344537815126</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.08200000000000005</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0.1657037037037037</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.3412962962962963</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0.02600000000000002</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.02600000000000002</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>-0.1755925925925926</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.1755925925925926</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>76.76233632622522</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>71.53789507983056</v>
+      </c>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="n">
+        <v>1.12346911550037</v>
+      </c>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="n">
+        <v>-1.577318830643641</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>5320.76719925354</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-1.107407407407408</v>
+      </c>
+      <c r="DI12" t="inlineStr"/>
+      <c r="DJ12" t="inlineStr"/>
+      <c r="DK12" t="inlineStr"/>
+      <c r="DL12" t="n">
+        <v>-2.94444444444445</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-5922.222222222215</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>4.043116907620885</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.7592592592592524</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SCsTyaGG</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0286666666666664</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.04326896551724135</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1567448275862069</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.09523809523809534</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.04761904761904767</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.009925558312654958</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.032258064516129</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.3571428571428568</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.9523809523809521</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.9640198511166247</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.239454094292804</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1.547619047619047</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.4761904761904763</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.996277915632753</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>6.238213399503721</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.02380952380952395</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.4044665012406947</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.0161290322580645</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.2380952380952381</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.3002481389578162</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0.3399503722084367</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.001831691427964799</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5891439909297049</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-2.345083654089423</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-2.190189799366146</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-117.012360979529</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>33.9972032416984</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-28.65528873107226</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>12.04155406118073</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-22.90000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.366666666666674</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-22.78666666666666</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>23.11999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-31.59999999999999</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-22.61333333333334</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>18.60666666666667</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-7.88095238095238</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-3.047619047619051</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-10.6575682382134</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.2208436724565743</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-8.690476190476183</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>8.69047619047619</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-12.83995037220843</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>12.83995037220843</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>9.399999999999977</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-103.2041379310345</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>135.8289655172414</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.3990000000000001</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.1380000000000001</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.2077655172413793</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0.1250206896551724</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0.657142857142857</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2600000000000002</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-3.261904761904759</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-6.452380952380953</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1.676178660049629</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-4.462779156327546</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>4.355531829442612</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>7.627458917237401</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>3.50946342214254</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0.3038365335679458</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0.01171389073315971</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.02617714264599844</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0.01588724681923933</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.03105093463557696</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.4047619047619048</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.119047619047619</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.1364764267990075</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.1017369727047147</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0.1380000000000001</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.3990000000000001</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.1250206896551724</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0.2077655172413793</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0.5369999999999999</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.5369999999999999</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.3327862068965516</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.3327862068965516</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>77.97768424990646</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>77.45470085470086</v>
+      </c>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="n">
+        <v>1.306262323770056</v>
+      </c>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="n">
+        <v>0.4607811908134778</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>13595.51683945891</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.4065945165945379</v>
+      </c>
+      <c r="DI13" t="inlineStr"/>
+      <c r="DJ13" t="inlineStr"/>
+      <c r="DK13" t="inlineStr"/>
+      <c r="DL13" t="n">
+        <v>0.0927922077922112</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>8974.660894660905</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.09456012572840677</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-1.201673881673898</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KnvLwLo4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.094</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.4257692307692309</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4258241758241756</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.3406593406593406</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-1.266666666666666</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.9666666666666668</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.162087912087912</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.8406593406593408</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.967032967032967</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>-1.552197802197801</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-1.166666666666667</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.162087912087912</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.3351648351648351</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.06318681318681318</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0.1181318681318679</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1.966683643154231</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.09141414141414117</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1.281792985286054</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.048223152000624</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-28.20658665117685</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>33.00547797687801</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>75.80921267142202</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>20.06099622805803</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-8.099999999999994</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>5.599999999999994</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>19.48444444444445</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.971851851851852</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-10.35</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.949629629629626</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-2.634074074074078</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-4.899999999999999</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.833333333333336</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-4.91758241758242</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.796703296703299</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-7.233333333333334</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>7.233333333333334</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.9203296703296715</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.9203296703296715</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>144.6</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-64.76923076923077</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>65.67948717948718</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-0.306</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0.8219999999999998</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.01038461538461544</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.04115384615384615</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.4333333333333336</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0.9333333333333336</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-0.04558404558404572</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0.6438746438746439</v>
+      </c>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-5.966666666666665</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-6.596153846153847</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-14.77472527472527</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>4.413301523745071</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-1.517524053026124</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>-0.7570736316601518</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-1.496003411397064</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.05045869119015615</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0.02273082371131323</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.01102694701027283</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.008167901613804943</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.01923076923076922</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>-0.08791208791208793</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.8219999999999998</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0.04115384615384615</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0.01038461538461544</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>-0.03076923076923086</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.03076923076923086</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>71.87369345630215</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>77.80239393939394</v>
+      </c>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="n">
+        <v>1.093302816931413</v>
+      </c>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="n">
+        <v>1.654996595638</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-33457.80519428723</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-1.278282828282812</v>
+      </c>
+      <c r="DI14" t="inlineStr"/>
+      <c r="DJ14" t="inlineStr"/>
+      <c r="DK14" t="inlineStr"/>
+      <c r="DL14" t="n">
+        <v>-0.6904040404040437</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-53101.85185185185</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-4.27329629665239</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-6.955387205387211</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>K0JghK0c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.5919999999999999</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.138</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.8823209549071616</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.6079310344827589</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.9666666666666667</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6333333333333332</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-2.514285714285714</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.942857142857143</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.533333333333334</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-4.77142857142857</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.742857142857142</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-9.733333333333333</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>4.166666666666668</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.7142857142857142</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.228571428571428</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-1.828571428571429</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.685714285714285</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.03180745982603561</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2.846392496392497</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.986688500063807</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-2.750354282656914</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-19.20433110182049</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.814624950288731</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>76.65811382164131</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-6.669018220292742</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-20.91666666666667</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-36.82758620689654</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>30.13793103448276</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-21.83333333333334</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>12.08333333333334</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-26.75862068965517</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>20.55172413793103</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-7.62857142857143</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-3.657142857142851</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-7.100000000000001</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.5666666666666629</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-13.71428571428572</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>13.71428571428572</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-12.83333333333334</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>12.83333333333334</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-187.8</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>65.19999999999999</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-154.4444444444444</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>105.8888888888889</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.4080000000000001</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-0.3086604774535809</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0.3191246684350133</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0.9142857142857144</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0.7428571428571429</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.6379310344827587</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.5517241379310347</v>
+      </c>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0.4571428571428591</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-2.285714285714285</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>-0.4333333333333336</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.7000000000000028</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-1.520123163589341</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-8.818414470833826</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>3.469596484197721</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-5.874495949665461</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.02780269276754174</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.01085457628678197</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0.00624074572889096</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0.01040049736242451</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.6571428571428573</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0.05714285714285716</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-1.462</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0.4080000000000001</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0.3191246684350133</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0.3086604774535809</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>-0.6277851458885941</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.6277851458885941</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>77.13436026936027</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>77.21515993265993</v>
+      </c>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="n">
+        <v>-1.984080298786239</v>
+      </c>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="n">
+        <v>3.186566293183944</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>-47897.31289951879</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-0.4132575757575978</v>
+      </c>
+      <c r="DI15" t="inlineStr"/>
+      <c r="DJ15" t="inlineStr"/>
+      <c r="DK15" t="inlineStr"/>
+      <c r="DL15" t="n">
+        <v>0.1372895622895633</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-106083.8383838383</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>-3.459433132227261</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-8.587500000000006</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WQcQHwPp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.2180000000000004</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2119999999999997</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.5539930555555557</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.03631944444444435</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.3142857142857143</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2931034482758621</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.07219827586206895</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.2285714285714286</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.771428571428572</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.453663793103448</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5118534482758621</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-3.77142857142857</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.77142857142857</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.2165948275862064</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0.05714285714285738</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.8987068965517242</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.0581896551724137</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.3714285714285715</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.5614224137931034</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0.4698275862068966</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0.9969371245001502</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.174869750132908</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.442134386123697</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-2.45470481657537</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-95.41064619691286</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>16.21434061405719</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>83.14228975872879</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-20.17604366878811</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.7741935483871032</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.292626728110605</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-5.583333333333336</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11.83333333333334</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-1.483870967741936</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13.13479262672811</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.228571428571428</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.314285714285717</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.8879310344827616</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.225215517241381</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-2.114285714285714</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.114285714285714</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-2.635775862068968</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>2.635775862068968</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>2.399999999999977</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>79.39999999999998</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-58.14303959131541</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>18.20817369093231</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0.01200000000000007</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.4992476851851851</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0.006226851851851865</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>1.028571428571428</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.05714285714285738</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.2370689655172415</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0.1045258620689653</v>
+      </c>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.1428571428571429</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>-1.600000000000001</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>3</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-0.65625</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.891163793103448</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>7.4418310049124</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-2.143343596652418</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.095541167192383</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-5.692664914556897</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.001686948197702126</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>-0.002904089283362297</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0.01007743882500926</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0.02137479460949619</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.02857142857142853</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0.05714285714285716</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0.06034482758620691</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>-0.1918103448275862</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0.01200000000000007</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>-0.382</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0.006226851851851865</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0.4992476851851851</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.394</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0.5054745370370369</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>-0.5054745370370369</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>77.8596985479798</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>77.22801159745605</v>
+      </c>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="n">
+        <v>3.11115483347487</v>
+      </c>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="n">
+        <v>0.1220354940395119</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>35112.04127896218</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>2.01422077922075</v>
+      </c>
+      <c r="DI16" t="inlineStr"/>
+      <c r="DJ16" t="inlineStr"/>
+      <c r="DK16" t="inlineStr"/>
+      <c r="DL16" t="n">
+        <v>-2.848174603174602</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>27269.40115440115</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>5.439694047579508</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>3.931839826839806</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>l6f1Na1N</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3819999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2306730769230771</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1470512820512822</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.09523809523809523</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.07671957671957674</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0.1653439153439153</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.619047619047619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.115079365079366</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-1.05952380952381</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>-3.404761904761905</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.047619047619046</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.563492063492065</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>-1.720899470899473</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.3121693121693121</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-0.322751322751323</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.5476190476190474</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>-0.3809523809523809</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0.05952380952380953</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0.6010989010989012</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3.429147143220371</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.3045807258858066</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.488819265766365</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-119.0032173039006</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>93.80811569710912</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-4.154526246738442</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>53.4792035518021</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.700000000000003</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-3.933333333333323</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.236467236467234</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.564102564102555</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>9.299999999999997</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-7.633333333333333</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>6.720797720797719</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>10.23646723646723</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-1.761904761904759</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-4.428571428571431</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>-2.943121693121689</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-3.153439153439152</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>5.904761904761905</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-5.904761904761905</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1.603174603174601</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>-1.603174603174601</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>16.19999999999999</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>29.00000000000006</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-22.02153846153846</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-39.74615384615379</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0.04176282051282051</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>-0.1766666666666666</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>-1.238095238095238</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.8809523809523812</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0.1415343915343912</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0.2923280423280423</v>
+      </c>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="n">
+        <v>-0.4166666666666667</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>-10.88095238095238</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>-2.357142857142858</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>-4.62962962962963</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>-5.593915343915345</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>9.407355006105007</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>-1.640954052935186</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>1.975605388076644</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.9114337765498597</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.007482744044608629</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>-0.007287553863618353</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>-0.01204505154594282</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>-0.009226863320609881</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>-0.1904761904761905</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0.02380952380952381</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0.06746031746031747</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0.1177248677248677</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0.1766666666666666</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>-0.04176282051282051</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>-0.468</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0.2184294871794871</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>-0.2184294871794871</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>78.68445998445999</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>77.11769547325103</v>
+      </c>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="n">
+        <v>-1.183830126253355</v>
+      </c>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="n">
+        <v>-4.966345351676487</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-19414.42116077414</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0.3458874458874277</v>
+      </c>
+      <c r="DI17" t="inlineStr"/>
+      <c r="DJ17" t="inlineStr"/>
+      <c r="DK17" t="inlineStr"/>
+      <c r="DL17" t="n">
+        <v>-2.280471380471383</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>-21714.68855218855</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>-6.630600538877218</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>-5.013552188552197</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>bXkCusHi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.3740000000000001</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.1740166666666667</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1295333333333331</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-0.2592592592592593</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1693121693121693</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.4285714285714284</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8571428571428577</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.8412698412698409</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.7420634920634921</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.5714285714285712</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.6362433862433861</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.728835978835978</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0.7023809523809524</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.05687830687830675</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.335978835978836</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.3108465608465609</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-0.2949110413396125</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0.9951519069166128</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.759264205251569</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-1.227953560307324</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.2021811768585735</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>68.40577625801041</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>-5.997052815615831</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>45.33676619359531</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-24.83333333333334</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>-7.183760683760696</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-4.491452991453002</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-7.333333333333329</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>14.66666666666666</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.075498575498578</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7.549857549857549</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.285714285714285</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>4.857142857142854</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.650793650793652</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.175925925925924</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-11.85714285714286</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>11.85714285714286</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-2.68783068783069</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2.68783068783069</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-151.2</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>79.40000000000003</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-59.70333333333332</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-29.36000000000001</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>0.5740000000000001</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0.5709833333333334</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-0.06953333333333335</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0.04761904761904789</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.03988603988603989</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.4031339031339032</v>
+      </c>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>-0.1666666666666666</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-0.428571428571427</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.8571428571428577</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0.9537037037037024</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>-2.907407407407408</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>-5.599878411019716</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-4.686327561327563</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-1.847622890490456</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>-0.09183411872465008</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>-0.006394914250484995</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.001774040970628929</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>-0.008449757145219276</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0.01825640232394528</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>0.06084656084656087</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>-1.166</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>-0.5740000000000001</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0.06953333333333335</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0.5709833333333334</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>-0.592</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0.50145</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>0.50145</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>77.34566030677142</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>77.25871717171717</v>
+      </c>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="n">
+        <v>0.4065142373965784</v>
+      </c>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="n">
+        <v>-0.9913978178684069</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>-2900.544716721179</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>0.1890331890331822</v>
+      </c>
+      <c r="DI18" t="inlineStr"/>
+      <c r="DJ18" t="inlineStr"/>
+      <c r="DK18" t="inlineStr"/>
+      <c r="DL18" t="n">
+        <v>1.97893217893218</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>-1735.209235209237</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-1.008850789733145</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>-1.070274170274189</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>GhdgPLWA</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3560000000000001</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3740000000000001</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5027976190476189</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.4141071428571431</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-0.03333333333333333</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.06666666666666665</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.6333333333333329</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.7000000000000002</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-1.541666666666667</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>-1.633333333333335</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.333333333333334</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.033333333333335</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>-1.933333333333334</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.7833333333333334</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>-0.8916666666666666</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>-0.5441257816257816</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.3969191919191921</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.3930211128740551</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.3781178070916202</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-49.39758445070785</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>105.4093787281836</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-32.74196694996425</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.492769186378979</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.2000000000000028</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-12.40000000000001</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-2.914542728635681</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-8.542728635682167</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-0.7999999999999972</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>13.73613193403299</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-3.806596701649177</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-6.033333333333335</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0.6000000000000014</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-1.516666666666662</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-7.733333333333334</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>7.733333333333334</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-2.333333333333336</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>2.333333333333336</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-60</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-29.79999999999995</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>64.125</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>-68</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.04399999999999998</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-1.374</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>0.4019642857142856</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-0.2525595238095238</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>1.966666666666667</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0.7666666666666668</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>0.4942028985507245</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-0.2797101449275363</v>
+      </c>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="n">
+        <v>-0.3333333333333334</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>4.666666666666668</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>7.483333333333334</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>6.866666666666667</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>-1.955092906784081</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>-3.637141003116367</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>1.326984570230358</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>6.585944978070749</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>-0.02095391494651245</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>-0.03754618734146596</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>-0.01508338797782612</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>-0.009280538159540712</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>-0.008333333333333331</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>1.374</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>-0.04399999999999998</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>0.2525595238095238</v>
+      </c>
+      <c r="CU19" t="n">
+        <v>-0.4019642857142856</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>-1.418</v>
+      </c>
+      <c r="CX19" t="n">
+        <v>0.6545238095238094</v>
+      </c>
+      <c r="CY19" t="n">
+        <v>-0.6545238095238094</v>
+      </c>
+      <c r="CZ19" t="n">
+        <v>78.14965963987703</v>
+      </c>
+      <c r="DA19" t="n">
+        <v>71.89554162312784</v>
+      </c>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="n">
+        <v>-1.541555911408864</v>
+      </c>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="n">
+        <v>-1.787571333894867</v>
+      </c>
+      <c r="DG19" t="n">
+        <v>60060.8506689389</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>0.841161616161628</v>
+      </c>
+      <c r="DI19" t="inlineStr"/>
+      <c r="DJ19" t="inlineStr"/>
+      <c r="DK19" t="inlineStr"/>
+      <c r="DL19" t="n">
+        <v>-1.869444444444444</v>
+      </c>
+      <c r="DM19" t="n">
+        <v>85432.57575757576</v>
+      </c>
+      <c r="DN19" t="n">
+        <v>4.432771721742313</v>
+      </c>
+      <c r="DO19" t="n">
+        <v>8.414898989899001</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4hy7UG8j</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45563.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>QHesBmSQ</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>-13</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.07200000000000006</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1062250712250712</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.2794301994301991</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.3095238095238094</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.3103448275862069</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.3103448275862069</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1428571428571432</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-0.3448275862068968</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.6206896551724141</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>-2.357142857142858</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.3333333333333339</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>-1.310344827586208</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>-0.8275862068965516</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.2619047619047619</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>-0.03448275862068972</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-0.0714285714285714</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-0.1724137931034482</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0.1379310344827587</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.8402282241567951</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>-1.416535250463822</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.270171972524112</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.5524114430461173</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>-9.416346010666757</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>109.0001529146221</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-6.166255473384695</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>9.701791481175945</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-7.200000000000003</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>20.86666666666667</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-5.142857142857153</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.066666666666663</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.433333333333337</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-4.678571428571431</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>8.035714285714285</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-2.785714285714285</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>6.047619047619051</v>
+      </c>
+      <c r="BF20" t="n">
         <v>-1</v>
       </c>
-      <c r="S3" t="n">
+      <c r="BG20" t="n">
+        <v>5.551724137931032</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-11</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>11.16666666666666</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-7.896551724137929</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7.931034482758619</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-69.19999999999999</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>72</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-70.56592592592591</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>74.96444444444444</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-0.128</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.1575071225071225</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0.4133333333333333</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.9523809523809521</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>1.738095238095238</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.2142857142857144</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>1.285714285714285</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>3.103448275862071</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>1.793103448275865</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>4.68523810252648</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>-4.746658257475005</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>2.322570811436652</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>-5.359979020415802</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>-0.01843976751054382</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>-0.01709558486747858</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>-0.004823975221497974</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>0.0002024947478102349</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>-0.1428571428571428</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>-0.103448275862069</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>-0.03448275862068967</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CT20" t="n">
+        <v>-0.4133333333333333</v>
+      </c>
+      <c r="CU20" t="n">
+        <v>0.1575071225071225</v>
+      </c>
+      <c r="CV20" t="n">
+        <v>-0.222</v>
+      </c>
+      <c r="CW20" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="CX20" t="n">
+        <v>-0.5708404558404558</v>
+      </c>
+      <c r="CY20" t="n">
+        <v>0.5708404558404558</v>
+      </c>
+      <c r="CZ20" t="n">
+        <v>77.08740179573513</v>
+      </c>
+      <c r="DA20" t="n">
+        <v>77.14801587301586</v>
+      </c>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="n">
+        <v>0.8057318880213984</v>
+      </c>
+      <c r="DD20" t="inlineStr"/>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="n">
+        <v>-2.3632468065931</v>
+      </c>
+      <c r="DG20" t="n">
+        <v>-13109.31313028643</v>
+      </c>
+      <c r="DH20" t="n">
+        <v>-0.3598484848484986</v>
+      </c>
+      <c r="DI20" t="inlineStr"/>
+      <c r="DJ20" t="inlineStr"/>
+      <c r="DK20" t="inlineStr"/>
+      <c r="DL20" t="n">
+        <v>-1.079816017316016</v>
+      </c>
+      <c r="DM20" t="n">
+        <v>-12429.61038961039</v>
+      </c>
+      <c r="DN20" t="n">
+        <v>-0.30810736188009</v>
+      </c>
+      <c r="DO20" t="n">
+        <v>-0.989231601731575</v>
+      </c>
+      <c r="DP20" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="n">
-        <v>0.3099999999999998</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-0.2933333333333332</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.6666666666666667</v>
-      </c>
-      <c r="X3" t="n">
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>8MkyzwoT</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45563.35416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>-2.666666666666666</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.333333333333334</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
+      <c r="P21" t="n">
+        <v>-0.3703333333333334</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.1658303464755075</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.6514336917562723</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.629032258064516</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.4804147465437788</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.833333333333333</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-1.965437788018433</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.399769585253456</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.833333333333332</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-5.561059907834101</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>7.22004608294931</v>
+      </c>
+      <c r="AF21" t="n">
         <v>-1</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG21" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-0.4308755760368661</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.7937788018433181</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>-0.7523041474654377</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0.7027649769585254</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-3.491341991341991</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-3.612111499611499</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.318054980879876</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-2.579036832443251</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>-42.60384473741894</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-42.18068448546856</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9.008263645195541</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-21.4799887769112</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-8.799999999999997</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-34.00370370370371</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>44.76296296296296</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-34.6</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>38.40000000000001</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-35.20370370370371</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>28.50740740740741</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-0.8333333333333357</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>14.16666666666667</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.0864055299539217</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>13.60253456221199</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-15.83333333333334</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>15.83333333333334</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-17.39861751152073</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>17.39861751152073</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>-286.6</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>93.19999999999999</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-262.3592592592593</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>121.5592592592592</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.7296666666666666</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-0.8139999999999998</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-0.2571087216248507</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0.1621863799283154</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>0.4699872286079183</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>0.5657726692209453</v>
+      </c>
+      <c r="BX21" t="n">
         <v>1</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="BY21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>1</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="CA21" t="n">
         <v>-1</v>
       </c>
-      <c r="AH3" t="n">
-        <v>3.333333333333334</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-5.333333333333334</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>19.33333333333333</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-19.33333333333333</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>76.90909090909092</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-345</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>-9416271.591970123</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.04785247432306505</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>-24897870.37037037</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.2425925925926435</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>-1.503618113912239</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>-257000000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.9083333333333314</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>-335</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>-0.375</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.03014705882352953</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-1.470716619981317</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.561041083099866</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-2.645370370370372</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>-2.216666666666669</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1</v>
+      <c r="CB21" t="n">
+        <v>1.666666666666668</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>5.59447004608295</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>3.294930875576039</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>3.663339474743152</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>-13.41401771111838</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0.6773407604377475</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>-10.89089872709219</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>-0.05175466400096902</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.00990138977773404</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>-0.02822068730780342</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>0.01911611655663749</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>-0.2050691244239632</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>0.03917050691244239</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>0.8139999999999998</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>0.7296666666666666</v>
+      </c>
+      <c r="CT21" t="n">
+        <v>-0.1621863799283154</v>
+      </c>
+      <c r="CU21" t="n">
+        <v>0.2571087216248507</v>
+      </c>
+      <c r="CV21" t="n">
+        <v>0.08433333333333337</v>
+      </c>
+      <c r="CW21" t="n">
+        <v>-0.08433333333333337</v>
+      </c>
+      <c r="CX21" t="n">
+        <v>-0.4192951015531661</v>
+      </c>
+      <c r="CY21" t="n">
+        <v>0.4192951015531661</v>
+      </c>
+      <c r="CZ21" t="n">
+        <v>76.82220418470419</v>
+      </c>
+      <c r="DA21" t="n">
+        <v>77.39312479635061</v>
+      </c>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="n">
+        <v>1.380303768411153</v>
+      </c>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="n">
+        <v>0.1811265890448865</v>
+      </c>
+      <c r="DG21" t="n">
+        <v>-48913.03898769828</v>
+      </c>
+      <c r="DH21" t="n">
+        <v>5.101515151515173</v>
+      </c>
+      <c r="DI21" t="inlineStr"/>
+      <c r="DJ21" t="inlineStr"/>
+      <c r="DK21" t="inlineStr"/>
+      <c r="DL21" t="n">
+        <v>1.243939393939389</v>
+      </c>
+      <c r="DM21" t="n">
+        <v>-69775.75757575758</v>
+      </c>
+      <c r="DN21" t="n">
+        <v>-3.233209674723497</v>
+      </c>
+      <c r="DO21" t="n">
+        <v>-4.057575757575762</v>
+      </c>
+      <c r="DP21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW13"/>
+  <dimension ref="A1:BW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,144 +695,144 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>EqY7Orsg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45592.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">emirates stadium
+  london </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>lId4TMwf</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,209 +859,209 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8266666666666669</v>
+        <v>0.4024999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.905614814814815</v>
+        <v>1.345370370370371</v>
       </c>
       <c r="R2" t="n">
-        <v>0.75</v>
+        <v>-0.2999999999999998</v>
       </c>
       <c r="S2" t="n">
-        <v>2.957142857142857</v>
+        <v>1.585714285714286</v>
       </c>
       <c r="T2" t="n">
-        <v>6.416666666666667</v>
+        <v>4.950000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>6.212857142857143</v>
+        <v>3.778571428571428</v>
       </c>
       <c r="V2" t="n">
-        <v>9.833333333333334</v>
+        <v>8.049999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>17.88571428571429</v>
+        <v>8.661428571428573</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.732857142857143</v>
+        <v>0.7785714285714287</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.5</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.01</v>
+        <v>0.6342857142857143</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.48306182121971</v>
+        <v>18.68447693090684</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.79118489318707</v>
+        <v>19.78705383152251</v>
       </c>
       <c r="AD2" t="n">
-        <v>824.7458402953209</v>
+        <v>888.5744039633655</v>
       </c>
       <c r="AE2" t="n">
-        <v>894.9609185522844</v>
+        <v>936.9556303881934</v>
       </c>
       <c r="AF2" t="n">
-        <v>30.5</v>
+        <v>-6</v>
       </c>
       <c r="AG2" t="n">
-        <v>39.35576923076924</v>
+        <v>12.16783216783216</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>-24</v>
       </c>
       <c r="AI2" t="n">
-        <v>46.90384615384616</v>
+        <v>39.04545454545454</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.8333333333333357</v>
+        <v>1.599999999999998</v>
       </c>
       <c r="AK2" t="n">
-        <v>9.390000000000004</v>
+        <v>3.69285714285714</v>
       </c>
       <c r="AL2" t="n">
-        <v>8</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="AM2" t="n">
-        <v>8.374285714285705</v>
+        <v>-0.462857142857132</v>
       </c>
       <c r="AN2" t="n">
-        <v>112</v>
+        <v>-50</v>
       </c>
       <c r="AO2" t="n">
-        <v>85.08333333333326</v>
+        <v>-24.49999999999989</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.984615384615384</v>
+        <v>-0.4404761904761907</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-0.3500000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.41666666666667</v>
+        <v>6.200000000000003</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.44142857142857</v>
+        <v>1.437142857142856</v>
       </c>
       <c r="AV2" t="n">
-        <v>-14.95887931512932</v>
+        <v>-6.18243378254941</v>
       </c>
       <c r="AW2" t="n">
-        <v>-5.606082879044084</v>
+        <v>-0.9399569320134553</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05994594563142951</v>
+        <v>0.01013117059361546</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0216511595289043</v>
+        <v>0.03292252020111551</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.4166666666666666</v>
+        <v>-0.55</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2542857142857143</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+        <v>-0.08571428571428574</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-1.301041666666666</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.5980249143971967</v>
+      </c>
       <c r="BD2" t="n">
-        <v>2.090221113268882</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.527401782364596</v>
-      </c>
+        <v>-4.474926839464899</v>
+      </c>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>18464132.39538239</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>31649.3145743146</v>
-      </c>
+        <v>0.07171717171717074</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
-        <v>3.951064213564223</v>
-      </c>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>0.5496933621933238</v>
-      </c>
+        <v>-0.8254419191919169</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-3631347.746456444</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
       <c r="BL2" t="n">
-        <v>3.611796536796533</v>
+        <v>-0.2859335184742804</v>
       </c>
       <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>1.307124819624804</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-3379.932438842618</v>
-      </c>
+        <v>-2.134526297977388</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>0.4607063925141728</v>
+        <v>-1.835290404040393</v>
       </c>
       <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>15648.16919191915</v>
+      </c>
       <c r="BT2" t="n">
-        <v>-0.07022231995057382</v>
+        <v>-0.3953282828282738</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.305648479254032</v>
+        <v>0.1588429686255779</v>
       </c>
       <c r="BV2" t="n">
-        <v>6028982.870676238</v>
+        <v>11982.3675645007</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.320833333333334</v>
+        <v>3175852.272727281</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>EcDtwrdn</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
+          <t xml:space="preserve">stamford bridge
+  london </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>p6ahwuwJ</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1088,209 +1088,207 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.273333333333334</v>
+        <v>1.0175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3048</v>
+        <v>1.163960292580982</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.75</v>
+        <v>1.8</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.524444444444445</v>
+        <v>1.211764705882353</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.833333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.527407407407407</v>
+        <v>3.713725490196079</v>
       </c>
       <c r="V3" t="n">
-        <v>-4.666666666666668</v>
+        <v>4.199999999999998</v>
       </c>
       <c r="W3" t="n">
-        <v>-9.482962962962963</v>
+        <v>7.664705882352941</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1.474074074074074</v>
+        <v>1.080392156862745</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1.68</v>
+        <v>1.523529411764706</v>
       </c>
       <c r="AB3" t="n">
-        <v>20.79411764705882</v>
+        <v>22.14322677322677</v>
       </c>
       <c r="AC3" t="n">
-        <v>25.59308002766895</v>
+        <v>19.03242812225172</v>
       </c>
       <c r="AD3" t="n">
-        <v>1089.059424324118</v>
+        <v>972.5757180759391</v>
       </c>
       <c r="AE3" t="n">
-        <v>1086.681684463652</v>
+        <v>866.3645645242561</v>
       </c>
       <c r="AF3" t="n">
-        <v>-47.83333333333333</v>
+        <v>24.66666666666669</v>
       </c>
       <c r="AG3" t="n">
-        <v>-60.24038461538461</v>
+        <v>35.69642857142857</v>
       </c>
       <c r="AH3" t="n">
-        <v>-43.83333333333334</v>
+        <v>-4.333333333333329</v>
       </c>
       <c r="AI3" t="n">
-        <v>-36.51602564102565</v>
+        <v>19.62053571428572</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-11</v>
+        <v>-10.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>-11.80888888888889</v>
+        <v>1.927450980392159</v>
       </c>
       <c r="AL3" t="n">
-        <v>-29.33333333333333</v>
+        <v>-4</v>
       </c>
       <c r="AM3" t="n">
-        <v>-24.52444444444444</v>
+        <v>16.61960784313726</v>
       </c>
       <c r="AN3" t="n">
-        <v>-328.3333333333334</v>
+        <v>-123.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-276.9583333333334</v>
+        <v>125.5925925925926</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.416666666666667</v>
+        <v>2.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4966329966329965</v>
+        <v>0.1941176470588233</v>
       </c>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>10.83333333333333</v>
+        <v>9.999999999999996</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.84</v>
+        <v>1.654901960784315</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.457455920078463</v>
+        <v>1.955327394041593</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.619433638041372</v>
+        <v>-4.453829242797788</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.01821357536242923</v>
+        <v>-0.01896372510622004</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.0144675204521035</v>
+        <v>-0.002678222792586921</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.08333333333333331</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.1288888888888889</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+        <v>0.1803921568627451</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>-4.335353535353534</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>-3.080528610249974</v>
+      </c>
       <c r="BD3" t="n">
-        <v>0.9070259084836039</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.846043931415451</v>
-      </c>
+        <v>-1.925434962354444</v>
+      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>-44675885.44171879</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-125544.8372615039</v>
-      </c>
+        <v>-0.5250000000000001</v>
+      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>-6.907427449094115</v>
-      </c>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="n">
-        <v>1.145093795093771</v>
-      </c>
+        <v>0.01338383838383095</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>8480040.86188006</v>
+      </c>
+      <c r="BK3" t="inlineStr"/>
       <c r="BL3" t="n">
-        <v>0.5744829244829255</v>
+        <v>3.42808109145183</v>
       </c>
       <c r="BM3" t="inlineStr"/>
       <c r="BN3" t="n">
-        <v>-6.21959275292609</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>-82195.7946966461</v>
-      </c>
+        <v>1.372677504527346</v>
+      </c>
+      <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
       <c r="BQ3" t="n">
-        <v>-1.166786308233676</v>
+        <v>-3.036868686868672</v>
       </c>
       <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
+      <c r="BS3" t="n">
+        <v>-7696.590909090883</v>
+      </c>
       <c r="BT3" t="n">
-        <v>-5.255760185042945</v>
+        <v>2.852777777777774</v>
       </c>
       <c r="BU3" t="n">
-        <v>-3.992402006127492</v>
+        <v>-0.1183566798698377</v>
       </c>
       <c r="BV3" t="n">
-        <v>-28895081.26553147</v>
+        <v>11646.47532621607</v>
       </c>
       <c r="BW3" t="n">
-        <v>-1.760012826679493</v>
+        <v>6952266.414141417</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ShJjaSDs</t>
+          <t>EJlHkLuh</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitality stadium
-  bournemouth </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hA1Zm19f</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1317,209 +1315,209 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Aotm1TVI</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.683333333333334</v>
+        <v>-0.3880000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.3936454849498332</v>
+        <v>0.03001436781609157</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>-1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2584615384615386</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="T4" t="n">
-        <v>4.666666666666667</v>
+        <v>-0.8000000000000007</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.152307692307692</v>
+        <v>-0.3275862068965516</v>
       </c>
       <c r="V4" t="n">
-        <v>17.66666666666667</v>
+        <v>-1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5369230769230757</v>
+        <v>1.759946949602121</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1.127692307692308</v>
+        <v>-0.02254641909814303</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1.444615384615385</v>
+        <v>-0.06763925729442954</v>
       </c>
       <c r="AB4" t="n">
-        <v>13.90394357104883</v>
+        <v>22.33531087270218</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.74838845071183</v>
+        <v>24.0179034719913</v>
       </c>
       <c r="AD4" t="n">
-        <v>861.7609814383254</v>
+        <v>998.8140351609502</v>
       </c>
       <c r="AE4" t="n">
-        <v>970.3913461408969</v>
+        <v>989.7971985991728</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.5</v>
+        <v>-48.66666666666667</v>
       </c>
       <c r="AG4" t="n">
-        <v>-21.75666666666666</v>
+        <v>-4.763888888888886</v>
       </c>
       <c r="AH4" t="n">
-        <v>-5.5</v>
+        <v>-28</v>
       </c>
       <c r="AI4" t="n">
-        <v>-15.02833333333334</v>
+        <v>4.300925925925924</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2.333333333333332</v>
+        <v>-11.8</v>
       </c>
       <c r="AK4" t="n">
-        <v>-2.458461538461538</v>
+        <v>3.03580901856764</v>
       </c>
       <c r="AL4" t="n">
-        <v>-4.666666666666657</v>
+        <v>-12.40000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-22.61538461538461</v>
+        <v>-13.32360742705571</v>
       </c>
       <c r="AN4" t="n">
-        <v>-50.00000000000006</v>
+        <v>-171.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>-210.219696969697</v>
+        <v>-137.375</v>
       </c>
       <c r="AP4" t="n">
-        <v>-2.666666666666667</v>
+        <v>-0.5999999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.7628205128205126</v>
+        <v>-0.3485714285714288</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.66666666666667</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.669230769230769</v>
+        <v>-5.388594164456233</v>
       </c>
       <c r="AV4" t="n">
-        <v>-5.497943049061206</v>
+        <v>13.93371910218216</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.945412243634214</v>
+        <v>9.854639460291327</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.02637835393270176</v>
+        <v>-0.0002690457239593533</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0008158437450973624</v>
+        <v>0.003532523175472646</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-1</v>
+        <v>-0.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.4400000000000001</v>
-      </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
+        <v>-0.103448275862069</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.970061728395056</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.996401525353733</v>
+      </c>
       <c r="BD4" t="n">
-        <v>1.24357916699671</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-0.1816396292858862</v>
-      </c>
+        <v>-3.561333352785596</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>-42905173.61111112</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>-97262.5</v>
-      </c>
+        <v>-0.2159611992945325</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>-6.946875000000006</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
-        <v>-1.167013888888903</v>
-      </c>
+        <v>-0.8423280423280488</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-5287633.029529475</v>
+      </c>
+      <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="n">
-        <v>-0.01701388888888289</v>
+        <v>-1.821678457707876</v>
       </c>
       <c r="BM4" t="inlineStr"/>
       <c r="BN4" t="n">
-        <v>-5.993055555555557</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-65235.93873934748</v>
-      </c>
+        <v>0.08684874947130083</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr"/>
       <c r="BQ4" t="n">
-        <v>-1.348442655667719</v>
+        <v>-0.5857142857142605</v>
       </c>
       <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
+      <c r="BS4" t="n">
+        <v>-13915.21164021162</v>
+      </c>
       <c r="BT4" t="n">
-        <v>-4.364642644138314</v>
+        <v>-2.779497354497352</v>
       </c>
       <c r="BU4" t="n">
-        <v>-3.445223900850493</v>
+        <v>-0.0258574939947489</v>
       </c>
       <c r="BV4" t="n">
-        <v>-20532666.19179343</v>
+        <v>-7316.916739986598</v>
       </c>
       <c r="BW4" t="n">
-        <v>-2.071874999999999</v>
+        <v>-10208349.86772487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n9EQB5cm</t>
+          <t>zD1kyMQb</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45592.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">coote d 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  james  park
-  newcastle </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>p6ahwuwJ</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,211 +1544,209 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>0K79iBXL</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2900000000000003</v>
+        <v>-0.5525</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.183511705685619</v>
+        <v>0.3108333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.586538461538462</v>
+        <v>1.08</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.916666666666667</v>
+        <v>-2.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.782051282051283</v>
+        <v>0.3599999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.5</v>
+        <v>-5.599999999999998</v>
       </c>
       <c r="W5" t="n">
-        <v>2.673076923076923</v>
+        <v>1.639999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4166666666666667</v>
+        <v>-0.2000000000000002</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.522435897435897</v>
+        <v>0.3599999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.25</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.201923076923077</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>25.9492303992304</v>
+        <v>25.00537185037185</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.27539560789965</v>
+        <v>20.41103568000627</v>
       </c>
       <c r="AD5" t="n">
-        <v>1065.744503760177</v>
+        <v>1033.321240211614</v>
       </c>
       <c r="AE5" t="n">
-        <v>1041.620110016067</v>
+        <v>1075.367774456912</v>
       </c>
       <c r="AF5" t="n">
-        <v>-100</v>
+        <v>-31.33333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>-17.2709090909091</v>
+        <v>-36.08695652173913</v>
       </c>
       <c r="AH5" t="n">
-        <v>-72</v>
+        <v>-23</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1.536363636363639</v>
+        <v>-6.260869565217384</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-8.999999999999996</v>
+        <v>-11.8</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.44230769230769</v>
+        <v>-3</v>
       </c>
       <c r="AL5" t="n">
-        <v>-37</v>
+        <v>-36.80000000000001</v>
       </c>
       <c r="AM5" t="n">
-        <v>-21.23717948717949</v>
+        <v>-33.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>-547.3333333333333</v>
+        <v>-335.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>-235.6418181818182</v>
+        <v>-331.9891304347826</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.5833333333333333</v>
+        <v>1.65</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.7541806020066888</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2</v>
-      </c>
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>0.5142857142857142</v>
+        <v>-0.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>-0.7999999999999972</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2.224358974358971</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="AV5" t="n">
-        <v>18.53291526744709</v>
+        <v>37.87571471156625</v>
       </c>
       <c r="AW5" t="n">
-        <v>10.77858110643956</v>
+        <v>12.63068276658319</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03172019252445872</v>
+        <v>-0.002605212041826475</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.03545029955045926</v>
+        <v>-0.008865481970736701</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1666666666666667</v>
+        <v>-0.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.6121794871794872</v>
-      </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.2217372134038769</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.172365388548311</v>
+      </c>
       <c r="BD5" t="n">
-        <v>3.255051478673408</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>3.510815701936647</v>
-      </c>
+        <v>-0.8861477560394064</v>
+      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
-        <v>14289337.12121212</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>42500.88383838384</v>
-      </c>
+        <v>-1.291534391534391</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>4.663510101010104</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="n">
-        <v>3.612373737373758</v>
-      </c>
+        <v>-3.580291005291002</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-13924752.79709445</v>
+      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>1.591287878787877</v>
+        <v>-5.672645978367072</v>
       </c>
       <c r="BM5" t="inlineStr"/>
       <c r="BN5" t="n">
-        <v>1.56805555555556</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>35460.8129073232</v>
-      </c>
+        <v>-3.266978655207495</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr"/>
       <c r="BQ5" t="n">
-        <v>0.6313061289976085</v>
+        <v>-1.655291005290991</v>
       </c>
       <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
+      <c r="BS5" t="n">
+        <v>-39090.34391534394</v>
+      </c>
       <c r="BT5" t="n">
-        <v>-0.2562215023077812</v>
+        <v>-3.817283950617295</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.474960458607327</v>
+        <v>-0.8222234557954373</v>
       </c>
       <c r="BV5" t="n">
-        <v>9121693.869209729</v>
+        <v>-16436.24811911705</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.8327020202020203</v>
+        <v>-20015661.37566138</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tWiaepD6</t>
+          <t>rw5cZaeB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45591.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">portman road
-  ipswich </t>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1777,209 +1773,209 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>vBIoDoo1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6499999999999999</v>
+        <v>-0.6600000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.457666666666667</v>
+        <v>0.9923076923076926</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>1.791871921182266</v>
       </c>
       <c r="T6" t="n">
-        <v>2.666666666666667</v>
+        <v>-0.1666666666666665</v>
       </c>
       <c r="U6" t="n">
-        <v>4.06</v>
+        <v>1.476600985221674</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="W6" t="n">
-        <v>11.27333333333334</v>
+        <v>4.873152709359607</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.553333333333333</v>
+        <v>0.5652709359605912</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.88</v>
+        <v>0.5357142857142856</v>
       </c>
       <c r="AB6" t="n">
-        <v>17.77041716453481</v>
+        <v>20.37657227032227</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.38251074015498</v>
+        <v>19.79920745666209</v>
       </c>
       <c r="AD6" t="n">
-        <v>761.3901708909452</v>
+        <v>967.3161358240334</v>
       </c>
       <c r="AE6" t="n">
-        <v>760.828274764531</v>
+        <v>946.9180953062432</v>
       </c>
       <c r="AF6" t="n">
-        <v>37</v>
+        <v>-6.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>25.73419540229884</v>
+        <v>18.76780626780626</v>
       </c>
       <c r="AH6" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>17.3974358974359</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI6" t="n">
-        <v>32.60919540229886</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>7.333333333333329</v>
-      </c>
       <c r="AK6" t="n">
-        <v>9.653333333333329</v>
+        <v>-2.532019704433495</v>
       </c>
       <c r="AL6" t="n">
-        <v>21.33333333333334</v>
+        <v>-23.33333333333333</v>
       </c>
       <c r="AM6" t="n">
-        <v>26.36</v>
+        <v>-12.71428571428571</v>
       </c>
       <c r="AN6" t="n">
-        <v>178</v>
+        <v>-184.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>241.7608695652174</v>
+        <v>-113.2481884057971</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.6666666666666667</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.5646551724137929</v>
+        <v>-0.4572158365261816</v>
       </c>
       <c r="AR6" t="inlineStr"/>
       <c r="AS6" t="n">
-        <v>-1.333333333333333</v>
+        <v>-1</v>
       </c>
       <c r="AT6" t="n">
-        <v>-5.666666666666668</v>
+        <v>-2.333333333333332</v>
       </c>
       <c r="AU6" t="n">
-        <v>-4.333333333333336</v>
+        <v>-0.6108374384236477</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.253800254151455</v>
+        <v>18.97414562307254</v>
       </c>
       <c r="AW6" t="n">
-        <v>-2.899569478101503</v>
+        <v>8.054312790331013</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01184920581125101</v>
+        <v>0.02016699316966819</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.001272512730085301</v>
+        <v>0.006572878005234178</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2933333333333333</v>
-      </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
+        <v>0.2426108374384237</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.8967171717171674</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.2377233960034459</v>
+      </c>
       <c r="BD6" t="n">
-        <v>-2.4502429086794</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.6429093681802662</v>
-      </c>
+        <v>0.04241022310071685</v>
+      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
-        <v>-4719655.934343435</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-3484.185606060608</v>
-      </c>
+        <v>0.05972222222222223</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="n">
-        <v>-2.487405303030314</v>
-      </c>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
-        <v>0.3784722222222285</v>
-      </c>
+        <v>-0.1147727272727366</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-886326.9966984792</v>
+      </c>
+      <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="n">
-        <v>-2.467803030303028</v>
+        <v>-0.3836045632400982</v>
       </c>
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="n">
-        <v>-0.8496843434343333</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1224.379794755179</v>
-      </c>
+        <v>-0.3998625900480022</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
       <c r="BQ6" t="n">
-        <v>-0.213902584916517</v>
+        <v>-1.497727272727246</v>
       </c>
       <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>-19943.18181818182</v>
+      </c>
       <c r="BT6" t="n">
-        <v>-2.104906191303257</v>
+        <v>0.3419191919191746</v>
       </c>
       <c r="BU6" t="n">
-        <v>-2.137605854614364</v>
+        <v>-0.01288691298282063</v>
       </c>
       <c r="BV6" t="n">
-        <v>-2405181.613292682</v>
+        <v>-21133.82785633424</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.4394255050505049</v>
+        <v>67967.17171717249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Y5lic6rf</t>
+          <t>zypxSHmo</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
-  london </t>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>WdKOwxDM</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2011,204 +2007,206 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6033333333333332</v>
+        <v>1.666</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.353301282051282</v>
+        <v>0.9676728110599082</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8133333333333332</v>
+        <v>1.335294117647059</v>
       </c>
       <c r="T7" t="n">
-        <v>4.166666666666666</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="U7" t="n">
-        <v>1.164444444444444</v>
+        <v>2.825490196078432</v>
       </c>
       <c r="V7" t="n">
-        <v>10.33333333333333</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
-        <v>3.26074074074074</v>
+        <v>11.04117647058824</v>
       </c>
       <c r="X7" t="n">
-        <v>0.25</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4474074074074075</v>
+        <v>1.864705882352941</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.25</v>
+        <v>3.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.04444444444444429</v>
+        <v>1.823529411764706</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.07763902763903</v>
+        <v>15.18328792854655</v>
       </c>
       <c r="AC7" t="n">
-        <v>19.74464845689545</v>
+        <v>15.90964696220469</v>
       </c>
       <c r="AD7" t="n">
-        <v>864.0841842464873</v>
+        <v>874.3284842510021</v>
       </c>
       <c r="AE7" t="n">
-        <v>889.2723224864662</v>
+        <v>883.6829551541744</v>
       </c>
       <c r="AF7" t="n">
-        <v>42.16666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.06730769230769</v>
+        <v>37.6875</v>
       </c>
       <c r="AH7" t="n">
-        <v>33.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="AI7" t="n">
-        <v>15.44871794871796</v>
+        <v>47.36607142857143</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.333333333333336</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.11851851851852</v>
+        <v>10.27843137254902</v>
       </c>
       <c r="AL7" t="n">
-        <v>-11.33333333333333</v>
+        <v>0.6666666666666643</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.229629629629628</v>
+        <v>6.121568627450984</v>
       </c>
       <c r="AN7" t="n">
-        <v>-17</v>
+        <v>122.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>43.79166666666669</v>
+        <v>195.9814814814815</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.166666666666667</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.1461538461538465</v>
-      </c>
-      <c r="AR7" t="inlineStr"/>
+        <v>-1.167342799188641</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
       <c r="AS7" t="n">
-        <v>1.666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.749999999999996</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.128888888888888</v>
+        <v>-1.80392156862745</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.5494524047031497</v>
+        <v>-6.330616609370114</v>
       </c>
       <c r="AW7" t="n">
-        <v>-5.230445376409838</v>
+        <v>-9.285136481148323</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.05986447482506944</v>
+        <v>0.002033505977885097</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01003067901641407</v>
+        <v>0.02046109724968038</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.03703703703703703</v>
-      </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+        <v>0.207843137254902</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.03854166666667425</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.2460457700815013</v>
+      </c>
       <c r="BD7" t="n">
-        <v>1.380567270016428</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>2.816192443276456</v>
-      </c>
+        <v>-1.049348124510971</v>
+      </c>
+      <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
-        <v>-14896796.53679653</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-36520.92352092353</v>
-      </c>
+        <v>2.009690656565657</v>
+      </c>
+      <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="n">
-        <v>-2.84718614718615</v>
-      </c>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
-        <v>0.4178932178932087</v>
-      </c>
+        <v>10.67414772727273</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>35804129.59060227</v>
+      </c>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="n">
-        <v>1.264935064935067</v>
+        <v>7.222887114724699</v>
       </c>
       <c r="BM7" t="inlineStr"/>
       <c r="BN7" t="n">
-        <v>-3.879653679653671</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>-20908.21585458722</v>
-      </c>
+        <v>9.101539734202262</v>
+      </c>
+      <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
       <c r="BQ7" t="n">
-        <v>-0.2595697396449279</v>
+        <v>-1.230271464646506</v>
       </c>
       <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
+      <c r="BS7" t="n">
+        <v>137232.0075757576</v>
+      </c>
       <c r="BT7" t="n">
-        <v>-4.019679460902083</v>
+        <v>9.348358585858591</v>
       </c>
       <c r="BU7" t="n">
-        <v>-1.919726098608081</v>
+        <v>1.424771625063485</v>
       </c>
       <c r="BV7" t="n">
-        <v>-10916370.97244649</v>
+        <v>98349.89435098114</v>
       </c>
       <c r="BW7" t="n">
-        <v>-0.8398268398268398</v>
+        <v>52571476.48358586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UiYgHRZP</t>
+          <t>ABRGMMB5</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">bond d 
   eng </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">old trafford
-  manchester </t>
+          <t xml:space="preserve">villa park
+  birmingham </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2235,209 +2233,209 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>8QQVnKh9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.203333333333334</v>
+        <v>0.7050000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2445289855072468</v>
+        <v>0.4776000000000002</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8169230769230769</v>
+        <v>0.3646153846153846</v>
       </c>
       <c r="T8" t="n">
-        <v>4.75</v>
+        <v>2.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.71846153846154</v>
+        <v>2.047692307692308</v>
       </c>
       <c r="V8" t="n">
-        <v>11.25</v>
+        <v>1.450000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>6.472307692307693</v>
+        <v>3.903076923076924</v>
       </c>
       <c r="X8" t="n">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5507692307692305</v>
+        <v>1.258461538461539</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.656923076923077</v>
+        <v>1.421538461538461</v>
       </c>
       <c r="AB8" t="n">
-        <v>15.84123324711139</v>
+        <v>21.31273254437341</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.45830457201209</v>
+        <v>21.07765582559797</v>
       </c>
       <c r="AD8" t="n">
-        <v>908.7342333863988</v>
+        <v>759.8132481914106</v>
       </c>
       <c r="AE8" t="n">
-        <v>805.1415897251827</v>
+        <v>760.1530146480472</v>
       </c>
       <c r="AF8" t="n">
-        <v>50</v>
+        <v>13.33333333333334</v>
       </c>
       <c r="AG8" t="n">
-        <v>52.985</v>
+        <v>9.880434782608702</v>
       </c>
       <c r="AH8" t="n">
-        <v>49.66666666666666</v>
+        <v>-12.16666666666666</v>
       </c>
       <c r="AI8" t="n">
-        <v>37.88666666666666</v>
+        <v>12.47463768115943</v>
       </c>
       <c r="AJ8" t="n">
-        <v>5</v>
+        <v>8.950000000000003</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.235384615384614</v>
+        <v>13.44307692307693</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>9.299999999999997</v>
       </c>
       <c r="AM8" t="n">
-        <v>17.28615384615384</v>
+        <v>17.59538461538462</v>
       </c>
       <c r="AN8" t="n">
-        <v>54.99999999999994</v>
+        <v>124.75</v>
       </c>
       <c r="AO8" t="n">
-        <v>174.4426877470356</v>
+        <v>159.3333333333334</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.25</v>
+        <v>-3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.3553846153846152</v>
+        <v>-1.12</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AT8" t="n">
-        <v>18.5</v>
+        <v>-4.199999999999999</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3153846153846196</v>
+        <v>-8.040000000000003</v>
       </c>
       <c r="AV8" t="n">
-        <v>-18.91393206554497</v>
+        <v>-1.605363188515366</v>
       </c>
       <c r="AW8" t="n">
-        <v>-6.539815866388672</v>
+        <v>-1.056890473441834</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.00165414802756482</v>
+        <v>0.01016051987874508</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02171606549309832</v>
+        <v>-0.006779066752411793</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.07999999999999999</v>
-      </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
+        <v>0.1184615384615385</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0.5215909090909108</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.5951404901465409</v>
+      </c>
       <c r="BD8" t="n">
-        <v>2.658299829434696</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.755219322790595</v>
-      </c>
+        <v>1.741896787969409</v>
+      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
-        <v>20341797.0378387</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>46389.09331409332</v>
-      </c>
+        <v>1.134375</v>
+      </c>
+      <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="n">
-        <v>5.023063973063969</v>
-      </c>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="n">
-        <v>-1.614450056116738</v>
-      </c>
+        <v>3.298200757575756</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>8484345.249946849</v>
+      </c>
+      <c r="BK8" t="inlineStr"/>
       <c r="BL8" t="n">
-        <v>0.7762987012986997</v>
+        <v>2.302561765206036</v>
       </c>
       <c r="BM8" t="inlineStr"/>
       <c r="BN8" t="n">
-        <v>3.733124899791562</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>37405.27512915122</v>
-      </c>
+        <v>1.501648431935351</v>
+      </c>
+      <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr"/>
       <c r="BQ8" t="n">
-        <v>0.9330471388585422</v>
+        <v>2.80495580808082</v>
       </c>
       <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
+      <c r="BS8" t="n">
+        <v>54298.1691919192</v>
+      </c>
       <c r="BT8" t="n">
-        <v>2.252504569829142</v>
+        <v>2.749368686868678</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.460175367192917</v>
+        <v>0.436614441690621</v>
       </c>
       <c r="BV8" t="n">
-        <v>14382159.43950867</v>
+        <v>35146.45672060344</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.376110309443642</v>
+        <v>14494977.9040404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Gl6s8NdC</t>
+          <t>viJXIvBU</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.45833333334</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">st  mary s stadium
-  southampton </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KrrdAMyI</t>
+          <t>j3Azpf5d</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2464,188 +2462,188 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>4rSZHs2M</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8866666666666668</v>
+        <v>1.865</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4627120669056159</v>
+        <v>1.103547826086957</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.5</v>
+        <v>1.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2695924764890283</v>
+        <v>1.617777777777778</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.833333333333334</v>
+        <v>4.933333333333334</v>
       </c>
       <c r="U9" t="n">
-        <v>1.620689655172414</v>
+        <v>4.456296296296296</v>
       </c>
       <c r="V9" t="n">
-        <v>1.083333333333332</v>
+        <v>9.4</v>
       </c>
       <c r="W9" t="n">
-        <v>5.832810867293627</v>
+        <v>10.16148148148148</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8333333333333335</v>
+        <v>2.566666666666666</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4587251828631138</v>
+        <v>1.02962962962963</v>
       </c>
       <c r="Z9" t="n">
-        <v>-1.25</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.3197492163009406</v>
+        <v>1.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>21.42171717171717</v>
+        <v>15.83270419810668</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.38390187967638</v>
+        <v>16.26474635100402</v>
       </c>
       <c r="AD9" t="n">
-        <v>755.724845653212</v>
+        <v>761.0753869088082</v>
       </c>
       <c r="AE9" t="n">
-        <v>816.5944893011051</v>
+        <v>806.6041772692249</v>
       </c>
       <c r="AF9" t="n">
-        <v>33.33333333333333</v>
+        <v>41.08333333333333</v>
       </c>
       <c r="AG9" t="n">
-        <v>38.78571428571428</v>
+        <v>53.96173913043478</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>37.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>38.66071428571428</v>
+        <v>45.47826086956522</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-2.833333333333332</v>
+        <v>7.866666666666664</v>
       </c>
       <c r="AK9" t="n">
-        <v>6.245559038662485</v>
+        <v>10.49185185185185</v>
       </c>
       <c r="AL9" t="n">
-        <v>19.66666666666667</v>
+        <v>14.26666666666667</v>
       </c>
       <c r="AM9" t="n">
-        <v>15.48798328108674</v>
+        <v>24.14222222222223</v>
       </c>
       <c r="AN9" t="n">
-        <v>357.6666666666666</v>
+        <v>100</v>
       </c>
       <c r="AO9" t="n">
-        <v>277.7333333333333</v>
+        <v>257.6452173913044</v>
       </c>
       <c r="AP9" t="n">
-        <v>-2</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.3577586206896552</v>
+        <v>-1.319444444444444</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>0.3333333333333333</v>
+        <v>-0.7</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.25</v>
+        <v>-4.133333333333336</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.998955067920585</v>
+        <v>-4.717037037037038</v>
       </c>
       <c r="AV9" t="n">
-        <v>-31.39634265974124</v>
+        <v>-4.016818342579656</v>
       </c>
       <c r="AW9" t="n">
-        <v>-19.89965456494971</v>
+        <v>-7.191749720323251</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.07767634538395832</v>
+        <v>-0.007411253523882881</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0464088381461349</v>
+        <v>0.03090808538764596</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.9166666666666666</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.0438871473354232</v>
-      </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0.7299262465929139</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-4.427089826176179</v>
+      </c>
       <c r="BD9" t="n">
-        <v>0.4145858618123839</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-0.9288341484032934</v>
-      </c>
+        <v>-0.4583955896267753</v>
+      </c>
+      <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
-        <v>-1515984.760802469</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>3885.725308641966</v>
-      </c>
+        <v>0.09098925765592436</v>
+      </c>
+      <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="n">
-        <v>-2.224961419753086</v>
-      </c>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
-        <v>1.327970679012367</v>
-      </c>
+        <v>-1.107050665383994</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-684206.1642206907</v>
+      </c>
+      <c r="BK9" t="inlineStr"/>
       <c r="BL9" t="n">
-        <v>-0.4598379629629683</v>
+        <v>2.399412692790548</v>
       </c>
       <c r="BM9" t="inlineStr"/>
       <c r="BN9" t="n">
-        <v>-1.079783950617283</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>-3936.283575099369</v>
-      </c>
+        <v>-2.659498215030027</v>
+      </c>
+      <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
       <c r="BQ9" t="n">
-        <v>-0.1022361806675531</v>
+        <v>0.7776895943562749</v>
       </c>
       <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr"/>
+      <c r="BS9" t="n">
+        <v>10373.68125701458</v>
+      </c>
       <c r="BT9" t="n">
-        <v>-0.5539894497582765</v>
+        <v>0.2592111592111621</v>
       </c>
       <c r="BU9" t="n">
-        <v>-2.767859395220071</v>
+        <v>-0.1042685620118655</v>
       </c>
       <c r="BV9" t="n">
-        <v>-1854675.709531553</v>
+        <v>96.88048623976647</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.08182870370370354</v>
+        <v>-1186740.820907485</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OE9k61RO</t>
+          <t>rPPOK0tI</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.35416666666</v>
+        <v>45591.45833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2655,18 +2653,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">tottenham hotspur stadium
+          <t xml:space="preserve">brentford community stadium
   london </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2693,7 +2691,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2705,197 +2703,197 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>2.6825</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.239350000000001</v>
+        <v>0.4124999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="S10" t="n">
-        <v>1.798076923076923</v>
+        <v>0.4307692307692308</v>
       </c>
       <c r="T10" t="n">
-        <v>5.916666666666666</v>
+        <v>5.2</v>
       </c>
       <c r="U10" t="n">
-        <v>5.727564102564103</v>
+        <v>-0.47948717948718</v>
       </c>
       <c r="V10" t="n">
-        <v>9.25</v>
+        <v>2.200000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>12.38461538461538</v>
+        <v>-0.6871794871794865</v>
       </c>
       <c r="X10" t="n">
-        <v>2.166666666666667</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.551282051282051</v>
+        <v>-0.09487179487179476</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.461538461538461</v>
+        <v>-0.4846153846153847</v>
       </c>
       <c r="AB10" t="n">
-        <v>19.47923169825344</v>
+        <v>22.24215730112755</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.60269140517912</v>
+        <v>21.03816188433591</v>
       </c>
       <c r="AD10" t="n">
-        <v>689.7368640930019</v>
+        <v>797.8221398001135</v>
       </c>
       <c r="AE10" t="n">
-        <v>726.4581226872547</v>
+        <v>781.1515544524282</v>
       </c>
       <c r="AF10" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>57.54166666666667</v>
+        <v>-1.69047619047619</v>
       </c>
       <c r="AH10" t="n">
-        <v>55.5</v>
+        <v>37.66666666666666</v>
       </c>
       <c r="AI10" t="n">
-        <v>56.00905797101449</v>
+        <v>0.672619047619051</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>2.200000000000006</v>
       </c>
       <c r="AK10" t="n">
-        <v>11.33974358974359</v>
+        <v>3.551282051282058</v>
       </c>
       <c r="AL10" t="n">
-        <v>37.5</v>
+        <v>8</v>
       </c>
       <c r="AM10" t="n">
-        <v>38.59615384615384</v>
+        <v>-6.189743589743586</v>
       </c>
       <c r="AN10" t="n">
-        <v>288.3333333333334</v>
+        <v>162</v>
       </c>
       <c r="AO10" t="n">
-        <v>407.1521739130434</v>
+        <v>203.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>-1.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.364548494983277</v>
+        <v>-0.8262068965517237</v>
       </c>
       <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>-0.7333333333333334</v>
+        <v>0.25</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5833333333333321</v>
+        <v>-7.999999999999996</v>
       </c>
       <c r="AU10" t="n">
-        <v>-3.131410256410255</v>
+        <v>-3.24871794871795</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.67220777352757</v>
+        <v>21.89691291640674</v>
       </c>
       <c r="AW10" t="n">
-        <v>-8.512467224601833</v>
+        <v>-1.233390428659883</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.05250406673777625</v>
+        <v>-0.06254635094023217</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.03805309165012988</v>
+        <v>0.004239086635646191</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1185897435897436</v>
-      </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0.1743686868686858</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-2.969934094495496</v>
+      </c>
       <c r="BD10" t="n">
-        <v>3.746405337581876</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>-4.380914043939253</v>
-      </c>
+        <v>0.5920043163464186</v>
+      </c>
+      <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
-        <v>19547685.18518518</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>26035.18518518518</v>
-      </c>
+        <v>0.1049277497194168</v>
+      </c>
+      <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="n">
-        <v>2.683333333333337</v>
-      </c>
-      <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="n">
-        <v>1.9027777777778</v>
-      </c>
+        <v>1.54325547138049</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>2822461.216699156</v>
+      </c>
+      <c r="BK10" t="inlineStr"/>
       <c r="BL10" t="n">
-        <v>-2.676543209876538</v>
+        <v>4.296953610879044</v>
       </c>
       <c r="BM10" t="inlineStr"/>
       <c r="BN10" t="n">
-        <v>4.13611111111112</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>-726.2278532236523</v>
-      </c>
+        <v>-0.1582944630093834</v>
+      </c>
+      <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
       <c r="BQ10" t="n">
-        <v>-0.1309731286972182</v>
+        <v>1.106684904601536</v>
       </c>
       <c r="BR10" t="inlineStr"/>
-      <c r="BS10" t="inlineStr"/>
+      <c r="BS10" t="n">
+        <v>11623.15867003368</v>
+      </c>
       <c r="BT10" t="n">
-        <v>2.90556749117674</v>
+        <v>2.037338664421995</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1058616621991888</v>
+        <v>0.03321266128283695</v>
       </c>
       <c r="BV10" t="n">
-        <v>6905417.390214313</v>
+        <v>3336.487631114825</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.4478395061728393</v>
+        <v>4415765.642536476</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>fsjksfhd</t>
+          <t>v5b6XwQN</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2922,227 +2920,209 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4500000000000002</v>
+        <v>-0.4199999999999997</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4548418972332011</v>
+        <v>0.8260999999999998</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.1500000000000001</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.377931034482758</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.15</v>
+        <v>-1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>2.25655172413793</v>
       </c>
       <c r="V11" t="n">
-        <v>1.350000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="W11" t="n">
-        <v>5.458333333333334</v>
+        <v>7.082758620689656</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2083333333333335</v>
+        <v>1.721379310344828</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.05</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.6249999999999999</v>
+        <v>1.928275862068966</v>
       </c>
       <c r="AB11" t="n">
-        <v>20.48552807486631</v>
+        <v>20.53740981240981</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.09121482947952</v>
+        <v>17.43967652650897</v>
       </c>
       <c r="AD11" t="n">
-        <v>911.0733535344025</v>
+        <v>716.299556048328</v>
       </c>
       <c r="AE11" t="n">
-        <v>954.4374915827134</v>
+        <v>782.2101386212155</v>
       </c>
       <c r="AF11" t="n">
-        <v>-45.91666666666666</v>
+        <v>60.66666666666667</v>
       </c>
       <c r="AG11" t="n">
-        <v>-5.869565217391298</v>
+        <v>86.0402576489533</v>
       </c>
       <c r="AH11" t="n">
-        <v>-33.16666666666666</v>
+        <v>11.16666666666666</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.260869565217398</v>
+        <v>53.33977455716587</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.600000000000001</v>
+        <v>10.59999999999999</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.666666666666668</v>
+        <v>11.48551724137931</v>
       </c>
       <c r="AL11" t="n">
-        <v>-17.09999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="AM11" t="n">
-        <v>-6.333333333333329</v>
+        <v>44.77517241379311</v>
       </c>
       <c r="AN11" t="n">
-        <v>-135.3333333333333</v>
+        <v>251.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>-43.04545454545445</v>
+        <v>178.44</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.05</v>
+        <v>-0.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.958333333333333</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.411034482758621</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
       <c r="AS11" t="n">
-        <v>-0.2</v>
+        <v>-1</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.149999999999999</v>
+        <v>-4.699999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>-6.026206896551722</v>
       </c>
       <c r="AV11" t="n">
-        <v>-3.795169662062097</v>
+        <v>-13.13343632678281</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.6552133455949942</v>
+        <v>-3.139659475584724</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.04923769293218074</v>
+        <v>0.009805502769564663</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.004222116632888739</v>
+        <v>0.02541180898762269</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.04999999999999999</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0.125</v>
+        <v>0.3903448275862069</v>
       </c>
       <c r="BB11" t="n">
-        <v>-110000</v>
+        <v>0.1518518518518484</v>
       </c>
       <c r="BC11" t="n">
-        <v>-86</v>
+        <v>1.020766590018074</v>
       </c>
       <c r="BD11" t="n">
-        <v>-4.417508625070241</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.8293367802653329</v>
-      </c>
+        <v>-3.824580906924183</v>
+      </c>
+      <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
-        <v>-28547727.27272727</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>-47507.61784511786</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-1</v>
-      </c>
+        <v>0.02195767195767195</v>
+      </c>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="n">
-        <v>-6.835395622895618</v>
+        <v>-1.519532627865942</v>
       </c>
       <c r="BJ11" t="n">
-        <v>-34500000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>-1.330555555555605</v>
-      </c>
+        <v>-3813254.489539482</v>
+      </c>
+      <c r="BK11" t="inlineStr"/>
       <c r="BL11" t="n">
-        <v>0.4669612794612767</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>-79</v>
-      </c>
+        <v>-1.689904644850131</v>
+      </c>
+      <c r="BM11" t="inlineStr"/>
       <c r="BN11" t="n">
-        <v>-4.725715488215499</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-20812.39870215314</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>0.8333333333333321</v>
-      </c>
+        <v>-2.171178431167789</v>
+      </c>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
       <c r="BQ11" t="n">
-        <v>-0.5780924303173025</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>-4</v>
-      </c>
+        <v>-2.306790123456778</v>
+      </c>
+      <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="n">
-        <v>2.5</v>
+        <v>-13474.51499118166</v>
       </c>
       <c r="BT11" t="n">
-        <v>-2.005624441238737</v>
+        <v>-1.130731922398581</v>
       </c>
       <c r="BU11" t="n">
-        <v>-4.704125861937911</v>
+        <v>0.05176677396104612</v>
       </c>
       <c r="BV11" t="n">
-        <v>-12792923.50260503</v>
+        <v>-10611.53881264981</v>
       </c>
       <c r="BW11" t="n">
-        <v>-1.181102693602694</v>
+        <v>-4281528.880070546</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ltBAlx0M</t>
+          <t>KMCY9qSa</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">hooper s 
   eng </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3169,204 +3149,188 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6158333333333332</v>
+        <v>0.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7454761904761908</v>
+        <v>0.5211333333333334</v>
       </c>
       <c r="R12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5811965811965811</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.6552706552706562</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>3.082621082621085</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3547008547008548</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.2008547008547009</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>21.6770313020313</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>19.17558909261927</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>860.7285676624964</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>874.9549656779469</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.652307692307687</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>8.515384615384612</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>0.25</v>
       </c>
-      <c r="S12" t="n">
-        <v>0.6071428571428571</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-0.3333333333333335</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.702380952380953</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>7.083333333333332</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.08333333333333326</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6071428571428574</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>16.87989842401607</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>19.96314013630921</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>946.054630651321</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>861.6011882822016</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>-21.66666666666667</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>22.24154589371982</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>27.31723027375202</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.916666666666664</v>
-      </c>
       <c r="AK12" t="n">
-        <v>15.5</v>
+        <v>0.507122507122503</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.5</v>
+        <v>-9.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>8.357142857142861</v>
+        <v>4.390313390313381</v>
       </c>
       <c r="AN12" t="n">
-        <v>-67.33333333333337</v>
+        <v>-40.33333333333331</v>
       </c>
       <c r="AO12" t="n">
-        <v>51.32689210950076</v>
+        <v>62.68560606060606</v>
       </c>
       <c r="AP12" t="n">
-        <v>-3.166666666666666</v>
+        <v>-0.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.75462962962963</v>
+        <v>-0.525641025641026</v>
       </c>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="AT12" t="n">
-        <v>-8.583333333333336</v>
+        <v>-5</v>
       </c>
       <c r="AU12" t="n">
-        <v>-10.55357142857143</v>
+        <v>2.497150997150996</v>
       </c>
       <c r="AV12" t="n">
-        <v>23.39177167472242</v>
+        <v>11.54713159553585</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.269667134414947</v>
+        <v>-1.410827985799807</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.02723229914810629</v>
+        <v>0.03269125151481447</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.01830218975560294</v>
+        <v>0.01885904830130114</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.5833333333333333</v>
+        <v>-0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0.02380952380952385</v>
+        <v>-0.1467236467236467</v>
       </c>
       <c r="BB12" t="n">
-        <v>-123000</v>
+        <v>0.9830246913580289</v>
       </c>
       <c r="BC12" t="n">
-        <v>-85</v>
+        <v>-2.026167315787735</v>
       </c>
       <c r="BD12" t="n">
-        <v>-2.22303873021886</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>-2.196291699394735</v>
-      </c>
+        <v>0.3498391096204614</v>
+      </c>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
-        <v>-5209077.380952384</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1936.038961038968</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-1</v>
-      </c>
+        <v>-0.1164021164021163</v>
+      </c>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="n">
-        <v>-1.116955266955259</v>
+        <v>-1.629232804232814</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-58500000</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>1.20912698412701</v>
-      </c>
+        <v>1123258.88149208</v>
+      </c>
+      <c r="BK12" t="inlineStr"/>
       <c r="BL12" t="n">
-        <v>-0.2957792207792203</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>-81</v>
-      </c>
+        <v>1.745381994393526</v>
+      </c>
+      <c r="BM12" t="inlineStr"/>
       <c r="BN12" t="n">
-        <v>-1.383044733044727</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>75.90115590023925</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>2.5</v>
-      </c>
+        <v>1.212546414653929</v>
+      </c>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
       <c r="BQ12" t="n">
-        <v>-0.4799005625971136</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>-2</v>
-      </c>
+        <v>0.631481481481444</v>
+      </c>
+      <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="n">
-        <v>4</v>
+        <v>-15546.16402116401</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0.04126796526274745</v>
+        <v>-1.931922398589066</v>
       </c>
       <c r="BU12" t="n">
-        <v>-0.8446863609130872</v>
+        <v>0.1609137687504563</v>
       </c>
       <c r="BV12" t="n">
-        <v>-2996741.07377018</v>
+        <v>-7092.817759856909</v>
       </c>
       <c r="BW12" t="n">
-        <v>-0.2615079365079365</v>
+        <v>-7753386.243386243</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nywy5cp3</t>
+          <t>2ot8gOsJ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -3376,18 +3340,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">anfield
+  liverpool </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>4fGZN2oK</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3414,194 +3378,2012 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6333333333333337</v>
+        <v>0.8266666666666669</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.186770833333334</v>
+        <v>1.905614814814815</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="S13" t="n">
-        <v>1.488636363636364</v>
+        <v>2.957142857142857</v>
       </c>
       <c r="T13" t="n">
-        <v>1.583333333333333</v>
+        <v>6.416666666666667</v>
       </c>
       <c r="U13" t="n">
-        <v>3.174242424242424</v>
+        <v>6.212857142857143</v>
       </c>
       <c r="V13" t="n">
-        <v>4.833333333333334</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="W13" t="n">
-        <v>6.670454545454545</v>
+        <v>17.88571428571429</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5833333333333334</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.681818181818182</v>
+        <v>1.732857142857143</v>
       </c>
       <c r="Z13" t="n">
-        <v>-1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.863636363636364</v>
+        <v>2.01</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.71346153846154</v>
+        <v>17.48306182121971</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.91863863837258</v>
+        <v>16.79118489318707</v>
       </c>
       <c r="AD13" t="n">
-        <v>758.7162835359597</v>
+        <v>824.7458402953209</v>
       </c>
       <c r="AE13" t="n">
-        <v>759.0276326857236</v>
+        <v>894.9609185522844</v>
       </c>
       <c r="AF13" t="n">
-        <v>66.33333333333334</v>
+        <v>30.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>57.89673913043478</v>
+        <v>39.35576923076924</v>
       </c>
       <c r="AH13" t="n">
-        <v>9.833333333333336</v>
+        <v>34</v>
       </c>
       <c r="AI13" t="n">
-        <v>34.19972826086957</v>
+        <v>46.90384615384616</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.75</v>
+        <v>0.8333333333333357</v>
       </c>
       <c r="AK13" t="n">
-        <v>10.81818181818182</v>
+        <v>9.390000000000004</v>
       </c>
       <c r="AL13" t="n">
-        <v>49.83333333333334</v>
+        <v>8</v>
       </c>
       <c r="AM13" t="n">
-        <v>38.60606060606061</v>
+        <v>8.374285714285705</v>
       </c>
       <c r="AN13" t="n">
-        <v>314.9999999999999</v>
+        <v>112</v>
       </c>
       <c r="AO13" t="n">
-        <v>350.6698717948718</v>
+        <v>85.08333333333326</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.2499999999999996</v>
+        <v>-1.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0.8560606060606064</v>
+        <v>-1.984615384615384</v>
       </c>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
-        <v>-0.05000000000000004</v>
+        <v>-0.3500000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0.1666666666666679</v>
+        <v>11.41666666666667</v>
       </c>
       <c r="AU13" t="n">
-        <v>-9.708333333333332</v>
+        <v>4.44142857142857</v>
       </c>
       <c r="AV13" t="n">
-        <v>-14.70089621952367</v>
+        <v>-14.95887931512932</v>
       </c>
       <c r="AW13" t="n">
-        <v>-7.725037689747966</v>
+        <v>-5.606082879044084</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.002017839022274467</v>
+        <v>0.05994594563142951</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0004193398327375641</v>
+        <v>0.0216511595289043</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.6666666666666666</v>
+        <v>-0.4166666666666666</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.2348484848484848</v>
+        <v>0.2542857142857143</v>
       </c>
       <c r="BB13" t="n">
-        <v>-15000</v>
+        <v>3.63914141414141</v>
       </c>
       <c r="BC13" t="n">
-        <v>67</v>
+        <v>1.514884621163226</v>
       </c>
       <c r="BD13" t="n">
-        <v>-2.853081275449682</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>-1.690555123411158</v>
-      </c>
+        <v>2.054964922091642</v>
+      </c>
+      <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
-        <v>20493927.36892737</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>43844.87734487735</v>
-      </c>
-      <c r="BH13" t="n">
+        <v>1.302146464646466</v>
+      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="n">
+        <v>3.878156565656568</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>5949885.115361378</v>
+      </c>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="n">
+        <v>-0.1197859507642107</v>
+      </c>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="n">
+        <v>1.2627298481775</v>
+      </c>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="n">
+        <v>0.5243686868686552</v>
+      </c>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="n">
+        <v>31671.59090909094</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1.240025252525243</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.4619302052511434</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-3590.164421771973</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>18043813.13131313</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SSZaQ4Ct</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.273333333333334</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.3048</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-1.524444444444445</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-3.833333333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-4.527407407407407</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-4.666666666666668</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-9.482962962962963</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-1.474074074074074</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20.79411764705882</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>25.59308002766895</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1089.059424324118</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1086.681684463652</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-47.83333333333333</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-60.24038461538461</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-43.83333333333334</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-36.51602564102565</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-11</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-11.80888888888889</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-29.33333333333333</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-24.52444444444444</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-328.3333333333334</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-276.9583333333334</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.416666666666667</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.4966329966329965</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
         <v>1</v>
       </c>
-      <c r="BI13" t="n">
-        <v>3.050072150072154</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-9750000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.1288840788841128</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-3.368278018278019</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>51</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>5.431721981721978</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>49917.87569585558</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>0.5942442834083699</v>
-      </c>
-      <c r="BR13" t="n">
+      <c r="AT14" t="n">
+        <v>10.83333333333333</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.457455920078463</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.619433638041372</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.01821357536242923</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.0144675204521035</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.08333333333333331</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.1288888888888889</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.2765873015873019</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.97873456558635</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.042361877947855</v>
+      </c>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="n">
+        <v>-1.822835497835498</v>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="n">
+        <v>-7.384812409812412</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-29208527.81258821</v>
+      </c>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
+        <v>-5.266013449079111</v>
+      </c>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="n">
+        <v>-4.008702372427862</v>
+      </c>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>1.306709956709966</v>
+      </c>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="n">
+        <v>-129942.4242424242</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-6.294985569985585</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-1.162400109028399</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-80998.16741530169</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-46137494.5887446</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ShJjaSDs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.683333333333334</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.3936454849498332</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.2584615384615386</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-1.152307692307692</v>
+      </c>
+      <c r="V15" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.5369230769230757</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-1.127692307692308</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-1.444615384615385</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13.90394357104883</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>20.74838845071183</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>861.7609814383254</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>970.3913461408969</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-21.75666666666666</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-15.02833333333334</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-2.458461538461538</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-4.666666666666657</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-22.61538461538461</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-50.00000000000006</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-210.219696969697</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-2.666666666666667</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.7628205128205126</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12.66666666666667</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.669230769230769</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-5.497943049061206</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.945412243634214</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.02637835393270176</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.0008158437450973624</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>-1</v>
       </c>
-      <c r="BS13" t="n">
-        <v>-11</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>5.254973213061433</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>3.208039840276683</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>17878444.61481071</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0.5060606060606063</v>
+      <c r="BA15" t="n">
+        <v>-0.4400000000000001</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0.01701388888888289</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.1816396292858933</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.24357916699671</v>
+      </c>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="n">
+        <v>-2.071874999999999</v>
+      </c>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="n">
+        <v>-6.946875000000006</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-20532666.19179343</v>
+      </c>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
+        <v>-4.364642644138314</v>
+      </c>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="n">
+        <v>-3.445223900850493</v>
+      </c>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="n">
+        <v>-1.167013888888903</v>
+      </c>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="n">
+        <v>-97262.5</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-5.993055555555557</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-1.34844265566772</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-65235.93873934748</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-42905173.61111112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>UiYgHRZP</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.203333333333334</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2445289855072468</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.8169230769230769</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.71846153846154</v>
+      </c>
+      <c r="V16" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>6.472307692307693</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5507692307692305</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.656923076923077</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15.84123324711139</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>20.45830457201209</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>908.7342333863988</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>805.1415897251827</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>52.985</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>49.66666666666666</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>37.88666666666666</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>3.235384615384614</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>17.28615384615384</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>54.99999999999994</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>174.4426877470356</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.3553846153846152</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.3153846153846196</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-18.91393206554497</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-6.539815866388672</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.00165414802756482</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.02171606549309832</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.07999999999999999</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.7204545454545475</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.217024878346148</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.880522051656925</v>
+      </c>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="n">
+        <v>1.341045374378707</v>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="n">
+        <v>4.943843193843193</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>14425041.38395312</v>
+      </c>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
+        <v>2.391393458718028</v>
+      </c>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="n">
+        <v>6.005314256081803</v>
+      </c>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="n">
+        <v>-1.337826679493361</v>
+      </c>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="n">
+        <v>45265.71669071668</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>3.704553471220137</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0.9712415833029868</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>40492.08068470678</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>20403810.02485169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>n9EQB5cm</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2900000000000003</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.183511705685619</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.586538461538462</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-0.916666666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.782051282051283</v>
+      </c>
+      <c r="V17" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.673076923076923</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.522435897435897</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.201923076923077</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.9492303992304</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>22.27539560789965</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1065.744503760177</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1041.620110016067</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-100</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>-17.2709090909091</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-72</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-1.536363636363639</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-8.999999999999996</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.44230769230769</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>-37</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-21.23717948717949</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-547.3333333333333</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-235.6418181818182</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.7541806020066888</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.5142857142857142</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-2.224358974358971</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.53291526744709</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>10.77858110643956</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0.03172019252445872</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.03545029955045926</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.6121794871794872</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.571773288439953</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.540241354730181</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.217460965732897</v>
+      </c>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="n">
+        <v>0.8333613916947249</v>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="n">
+        <v>4.635297418630756</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>9014180.380404595</v>
+      </c>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
+        <v>-0.3816575081364988</v>
+      </c>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="n">
+        <v>4.276960797263001</v>
+      </c>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="n">
+        <v>3.384287317620647</v>
+      </c>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="n">
+        <v>42706.62177328842</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1.58021885521886</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0.6235440233925897</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>35371.35706396373</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>14434342.7328844</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y5lic6rf</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6033333333333332</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.353301282051282</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.8133333333333332</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.166666666666666</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.164444444444444</v>
+      </c>
+      <c r="V18" t="n">
+        <v>10.33333333333333</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.26074074074074</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4474074074074075</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0.04444444444444429</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>18.07763902763903</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>19.74464845689545</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>864.0841842464873</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>889.2723224864662</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>42.16666666666667</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16.06730769230769</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>33.83333333333334</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>15.44871794871796</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>5.333333333333336</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-1.11851851851852</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-11.33333333333333</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.229629629629628</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-17</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>43.79166666666669</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.1461538461538465</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.749999999999996</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.128888888888888</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.5494524047031497</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-5.230445376409838</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.05986447482506944</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.01003067901641407</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.03703703703703703</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.165909090909089</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.801577808156754</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>1.272612403937472</v>
+      </c>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="n">
+        <v>-0.8611111111111109</v>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="n">
+        <v>-2.971464646464639</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-10652806.00688906</v>
+      </c>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
+        <v>-3.982160148257123</v>
+      </c>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="n">
+        <v>-1.830401942562276</v>
+      </c>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="n">
+        <v>0.4613636363636431</v>
+      </c>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="n">
+        <v>-37233.58585858587</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-3.886868686868667</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-0.2646361027046098</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-20473.58631640312</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-15010568.18181818</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>tWiaepD6</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pawson c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.457666666666667</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>11.27333333333334</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.553333333333333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>17.77041716453481</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16.38251074015498</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>761.3901708909452</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>760.828274764531</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>25.73419540229884</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>32.60919540229886</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>7.333333333333329</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>9.653333333333329</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>21.33333333333334</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>26.36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>178</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>241.7608695652174</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.6666666666666667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.5646551724137929</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-5.666666666666668</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-4.333333333333336</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-2.253800254151455</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-2.899569478101503</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.01184920581125101</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>-0.001272512730085301</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-2.467803030303028</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>-0.6429093681802662</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-2.4502429086794</v>
+      </c>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="n">
+        <v>-0.4394255050505051</v>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="n">
+        <v>-2.487405303030314</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-2405181.613292682</v>
+      </c>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
+        <v>-2.104906191303257</v>
+      </c>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="n">
+        <v>-2.137605854614364</v>
+      </c>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="n">
+        <v>0.3784722222222285</v>
+      </c>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="n">
+        <v>-3484.185606060608</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-0.8496843434343333</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-0.213902584916517</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1224.379794755179</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-4719655.934343435</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Gl6s8NdC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45584.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bond d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8866666666666668</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4627120669056159</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2695924764890283</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1.833333333333334</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.620689655172414</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.083333333333332</v>
+      </c>
+      <c r="W20" t="n">
+        <v>5.832810867293627</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.8333333333333335</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4587251828631138</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.3197492163009406</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>21.42171717171717</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>17.38390187967638</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>755.724845653212</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>816.5944893011051</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>38.78571428571428</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>38.66071428571428</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>-2.833333333333332</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>6.245559038662485</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>19.66666666666667</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>15.48798328108674</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>357.6666666666666</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>277.7333333333333</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.3577586206896552</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.998955067920585</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-31.39634265974124</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-19.89965456494971</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.07767634538395832</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.0464088381461349</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.9166666666666666</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.0438871473354232</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.4598379629629683</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>-0.9288341484032934</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0.4145858618123839</v>
+      </c>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="n">
+        <v>-0.08182870370370376</v>
+      </c>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="n">
+        <v>-2.224961419753086</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-1854675.709531553</v>
+      </c>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
+        <v>-0.5539894497582765</v>
+      </c>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="n">
+        <v>-2.767859395220071</v>
+      </c>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="n">
+        <v>1.327970679012367</v>
+      </c>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="n">
+        <v>3885.725308641966</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-1.079783950617283</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-0.1022361806675531</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-3936.283575099369</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>-1515984.760802469</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OE9k61RO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45584.35416666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.239350000000001</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.798076923076923</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5.916666666666666</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5.727564102564103</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>12.38461538461538</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.551282051282051</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.461538461538461</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>19.47923169825344</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>18.60269140517912</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>689.7368640930019</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>726.4581226872547</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>62</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>57.54166666666667</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>56.00905797101449</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>11.33974358974359</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>38.59615384615384</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>288.3333333333334</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>407.1521739130434</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-1.364548494983277</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-0.7333333333333334</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.5833333333333321</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-3.131410256410255</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>18.67220777352757</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-8.512467224601833</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.05250406673777625</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.03805309165012988</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.1185897435897436</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-2.672045855379185</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>-4.27549750086515</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.778172753172782</v>
+      </c>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="n">
+        <v>0.4560405643738972</v>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="n">
+        <v>2.647883597883592</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>6778035.877294458</v>
+      </c>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
+        <v>2.840250775912537</v>
+      </c>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="n">
+        <v>0.159866381802658</v>
+      </c>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="n">
+        <v>1.94880952380953</v>
+      </c>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="n">
+        <v>24883.86243386244</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4.045370370370378</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-0.1476273136812352</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-820.8898672133946</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>19174272.48677249</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -982,55 +982,55 @@
       <c r="BA2" t="n">
         <v>-0.08571428571428574</v>
       </c>
-      <c r="BB2" t="n">
-        <v>-1.301041666666666</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>-0.5980249143971967</v>
+        <v>-3631347.746456444</v>
       </c>
       <c r="BD2" t="n">
-        <v>-4.474926839464899</v>
+        <v>-2.134526297977388</v>
       </c>
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
+        <v>-0.2859335184742804</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-1.301041666666666</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>11982.3675645007</v>
+      </c>
+      <c r="BL2" t="n">
         <v>0.07171717171717074</v>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="n">
+      <c r="BM2" t="n">
         <v>-0.8254419191919169</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>-3631347.746456444</v>
-      </c>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="n">
-        <v>-0.2859335184742804</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="n">
-        <v>-2.134526297977388</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>3175852.272727281</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.5980249143971967</v>
+      </c>
       <c r="BQ2" t="n">
-        <v>-1.835290404040393</v>
+        <v>15648.16919191915</v>
       </c>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="n">
-        <v>15648.16919191915</v>
+        <v>0.1588429686255779</v>
       </c>
       <c r="BT2" t="n">
+        <v>-1.835290404040393</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>-4.474926839464899</v>
+      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="n">
         <v>-0.3953282828282738</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.1588429686255779</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>11982.3675645007</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>3175852.272727281</v>
       </c>
     </row>
     <row r="3">
@@ -1209,55 +1209,55 @@
       <c r="BA3" t="n">
         <v>0.1803921568627451</v>
       </c>
-      <c r="BB3" t="n">
-        <v>-4.335353535353534</v>
-      </c>
+      <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>-3.080528610249974</v>
+        <v>8480040.86188006</v>
       </c>
       <c r="BD3" t="n">
-        <v>-1.925434962354444</v>
+        <v>1.372677504527346</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
+        <v>3.42808109145183</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>-4.335353535353534</v>
+      </c>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="n">
+        <v>11646.47532621607</v>
+      </c>
+      <c r="BL3" t="n">
         <v>-0.5250000000000001</v>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="n">
+      <c r="BM3" t="n">
         <v>0.01338383838383095</v>
       </c>
-      <c r="BJ3" t="n">
-        <v>8480040.86188006</v>
-      </c>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="n">
-        <v>3.42808109145183</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="n">
-        <v>1.372677504527346</v>
-      </c>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="n">
+        <v>6952266.414141417</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>-3.080528610249974</v>
+      </c>
       <c r="BQ3" t="n">
-        <v>-3.036868686868672</v>
+        <v>-7696.590909090883</v>
       </c>
       <c r="BR3" t="inlineStr"/>
       <c r="BS3" t="n">
-        <v>-7696.590909090883</v>
+        <v>-0.1183566798698377</v>
       </c>
       <c r="BT3" t="n">
+        <v>-3.036868686868672</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-1.925434962354444</v>
+      </c>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="n">
         <v>2.852777777777774</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>-0.1183566798698377</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>11646.47532621607</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>6952266.414141417</v>
       </c>
     </row>
     <row r="4">
@@ -1438,55 +1438,55 @@
       <c r="BA4" t="n">
         <v>-0.103448275862069</v>
       </c>
-      <c r="BB4" t="n">
-        <v>1.970061728395056</v>
-      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>1.996401525353733</v>
+        <v>-5287633.029529475</v>
       </c>
       <c r="BD4" t="n">
-        <v>-3.561333352785596</v>
+        <v>0.08684874947130083</v>
       </c>
       <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
+        <v>-1.821678457707876</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.970061728395056</v>
+      </c>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="n">
+        <v>-7316.916739986598</v>
+      </c>
+      <c r="BL4" t="n">
         <v>-0.2159611992945325</v>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="n">
+      <c r="BM4" t="n">
         <v>-0.8423280423280488</v>
       </c>
-      <c r="BJ4" t="n">
-        <v>-5287633.029529475</v>
-      </c>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="n">
-        <v>-1.821678457707876</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="n">
-        <v>0.08684874947130083</v>
-      </c>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="n">
+        <v>-10208349.86772487</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1.996401525353733</v>
+      </c>
       <c r="BQ4" t="n">
-        <v>-0.5857142857142605</v>
+        <v>-13915.21164021162</v>
       </c>
       <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="n">
-        <v>-13915.21164021162</v>
+        <v>-0.0258574939947489</v>
       </c>
       <c r="BT4" t="n">
+        <v>-0.5857142857142605</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-3.561333352785596</v>
+      </c>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="n">
         <v>-2.779497354497352</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-0.0258574939947489</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>-7316.916739986598</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>-10208349.86772487</v>
       </c>
     </row>
     <row r="5">
@@ -1667,55 +1667,55 @@
       <c r="BA5" t="n">
         <v>-0.08000000000000002</v>
       </c>
-      <c r="BB5" t="n">
-        <v>0.2217372134038769</v>
-      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>3.172365388548311</v>
+        <v>-13924752.79709445</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.8861477560394064</v>
+        <v>-3.266978655207495</v>
       </c>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="n">
+        <v>-5.672645978367072</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.2217372134038769</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="n">
+        <v>-16436.24811911705</v>
+      </c>
+      <c r="BL5" t="n">
         <v>-1.291534391534391</v>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="n">
+      <c r="BM5" t="n">
         <v>-3.580291005291002</v>
       </c>
-      <c r="BJ5" t="n">
-        <v>-13924752.79709445</v>
-      </c>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="n">
-        <v>-5.672645978367072</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="n">
-        <v>-3.266978655207495</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="n">
+        <v>-20015661.37566138</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3.172365388548311</v>
+      </c>
       <c r="BQ5" t="n">
-        <v>-1.655291005290991</v>
+        <v>-39090.34391534394</v>
       </c>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>-39090.34391534394</v>
+        <v>-0.8222234557954373</v>
       </c>
       <c r="BT5" t="n">
+        <v>-1.655291005290991</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0.8861477560394064</v>
+      </c>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="n">
         <v>-3.817283950617295</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-0.8222234557954373</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>-16436.24811911705</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>-20015661.37566138</v>
       </c>
     </row>
     <row r="6">
@@ -1896,55 +1896,55 @@
       <c r="BA6" t="n">
         <v>0.2426108374384237</v>
       </c>
-      <c r="BB6" t="n">
-        <v>0.8967171717171674</v>
-      </c>
+      <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="n">
-        <v>0.2377233960034459</v>
+        <v>-886326.9966984792</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04241022310071685</v>
+        <v>-0.3998625900480022</v>
       </c>
       <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="n">
+        <v>-0.3836045632400982</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.8967171717171674</v>
+      </c>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
+        <v>-21133.82785633424</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.05972222222222223</v>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="n">
+      <c r="BM6" t="n">
         <v>-0.1147727272727366</v>
       </c>
-      <c r="BJ6" t="n">
-        <v>-886326.9966984792</v>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="n">
-        <v>-0.3836045632400982</v>
-      </c>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="n">
-        <v>-0.3998625900480022</v>
-      </c>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>67967.17171717249</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.2377233960034459</v>
+      </c>
       <c r="BQ6" t="n">
-        <v>-1.497727272727246</v>
+        <v>-19943.18181818182</v>
       </c>
       <c r="BR6" t="inlineStr"/>
       <c r="BS6" t="n">
-        <v>-19943.18181818182</v>
+        <v>-0.01288691298282063</v>
       </c>
       <c r="BT6" t="n">
+        <v>-1.497727272727246</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.04241022310071685</v>
+      </c>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="n">
         <v>0.3419191919191746</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>-0.01288691298282063</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>-21133.82785633424</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>67967.17171717249</v>
       </c>
     </row>
     <row r="7">
@@ -2127,55 +2127,55 @@
       <c r="BA7" t="n">
         <v>0.207843137254902</v>
       </c>
-      <c r="BB7" t="n">
-        <v>0.03854166666667425</v>
-      </c>
+      <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="n">
-        <v>0.2460457700815013</v>
+        <v>35804129.59060227</v>
       </c>
       <c r="BD7" t="n">
-        <v>-1.049348124510971</v>
+        <v>9.101539734202262</v>
       </c>
       <c r="BE7" t="inlineStr"/>
       <c r="BF7" t="n">
+        <v>7.222887114724699</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.03854166666667425</v>
+      </c>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="n">
+        <v>98349.89435098114</v>
+      </c>
+      <c r="BL7" t="n">
         <v>2.009690656565657</v>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="n">
+      <c r="BM7" t="n">
         <v>10.67414772727273</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>35804129.59060227</v>
-      </c>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="n">
-        <v>7.222887114724699</v>
-      </c>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="n">
-        <v>9.101539734202262</v>
-      </c>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="n">
+        <v>52571476.48358586</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.2460457700815013</v>
+      </c>
       <c r="BQ7" t="n">
-        <v>-1.230271464646506</v>
+        <v>137232.0075757576</v>
       </c>
       <c r="BR7" t="inlineStr"/>
       <c r="BS7" t="n">
-        <v>137232.0075757576</v>
+        <v>1.424771625063485</v>
       </c>
       <c r="BT7" t="n">
+        <v>-1.230271464646506</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-1.049348124510971</v>
+      </c>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="n">
         <v>9.348358585858591</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.424771625063485</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>98349.89435098114</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>52571476.48358586</v>
       </c>
     </row>
     <row r="8">
@@ -2356,55 +2356,55 @@
       <c r="BA8" t="n">
         <v>0.1184615384615385</v>
       </c>
-      <c r="BB8" t="n">
-        <v>0.5215909090909108</v>
-      </c>
+      <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="n">
-        <v>-0.5951404901465409</v>
+        <v>8484345.249946849</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.741896787969409</v>
+        <v>1.501648431935351</v>
       </c>
       <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="n">
+        <v>2.302561765206036</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0.5215909090909108</v>
+      </c>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="n">
+        <v>35146.45672060344</v>
+      </c>
+      <c r="BL8" t="n">
         <v>1.134375</v>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="n">
+      <c r="BM8" t="n">
         <v>3.298200757575756</v>
       </c>
-      <c r="BJ8" t="n">
-        <v>8484345.249946849</v>
-      </c>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="n">
-        <v>2.302561765206036</v>
-      </c>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="n">
-        <v>1.501648431935351</v>
-      </c>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="n">
+        <v>14494977.9040404</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0.5951404901465409</v>
+      </c>
       <c r="BQ8" t="n">
-        <v>2.80495580808082</v>
+        <v>54298.1691919192</v>
       </c>
       <c r="BR8" t="inlineStr"/>
       <c r="BS8" t="n">
-        <v>54298.1691919192</v>
+        <v>0.436614441690621</v>
       </c>
       <c r="BT8" t="n">
+        <v>2.80495580808082</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>1.741896787969409</v>
+      </c>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="n">
         <v>2.749368686868678</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>0.436614441690621</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>35146.45672060344</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>14494977.9040404</v>
       </c>
     </row>
     <row r="9">
@@ -2585,55 +2585,55 @@
       <c r="BA9" t="n">
         <v>0.1481481481481481</v>
       </c>
-      <c r="BB9" t="n">
-        <v>-0.7299262465929139</v>
-      </c>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="n">
-        <v>-4.427089826176179</v>
+        <v>-684206.1642206907</v>
       </c>
       <c r="BD9" t="n">
-        <v>-0.4583955896267753</v>
+        <v>-2.659498215030027</v>
       </c>
       <c r="BE9" t="inlineStr"/>
       <c r="BF9" t="n">
+        <v>2.399412692790548</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.7299262465929139</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="n">
+        <v>96.88048623976647</v>
+      </c>
+      <c r="BL9" t="n">
         <v>0.09098925765592436</v>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="n">
+      <c r="BM9" t="n">
         <v>-1.107050665383994</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>-684206.1642206907</v>
-      </c>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="n">
-        <v>2.399412692790548</v>
-      </c>
-      <c r="BM9" t="inlineStr"/>
-      <c r="BN9" t="n">
-        <v>-2.659498215030027</v>
-      </c>
-      <c r="BO9" t="inlineStr"/>
-      <c r="BP9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="n">
+        <v>-1186740.820907485</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-4.427089826176179</v>
+      </c>
       <c r="BQ9" t="n">
-        <v>0.7776895943562749</v>
+        <v>10373.68125701458</v>
       </c>
       <c r="BR9" t="inlineStr"/>
       <c r="BS9" t="n">
-        <v>10373.68125701458</v>
+        <v>-0.1042685620118655</v>
       </c>
       <c r="BT9" t="n">
+        <v>0.7776895943562749</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0.4583955896267753</v>
+      </c>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="n">
         <v>0.2592111592111621</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>-0.1042685620118655</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>96.88048623976647</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>-1186740.820907485</v>
       </c>
     </row>
     <row r="10">
@@ -2814,55 +2814,55 @@
       <c r="BA10" t="n">
         <v>-0.1666666666666667</v>
       </c>
-      <c r="BB10" t="n">
-        <v>-0.1743686868686858</v>
-      </c>
+      <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="n">
-        <v>-2.969934094495496</v>
+        <v>2822461.216699156</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.5920043163464186</v>
+        <v>-0.1582944630093834</v>
       </c>
       <c r="BE10" t="inlineStr"/>
       <c r="BF10" t="n">
+        <v>4.296953610879044</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.1743686868686858</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="n">
+        <v>3336.487631114825</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0.1049277497194168</v>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="n">
+      <c r="BM10" t="n">
         <v>1.54325547138049</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>2822461.216699156</v>
-      </c>
-      <c r="BK10" t="inlineStr"/>
-      <c r="BL10" t="n">
-        <v>4.296953610879044</v>
-      </c>
-      <c r="BM10" t="inlineStr"/>
-      <c r="BN10" t="n">
-        <v>-0.1582944630093834</v>
-      </c>
-      <c r="BO10" t="inlineStr"/>
-      <c r="BP10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="n">
+        <v>4415765.642536476</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>-2.969934094495496</v>
+      </c>
       <c r="BQ10" t="n">
-        <v>1.106684904601536</v>
+        <v>11623.15867003368</v>
       </c>
       <c r="BR10" t="inlineStr"/>
       <c r="BS10" t="n">
-        <v>11623.15867003368</v>
+        <v>0.03321266128283695</v>
       </c>
       <c r="BT10" t="n">
+        <v>1.106684904601536</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.5920043163464186</v>
+      </c>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="n">
         <v>2.037338664421995</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>0.03321266128283695</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>3336.487631114825</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>4415765.642536476</v>
       </c>
     </row>
     <row r="11">
@@ -3043,55 +3043,55 @@
       <c r="BA11" t="n">
         <v>0.3903448275862069</v>
       </c>
-      <c r="BB11" t="n">
-        <v>0.1518518518518484</v>
-      </c>
+      <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="n">
-        <v>1.020766590018074</v>
+        <v>-3813254.489539482</v>
       </c>
       <c r="BD11" t="n">
-        <v>-3.824580906924183</v>
+        <v>-2.171178431167789</v>
       </c>
       <c r="BE11" t="inlineStr"/>
       <c r="BF11" t="n">
+        <v>-1.689904644850131</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.1518518518518484</v>
+      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="n">
+        <v>-10611.53881264981</v>
+      </c>
+      <c r="BL11" t="n">
         <v>0.02195767195767195</v>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="n">
+      <c r="BM11" t="n">
         <v>-1.519532627865942</v>
       </c>
-      <c r="BJ11" t="n">
-        <v>-3813254.489539482</v>
-      </c>
-      <c r="BK11" t="inlineStr"/>
-      <c r="BL11" t="n">
-        <v>-1.689904644850131</v>
-      </c>
-      <c r="BM11" t="inlineStr"/>
-      <c r="BN11" t="n">
-        <v>-2.171178431167789</v>
-      </c>
-      <c r="BO11" t="inlineStr"/>
-      <c r="BP11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="n">
+        <v>-4281528.880070546</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1.020766590018074</v>
+      </c>
       <c r="BQ11" t="n">
-        <v>-2.306790123456778</v>
+        <v>-13474.51499118166</v>
       </c>
       <c r="BR11" t="inlineStr"/>
       <c r="BS11" t="n">
-        <v>-13474.51499118166</v>
+        <v>0.05176677396104612</v>
       </c>
       <c r="BT11" t="n">
+        <v>-2.306790123456778</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-3.824580906924183</v>
+      </c>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="n">
         <v>-1.130731922398581</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>0.05176677396104612</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>-10611.53881264981</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>-4281528.880070546</v>
       </c>
     </row>
     <row r="12">
@@ -3272,55 +3272,55 @@
       <c r="BA12" t="n">
         <v>-0.1467236467236467</v>
       </c>
-      <c r="BB12" t="n">
-        <v>0.9830246913580289</v>
-      </c>
+      <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="n">
-        <v>-2.026167315787735</v>
+        <v>1123258.88149208</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.3498391096204614</v>
+        <v>1.212546414653929</v>
       </c>
       <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="n">
+        <v>1.745381994393526</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.9830246913580289</v>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="n">
+        <v>-7092.817759856909</v>
+      </c>
+      <c r="BL12" t="n">
         <v>-0.1164021164021163</v>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="n">
+      <c r="BM12" t="n">
         <v>-1.629232804232814</v>
       </c>
-      <c r="BJ12" t="n">
-        <v>1123258.88149208</v>
-      </c>
-      <c r="BK12" t="inlineStr"/>
-      <c r="BL12" t="n">
-        <v>1.745381994393526</v>
-      </c>
-      <c r="BM12" t="inlineStr"/>
-      <c r="BN12" t="n">
-        <v>1.212546414653929</v>
-      </c>
-      <c r="BO12" t="inlineStr"/>
-      <c r="BP12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="n">
+        <v>-7753386.243386243</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-2.026167315787735</v>
+      </c>
       <c r="BQ12" t="n">
-        <v>0.631481481481444</v>
+        <v>-15546.16402116401</v>
       </c>
       <c r="BR12" t="inlineStr"/>
       <c r="BS12" t="n">
-        <v>-15546.16402116401</v>
+        <v>0.1609137687504563</v>
       </c>
       <c r="BT12" t="n">
+        <v>0.631481481481444</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.3498391096204614</v>
+      </c>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="n">
         <v>-1.931922398589066</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0.1609137687504563</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>-7092.817759856909</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>-7753386.243386243</v>
       </c>
     </row>
     <row r="13">
@@ -3501,55 +3501,55 @@
       <c r="BA13" t="n">
         <v>0.2542857142857143</v>
       </c>
-      <c r="BB13" t="n">
-        <v>3.63914141414141</v>
-      </c>
+      <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="n">
-        <v>1.514884621163226</v>
+        <v>5949885.115361378</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.054964922091642</v>
+        <v>1.2627298481775</v>
       </c>
       <c r="BE13" t="inlineStr"/>
       <c r="BF13" t="n">
+        <v>-0.1197859507642107</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.63914141414141</v>
+      </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="n">
+        <v>-3590.164421771973</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.302146464646466</v>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="n">
+      <c r="BM13" t="n">
         <v>3.878156565656568</v>
       </c>
-      <c r="BJ13" t="n">
-        <v>5949885.115361378</v>
-      </c>
-      <c r="BK13" t="inlineStr"/>
-      <c r="BL13" t="n">
-        <v>-0.1197859507642107</v>
-      </c>
-      <c r="BM13" t="inlineStr"/>
-      <c r="BN13" t="n">
-        <v>1.2627298481775</v>
-      </c>
-      <c r="BO13" t="inlineStr"/>
-      <c r="BP13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="n">
+        <v>18043813.13131313</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1.514884621163226</v>
+      </c>
       <c r="BQ13" t="n">
-        <v>0.5243686868686552</v>
+        <v>31671.59090909094</v>
       </c>
       <c r="BR13" t="inlineStr"/>
       <c r="BS13" t="n">
-        <v>31671.59090909094</v>
+        <v>0.4619302052511434</v>
       </c>
       <c r="BT13" t="n">
+        <v>0.5243686868686552</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>2.054964922091642</v>
+      </c>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="n">
         <v>1.240025252525243</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0.4619302052511434</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>-3590.164421771973</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>18043813.13131313</v>
       </c>
     </row>
     <row r="14">
@@ -3730,55 +3730,55 @@
       <c r="BA14" t="n">
         <v>-0.1288888888888889</v>
       </c>
-      <c r="BB14" t="n">
-        <v>0.2765873015873019</v>
-      </c>
+      <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="n">
-        <v>1.97873456558635</v>
+        <v>-29208527.81258821</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.042361877947855</v>
+        <v>-4.008702372427862</v>
       </c>
       <c r="BE14" t="inlineStr"/>
       <c r="BF14" t="n">
+        <v>-5.266013449079111</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.2765873015873019</v>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="n">
+        <v>-80998.16741530169</v>
+      </c>
+      <c r="BL14" t="n">
         <v>-1.822835497835498</v>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="n">
+      <c r="BM14" t="n">
         <v>-7.384812409812412</v>
       </c>
-      <c r="BJ14" t="n">
-        <v>-29208527.81258821</v>
-      </c>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
-        <v>-5.266013449079111</v>
-      </c>
-      <c r="BM14" t="inlineStr"/>
-      <c r="BN14" t="n">
-        <v>-4.008702372427862</v>
-      </c>
-      <c r="BO14" t="inlineStr"/>
-      <c r="BP14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="n">
+        <v>-46137494.5887446</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1.97873456558635</v>
+      </c>
       <c r="BQ14" t="n">
-        <v>1.306709956709966</v>
+        <v>-129942.4242424242</v>
       </c>
       <c r="BR14" t="inlineStr"/>
       <c r="BS14" t="n">
-        <v>-129942.4242424242</v>
+        <v>-1.162400109028399</v>
       </c>
       <c r="BT14" t="n">
+        <v>1.306709956709966</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.042361877947855</v>
+      </c>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="n">
         <v>-6.294985569985585</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>-1.162400109028399</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-80998.16741530169</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>-46137494.5887446</v>
       </c>
     </row>
     <row r="15">
@@ -3959,55 +3959,55 @@
       <c r="BA15" t="n">
         <v>-0.4400000000000001</v>
       </c>
-      <c r="BB15" t="n">
-        <v>-0.01701388888888289</v>
-      </c>
+      <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="n">
-        <v>-0.1816396292858933</v>
+        <v>-20532666.19179343</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.24357916699671</v>
+        <v>-3.445223900850493</v>
       </c>
       <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="n">
+        <v>-4.364642644138314</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.01701388888888289</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="n">
+        <v>-65235.93873934748</v>
+      </c>
+      <c r="BL15" t="n">
         <v>-2.071874999999999</v>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="n">
+      <c r="BM15" t="n">
         <v>-6.946875000000006</v>
       </c>
-      <c r="BJ15" t="n">
-        <v>-20532666.19179343</v>
-      </c>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="n">
-        <v>-4.364642644138314</v>
-      </c>
-      <c r="BM15" t="inlineStr"/>
-      <c r="BN15" t="n">
-        <v>-3.445223900850493</v>
-      </c>
-      <c r="BO15" t="inlineStr"/>
-      <c r="BP15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="n">
+        <v>-42905173.61111112</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-0.1816396292858933</v>
+      </c>
       <c r="BQ15" t="n">
-        <v>-1.167013888888903</v>
+        <v>-97262.5</v>
       </c>
       <c r="BR15" t="inlineStr"/>
       <c r="BS15" t="n">
-        <v>-97262.5</v>
+        <v>-1.34844265566772</v>
       </c>
       <c r="BT15" t="n">
+        <v>-1.167013888888903</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.24357916699671</v>
+      </c>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="n">
         <v>-5.993055555555557</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>-1.34844265566772</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>-65235.93873934748</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>-42905173.61111112</v>
       </c>
     </row>
     <row r="16">
@@ -4188,55 +4188,55 @@
       <c r="BA16" t="n">
         <v>0.07999999999999999</v>
       </c>
-      <c r="BB16" t="n">
-        <v>0.7204545454545475</v>
-      </c>
+      <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="n">
-        <v>3.217024878346148</v>
+        <v>14425041.38395312</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.880522051656925</v>
+        <v>6.005314256081803</v>
       </c>
       <c r="BE16" t="inlineStr"/>
       <c r="BF16" t="n">
+        <v>2.391393458718028</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0.7204545454545475</v>
+      </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="n">
+        <v>40492.08068470678</v>
+      </c>
+      <c r="BL16" t="n">
         <v>1.341045374378707</v>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="n">
+      <c r="BM16" t="n">
         <v>4.943843193843193</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>14425041.38395312</v>
-      </c>
-      <c r="BK16" t="inlineStr"/>
-      <c r="BL16" t="n">
-        <v>2.391393458718028</v>
-      </c>
-      <c r="BM16" t="inlineStr"/>
-      <c r="BN16" t="n">
-        <v>6.005314256081803</v>
-      </c>
-      <c r="BO16" t="inlineStr"/>
-      <c r="BP16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="n">
+        <v>20403810.02485169</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3.217024878346148</v>
+      </c>
       <c r="BQ16" t="n">
-        <v>-1.337826679493361</v>
+        <v>45265.71669071668</v>
       </c>
       <c r="BR16" t="inlineStr"/>
       <c r="BS16" t="n">
-        <v>45265.71669071668</v>
+        <v>0.9712415833029868</v>
       </c>
       <c r="BT16" t="n">
+        <v>-1.337826679493361</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>2.880522051656925</v>
+      </c>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="n">
         <v>3.704553471220137</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>0.9712415833029868</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>40492.08068470678</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>20403810.02485169</v>
       </c>
     </row>
     <row r="17">
@@ -4419,55 +4419,55 @@
       <c r="BA17" t="n">
         <v>0.6121794871794872</v>
       </c>
-      <c r="BB17" t="n">
-        <v>1.571773288439953</v>
-      </c>
+      <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="n">
-        <v>3.540241354730181</v>
+        <v>9014180.380404595</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.217460965732897</v>
+        <v>4.276960797263001</v>
       </c>
       <c r="BE17" t="inlineStr"/>
       <c r="BF17" t="n">
+        <v>-0.3816575081364988</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.571773288439953</v>
+      </c>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="n">
+        <v>35371.35706396373</v>
+      </c>
+      <c r="BL17" t="n">
         <v>0.8333613916947249</v>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="n">
+      <c r="BM17" t="n">
         <v>4.635297418630756</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>9014180.380404595</v>
-      </c>
-      <c r="BK17" t="inlineStr"/>
-      <c r="BL17" t="n">
-        <v>-0.3816575081364988</v>
-      </c>
-      <c r="BM17" t="inlineStr"/>
-      <c r="BN17" t="n">
-        <v>4.276960797263001</v>
-      </c>
-      <c r="BO17" t="inlineStr"/>
-      <c r="BP17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="n">
+        <v>14434342.7328844</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>3.540241354730181</v>
+      </c>
       <c r="BQ17" t="n">
-        <v>3.384287317620647</v>
+        <v>42706.62177328842</v>
       </c>
       <c r="BR17" t="inlineStr"/>
       <c r="BS17" t="n">
-        <v>42706.62177328842</v>
+        <v>0.6235440233925897</v>
       </c>
       <c r="BT17" t="n">
+        <v>3.384287317620647</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.217460965732897</v>
+      </c>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="n">
         <v>1.58021885521886</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>0.6235440233925897</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>35371.35706396373</v>
-      </c>
-      <c r="BW17" t="n">
-        <v>14434342.7328844</v>
       </c>
     </row>
     <row r="18">
@@ -4648,55 +4648,55 @@
       <c r="BA18" t="n">
         <v>-0.03703703703703703</v>
       </c>
-      <c r="BB18" t="n">
-        <v>1.165909090909089</v>
-      </c>
+      <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="n">
-        <v>2.801577808156754</v>
+        <v>-10652806.00688906</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.272612403937472</v>
+        <v>-1.830401942562276</v>
       </c>
       <c r="BE18" t="inlineStr"/>
       <c r="BF18" t="n">
+        <v>-3.982160148257123</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>1.165909090909089</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="n">
+        <v>-20473.58631640312</v>
+      </c>
+      <c r="BL18" t="n">
         <v>-0.8611111111111109</v>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="n">
+      <c r="BM18" t="n">
         <v>-2.971464646464639</v>
       </c>
-      <c r="BJ18" t="n">
-        <v>-10652806.00688906</v>
-      </c>
-      <c r="BK18" t="inlineStr"/>
-      <c r="BL18" t="n">
-        <v>-3.982160148257123</v>
-      </c>
-      <c r="BM18" t="inlineStr"/>
-      <c r="BN18" t="n">
-        <v>-1.830401942562276</v>
-      </c>
-      <c r="BO18" t="inlineStr"/>
-      <c r="BP18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="n">
+        <v>-15010568.18181818</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2.801577808156754</v>
+      </c>
       <c r="BQ18" t="n">
-        <v>0.4613636363636431</v>
+        <v>-37233.58585858587</v>
       </c>
       <c r="BR18" t="inlineStr"/>
       <c r="BS18" t="n">
-        <v>-37233.58585858587</v>
+        <v>-0.2646361027046098</v>
       </c>
       <c r="BT18" t="n">
+        <v>0.4613636363636431</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>1.272612403937472</v>
+      </c>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="n">
         <v>-3.886868686868667</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>-0.2646361027046098</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>-20473.58631640312</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>-15010568.18181818</v>
       </c>
     </row>
     <row r="19">
@@ -4877,55 +4877,55 @@
       <c r="BA19" t="n">
         <v>0.2933333333333333</v>
       </c>
-      <c r="BB19" t="n">
-        <v>-2.467803030303028</v>
-      </c>
+      <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="n">
-        <v>-0.6429093681802662</v>
+        <v>-2405181.613292682</v>
       </c>
       <c r="BD19" t="n">
-        <v>-2.4502429086794</v>
+        <v>-2.137605854614364</v>
       </c>
       <c r="BE19" t="inlineStr"/>
       <c r="BF19" t="n">
+        <v>-2.104906191303257</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-2.467803030303028</v>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="n">
+        <v>1224.379794755179</v>
+      </c>
+      <c r="BL19" t="n">
         <v>-0.4394255050505051</v>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="n">
+      <c r="BM19" t="n">
         <v>-2.487405303030314</v>
       </c>
-      <c r="BJ19" t="n">
-        <v>-2405181.613292682</v>
-      </c>
-      <c r="BK19" t="inlineStr"/>
-      <c r="BL19" t="n">
-        <v>-2.104906191303257</v>
-      </c>
-      <c r="BM19" t="inlineStr"/>
-      <c r="BN19" t="n">
-        <v>-2.137605854614364</v>
-      </c>
-      <c r="BO19" t="inlineStr"/>
-      <c r="BP19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="n">
+        <v>-4719655.934343435</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-0.6429093681802662</v>
+      </c>
       <c r="BQ19" t="n">
-        <v>0.3784722222222285</v>
+        <v>-3484.185606060608</v>
       </c>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="n">
-        <v>-3484.185606060608</v>
+        <v>-0.213902584916517</v>
       </c>
       <c r="BT19" t="n">
+        <v>0.3784722222222285</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-2.4502429086794</v>
+      </c>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="n">
         <v>-0.8496843434343333</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>-0.213902584916517</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1224.379794755179</v>
-      </c>
-      <c r="BW19" t="n">
-        <v>-4719655.934343435</v>
       </c>
     </row>
     <row r="20">
@@ -5106,55 +5106,55 @@
       <c r="BA20" t="n">
         <v>-0.0438871473354232</v>
       </c>
-      <c r="BB20" t="n">
-        <v>-0.4598379629629683</v>
-      </c>
+      <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="n">
-        <v>-0.9288341484032934</v>
+        <v>-1854675.709531553</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.4145858618123839</v>
+        <v>-2.767859395220071</v>
       </c>
       <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="n">
+        <v>-0.5539894497582765</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-0.4598379629629683</v>
+      </c>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="n">
+        <v>-3936.283575099369</v>
+      </c>
+      <c r="BL20" t="n">
         <v>-0.08182870370370376</v>
       </c>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="n">
+      <c r="BM20" t="n">
         <v>-2.224961419753086</v>
       </c>
-      <c r="BJ20" t="n">
-        <v>-1854675.709531553</v>
-      </c>
-      <c r="BK20" t="inlineStr"/>
-      <c r="BL20" t="n">
-        <v>-0.5539894497582765</v>
-      </c>
-      <c r="BM20" t="inlineStr"/>
-      <c r="BN20" t="n">
-        <v>-2.767859395220071</v>
-      </c>
-      <c r="BO20" t="inlineStr"/>
-      <c r="BP20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="n">
+        <v>-1515984.760802469</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>-0.9288341484032934</v>
+      </c>
       <c r="BQ20" t="n">
-        <v>1.327970679012367</v>
+        <v>3885.725308641966</v>
       </c>
       <c r="BR20" t="inlineStr"/>
       <c r="BS20" t="n">
-        <v>3885.725308641966</v>
+        <v>-0.1022361806675531</v>
       </c>
       <c r="BT20" t="n">
+        <v>1.327970679012367</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>0.4145858618123839</v>
+      </c>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="n">
         <v>-1.079783950617283</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>-0.1022361806675531</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>-3936.283575099369</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>-1515984.760802469</v>
       </c>
     </row>
     <row r="21">
@@ -5335,55 +5335,55 @@
       <c r="BA21" t="n">
         <v>0.1185897435897436</v>
       </c>
-      <c r="BB21" t="n">
-        <v>-2.672045855379185</v>
-      </c>
+      <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="n">
-        <v>-4.27549750086515</v>
+        <v>6778035.877294458</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.778172753172782</v>
+        <v>0.159866381802658</v>
       </c>
       <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="n">
+        <v>2.840250775912537</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-2.672045855379185</v>
+      </c>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="n">
+        <v>-820.8898672133946</v>
+      </c>
+      <c r="BL21" t="n">
         <v>0.4560405643738972</v>
       </c>
-      <c r="BG21" t="inlineStr"/>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="n">
+      <c r="BM21" t="n">
         <v>2.647883597883592</v>
       </c>
-      <c r="BJ21" t="n">
-        <v>6778035.877294458</v>
-      </c>
-      <c r="BK21" t="inlineStr"/>
-      <c r="BL21" t="n">
-        <v>2.840250775912537</v>
-      </c>
-      <c r="BM21" t="inlineStr"/>
-      <c r="BN21" t="n">
-        <v>0.159866381802658</v>
-      </c>
-      <c r="BO21" t="inlineStr"/>
-      <c r="BP21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="n">
+        <v>19174272.48677249</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-4.27549750086515</v>
+      </c>
       <c r="BQ21" t="n">
-        <v>1.94880952380953</v>
+        <v>24883.86243386244</v>
       </c>
       <c r="BR21" t="inlineStr"/>
       <c r="BS21" t="n">
-        <v>24883.86243386244</v>
+        <v>-0.1476273136812352</v>
       </c>
       <c r="BT21" t="n">
+        <v>1.94880952380953</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>3.778172753172782</v>
+      </c>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="n">
         <v>4.045370370370378</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>-0.1476273136812352</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>-820.8898672133946</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>19174272.48677249</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
         </is>
       </c>
     </row>
@@ -982,55 +982,71 @@
       <c r="BA2" t="n">
         <v>-0.08571428571428574</v>
       </c>
-      <c r="BB2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>7.916666666666657</v>
+      </c>
       <c r="BC2" t="n">
-        <v>-3631347.746456444</v>
+        <v>14577.70562770563</v>
       </c>
       <c r="BD2" t="n">
-        <v>-2.134526297977388</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>506083.3333333334</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>246.9166666666667</v>
+      </c>
       <c r="BF2" t="n">
-        <v>-0.2859335184742804</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>-1.301041666666666</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
+        <v>3.508333333333336</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-0.3053525925420359</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>133708333.3333333</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>242.1666666666667</v>
+      </c>
       <c r="BK2" t="n">
-        <v>11982.3675645007</v>
+        <v>-2.03542568542565</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.07171717171717074</v>
+        <v>-4.151702102245594</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.8254419191919169</v>
-      </c>
-      <c r="BN2" t="inlineStr"/>
+        <v>-2.487672911974144</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.07974910700066085</v>
+      </c>
       <c r="BO2" t="n">
-        <v>3175852.272727281</v>
+        <v>-0.3969696969696912</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.5980249143971967</v>
+        <v>-4494754.567378797</v>
       </c>
       <c r="BQ2" t="n">
-        <v>15648.16919191915</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
+        <v>0.07330447330447276</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>-0.96789321789322</v>
+      </c>
       <c r="BS2" t="n">
-        <v>0.1588429686255779</v>
+        <v>3</v>
       </c>
       <c r="BT2" t="n">
-        <v>-1.835290404040393</v>
+        <v>-0.7798856164539387</v>
       </c>
       <c r="BU2" t="n">
-        <v>-4.474926839464899</v>
-      </c>
-      <c r="BV2" t="inlineStr"/>
+        <v>-1.290656565656565</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>9408.420073715082</v>
+      </c>
       <c r="BW2" t="n">
-        <v>-0.3953282828282738</v>
+        <v>2185822.51082252</v>
       </c>
     </row>
     <row r="3">
@@ -1209,55 +1225,71 @@
       <c r="BA3" t="n">
         <v>0.1803921568627451</v>
       </c>
-      <c r="BB3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>-8.050000000000011</v>
+      </c>
       <c r="BC3" t="n">
-        <v>8480040.86188006</v>
+        <v>-7628.156565656536</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.372677504527346</v>
-      </c>
-      <c r="BE3" t="inlineStr"/>
+        <v>-260833.3333333333</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-150.5</v>
+      </c>
       <c r="BF3" t="n">
-        <v>3.42808109145183</v>
+        <v>-6.333333333333334</v>
       </c>
       <c r="BG3" t="n">
-        <v>-4.335353535353534</v>
-      </c>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
+        <v>-2.949999999999996</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.202786785797613</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>-67450000</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-145.8333333333333</v>
+      </c>
       <c r="BK3" t="n">
-        <v>11646.47532621607</v>
+        <v>-2.944318181818176</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.5250000000000001</v>
+        <v>-1.836902070130577</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.01338383838383095</v>
-      </c>
-      <c r="BN3" t="inlineStr"/>
+        <v>1.2313695662138</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-0.1651000771888931</v>
+      </c>
       <c r="BO3" t="n">
-        <v>6952266.414141417</v>
+        <v>2.943087121212116</v>
       </c>
       <c r="BP3" t="n">
-        <v>-3.080528610249974</v>
+        <v>7639102.11563462</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-7696.590909090883</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
+        <v>-0.5242739898989901</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0.02885101010100755</v>
+      </c>
       <c r="BS3" t="n">
-        <v>-0.1183566798698377</v>
+        <v>-1.666666666666667</v>
       </c>
       <c r="BT3" t="n">
-        <v>-3.036868686868672</v>
+        <v>-3.052484432384784</v>
       </c>
       <c r="BU3" t="n">
-        <v>-1.925434962354444</v>
-      </c>
-      <c r="BV3" t="inlineStr"/>
+        <v>-4.401199494949495</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>10666.07403658006</v>
+      </c>
       <c r="BW3" t="n">
-        <v>2.852777777777774</v>
+        <v>7151579.071969699</v>
       </c>
     </row>
     <row r="4">
@@ -1438,55 +1470,71 @@
       <c r="BA4" t="n">
         <v>-0.103448275862069</v>
       </c>
-      <c r="BB4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>0.9444444444444571</v>
+      </c>
       <c r="BC4" t="n">
-        <v>-5287633.029529475</v>
+        <v>-13361.80555555555</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.08684874947130083</v>
-      </c>
-      <c r="BE4" t="inlineStr"/>
+        <v>-136666.6666666667</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-141.8333333333333</v>
+      </c>
       <c r="BF4" t="n">
-        <v>-1.821678457707876</v>
+        <v>-2.333333333333333</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.970061728395056</v>
-      </c>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
+        <v>4.555555555555554</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-1.904393824837626</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-29166666.66666666</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-149.8333333333333</v>
+      </c>
       <c r="BK4" t="n">
-        <v>-7316.916739986598</v>
+        <v>-0.6322916666666458</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.2159611992945325</v>
+        <v>-3.013612319928001</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.8423280423280488</v>
-      </c>
-      <c r="BN4" t="inlineStr"/>
+        <v>-0.09835620145494772</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>-0.05569796828988016</v>
+      </c>
       <c r="BO4" t="n">
-        <v>-10208349.86772487</v>
+        <v>-2.705208333333346</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.996401525353733</v>
+        <v>-5727426.760768412</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-13915.21164021162</v>
-      </c>
-      <c r="BR4" t="inlineStr"/>
+        <v>-0.1892361111111112</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0.7534722222222285</v>
+      </c>
       <c r="BS4" t="n">
-        <v>-0.0258574939947489</v>
+        <v>-1.833333333333333</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0.5857142857142605</v>
+        <v>1.902731236725462</v>
       </c>
       <c r="BU4" t="n">
-        <v>-3.561333352785596</v>
-      </c>
-      <c r="BV4" t="inlineStr"/>
+        <v>1.936805555555555</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-9510.036226028868</v>
+      </c>
       <c r="BW4" t="n">
-        <v>-2.779497354497352</v>
+        <v>-10150694.44444444</v>
       </c>
     </row>
     <row r="5">
@@ -1667,55 +1715,71 @@
       <c r="BA5" t="n">
         <v>-0.08000000000000002</v>
       </c>
-      <c r="BB5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>1.62380952380957</v>
+      </c>
       <c r="BC5" t="n">
+        <v>-39090.34391534394</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-90857.14285714287</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.1999999999999886</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-3.314285714285715</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.3476190476190482</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-5.672645978367072</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-34264285.71428572</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.2571428571428669</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>-1.655291005290991</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0.8861477560394064</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-3.266978655207495</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0.8222234557954373</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-3.817283950617295</v>
+      </c>
+      <c r="BP5" t="n">
         <v>-13924752.79709445</v>
       </c>
-      <c r="BD5" t="n">
-        <v>-3.266978655207495</v>
-      </c>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
-        <v>-5.672645978367072</v>
-      </c>
-      <c r="BG5" t="n">
+      <c r="BQ5" t="n">
+        <v>-1.291534391534391</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-3.580291005291002</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>3.172365388548311</v>
+      </c>
+      <c r="BU5" t="n">
         <v>0.2217372134038769</v>
       </c>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="n">
+      <c r="BV5" t="n">
         <v>-16436.24811911705</v>
       </c>
-      <c r="BL5" t="n">
-        <v>-1.291534391534391</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>-3.580291005291002</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="n">
+      <c r="BW5" t="n">
         <v>-20015661.37566138</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>3.172365388548311</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-39090.34391534394</v>
-      </c>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="n">
-        <v>-0.8222234557954373</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>-1.655291005290991</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-0.8861477560394064</v>
-      </c>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="n">
-        <v>-3.817283950617295</v>
       </c>
     </row>
     <row r="6">
@@ -1896,55 +1960,71 @@
       <c r="BA6" t="n">
         <v>0.2426108374384237</v>
       </c>
-      <c r="BB6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>-3.594444444444434</v>
+      </c>
       <c r="BC6" t="n">
-        <v>-886326.9966984792</v>
+        <v>-19863.54617604618</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.3998625900480022</v>
-      </c>
-      <c r="BE6" t="inlineStr"/>
+        <v>121000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>268.3333333333333</v>
+      </c>
       <c r="BF6" t="n">
-        <v>-0.3836045632400982</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.8967171717171674</v>
-      </c>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
+        <v>-4.411111111111111</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0.3906131046596073</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>31829166.66666666</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>295.6666666666667</v>
+      </c>
       <c r="BK6" t="n">
-        <v>-21133.82785633424</v>
+        <v>-1.459379509379517</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.05972222222222223</v>
+        <v>-0.2852595135044282</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.1147727272727366</v>
-      </c>
-      <c r="BN6" t="inlineStr"/>
+        <v>-0.5212222253982191</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.001444251879834102</v>
+      </c>
       <c r="BO6" t="n">
-        <v>67967.17171717249</v>
+        <v>0.5331168831168753</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.2377233960034459</v>
+        <v>-1186846.132155355</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-19943.18181818182</v>
-      </c>
-      <c r="BR6" t="inlineStr"/>
+        <v>0.04826839826839824</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0.01031746031745229</v>
+      </c>
       <c r="BS6" t="n">
-        <v>-0.01288691298282063</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="BT6" t="n">
-        <v>-1.497727272727246</v>
+        <v>0.4641779509386588</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.04241022310071685</v>
-      </c>
-      <c r="BV6" t="inlineStr"/>
+        <v>0.6926767676767689</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-22127.73025141951</v>
+      </c>
       <c r="BW6" t="n">
-        <v>0.3419191919191746</v>
+        <v>348980.8802308831</v>
       </c>
     </row>
     <row r="7">
@@ -2127,55 +2207,71 @@
       <c r="BA7" t="n">
         <v>0.207843137254902</v>
       </c>
-      <c r="BB7" t="inlineStr"/>
+      <c r="BB7" t="n">
+        <v>-9.803571428571473</v>
+      </c>
       <c r="BC7" t="n">
-        <v>35804129.59060227</v>
+        <v>138409.0909090909</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.101539734202262</v>
-      </c>
-      <c r="BE7" t="inlineStr"/>
+        <v>255904.7619047619</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>15.64285714285714</v>
+      </c>
       <c r="BF7" t="n">
-        <v>7.222887114724699</v>
+        <v>3.095238095238095</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.03854166666667425</v>
-      </c>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
+        <v>0.446428571428573</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.538455506267042</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>66818452.38095238</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>15</v>
+      </c>
       <c r="BK7" t="n">
-        <v>98349.89435098114</v>
+        <v>-0.9269480519480737</v>
       </c>
       <c r="BL7" t="n">
-        <v>2.009690656565657</v>
+        <v>-1.115384886548782</v>
       </c>
       <c r="BM7" t="n">
-        <v>10.67414772727273</v>
-      </c>
-      <c r="BN7" t="inlineStr"/>
+        <v>8.862939743435106</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.416785236285043</v>
+      </c>
       <c r="BO7" t="n">
-        <v>52571476.48358586</v>
+        <v>9.36323953823954</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2460457700815013</v>
+        <v>35835013.55385885</v>
       </c>
       <c r="BQ7" t="n">
-        <v>137232.0075757576</v>
-      </c>
-      <c r="BR7" t="inlineStr"/>
+        <v>2.001010101010102</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>10.89116161616161</v>
+      </c>
       <c r="BS7" t="n">
-        <v>1.424771625063485</v>
+        <v>-0.02380952380952372</v>
       </c>
       <c r="BT7" t="n">
-        <v>-1.230271464646506</v>
+        <v>-0.1886401599346641</v>
       </c>
       <c r="BU7" t="n">
-        <v>-1.049348124510971</v>
-      </c>
-      <c r="BV7" t="inlineStr"/>
+        <v>0.1761904761904809</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>97736.90339480778</v>
+      </c>
       <c r="BW7" t="n">
-        <v>9.348358585858591</v>
+        <v>52560520.38239539</v>
       </c>
     </row>
     <row r="8">
@@ -2356,55 +2452,71 @@
       <c r="BA8" t="n">
         <v>0.1184615384615385</v>
       </c>
-      <c r="BB8" t="inlineStr"/>
+      <c r="BB8" t="n">
+        <v>8.763888888888886</v>
+      </c>
       <c r="BC8" t="n">
-        <v>8484345.249946849</v>
+        <v>52399.20634920635</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.501648431935351</v>
-      </c>
-      <c r="BE8" t="inlineStr"/>
+        <v>255333.3333333333</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>138.8333333333333</v>
+      </c>
       <c r="BF8" t="n">
-        <v>2.302561765206036</v>
+        <v>3.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.5215909090909108</v>
-      </c>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
+        <v>1.305555555555561</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>2.032859704453159</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>57066666.66666667</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>140.5</v>
+      </c>
       <c r="BK8" t="n">
-        <v>35146.45672060344</v>
+        <v>2.691378066378064</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.134375</v>
+        <v>2.099582723665719</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.298200757575756</v>
-      </c>
-      <c r="BN8" t="inlineStr"/>
+        <v>1.158346507245867</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.4241580013879205</v>
+      </c>
       <c r="BO8" t="n">
-        <v>14494977.9040404</v>
+        <v>2.751226551226551</v>
       </c>
       <c r="BP8" t="n">
-        <v>-0.5951404901465409</v>
+        <v>8015442.190415449</v>
       </c>
       <c r="BQ8" t="n">
-        <v>54298.1691919192</v>
-      </c>
-      <c r="BR8" t="inlineStr"/>
+        <v>1.089935064935065</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>3.040800865800861</v>
+      </c>
       <c r="BS8" t="n">
-        <v>0.436614441690621</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BT8" t="n">
-        <v>2.80495580808082</v>
+        <v>-0.5713170227525133</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.741896787969409</v>
-      </c>
-      <c r="BV8" t="inlineStr"/>
+        <v>0.3766233766233782</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>34153.77366708421</v>
+      </c>
       <c r="BW8" t="n">
-        <v>2.749368686868678</v>
+        <v>13938416.30591631</v>
       </c>
     </row>
     <row r="9">
@@ -2585,55 +2697,71 @@
       <c r="BA9" t="n">
         <v>0.1481481481481481</v>
       </c>
-      <c r="BB9" t="inlineStr"/>
+      <c r="BB9" t="n">
+        <v>-13.46111111111108</v>
+      </c>
       <c r="BC9" t="n">
-        <v>-684206.1642206907</v>
+        <v>8321.085858585859</v>
       </c>
       <c r="BD9" t="n">
-        <v>-2.659498215030027</v>
-      </c>
-      <c r="BE9" t="inlineStr"/>
+        <v>62500</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-1.366666666666646</v>
+      </c>
       <c r="BF9" t="n">
-        <v>2.399412692790548</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.7299262465929139</v>
-      </c>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
+        <v>7.672222222222217</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.542002322867631</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>21340000</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-6.900000000000006</v>
+      </c>
       <c r="BK9" t="n">
-        <v>96.88048623976647</v>
+        <v>0.6546296296296248</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.09098925765592436</v>
+        <v>-0.5012928644171097</v>
       </c>
       <c r="BM9" t="n">
-        <v>-1.107050665383994</v>
-      </c>
-      <c r="BN9" t="inlineStr"/>
+        <v>-2.642750709300074</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0.08741082791552257</v>
+      </c>
       <c r="BO9" t="n">
-        <v>-1186740.820907485</v>
+        <v>0.3307659932659988</v>
       </c>
       <c r="BP9" t="n">
-        <v>-4.427089826176179</v>
+        <v>-637177.5869221911</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10373.68125701458</v>
-      </c>
-      <c r="BR9" t="inlineStr"/>
+        <v>0.02723063973063966</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-1.337710437710442</v>
+      </c>
       <c r="BS9" t="n">
-        <v>-0.1042685620118655</v>
+        <v>-0.1333333333333333</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.7776895943562749</v>
+        <v>-4.532106489230813</v>
       </c>
       <c r="BU9" t="n">
-        <v>-0.4583955896267753</v>
-      </c>
-      <c r="BV9" t="inlineStr"/>
+        <v>-1.178409090909089</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-147.2594529802664</v>
+      </c>
       <c r="BW9" t="n">
-        <v>0.2592111592111621</v>
+        <v>-1614810.606060605</v>
       </c>
     </row>
     <row r="10">
@@ -2814,55 +2942,71 @@
       <c r="BA10" t="n">
         <v>-0.1666666666666667</v>
       </c>
-      <c r="BB10" t="inlineStr"/>
+      <c r="BB10" t="n">
+        <v>-3.065476190476204</v>
+      </c>
       <c r="BC10" t="n">
-        <v>2822461.216699156</v>
+        <v>11027.64550264551</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.1582944630093834</v>
-      </c>
-      <c r="BE10" t="inlineStr"/>
+        <v>116476.1904761905</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>64.78571428571428</v>
+      </c>
       <c r="BF10" t="n">
-        <v>4.296953610879044</v>
+        <v>0.4523809523809521</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1743686868686858</v>
-      </c>
-      <c r="BH10" t="inlineStr"/>
-      <c r="BI10" t="inlineStr"/>
-      <c r="BJ10" t="inlineStr"/>
+        <v>-2.486904761904761</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>4.058815855776999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>34783333.33333334</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>69.28571428571428</v>
+      </c>
       <c r="BK10" t="n">
-        <v>3336.487631114825</v>
+        <v>1.00135481802144</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.1049277497194168</v>
+        <v>0.6190779528185715</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.54325547138049</v>
-      </c>
-      <c r="BN10" t="inlineStr"/>
+        <v>-0.3805815796104071</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.03606204665101931</v>
+      </c>
       <c r="BO10" t="n">
-        <v>4415765.642536476</v>
+        <v>1.932098765432102</v>
       </c>
       <c r="BP10" t="n">
-        <v>-2.969934094495496</v>
+        <v>2719343.974188117</v>
       </c>
       <c r="BQ10" t="n">
-        <v>11623.15867003368</v>
-      </c>
-      <c r="BR10" t="inlineStr"/>
+        <v>0.09567901234567922</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1.450781625781644</v>
+      </c>
       <c r="BS10" t="n">
-        <v>0.03321266128283695</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="BT10" t="n">
-        <v>1.106684904601536</v>
+        <v>-2.98416908673801</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.5920043163464186</v>
-      </c>
-      <c r="BV10" t="inlineStr"/>
+        <v>-0.1213564213564204</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>3253.204273912292</v>
+      </c>
       <c r="BW10" t="n">
-        <v>2.037338664421995</v>
+        <v>4303366.201699534</v>
       </c>
     </row>
     <row r="11">
@@ -3043,55 +3187,71 @@
       <c r="BA11" t="n">
         <v>0.3903448275862069</v>
       </c>
-      <c r="BB11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>-2.261904761904759</v>
+      </c>
       <c r="BC11" t="n">
-        <v>-3813254.489539482</v>
+        <v>-14403.08641975308</v>
       </c>
       <c r="BD11" t="n">
-        <v>-2.171178431167789</v>
-      </c>
-      <c r="BE11" t="inlineStr"/>
+        <v>-964.2857142857101</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>57.46428571428572</v>
+      </c>
       <c r="BF11" t="n">
-        <v>-1.689904644850131</v>
+        <v>-1.035714285714286</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1518518518518484</v>
-      </c>
-      <c r="BH11" t="inlineStr"/>
-      <c r="BI11" t="inlineStr"/>
-      <c r="BJ11" t="inlineStr"/>
+        <v>-1.845238095238098</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-1.95538812991083</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-9928571.428571429</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>64.42857142857142</v>
+      </c>
       <c r="BK11" t="n">
-        <v>-10611.53881264981</v>
+        <v>-2.006790123456796</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.02195767195767195</v>
+        <v>-3.763817018035297</v>
       </c>
       <c r="BM11" t="n">
-        <v>-1.519532627865942</v>
-      </c>
-      <c r="BN11" t="inlineStr"/>
+        <v>-2.311778629580488</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.03084590561370715</v>
+      </c>
       <c r="BO11" t="n">
-        <v>-4281528.880070546</v>
+        <v>-1.079938271604931</v>
       </c>
       <c r="BP11" t="n">
-        <v>1.020766590018074</v>
+        <v>-4152502.417877482</v>
       </c>
       <c r="BQ11" t="n">
-        <v>-13474.51499118166</v>
-      </c>
-      <c r="BR11" t="inlineStr"/>
+        <v>0.03148148148148167</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-1.553395061728381</v>
+      </c>
       <c r="BS11" t="n">
-        <v>0.05176677396104612</v>
+        <v>0.9642857142857144</v>
       </c>
       <c r="BT11" t="n">
-        <v>-2.306790123456778</v>
+        <v>1.086390131101176</v>
       </c>
       <c r="BU11" t="n">
-        <v>-3.824580906924183</v>
-      </c>
-      <c r="BV11" t="inlineStr"/>
+        <v>0.08888888888888502</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-11050.78805401303</v>
+      </c>
       <c r="BW11" t="n">
-        <v>-1.130731922398581</v>
+        <v>-4360100.308641975</v>
       </c>
     </row>
     <row r="12">
@@ -3105,7 +3265,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">hooper s 
+          <t xml:space="preserve">robinson t 
   eng </t>
         </is>
       </c>
@@ -3272,55 +3432,71 @@
       <c r="BA12" t="n">
         <v>-0.1467236467236467</v>
       </c>
-      <c r="BB12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>3.733333333333292</v>
+      </c>
       <c r="BC12" t="n">
-        <v>1123258.88149208</v>
+        <v>-14617.59259259258</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.212546414653929</v>
-      </c>
-      <c r="BE12" t="inlineStr"/>
+        <v>-50750</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-46.94999999999999</v>
+      </c>
       <c r="BF12" t="n">
-        <v>1.745381994393526</v>
+        <v>1.35</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.9830246913580289</v>
-      </c>
-      <c r="BH12" t="inlineStr"/>
-      <c r="BI12" t="inlineStr"/>
-      <c r="BJ12" t="inlineStr"/>
+        <v>1.300000000000001</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>2.010865479454225</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-8500000</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-50.40000000000001</v>
+      </c>
       <c r="BK12" t="n">
-        <v>-7092.817759856909</v>
+        <v>0.3314814814814611</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0.1164021164021163</v>
+        <v>0.2890752207315757</v>
       </c>
       <c r="BM12" t="n">
-        <v>-1.629232804232814</v>
-      </c>
-      <c r="BN12" t="inlineStr"/>
+        <v>1.353146613066627</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.1818346370977952</v>
+      </c>
       <c r="BO12" t="n">
-        <v>-7753386.243386243</v>
+        <v>-1.982716049382717</v>
       </c>
       <c r="BP12" t="n">
-        <v>-2.026167315787735</v>
+        <v>1462506.809830081</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-15546.16402116401</v>
-      </c>
-      <c r="BR12" t="inlineStr"/>
+        <v>-0.125925925925926</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-1.595370370370375</v>
+      </c>
       <c r="BS12" t="n">
-        <v>0.1609137687504563</v>
+        <v>-0.6499999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.631481481481444</v>
+        <v>-2.091790856870837</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.3498391096204614</v>
-      </c>
-      <c r="BV12" t="inlineStr"/>
+        <v>1.045987654320992</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-6653.568518493696</v>
+      </c>
       <c r="BW12" t="n">
-        <v>-1.931922398589066</v>
+        <v>-7674814.814814813</v>
       </c>
     </row>
     <row r="13">
@@ -3334,7 +3510,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">kavanagh c 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
@@ -3501,55 +3677,71 @@
       <c r="BA13" t="n">
         <v>0.2542857142857143</v>
       </c>
-      <c r="BB13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>-7.666666666666657</v>
+      </c>
       <c r="BC13" t="n">
-        <v>5949885.115361378</v>
+        <v>31198.89971139973</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.2627298481775</v>
-      </c>
-      <c r="BE13" t="inlineStr"/>
+        <v>18250</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-52.25</v>
+      </c>
       <c r="BF13" t="n">
-        <v>-0.1197859507642107</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.63914141414141</v>
-      </c>
-      <c r="BH13" t="inlineStr"/>
-      <c r="BI13" t="inlineStr"/>
-      <c r="BJ13" t="inlineStr"/>
+        <v>0.8333333333333321</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0.107550295632592</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>33625000</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-66.16666666666666</v>
+      </c>
       <c r="BK13" t="n">
-        <v>-3590.164421771973</v>
+        <v>0.5960317460317128</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.302146464646466</v>
+        <v>1.947288753798233</v>
       </c>
       <c r="BM13" t="n">
-        <v>3.878156565656568</v>
-      </c>
-      <c r="BN13" t="inlineStr"/>
+        <v>1.304282828065098</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.4876474486702498</v>
+      </c>
       <c r="BO13" t="n">
-        <v>18043813.13131313</v>
+        <v>1.168253968253964</v>
       </c>
       <c r="BP13" t="n">
-        <v>1.514884621163226</v>
+        <v>6298492.036390662</v>
       </c>
       <c r="BQ13" t="n">
-        <v>31671.59090909094</v>
-      </c>
-      <c r="BR13" t="inlineStr"/>
+        <v>1.287662337662338</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>3.834595959595958</v>
+      </c>
       <c r="BS13" t="n">
-        <v>0.4619302052511434</v>
+        <v>-1</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.5243686868686552</v>
+        <v>1.596670705162044</v>
       </c>
       <c r="BU13" t="n">
-        <v>2.054964922091642</v>
-      </c>
-      <c r="BV13" t="inlineStr"/>
+        <v>3.640909090909087</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-2595.589961553094</v>
+      </c>
       <c r="BW13" t="n">
-        <v>1.240025252525243</v>
+        <v>17697285.35353535</v>
       </c>
     </row>
     <row r="14">
@@ -3563,7 +3755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bankes p 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
@@ -3730,55 +3922,71 @@
       <c r="BA14" t="n">
         <v>-0.1288888888888889</v>
       </c>
-      <c r="BB14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>16.20634920634922</v>
+      </c>
       <c r="BC14" t="n">
-        <v>-29208527.81258821</v>
+        <v>-129822.9797979798</v>
       </c>
       <c r="BD14" t="n">
-        <v>-4.008702372427862</v>
-      </c>
-      <c r="BE14" t="inlineStr"/>
+        <v>-203071.4285714286</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.023809523809518</v>
+      </c>
       <c r="BF14" t="n">
-        <v>-5.266013449079111</v>
+        <v>-2.095238095238095</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.2765873015873019</v>
-      </c>
-      <c r="BH14" t="inlineStr"/>
-      <c r="BI14" t="inlineStr"/>
-      <c r="BJ14" t="inlineStr"/>
+        <v>0.2063492063492092</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-5.289813541506646</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-57614285.71428572</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0.5</v>
+      </c>
       <c r="BK14" t="n">
-        <v>-80998.16741530169</v>
+        <v>1.354461279461304</v>
       </c>
       <c r="BL14" t="n">
-        <v>-1.822835497835498</v>
+        <v>1.24332081371071</v>
       </c>
       <c r="BM14" t="n">
-        <v>-7.384812409812412</v>
-      </c>
-      <c r="BN14" t="inlineStr"/>
+        <v>-3.960202256893439</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-1.172753644381934</v>
+      </c>
       <c r="BO14" t="n">
-        <v>-46137494.5887446</v>
+        <v>-6.229377104377122</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.97873456558635</v>
+        <v>-29164734.28086576</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-129942.4242424242</v>
-      </c>
-      <c r="BR14" t="inlineStr"/>
+        <v>-1.800084175084175</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-7.349031986531983</v>
+      </c>
       <c r="BS14" t="n">
-        <v>-1.162400109028399</v>
+        <v>0.1904761904761907</v>
       </c>
       <c r="BT14" t="n">
-        <v>1.306709956709966</v>
+        <v>2.03810894665191</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.042361877947855</v>
-      </c>
-      <c r="BV14" t="inlineStr"/>
+        <v>0.2611111111111057</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-80624.73331944112</v>
+      </c>
       <c r="BW14" t="n">
-        <v>-6.294985569985585</v>
+        <v>-46024141.41414142</v>
       </c>
     </row>
     <row r="15">
@@ -3792,7 +4000,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">jones r 
   eng </t>
         </is>
       </c>
@@ -3959,55 +4167,71 @@
       <c r="BA15" t="n">
         <v>-0.4400000000000001</v>
       </c>
-      <c r="BB15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>-0.08333333333334281</v>
+      </c>
       <c r="BC15" t="n">
-        <v>-20532666.19179343</v>
+        <v>-95117.46031746034</v>
       </c>
       <c r="BD15" t="n">
-        <v>-3.445223900850493</v>
-      </c>
-      <c r="BE15" t="inlineStr"/>
+        <v>-542833.3333333334</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>-193.1666666666667</v>
+      </c>
       <c r="BF15" t="n">
-        <v>-4.364642644138314</v>
+        <v>-7.666666666666667</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.01701388888888289</v>
-      </c>
-      <c r="BH15" t="inlineStr"/>
-      <c r="BI15" t="inlineStr"/>
-      <c r="BJ15" t="inlineStr"/>
+        <v>0.1388888888888857</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-4.183741253164882</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-240066666.6666667</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-192.5</v>
+      </c>
       <c r="BK15" t="n">
-        <v>-65235.93873934748</v>
+        <v>-0.9464285714285836</v>
       </c>
       <c r="BL15" t="n">
-        <v>-2.071874999999999</v>
+        <v>0.6954680275880492</v>
       </c>
       <c r="BM15" t="n">
-        <v>-6.946875000000006</v>
-      </c>
-      <c r="BN15" t="inlineStr"/>
+        <v>-2.990545002332553</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-1.282148749334537</v>
+      </c>
       <c r="BO15" t="n">
-        <v>-42905173.61111112</v>
+        <v>-5.993650793650801</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.1816396292858933</v>
+        <v>-19801023.26681154</v>
       </c>
       <c r="BQ15" t="n">
-        <v>-97262.5</v>
-      </c>
-      <c r="BR15" t="inlineStr"/>
+        <v>-2.048809523809524</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>-6.718650793650795</v>
+      </c>
       <c r="BS15" t="n">
-        <v>-1.34844265566772</v>
+        <v>-2.166666666666667</v>
       </c>
       <c r="BT15" t="n">
-        <v>-1.167013888888903</v>
+        <v>-0.131907875646462</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.24357916699671</v>
-      </c>
-      <c r="BV15" t="inlineStr"/>
+        <v>0.02976190476190865</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-63531.54903544473</v>
+      </c>
       <c r="BW15" t="n">
-        <v>-5.993055555555557</v>
+        <v>-41444007.93650794</v>
       </c>
     </row>
     <row r="16">
@@ -4021,7 +4245,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
@@ -4188,55 +4412,71 @@
       <c r="BA16" t="n">
         <v>0.07999999999999999</v>
       </c>
-      <c r="BB16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>4</v>
+      </c>
       <c r="BC16" t="n">
-        <v>14425041.38395312</v>
+        <v>44405.59764309764</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.005314256081803</v>
-      </c>
-      <c r="BE16" t="inlineStr"/>
+        <v>-28000</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-76</v>
+      </c>
       <c r="BF16" t="n">
-        <v>2.391393458718028</v>
+        <v>1</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.7204545454545475</v>
-      </c>
-      <c r="BH16" t="inlineStr"/>
-      <c r="BI16" t="inlineStr"/>
-      <c r="BJ16" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.556437938048219</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-17000000</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-79</v>
+      </c>
       <c r="BK16" t="n">
-        <v>40492.08068470678</v>
+        <v>-1.327707631874318</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.341045374378707</v>
+        <v>2.741587102677329</v>
       </c>
       <c r="BM16" t="n">
-        <v>4.943843193843193</v>
-      </c>
-      <c r="BN16" t="inlineStr"/>
+        <v>6.261302612963021</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.034107883669287</v>
+      </c>
       <c r="BO16" t="n">
-        <v>20403810.02485169</v>
+        <v>3.634315375982055</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.217024878346148</v>
+        <v>15147008.20433512</v>
       </c>
       <c r="BQ16" t="n">
-        <v>45265.71669071668</v>
-      </c>
-      <c r="BR16" t="inlineStr"/>
+        <v>1.309497755331088</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>4.828367003367006</v>
+      </c>
       <c r="BS16" t="n">
-        <v>0.9712415833029868</v>
+        <v>-1</v>
       </c>
       <c r="BT16" t="n">
-        <v>-1.337826679493361</v>
+        <v>3.291955379392721</v>
       </c>
       <c r="BU16" t="n">
-        <v>2.880522051656925</v>
-      </c>
-      <c r="BV16" t="inlineStr"/>
+        <v>0.7162878787878775</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>42815.95316639175</v>
+      </c>
       <c r="BW16" t="n">
-        <v>3.704553471220137</v>
+        <v>20341235.62008979</v>
       </c>
     </row>
     <row r="17">
@@ -4250,7 +4490,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">bankes p 
   eng </t>
         </is>
       </c>
@@ -4419,55 +4659,71 @@
       <c r="BA17" t="n">
         <v>0.6121794871794872</v>
       </c>
-      <c r="BB17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BC17" t="n">
-        <v>9014180.380404595</v>
+        <v>44571.33838383836</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.276960797263001</v>
-      </c>
-      <c r="BE17" t="inlineStr"/>
+        <v>262000</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>235</v>
+      </c>
       <c r="BF17" t="n">
-        <v>-0.3816575081364988</v>
+        <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.571773288439953</v>
-      </c>
-      <c r="BH17" t="inlineStr"/>
-      <c r="BI17" t="inlineStr"/>
-      <c r="BJ17" t="inlineStr"/>
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.2751527401318299</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>67600000</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>249</v>
+      </c>
       <c r="BK17" t="n">
-        <v>35371.35706396373</v>
+        <v>3.367045454545462</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8333613916947249</v>
+        <v>2.970866412536509</v>
       </c>
       <c r="BM17" t="n">
-        <v>4.635297418630756</v>
-      </c>
-      <c r="BN17" t="inlineStr"/>
+        <v>4.35302111431217</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>0.6637832219688375</v>
+      </c>
       <c r="BO17" t="n">
-        <v>14434342.7328844</v>
+        <v>1.352746212121218</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.540241354730181</v>
+        <v>9764297.017629083</v>
       </c>
       <c r="BQ17" t="n">
-        <v>42706.62177328842</v>
-      </c>
-      <c r="BR17" t="inlineStr"/>
+        <v>0.8736426767676768</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>4.814709595959599</v>
+      </c>
       <c r="BS17" t="n">
-        <v>0.6235440233925897</v>
+        <v>3</v>
       </c>
       <c r="BT17" t="n">
-        <v>3.384287317620647</v>
+        <v>3.557839458854065</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.217460965732897</v>
-      </c>
-      <c r="BV17" t="inlineStr"/>
+        <v>2.101578282828285</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>36222.4641969592</v>
+      </c>
       <c r="BW17" t="n">
-        <v>1.58021885521886</v>
+        <v>14549746.68560606</v>
       </c>
     </row>
     <row r="18">
@@ -4481,7 +4737,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">jones r 
+          <t xml:space="preserve">england d 
   eng </t>
         </is>
       </c>
@@ -4648,55 +4904,71 @@
       <c r="BA18" t="n">
         <v>-0.03703703703703703</v>
       </c>
-      <c r="BB18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>12</v>
+      </c>
       <c r="BC18" t="n">
-        <v>-10652806.00688906</v>
+        <v>-36026.78571428571</v>
       </c>
       <c r="BD18" t="n">
-        <v>-1.830401942562276</v>
-      </c>
-      <c r="BE18" t="inlineStr"/>
+        <v>-64000</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-8</v>
+      </c>
       <c r="BF18" t="n">
-        <v>-3.982160148257123</v>
+        <v>-2</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.165909090909089</v>
-      </c>
-      <c r="BH18" t="inlineStr"/>
-      <c r="BI18" t="inlineStr"/>
-      <c r="BJ18" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-3.774350375161518</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-25300000</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-8</v>
+      </c>
       <c r="BK18" t="n">
-        <v>-20473.58631640312</v>
+        <v>0.5217171717171709</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0.8611111111111109</v>
+        <v>1.367471929223143</v>
       </c>
       <c r="BM18" t="n">
-        <v>-2.971464646464639</v>
-      </c>
-      <c r="BN18" t="inlineStr"/>
+        <v>-1.406845910300888</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-0.2649057266967534</v>
+      </c>
       <c r="BO18" t="n">
-        <v>-15010568.18181818</v>
+        <v>-3.909163059163049</v>
       </c>
       <c r="BP18" t="n">
-        <v>2.801577808156754</v>
+        <v>-10134420.99257531</v>
       </c>
       <c r="BQ18" t="n">
-        <v>-37233.58585858587</v>
-      </c>
-      <c r="BR18" t="inlineStr"/>
+        <v>-0.8212842712842714</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-2.82849927849928</v>
+      </c>
       <c r="BS18" t="n">
-        <v>-0.2646361027046098</v>
+        <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.4613636363636431</v>
+        <v>2.800017495036293</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.272612403937472</v>
-      </c>
-      <c r="BV18" t="inlineStr"/>
+        <v>1.326948051948051</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-18718.58096681569</v>
+      </c>
       <c r="BW18" t="n">
-        <v>-3.886868686868667</v>
+        <v>-14709031.38528138</v>
       </c>
     </row>
     <row r="19">
@@ -4710,7 +4982,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">pawson c 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
@@ -4877,55 +5149,71 @@
       <c r="BA19" t="n">
         <v>0.2933333333333333</v>
       </c>
-      <c r="BB19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>-7.5</v>
+      </c>
       <c r="BC19" t="n">
-        <v>-2405181.613292682</v>
+        <v>-2878.030303030304</v>
       </c>
       <c r="BD19" t="n">
-        <v>-2.137605854614364</v>
-      </c>
-      <c r="BE19" t="inlineStr"/>
+        <v>-50000</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-3</v>
+      </c>
       <c r="BF19" t="n">
-        <v>-2.104906191303257</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-2.467803030303028</v>
-      </c>
-      <c r="BH19" t="inlineStr"/>
-      <c r="BI19" t="inlineStr"/>
-      <c r="BJ19" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-1.971585579161726</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-5700000</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>-19</v>
+      </c>
       <c r="BK19" t="n">
-        <v>1224.379794755179</v>
+        <v>0.4065656565657036</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0.4394255050505051</v>
+        <v>-2.269629699045623</v>
       </c>
       <c r="BM19" t="n">
-        <v>-2.487405303030314</v>
-      </c>
-      <c r="BN19" t="inlineStr"/>
+        <v>-2.017298474643809</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-0.2312743589798822</v>
+      </c>
       <c r="BO19" t="n">
-        <v>-4719655.934343435</v>
+        <v>-0.8411976911976922</v>
       </c>
       <c r="BP19" t="n">
-        <v>-0.6429093681802662</v>
+        <v>-2267870.215195942</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-3484.185606060608</v>
-      </c>
-      <c r="BR19" t="inlineStr"/>
+        <v>-0.4242784992784994</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-2.427164502164516</v>
+      </c>
       <c r="BS19" t="n">
-        <v>-0.213902584916517</v>
+        <v>0</v>
       </c>
       <c r="BT19" t="n">
-        <v>0.3784722222222285</v>
+        <v>-0.8270492207280391</v>
       </c>
       <c r="BU19" t="n">
-        <v>-2.4502429086794</v>
-      </c>
-      <c r="BV19" t="inlineStr"/>
+        <v>-2.391774891774894</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>1414.226577638787</v>
+      </c>
       <c r="BW19" t="n">
-        <v>-0.8496843434343333</v>
+        <v>-4757853.535353538</v>
       </c>
     </row>
     <row r="20">
@@ -4939,7 +5227,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">taylor a 
   eng </t>
         </is>
       </c>
@@ -5106,55 +5394,71 @@
       <c r="BA20" t="n">
         <v>-0.0438871473354232</v>
       </c>
-      <c r="BB20" t="inlineStr"/>
+      <c r="BB20" t="n">
+        <v>1</v>
+      </c>
       <c r="BC20" t="n">
-        <v>-1854675.709531553</v>
+        <v>2708.641975308637</v>
       </c>
       <c r="BD20" t="n">
-        <v>-2.767859395220071</v>
-      </c>
-      <c r="BE20" t="inlineStr"/>
+        <v>-41000</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-64</v>
+      </c>
       <c r="BF20" t="n">
-        <v>-0.5539894497582765</v>
+        <v>-1</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.4598379629629683</v>
-      </c>
-      <c r="BH20" t="inlineStr"/>
-      <c r="BI20" t="inlineStr"/>
-      <c r="BJ20" t="inlineStr"/>
+        <v>-1.666666666666668</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-0.8695578413006189</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-61</v>
+      </c>
       <c r="BK20" t="n">
-        <v>-3936.283575099369</v>
+        <v>1.024647266313934</v>
       </c>
       <c r="BL20" t="n">
-        <v>-0.08182870370370376</v>
+        <v>0.4806226238501949</v>
       </c>
       <c r="BM20" t="n">
-        <v>-2.224961419753086</v>
-      </c>
-      <c r="BN20" t="inlineStr"/>
+        <v>-2.529259404452915</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-0.09424979188911076</v>
+      </c>
       <c r="BO20" t="n">
-        <v>-1515984.760802469</v>
+        <v>-1.094664902998232</v>
       </c>
       <c r="BP20" t="n">
-        <v>-0.9288341484032934</v>
+        <v>-1885559.672788129</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3885.725308641966</v>
-      </c>
-      <c r="BR20" t="inlineStr"/>
+        <v>-0.07314814814814841</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-2.441975308641972</v>
+      </c>
       <c r="BS20" t="n">
-        <v>-0.1022361806675531</v>
+        <v>-1</v>
       </c>
       <c r="BT20" t="n">
-        <v>1.327970679012367</v>
+        <v>-0.494148218387128</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.4145858618123839</v>
-      </c>
-      <c r="BV20" t="inlineStr"/>
+        <v>-0.597486772486775</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-3323.292618926011</v>
+      </c>
       <c r="BW20" t="n">
-        <v>-1.079783950617283</v>
+        <v>-1505028.659611993</v>
       </c>
     </row>
     <row r="21">
@@ -5168,7 +5472,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">taylor a 
+          <t xml:space="preserve">madley a 
   eng </t>
         </is>
       </c>
@@ -5335,55 +5639,71 @@
       <c r="BA21" t="n">
         <v>0.1185897435897436</v>
       </c>
-      <c r="BB21" t="inlineStr"/>
+      <c r="BB21" t="n">
+        <v>2</v>
+      </c>
       <c r="BC21" t="n">
-        <v>6778035.877294458</v>
+        <v>25190.5753968254</v>
       </c>
       <c r="BD21" t="n">
-        <v>0.159866381802658</v>
-      </c>
-      <c r="BE21" t="inlineStr"/>
+        <v>284500</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>163.5</v>
+      </c>
       <c r="BF21" t="n">
-        <v>2.840250775912537</v>
+        <v>5.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>-2.672045855379185</v>
-      </c>
-      <c r="BH21" t="inlineStr"/>
-      <c r="BI21" t="inlineStr"/>
-      <c r="BJ21" t="inlineStr"/>
+        <v>-4.333333333333332</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2.757921663712096</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>174.5</v>
+      </c>
       <c r="BK21" t="n">
-        <v>-820.8898672133946</v>
+        <v>1.985267857142873</v>
       </c>
       <c r="BL21" t="n">
-        <v>0.4560405643738972</v>
+        <v>3.369386669294784</v>
       </c>
       <c r="BM21" t="n">
-        <v>2.647883597883592</v>
-      </c>
-      <c r="BN21" t="inlineStr"/>
+        <v>0.08908297584768832</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-0.1806531397524043</v>
+      </c>
       <c r="BO21" t="n">
-        <v>19174272.48677249</v>
+        <v>4.041319444444454</v>
       </c>
       <c r="BP21" t="n">
-        <v>-4.27549750086515</v>
+        <v>6495862.788151396</v>
       </c>
       <c r="BQ21" t="n">
-        <v>24883.86243386244</v>
-      </c>
-      <c r="BR21" t="inlineStr"/>
+        <v>0.460863095238095</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>2.674503968253958</v>
+      </c>
       <c r="BS21" t="n">
-        <v>-0.1476273136812352</v>
+        <v>2</v>
       </c>
       <c r="BT21" t="n">
-        <v>1.94880952380953</v>
+        <v>-4.256757713283452</v>
       </c>
       <c r="BU21" t="n">
-        <v>3.778172753172782</v>
-      </c>
-      <c r="BV21" t="inlineStr"/>
+        <v>-2.634623015873014</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-951.6428628560971</v>
+      </c>
       <c r="BW21" t="n">
-        <v>4.045370370370378</v>
+        <v>19179191.46825397</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
         </is>
       </c>
     </row>
@@ -983,70 +983,70 @@
         <v>-0.08571428571428574</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.916666666666657</v>
+        <v>14577.70562770563</v>
       </c>
       <c r="BC2" t="n">
-        <v>14577.70562770563</v>
+        <v>506083.3333333334</v>
       </c>
       <c r="BD2" t="n">
-        <v>506083.3333333334</v>
+        <v>-4.151702102245594</v>
       </c>
       <c r="BE2" t="n">
-        <v>246.9166666666667</v>
+        <v>0.07974910700066085</v>
       </c>
       <c r="BF2" t="n">
-        <v>8</v>
+        <v>9408.420073715082</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.508333333333336</v>
+        <v>-0.3969696969696912</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0.3053525925420359</v>
+        <v>242.1666666666667</v>
       </c>
       <c r="BI2" t="n">
         <v>133708333.3333333</v>
       </c>
       <c r="BJ2" t="n">
-        <v>242.1666666666667</v>
+        <v>3.508333333333336</v>
       </c>
       <c r="BK2" t="n">
+        <v>246.9166666666667</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2185822.51082252</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.07330447330447276</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>-1.290656565656565</v>
+      </c>
+      <c r="BO2" t="n">
         <v>-2.03542568542565</v>
       </c>
-      <c r="BL2" t="n">
-        <v>-4.151702102245594</v>
-      </c>
-      <c r="BM2" t="n">
+      <c r="BP2" t="n">
+        <v>8</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>-2.487672911974144</v>
       </c>
-      <c r="BN2" t="n">
-        <v>0.07974910700066085</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-0.3969696969696912</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-4494754.567378797</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.07330447330447276</v>
-      </c>
       <c r="BR2" t="n">
-        <v>-0.96789321789322</v>
+        <v>-0.7798856164539387</v>
       </c>
       <c r="BS2" t="n">
         <v>3</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.7798856164539387</v>
+        <v>-0.96789321789322</v>
       </c>
       <c r="BU2" t="n">
-        <v>-1.290656565656565</v>
+        <v>-0.3053525925420359</v>
       </c>
       <c r="BV2" t="n">
-        <v>9408.420073715082</v>
+        <v>-4494754.567378797</v>
       </c>
       <c r="BW2" t="n">
-        <v>2185822.51082252</v>
+        <v>7.916666666666657</v>
       </c>
     </row>
     <row r="3">
@@ -1226,70 +1226,70 @@
         <v>0.1803921568627451</v>
       </c>
       <c r="BB3" t="n">
-        <v>-8.050000000000011</v>
+        <v>-7628.156565656536</v>
       </c>
       <c r="BC3" t="n">
-        <v>-7628.156565656536</v>
+        <v>-260833.3333333333</v>
       </c>
       <c r="BD3" t="n">
-        <v>-260833.3333333333</v>
+        <v>-1.836902070130577</v>
       </c>
       <c r="BE3" t="n">
-        <v>-150.5</v>
+        <v>-0.1651000771888931</v>
       </c>
       <c r="BF3" t="n">
-        <v>-6.333333333333334</v>
+        <v>10666.07403658006</v>
       </c>
       <c r="BG3" t="n">
-        <v>-2.949999999999996</v>
+        <v>2.943087121212116</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.202786785797613</v>
+        <v>-145.8333333333333</v>
       </c>
       <c r="BI3" t="n">
         <v>-67450000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-145.8333333333333</v>
+        <v>-2.949999999999996</v>
       </c>
       <c r="BK3" t="n">
+        <v>-150.5</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>7151579.071969699</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>-0.5242739898989901</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>-4.401199494949495</v>
+      </c>
+      <c r="BO3" t="n">
         <v>-2.944318181818176</v>
       </c>
-      <c r="BL3" t="n">
-        <v>-1.836902070130577</v>
-      </c>
-      <c r="BM3" t="n">
+      <c r="BP3" t="n">
+        <v>-6.333333333333334</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>1.2313695662138</v>
       </c>
-      <c r="BN3" t="n">
-        <v>-0.1651000771888931</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>2.943087121212116</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>7639102.11563462</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>-0.5242739898989901</v>
-      </c>
       <c r="BR3" t="n">
-        <v>0.02885101010100755</v>
+        <v>-3.052484432384784</v>
       </c>
       <c r="BS3" t="n">
         <v>-1.666666666666667</v>
       </c>
       <c r="BT3" t="n">
-        <v>-3.052484432384784</v>
+        <v>0.02885101010100755</v>
       </c>
       <c r="BU3" t="n">
-        <v>-4.401199494949495</v>
+        <v>3.202786785797613</v>
       </c>
       <c r="BV3" t="n">
-        <v>10666.07403658006</v>
+        <v>7639102.11563462</v>
       </c>
       <c r="BW3" t="n">
-        <v>7151579.071969699</v>
+        <v>-8.050000000000011</v>
       </c>
     </row>
     <row r="4">
@@ -1471,70 +1471,70 @@
         <v>-0.103448275862069</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.9444444444444571</v>
+        <v>-13361.80555555555</v>
       </c>
       <c r="BC4" t="n">
-        <v>-13361.80555555555</v>
+        <v>-136666.6666666667</v>
       </c>
       <c r="BD4" t="n">
-        <v>-136666.6666666667</v>
+        <v>-3.013612319928001</v>
       </c>
       <c r="BE4" t="n">
-        <v>-141.8333333333333</v>
+        <v>-0.05569796828988016</v>
       </c>
       <c r="BF4" t="n">
-        <v>-2.333333333333333</v>
+        <v>-9510.036226028868</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.555555555555554</v>
+        <v>-2.705208333333346</v>
       </c>
       <c r="BH4" t="n">
-        <v>-1.904393824837626</v>
+        <v>-149.8333333333333</v>
       </c>
       <c r="BI4" t="n">
         <v>-29166666.66666666</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-149.8333333333333</v>
+        <v>4.555555555555554</v>
       </c>
       <c r="BK4" t="n">
+        <v>-141.8333333333333</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-10150694.44444444</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>-0.1892361111111112</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.936805555555555</v>
+      </c>
+      <c r="BO4" t="n">
         <v>-0.6322916666666458</v>
       </c>
-      <c r="BL4" t="n">
-        <v>-3.013612319928001</v>
-      </c>
-      <c r="BM4" t="n">
+      <c r="BP4" t="n">
+        <v>-2.333333333333333</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>-0.09835620145494772</v>
       </c>
-      <c r="BN4" t="n">
-        <v>-0.05569796828988016</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-2.705208333333346</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-5727426.760768412</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-0.1892361111111112</v>
-      </c>
       <c r="BR4" t="n">
-        <v>-0.7534722222222285</v>
+        <v>1.902731236725462</v>
       </c>
       <c r="BS4" t="n">
         <v>-1.833333333333333</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.902731236725462</v>
+        <v>-0.7534722222222285</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.936805555555555</v>
+        <v>-1.904393824837626</v>
       </c>
       <c r="BV4" t="n">
-        <v>-9510.036226028868</v>
+        <v>-5727426.760768412</v>
       </c>
       <c r="BW4" t="n">
-        <v>-10150694.44444444</v>
+        <v>0.9444444444444571</v>
       </c>
     </row>
     <row r="5">
@@ -1716,70 +1716,70 @@
         <v>-0.08000000000000002</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.62380952380957</v>
+        <v>-39013.14484126987</v>
       </c>
       <c r="BC5" t="n">
-        <v>-39090.34391534394</v>
+        <v>-90857.14285714287</v>
       </c>
       <c r="BD5" t="n">
-        <v>-90857.14285714287</v>
+        <v>-0.8921369566106421</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1999999999999886</v>
+        <v>-0.8394062486361249</v>
       </c>
       <c r="BF5" t="n">
-        <v>-3.314285714285715</v>
+        <v>-17010.22259903839</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.3476190476190482</v>
+        <v>-3.801388888888894</v>
       </c>
       <c r="BH5" t="n">
-        <v>-5.672645978367072</v>
+        <v>0.2571428571428669</v>
       </c>
       <c r="BI5" t="n">
         <v>-34264285.71428572</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.2571428571428669</v>
+        <v>-0.3476190476190482</v>
       </c>
       <c r="BK5" t="n">
-        <v>-1.655291005290991</v>
+        <v>0.1999999999999886</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.8861477560394064</v>
+        <v>-19957559.52380953</v>
       </c>
       <c r="BM5" t="n">
-        <v>-3.266978655207495</v>
+        <v>-1.296626984126984</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.8222234557954373</v>
+        <v>0.2335813492063465</v>
       </c>
       <c r="BO5" t="n">
-        <v>-3.817283950617295</v>
+        <v>-1.859226190476193</v>
       </c>
       <c r="BP5" t="n">
-        <v>-13924752.79709445</v>
+        <v>-3.314285714285715</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-1.291534391534391</v>
+        <v>-3.488703601609942</v>
       </c>
       <c r="BR5" t="n">
-        <v>-3.580291005291002</v>
+        <v>3.189739768745191</v>
       </c>
       <c r="BS5" t="n">
         <v>0.1142857142857143</v>
       </c>
       <c r="BT5" t="n">
-        <v>3.172365388548311</v>
+        <v>-3.563740079365061</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.2217372134038769</v>
+        <v>-5.874763993746186</v>
       </c>
       <c r="BV5" t="n">
-        <v>-16436.24811911705</v>
+        <v>-14275905.11838093</v>
       </c>
       <c r="BW5" t="n">
-        <v>-20015661.37566138</v>
+        <v>1.62380952380957</v>
       </c>
     </row>
     <row r="6">
@@ -1961,70 +1961,70 @@
         <v>0.2426108374384237</v>
       </c>
       <c r="BB6" t="n">
-        <v>-3.594444444444434</v>
+        <v>-19863.54617604618</v>
       </c>
       <c r="BC6" t="n">
-        <v>-19863.54617604618</v>
+        <v>121000</v>
       </c>
       <c r="BD6" t="n">
-        <v>121000</v>
+        <v>-0.2852595135044282</v>
       </c>
       <c r="BE6" t="n">
-        <v>268.3333333333333</v>
+        <v>0.001444251879834102</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.833333333333333</v>
+        <v>-22127.73025141951</v>
       </c>
       <c r="BG6" t="n">
-        <v>-4.411111111111111</v>
+        <v>0.5331168831168753</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.3906131046596073</v>
+        <v>295.6666666666667</v>
       </c>
       <c r="BI6" t="n">
         <v>31829166.66666666</v>
       </c>
       <c r="BJ6" t="n">
-        <v>295.6666666666667</v>
+        <v>-4.411111111111111</v>
       </c>
       <c r="BK6" t="n">
+        <v>268.3333333333333</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>348980.8802308831</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04826839826839824</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.6926767676767689</v>
+      </c>
+      <c r="BO6" t="n">
         <v>-1.459379509379517</v>
       </c>
-      <c r="BL6" t="n">
-        <v>-0.2852595135044282</v>
-      </c>
-      <c r="BM6" t="n">
+      <c r="BP6" t="n">
+        <v>3.833333333333333</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>-0.5212222253982191</v>
       </c>
-      <c r="BN6" t="n">
-        <v>0.001444251879834102</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>0.5331168831168753</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-1186846.132155355</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0.04826839826839824</v>
-      </c>
       <c r="BR6" t="n">
-        <v>-0.01031746031745229</v>
+        <v>0.4641779509386588</v>
       </c>
       <c r="BS6" t="n">
         <v>3.666666666666667</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.4641779509386588</v>
+        <v>-0.01031746031745229</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.6926767676767689</v>
+        <v>-0.3906131046596073</v>
       </c>
       <c r="BV6" t="n">
-        <v>-22127.73025141951</v>
+        <v>-1186846.132155355</v>
       </c>
       <c r="BW6" t="n">
-        <v>348980.8802308831</v>
+        <v>-3.594444444444434</v>
       </c>
     </row>
     <row r="7">
@@ -2208,70 +2208,70 @@
         <v>0.207843137254902</v>
       </c>
       <c r="BB7" t="n">
-        <v>-9.803571428571473</v>
+        <v>138409.0909090909</v>
       </c>
       <c r="BC7" t="n">
-        <v>138409.0909090909</v>
+        <v>255904.7619047619</v>
       </c>
       <c r="BD7" t="n">
-        <v>255904.7619047619</v>
+        <v>-1.115384886548782</v>
       </c>
       <c r="BE7" t="n">
-        <v>15.64285714285714</v>
+        <v>1.416785236285043</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.095238095238095</v>
+        <v>97736.90339480778</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.446428571428573</v>
+        <v>9.36323953823954</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.538455506267042</v>
+        <v>15</v>
       </c>
       <c r="BI7" t="n">
         <v>66818452.38095238</v>
       </c>
       <c r="BJ7" t="n">
-        <v>15</v>
+        <v>0.446428571428573</v>
       </c>
       <c r="BK7" t="n">
+        <v>15.64285714285714</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>52560520.38239539</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>2.001010101010102</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.1761904761904809</v>
+      </c>
+      <c r="BO7" t="n">
         <v>-0.9269480519480737</v>
       </c>
-      <c r="BL7" t="n">
-        <v>-1.115384886548782</v>
-      </c>
-      <c r="BM7" t="n">
+      <c r="BP7" t="n">
+        <v>3.095238095238095</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>8.862939743435106</v>
       </c>
-      <c r="BN7" t="n">
-        <v>1.416785236285043</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>9.36323953823954</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>35835013.55385885</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>2.001010101010102</v>
-      </c>
       <c r="BR7" t="n">
-        <v>10.89116161616161</v>
+        <v>-0.1886401599346641</v>
       </c>
       <c r="BS7" t="n">
         <v>-0.02380952380952372</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.1886401599346641</v>
+        <v>10.89116161616161</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.1761904761904809</v>
+        <v>7.538455506267042</v>
       </c>
       <c r="BV7" t="n">
-        <v>97736.90339480778</v>
+        <v>35835013.55385885</v>
       </c>
       <c r="BW7" t="n">
-        <v>52560520.38239539</v>
+        <v>-9.803571428571473</v>
       </c>
     </row>
     <row r="8">
@@ -2453,70 +2453,70 @@
         <v>0.1184615384615385</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.763888888888886</v>
+        <v>52399.20634920635</v>
       </c>
       <c r="BC8" t="n">
-        <v>52399.20634920635</v>
+        <v>255333.3333333333</v>
       </c>
       <c r="BD8" t="n">
-        <v>255333.3333333333</v>
+        <v>2.099582723665719</v>
       </c>
       <c r="BE8" t="n">
-        <v>138.8333333333333</v>
+        <v>0.4241580013879205</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.5</v>
+        <v>34153.77366708421</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.305555555555561</v>
+        <v>2.751226551226551</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.032859704453159</v>
+        <v>140.5</v>
       </c>
       <c r="BI8" t="n">
         <v>57066666.66666667</v>
       </c>
       <c r="BJ8" t="n">
-        <v>140.5</v>
+        <v>1.305555555555561</v>
       </c>
       <c r="BK8" t="n">
+        <v>138.8333333333333</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>13938416.30591631</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.089935064935065</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.3766233766233782</v>
+      </c>
+      <c r="BO8" t="n">
         <v>2.691378066378064</v>
       </c>
-      <c r="BL8" t="n">
-        <v>2.099582723665719</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BP8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>1.158346507245867</v>
       </c>
-      <c r="BN8" t="n">
-        <v>0.4241580013879205</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>2.751226551226551</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>8015442.190415449</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.089935064935065</v>
-      </c>
       <c r="BR8" t="n">
-        <v>3.040800865800861</v>
+        <v>-0.5713170227525133</v>
       </c>
       <c r="BS8" t="n">
         <v>1.666666666666667</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0.5713170227525133</v>
+        <v>3.040800865800861</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.3766233766233782</v>
+        <v>2.032859704453159</v>
       </c>
       <c r="BV8" t="n">
-        <v>34153.77366708421</v>
+        <v>8015442.190415449</v>
       </c>
       <c r="BW8" t="n">
-        <v>13938416.30591631</v>
+        <v>8.763888888888886</v>
       </c>
     </row>
     <row r="9">
@@ -2698,70 +2698,70 @@
         <v>0.1481481481481481</v>
       </c>
       <c r="BB9" t="n">
-        <v>-13.46111111111108</v>
+        <v>8321.085858585859</v>
       </c>
       <c r="BC9" t="n">
-        <v>8321.085858585859</v>
+        <v>62500</v>
       </c>
       <c r="BD9" t="n">
-        <v>62500</v>
+        <v>-0.5012928644171097</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.366666666666646</v>
+        <v>-0.08741082791552257</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.8666666666666667</v>
+        <v>-147.2594529802664</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.672222222222217</v>
+        <v>0.3307659932659988</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.542002322867631</v>
+        <v>-6.900000000000006</v>
       </c>
       <c r="BI9" t="n">
         <v>21340000</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-6.900000000000006</v>
+        <v>7.672222222222217</v>
       </c>
       <c r="BK9" t="n">
+        <v>-1.366666666666646</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-1614810.606060605</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.02723063973063966</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-1.178409090909089</v>
+      </c>
+      <c r="BO9" t="n">
         <v>0.6546296296296248</v>
       </c>
-      <c r="BL9" t="n">
-        <v>-0.5012928644171097</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BP9" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>-2.642750709300074</v>
       </c>
-      <c r="BN9" t="n">
-        <v>-0.08741082791552257</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.3307659932659988</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-637177.5869221911</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.02723063973063966</v>
-      </c>
       <c r="BR9" t="n">
-        <v>-1.337710437710442</v>
+        <v>-4.532106489230813</v>
       </c>
       <c r="BS9" t="n">
         <v>-0.1333333333333333</v>
       </c>
       <c r="BT9" t="n">
-        <v>-4.532106489230813</v>
+        <v>-1.337710437710442</v>
       </c>
       <c r="BU9" t="n">
-        <v>-1.178409090909089</v>
+        <v>2.542002322867631</v>
       </c>
       <c r="BV9" t="n">
-        <v>-147.2594529802664</v>
+        <v>-637177.5869221911</v>
       </c>
       <c r="BW9" t="n">
-        <v>-1614810.606060605</v>
+        <v>-13.46111111111108</v>
       </c>
     </row>
     <row r="10">
@@ -2943,70 +2943,70 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="BB10" t="n">
-        <v>-3.065476190476204</v>
+        <v>10365.25072150072</v>
       </c>
       <c r="BC10" t="n">
-        <v>11027.64550264551</v>
+        <v>120166.6666666667</v>
       </c>
       <c r="BD10" t="n">
-        <v>116476.1904761905</v>
+        <v>1.10104110723239</v>
       </c>
       <c r="BE10" t="n">
-        <v>64.78571428571428</v>
+        <v>0.02492801945339562</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4523809523809521</v>
+        <v>2568.065065938659</v>
       </c>
       <c r="BG10" t="n">
-        <v>-2.486904761904761</v>
+        <v>1.994760101010101</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.058815855776999</v>
+        <v>72.66666666666669</v>
       </c>
       <c r="BI10" t="n">
-        <v>34783333.33333334</v>
+        <v>34033333.33333334</v>
       </c>
       <c r="BJ10" t="n">
-        <v>69.28571428571428</v>
+        <v>-2.452777777777776</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.00135481802144</v>
+        <v>68.16666666666669</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.6190779528185715</v>
+        <v>4159368.235930735</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.3805815796104071</v>
+        <v>0.09416035353535368</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.03606204665101931</v>
+        <v>-0.2690836940836938</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.932098765432102</v>
+        <v>0.8000360750360471</v>
       </c>
       <c r="BP10" t="n">
-        <v>2719343.974188117</v>
+        <v>0.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.09567901234567922</v>
+        <v>-0.6375192072443099</v>
       </c>
       <c r="BR10" t="n">
-        <v>1.450781625781644</v>
+        <v>-3.142662832676933</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="BT10" t="n">
-        <v>-2.98416908673801</v>
+        <v>1.304148629148642</v>
       </c>
       <c r="BU10" t="n">
-        <v>-0.1213564213564204</v>
+        <v>4.021410856009069</v>
       </c>
       <c r="BV10" t="n">
-        <v>3253.204273912292</v>
+        <v>2576322.926922963</v>
       </c>
       <c r="BW10" t="n">
-        <v>4303366.201699534</v>
+        <v>-3.436111111111103</v>
       </c>
     </row>
     <row r="11">
@@ -3188,70 +3188,70 @@
         <v>0.3903448275862069</v>
       </c>
       <c r="BB11" t="n">
-        <v>-2.261904761904759</v>
+        <v>-14403.08641975308</v>
       </c>
       <c r="BC11" t="n">
-        <v>-14403.08641975308</v>
+        <v>-964.2857142857101</v>
       </c>
       <c r="BD11" t="n">
-        <v>-964.2857142857101</v>
+        <v>-3.763817018035297</v>
       </c>
       <c r="BE11" t="n">
-        <v>57.46428571428572</v>
+        <v>0.03084590561370715</v>
       </c>
       <c r="BF11" t="n">
-        <v>-1.035714285714286</v>
+        <v>-11050.78805401303</v>
       </c>
       <c r="BG11" t="n">
-        <v>-1.845238095238098</v>
+        <v>-1.079938271604931</v>
       </c>
       <c r="BH11" t="n">
-        <v>-1.95538812991083</v>
+        <v>64.42857142857142</v>
       </c>
       <c r="BI11" t="n">
         <v>-9928571.428571429</v>
       </c>
       <c r="BJ11" t="n">
-        <v>64.42857142857142</v>
+        <v>-1.845238095238098</v>
       </c>
       <c r="BK11" t="n">
+        <v>57.46428571428572</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-4360100.308641975</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.03148148148148167</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.08888888888888502</v>
+      </c>
+      <c r="BO11" t="n">
         <v>-2.006790123456796</v>
       </c>
-      <c r="BL11" t="n">
-        <v>-3.763817018035297</v>
-      </c>
-      <c r="BM11" t="n">
+      <c r="BP11" t="n">
+        <v>-1.035714285714286</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>-2.311778629580488</v>
       </c>
-      <c r="BN11" t="n">
-        <v>0.03084590561370715</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-1.079938271604931</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-4152502.417877482</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>0.03148148148148167</v>
-      </c>
       <c r="BR11" t="n">
-        <v>-1.553395061728381</v>
+        <v>1.086390131101176</v>
       </c>
       <c r="BS11" t="n">
         <v>0.9642857142857144</v>
       </c>
       <c r="BT11" t="n">
-        <v>1.086390131101176</v>
+        <v>-1.553395061728381</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.08888888888888502</v>
+        <v>-1.95538812991083</v>
       </c>
       <c r="BV11" t="n">
-        <v>-11050.78805401303</v>
+        <v>-4152502.417877482</v>
       </c>
       <c r="BW11" t="n">
-        <v>-4360100.308641975</v>
+        <v>-2.261904761904759</v>
       </c>
     </row>
     <row r="12">
@@ -3433,70 +3433,70 @@
         <v>-0.1467236467236467</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.733333333333292</v>
+        <v>-14694.79166666666</v>
       </c>
       <c r="BC12" t="n">
-        <v>-14617.59259259258</v>
+        <v>-50750</v>
       </c>
       <c r="BD12" t="n">
-        <v>-50750</v>
+        <v>0.2950644213028113</v>
       </c>
       <c r="BE12" t="n">
-        <v>-46.94999999999999</v>
+        <v>0.1990174299384828</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.35</v>
+        <v>-6079.594038572359</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.300000000000001</v>
+        <v>-1.998611111111117</v>
       </c>
       <c r="BH12" t="n">
-        <v>2.010865479454225</v>
+        <v>-50.40000000000001</v>
       </c>
       <c r="BI12" t="n">
         <v>-8500000</v>
       </c>
       <c r="BJ12" t="n">
-        <v>-50.40000000000001</v>
+        <v>1.300000000000001</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.3314814814814611</v>
+        <v>-46.94999999999999</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.2890752207315757</v>
+        <v>-7732916.666666664</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.353146613066627</v>
+        <v>-0.1208333333333333</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.1818346370977952</v>
+        <v>1.034143518518523</v>
       </c>
       <c r="BO12" t="n">
-        <v>-1.982716049382717</v>
+        <v>0.5354166666666629</v>
       </c>
       <c r="BP12" t="n">
-        <v>1462506.809830081</v>
+        <v>1.35</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0.125925925925926</v>
+        <v>1.574871559469074</v>
       </c>
       <c r="BR12" t="n">
-        <v>-1.595370370370375</v>
+        <v>-2.109165237067717</v>
       </c>
       <c r="BS12" t="n">
         <v>-0.6499999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>-2.091790856870837</v>
+        <v>-1.611921296296316</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.045987654320992</v>
+        <v>2.212983494833338</v>
       </c>
       <c r="BV12" t="n">
-        <v>-6653.568518493696</v>
+        <v>1813659.13111656</v>
       </c>
       <c r="BW12" t="n">
-        <v>-7674814.814814813</v>
+        <v>3.733333333333292</v>
       </c>
     </row>
     <row r="13">
@@ -3678,70 +3678,70 @@
         <v>0.2542857142857143</v>
       </c>
       <c r="BB13" t="n">
-        <v>-7.666666666666657</v>
+        <v>31198.89971139973</v>
       </c>
       <c r="BC13" t="n">
-        <v>31198.89971139973</v>
+        <v>18250</v>
       </c>
       <c r="BD13" t="n">
-        <v>18250</v>
+        <v>1.947288753798233</v>
       </c>
       <c r="BE13" t="n">
-        <v>-52.25</v>
+        <v>0.4876474486702498</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.3333333333333335</v>
+        <v>-2595.589961553094</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.8333333333333321</v>
+        <v>1.168253968253964</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.107550295632592</v>
+        <v>-66.16666666666666</v>
       </c>
       <c r="BI13" t="n">
         <v>33625000</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-66.16666666666666</v>
+        <v>0.8333333333333321</v>
       </c>
       <c r="BK13" t="n">
+        <v>-52.25</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>17697285.35353535</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.287662337662338</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>3.640909090909087</v>
+      </c>
+      <c r="BO13" t="n">
         <v>0.5960317460317128</v>
       </c>
-      <c r="BL13" t="n">
-        <v>1.947288753798233</v>
-      </c>
-      <c r="BM13" t="n">
+      <c r="BP13" t="n">
+        <v>0.3333333333333335</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>1.304282828065098</v>
       </c>
-      <c r="BN13" t="n">
-        <v>0.4876474486702498</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.168253968253964</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>6298492.036390662</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.287662337662338</v>
-      </c>
       <c r="BR13" t="n">
-        <v>3.834595959595958</v>
+        <v>1.596670705162044</v>
       </c>
       <c r="BS13" t="n">
         <v>-1</v>
       </c>
       <c r="BT13" t="n">
-        <v>1.596670705162044</v>
+        <v>3.834595959595958</v>
       </c>
       <c r="BU13" t="n">
-        <v>3.640909090909087</v>
+        <v>-0.107550295632592</v>
       </c>
       <c r="BV13" t="n">
-        <v>-2595.589961553094</v>
+        <v>6298492.036390662</v>
       </c>
       <c r="BW13" t="n">
-        <v>17697285.35353535</v>
+        <v>-7.666666666666657</v>
       </c>
     </row>
     <row r="14">
@@ -3923,70 +3923,70 @@
         <v>-0.1288888888888889</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.20634920634922</v>
+        <v>-129822.9797979798</v>
       </c>
       <c r="BC14" t="n">
-        <v>-129822.9797979798</v>
+        <v>-395000</v>
       </c>
       <c r="BD14" t="n">
-        <v>-203071.4285714286</v>
+        <v>1.24332081371071</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.023809523809518</v>
+        <v>-1.172753644381934</v>
       </c>
       <c r="BF14" t="n">
-        <v>-2.095238095238095</v>
+        <v>-80624.73331944112</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.2063492063492092</v>
+        <v>-6.229377104377122</v>
       </c>
       <c r="BH14" t="n">
+        <v>-23</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-98200000</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-3.666666666666664</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-28</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>-46024141.41414142</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-1.800084175084175</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.2611111111111057</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.354461279461304</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-5</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-3.960202256893439</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>2.03810894665191</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-7.349031986531983</v>
+      </c>
+      <c r="BU14" t="n">
         <v>-5.289813541506646</v>
       </c>
-      <c r="BI14" t="n">
-        <v>-57614285.71428572</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.354461279461304</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.24332081371071</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>-3.960202256893439</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>-1.172753644381934</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>-6.229377104377122</v>
-      </c>
-      <c r="BP14" t="n">
+      <c r="BV14" t="n">
         <v>-29164734.28086576</v>
       </c>
-      <c r="BQ14" t="n">
-        <v>-1.800084175084175</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>-7.349031986531983</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>0.1904761904761907</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>2.03810894665191</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>0.2611111111111057</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>-80624.73331944112</v>
-      </c>
       <c r="BW14" t="n">
-        <v>-46024141.41414142</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -4168,70 +4168,70 @@
         <v>-0.4400000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0.08333333333334281</v>
+        <v>-95117.46031746034</v>
       </c>
       <c r="BC15" t="n">
-        <v>-95117.46031746034</v>
+        <v>-388833.3333333333</v>
       </c>
       <c r="BD15" t="n">
-        <v>-542833.3333333334</v>
+        <v>0.6954680275880492</v>
       </c>
       <c r="BE15" t="n">
-        <v>-193.1666666666667</v>
+        <v>-1.282148749334537</v>
       </c>
       <c r="BF15" t="n">
-        <v>-7.666666666666667</v>
+        <v>-63531.54903544473</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.1388888888888857</v>
+        <v>-5.993650793650801</v>
       </c>
       <c r="BH15" t="n">
-        <v>-4.183741253164882</v>
+        <v>-181.5</v>
       </c>
       <c r="BI15" t="n">
-        <v>-240066666.6666667</v>
+        <v>-136966666.6666667</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-192.5</v>
+        <v>-2.861111111111114</v>
       </c>
       <c r="BK15" t="n">
+        <v>-184.1666666666667</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-41444007.93650794</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-2.048809523809524</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0.02976190476190865</v>
+      </c>
+      <c r="BO15" t="n">
         <v>-0.9464285714285836</v>
       </c>
-      <c r="BL15" t="n">
-        <v>0.6954680275880492</v>
-      </c>
-      <c r="BM15" t="n">
+      <c r="BP15" t="n">
+        <v>-5.666666666666667</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>-2.990545002332553</v>
       </c>
-      <c r="BN15" t="n">
-        <v>-1.282148749334537</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>-5.993650793650801</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-19801023.26681154</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>-2.048809523809524</v>
-      </c>
       <c r="BR15" t="n">
-        <v>-6.718650793650795</v>
+        <v>-0.131907875646462</v>
       </c>
       <c r="BS15" t="n">
         <v>-2.166666666666667</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0.131907875646462</v>
+        <v>-6.718650793650795</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.02976190476190865</v>
+        <v>-4.183741253164882</v>
       </c>
       <c r="BV15" t="n">
-        <v>-63531.54903544473</v>
+        <v>-19801023.26681154</v>
       </c>
       <c r="BW15" t="n">
-        <v>-41444007.93650794</v>
+        <v>-3.083333333333343</v>
       </c>
     </row>
     <row r="16">
@@ -4413,70 +4413,70 @@
         <v>0.07999999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>45067.99242424243</v>
       </c>
       <c r="BC16" t="n">
-        <v>44405.59764309764</v>
+        <v>-28000</v>
       </c>
       <c r="BD16" t="n">
-        <v>-28000</v>
+        <v>2.25962394826351</v>
       </c>
       <c r="BE16" t="n">
-        <v>-76</v>
+        <v>1.045241910866911</v>
       </c>
       <c r="BF16" t="n">
-        <v>1</v>
+        <v>43501.09237436538</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>3.571654040404056</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.556437938048219</v>
+        <v>-79</v>
       </c>
       <c r="BI16" t="n">
         <v>-17000000</v>
       </c>
       <c r="BJ16" t="n">
-        <v>-79</v>
+        <v>2.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>-1.327707631874318</v>
+        <v>-76</v>
       </c>
       <c r="BL16" t="n">
-        <v>2.741587102677329</v>
+        <v>20485233.58585859</v>
       </c>
       <c r="BM16" t="n">
-        <v>6.261302612963021</v>
+        <v>1.311016414141414</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.034107883669287</v>
+        <v>0.8640151515151508</v>
       </c>
       <c r="BO16" t="n">
-        <v>3.634315375982055</v>
+        <v>-1.126388888888926</v>
       </c>
       <c r="BP16" t="n">
-        <v>15147008.20433512</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.309497755331088</v>
+        <v>6.518240240596924</v>
       </c>
       <c r="BR16" t="n">
-        <v>4.828367003367006</v>
+        <v>3.450449125331644</v>
       </c>
       <c r="BS16" t="n">
         <v>-1</v>
       </c>
       <c r="BT16" t="n">
-        <v>3.291955379392721</v>
+        <v>4.975000000000009</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.7162878787878775</v>
+        <v>2.593842937816149</v>
       </c>
       <c r="BV16" t="n">
-        <v>42815.95316639175</v>
+        <v>15290029.25160027</v>
       </c>
       <c r="BW16" t="n">
-        <v>20341235.62008979</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -4660,70 +4660,70 @@
         <v>0.6121794871794872</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.5</v>
+        <v>44571.33838383836</v>
       </c>
       <c r="BC17" t="n">
-        <v>44571.33838383836</v>
+        <v>94000</v>
       </c>
       <c r="BD17" t="n">
-        <v>262000</v>
+        <v>2.970866412536509</v>
       </c>
       <c r="BE17" t="n">
-        <v>235</v>
+        <v>0.6637832219688375</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>36222.4641969592</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.6999999999999993</v>
+        <v>1.352746212121218</v>
       </c>
       <c r="BH17" t="n">
+        <v>167</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>14549746.68560606</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.8736426767676768</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>2.101578282828285</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.367045454545462</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.35302111431217</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>3.557839458854065</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>4.814709595959599</v>
+      </c>
+      <c r="BU17" t="n">
         <v>-0.2751527401318299</v>
       </c>
-      <c r="BI17" t="n">
-        <v>67600000</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>249</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>3.367045454545462</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>2.970866412536509</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>4.35302111431217</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0.6637832219688375</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.352746212121218</v>
-      </c>
-      <c r="BP17" t="n">
+      <c r="BV17" t="n">
         <v>9764297.017629083</v>
       </c>
-      <c r="BQ17" t="n">
-        <v>0.8736426767676768</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>4.814709595959599</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>3.557839458854065</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>2.101578282828285</v>
-      </c>
-      <c r="BV17" t="n">
-        <v>36222.4641969592</v>
-      </c>
       <c r="BW17" t="n">
-        <v>14549746.68560606</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="18">
@@ -4905,70 +4905,70 @@
         <v>-0.03703703703703703</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>-36026.78571428571</v>
       </c>
       <c r="BC18" t="n">
-        <v>-36026.78571428571</v>
+        <v>-111000</v>
       </c>
       <c r="BD18" t="n">
-        <v>-64000</v>
+        <v>1.367471929223143</v>
       </c>
       <c r="BE18" t="n">
-        <v>-8</v>
+        <v>-0.2649057266967534</v>
       </c>
       <c r="BF18" t="n">
-        <v>-2</v>
+        <v>-18718.58096681569</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>-3.909163059163049</v>
       </c>
       <c r="BH18" t="n">
-        <v>-3.774350375161518</v>
+        <v>-16</v>
       </c>
       <c r="BI18" t="n">
-        <v>-25300000</v>
+        <v>-47300000</v>
       </c>
       <c r="BJ18" t="n">
-        <v>-8</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
+        <v>-14</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-14709031.38528138</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-0.8212842712842714</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.326948051948051</v>
+      </c>
+      <c r="BO18" t="n">
         <v>0.5217171717171709</v>
       </c>
-      <c r="BL18" t="n">
-        <v>1.367471929223143</v>
-      </c>
-      <c r="BM18" t="n">
+      <c r="BP18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>-1.406845910300888</v>
       </c>
-      <c r="BN18" t="n">
-        <v>-0.2649057266967534</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>-3.909163059163049</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>-10134420.99257531</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>-0.8212842712842714</v>
-      </c>
       <c r="BR18" t="n">
-        <v>-2.82849927849928</v>
+        <v>2.800017495036293</v>
       </c>
       <c r="BS18" t="n">
         <v>0</v>
       </c>
       <c r="BT18" t="n">
-        <v>2.800017495036293</v>
+        <v>-2.82849927849928</v>
       </c>
       <c r="BU18" t="n">
-        <v>1.326948051948051</v>
+        <v>-3.774350375161518</v>
       </c>
       <c r="BV18" t="n">
-        <v>-18718.58096681569</v>
+        <v>-10134420.99257531</v>
       </c>
       <c r="BW18" t="n">
-        <v>-14709031.38528138</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -5150,70 +5150,70 @@
         <v>0.2933333333333333</v>
       </c>
       <c r="BB19" t="n">
-        <v>-7.5</v>
+        <v>-2878.030303030304</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2878.030303030304</v>
+        <v>22000</v>
       </c>
       <c r="BD19" t="n">
-        <v>-50000</v>
+        <v>-2.269629699045623</v>
       </c>
       <c r="BE19" t="n">
-        <v>-3</v>
+        <v>-0.2312743589798822</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1414.226577638787</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.5</v>
+        <v>-0.8411976911976922</v>
       </c>
       <c r="BH19" t="n">
+        <v>127</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-1800000</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>6</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>136</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-4757853.535353538</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-0.4242784992784994</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-2.391774891774894</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.4065656565657036</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>-2.017298474643809</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>-0.8270492207280391</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-2.427164502164516</v>
+      </c>
+      <c r="BU19" t="n">
         <v>-1.971585579161726</v>
       </c>
-      <c r="BI19" t="n">
-        <v>-5700000</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>-19</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.4065656565657036</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>-2.269629699045623</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>-2.017298474643809</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>-0.2312743589798822</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>-0.8411976911976922</v>
-      </c>
-      <c r="BP19" t="n">
+      <c r="BV19" t="n">
         <v>-2267870.215195942</v>
       </c>
-      <c r="BQ19" t="n">
-        <v>-0.4242784992784994</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>-2.427164502164516</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>-0.8270492207280391</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>-2.391774891774894</v>
-      </c>
-      <c r="BV19" t="n">
-        <v>1414.226577638787</v>
-      </c>
       <c r="BW19" t="n">
-        <v>-4757853.535353538</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="20">
@@ -5395,70 +5395,70 @@
         <v>-0.0438871473354232</v>
       </c>
       <c r="BB20" t="n">
-        <v>1</v>
+        <v>2708.641975308637</v>
       </c>
       <c r="BC20" t="n">
-        <v>2708.641975308637</v>
+        <v>2000</v>
       </c>
       <c r="BD20" t="n">
-        <v>-41000</v>
+        <v>0.4806226238501949</v>
       </c>
       <c r="BE20" t="n">
-        <v>-64</v>
+        <v>-0.09424979188911076</v>
       </c>
       <c r="BF20" t="n">
-        <v>-1</v>
+        <v>-3323.292618926011</v>
       </c>
       <c r="BG20" t="n">
-        <v>-1.666666666666668</v>
+        <v>-1.094664902998232</v>
       </c>
       <c r="BH20" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-0.3333333333333357</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-1505028.659611993</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-0.07314814814814841</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-0.597486772486775</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>1.024647266313934</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-2.529259404452915</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-0.494148218387128</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>-2.441975308641972</v>
+      </c>
+      <c r="BU20" t="n">
         <v>-0.8695578413006189</v>
       </c>
-      <c r="BI20" t="n">
-        <v>1600000</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>-61</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.024647266313934</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.4806226238501949</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>-2.529259404452915</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>-0.09424979188911076</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>-1.094664902998232</v>
-      </c>
-      <c r="BP20" t="n">
+      <c r="BV20" t="n">
         <v>-1885559.672788129</v>
       </c>
-      <c r="BQ20" t="n">
-        <v>-0.07314814814814841</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>-2.441975308641972</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>-0.494148218387128</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>-0.597486772486775</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>-3323.292618926011</v>
-      </c>
       <c r="BW20" t="n">
-        <v>-1505028.659611993</v>
+        <v>1.666666666666657</v>
       </c>
     </row>
     <row r="21">
@@ -5640,70 +5640,70 @@
         <v>0.1185897435897436</v>
       </c>
       <c r="BB21" t="n">
-        <v>2</v>
+        <v>25190.5753968254</v>
       </c>
       <c r="BC21" t="n">
-        <v>25190.5753968254</v>
+        <v>284500</v>
       </c>
       <c r="BD21" t="n">
-        <v>284500</v>
+        <v>3.369386669294784</v>
       </c>
       <c r="BE21" t="n">
-        <v>163.5</v>
+        <v>-0.1806531397524043</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.5</v>
+        <v>-951.6428628560971</v>
       </c>
       <c r="BG21" t="n">
-        <v>-4.333333333333332</v>
+        <v>4.041319444444454</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.757921663712096</v>
+        <v>174.5</v>
       </c>
       <c r="BI21" t="n">
         <v>89000000</v>
       </c>
       <c r="BJ21" t="n">
-        <v>174.5</v>
+        <v>-4.333333333333332</v>
       </c>
       <c r="BK21" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>19179191.46825397</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0.460863095238095</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-2.634623015873014</v>
+      </c>
+      <c r="BO21" t="n">
         <v>1.985267857142873</v>
       </c>
-      <c r="BL21" t="n">
-        <v>3.369386669294784</v>
-      </c>
-      <c r="BM21" t="n">
+      <c r="BP21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BQ21" t="n">
         <v>0.08908297584768832</v>
       </c>
-      <c r="BN21" t="n">
-        <v>-0.1806531397524043</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>4.041319444444454</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>6495862.788151396</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>0.460863095238095</v>
-      </c>
       <c r="BR21" t="n">
-        <v>2.674503968253958</v>
+        <v>-4.256757713283452</v>
       </c>
       <c r="BS21" t="n">
         <v>2</v>
       </c>
       <c r="BT21" t="n">
-        <v>-4.256757713283452</v>
+        <v>2.674503968253958</v>
       </c>
       <c r="BU21" t="n">
-        <v>-2.634623015873014</v>
+        <v>2.757921663712096</v>
       </c>
       <c r="BV21" t="n">
-        <v>-951.6428628560971</v>
+        <v>6495862.788151396</v>
       </c>
       <c r="BW21" t="n">
-        <v>19179191.46825397</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW4"/>
+  <dimension ref="A1:BW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,144 +695,144 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>KMCY9qSa</t>
+          <t>ratYowuH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">robinson t 
+          <t xml:space="preserve">barrott s 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">city ground
-  nottingham </t>
+          <t xml:space="preserve">craven cottage
+  london </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UsushcZr</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>xYe7DwID</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,204 +859,204 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.59</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5211333333333334</v>
+        <v>0.2155555555555551</v>
       </c>
       <c r="R2" t="n">
-        <v>0.75</v>
+        <v>2.55</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5811965811965811</v>
+        <v>0.5521978021978023</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6552706552706562</v>
+        <v>1.392857142857142</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.25</v>
+        <v>15.05</v>
       </c>
       <c r="W2" t="n">
-        <v>3.082621082621085</v>
+        <v>7.192307692307692</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.25</v>
+        <v>1.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3547008547008548</v>
+        <v>0.6675824175824174</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.75</v>
+        <v>2.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.2008547008547009</v>
+        <v>1.582417582417582</v>
       </c>
       <c r="AB2" t="n">
-        <v>21.6770313020313</v>
+        <v>16.32671258184988</v>
       </c>
       <c r="AC2" t="n">
-        <v>19.17558909261927</v>
+        <v>18.28475840710841</v>
       </c>
       <c r="AD2" t="n">
-        <v>860.7285676624964</v>
+        <v>864.0890708403604</v>
       </c>
       <c r="AE2" t="n">
-        <v>874.9549656779469</v>
+        <v>811.631631034975</v>
       </c>
       <c r="AF2" t="n">
-        <v>7</v>
+        <v>70.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.652307692307687</v>
+        <v>48.81730769230769</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.515384615384612</v>
+        <v>36.28205128205128</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25</v>
+        <v>10.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.507122507122503</v>
+        <v>9.598901098901099</v>
       </c>
       <c r="AL2" t="n">
-        <v>-9.25</v>
+        <v>-3.599999999999994</v>
       </c>
       <c r="AM2" t="n">
-        <v>4.390313390313381</v>
+        <v>16.57692307692308</v>
       </c>
       <c r="AN2" t="n">
-        <v>-40.33333333333331</v>
+        <v>56.75</v>
       </c>
       <c r="AO2" t="n">
-        <v>62.68560606060606</v>
+        <v>194.8765217391305</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.25</v>
+        <v>1.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.525641025641026</v>
+        <v>0.06552706552706566</v>
       </c>
       <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>-1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
-        <v>-5</v>
+        <v>10.05</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.497150997150996</v>
+        <v>-2.052197802197803</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.54713159553585</v>
+        <v>-13.0655034637207</v>
       </c>
       <c r="AW2" t="n">
-        <v>-1.410827985799807</v>
+        <v>-7.510588563964713</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03269125151481447</v>
+        <v>0.04529053688436585</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.01885904830130114</v>
+        <v>0.01766887663929214</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.1467236467236467</v>
+        <v>0.04120879120879123</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.611921296296316</v>
+        <v>1.977777777777781</v>
       </c>
       <c r="BC2" t="n">
-        <v>-6079.594038572359</v>
+        <v>0.2969977553310887</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>3.38421814399122</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.574871559469074</v>
+        <v>17448.06183130934</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.1208333333333333</v>
+        <v>0.1910637604478183</v>
       </c>
       <c r="BG2" t="n">
-        <v>4</v>
+        <v>11.09047619047621</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-1.663916947250272</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.1990174299384828</v>
+        <v>12651.6835016835</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-7732916.666666664</v>
+        <v>-32414285.71428572</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.212983494833338</v>
+        <v>0.1368125701459064</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5354166666666629</v>
+        <v>-1.885714285714286</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.2950644213028113</v>
+        <v>1.15286195286194</v>
       </c>
       <c r="BN2" t="n">
-        <v>-2.109165237067717</v>
+        <v>2.948807959915897</v>
       </c>
       <c r="BO2" t="n">
-        <v>1813659.13111656</v>
+        <v>-108914.2857142857</v>
       </c>
       <c r="BP2" t="n">
-        <v>18100000</v>
+        <v>-1.885714285714286</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-14694.79166666666</v>
+        <v>3.547619047619051</v>
       </c>
       <c r="BR2" t="n">
-        <v>-1.998611111111117</v>
+        <v>-1.638545740357344</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.034143518518523</v>
+        <v>-148.4571428571429</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>363902.9180695843</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.25</v>
+        <v>-155.4571428571428</v>
       </c>
       <c r="BV2" t="n">
-        <v>-4.25</v>
+        <v>1.649782971922576</v>
       </c>
       <c r="BW2" t="n">
-        <v>41000</v>
+        <v>643682.7096929122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2ot8gOsJ</t>
+          <t>zil0kCo9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">anfield
-  liverpool </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>lId4TMwf</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1104,439 +1104,4610 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>CznGurCt</t>
+          <t>dpjHQ7zJ</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>IoJ2QpOs</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8266666666666669</v>
+        <v>-0.2749999999999997</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.905614814814815</v>
+        <v>0.3222615384615386</v>
       </c>
       <c r="R3" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.957142857142857</v>
+        <v>1.132478632478632</v>
       </c>
       <c r="T3" t="n">
-        <v>6.416666666666667</v>
+        <v>4.449999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>6.212857142857143</v>
+        <v>1.756410256410255</v>
       </c>
       <c r="V3" t="n">
-        <v>9.833333333333334</v>
+        <v>6.699999999999999</v>
       </c>
       <c r="W3" t="n">
-        <v>17.88571428571429</v>
+        <v>5.012820512820511</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.666666666666667</v>
+        <v>-1.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.732857142857143</v>
+        <v>0.1438746438746437</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1.5</v>
+        <v>-0.8999999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.01</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.48306182121971</v>
+        <v>17.39545322621696</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.79118489318707</v>
+        <v>21.70090009706729</v>
       </c>
       <c r="AD3" t="n">
-        <v>824.7458402953209</v>
+        <v>981.3238883712061</v>
       </c>
       <c r="AE3" t="n">
-        <v>894.9609185522844</v>
+        <v>978.6748829013491</v>
       </c>
       <c r="AF3" t="n">
-        <v>30.5</v>
+        <v>3.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>39.35576923076924</v>
+        <v>3.984999999999999</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>22.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>46.90384615384616</v>
+        <v>17.47</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.8333333333333357</v>
+        <v>-2.899999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>9.390000000000004</v>
+        <v>3.019943019943014</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>-11.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>8.374285714285705</v>
+        <v>-10.13675213675214</v>
       </c>
       <c r="AN3" t="n">
-        <v>112</v>
+        <v>-164.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>85.08333333333326</v>
+        <v>-118.01</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1.5</v>
+        <v>0.4500000000000002</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1.984615384615384</v>
+        <v>-0.6495726495726495</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>-0.3500000000000001</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.41666666666667</v>
+        <v>11.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.44142857142857</v>
+        <v>3.809116809116809</v>
       </c>
       <c r="AV3" t="n">
-        <v>-14.95887931512932</v>
+        <v>-0.2241021413151074</v>
       </c>
       <c r="AW3" t="n">
-        <v>-5.606082879044084</v>
+        <v>2.562009169250826</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.05994594563142951</v>
+        <v>0.03052719013781589</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0216511595289043</v>
+        <v>0.01219290129318897</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.4166666666666666</v>
+        <v>-0.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2542857142857143</v>
+        <v>0.03846153846153846</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.860750360750359</v>
+        <v>3.107936507936508</v>
       </c>
       <c r="BC3" t="n">
-        <v>-3108.539558948178</v>
+        <v>0.6515873015873015</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>2.812969258446234</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.25300993637866</v>
+        <v>-16829.46929715024</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.293362193362194</v>
+        <v>0.148175526958422</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>-0.6706349206349387</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0.9416666666666487</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.4257224323749325</v>
+        <v>2725.39682539682</v>
       </c>
       <c r="BJ3" t="n">
-        <v>17881240.98124098</v>
+        <v>20571428.57142857</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.2160191085656891</v>
+        <v>-0.503571428571405</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5473304473304097</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.728751119753099</v>
+        <v>0.5498015873015873</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.60657143517556</v>
+        <v>-1.096318666713401</v>
       </c>
       <c r="BO3" t="n">
-        <v>5712231.340632781</v>
+        <v>104309.5238095238</v>
       </c>
       <c r="BP3" t="n">
-        <v>46500000</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="BQ3" t="n">
-        <v>31481.81818181821</v>
+        <v>3.178571428571431</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.222366522366528</v>
+        <v>-2.078729950604952</v>
       </c>
       <c r="BS3" t="n">
-        <v>3.600577200577199</v>
+        <v>45.92857142857142</v>
       </c>
       <c r="BT3" t="n">
-        <v>25</v>
+        <v>-1224404.761904765</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.666666666666668</v>
+        <v>32.90476190476193</v>
       </c>
       <c r="BV3" t="n">
-        <v>-5</v>
+        <v>2.627179098313945</v>
       </c>
       <c r="BW3" t="n">
-        <v>49000</v>
+        <v>-6718122.031477295</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SSZaQ4Ct</t>
+          <t>drzevnw8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45599.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>48</v>
+      </c>
+      <c r="H4" t="n">
+        <v>481</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.1725</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.7392000000000003</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.301538461538461</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.653846153846153</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>5.586153846153845</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.7215384615384615</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.3876923076923078</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>15.59690205929336</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19.13295051146706</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>752.3199405888154</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>804.5429237101957</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>40.66666666666667</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>31.875</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>31.33333333333334</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>33.55072463768116</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.253846153846155</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>169</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>181.72</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.8666666666666663</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-1.105769230769231</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-3.300000000000001</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.044615384615387</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-7.877571899982385</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-7.88353577106491</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.0170650536814863</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.02022457865906983</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0.5068542568542576</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.4936147186147184</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.4169434625009885</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-4474.686089273979</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.3099442692063252</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-4.154761904761898</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.632936507936506</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>8010.533910533908</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-8960714.285714276</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.3743867243867385</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.804401154401148</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.836741160498349</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-96428.57142857142</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-1.714285714285714</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-2.761904761904763</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1.339901082403856</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>-90.99999999999997</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>14491747.83549784</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-88.00000000000003</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>2.641442564671365</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>4805863.558809757</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hooper s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>481</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.0008333333333333526</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1441025641025644</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1500000000000001</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2637362637362638</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1208791208791204</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-5.199999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.3406593406593394</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.4697802197802197</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4697802197802197</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>19.55083898944193</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20.88675785221179</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>977.4693641280616</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>836.2555052205487</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>14.34461538461538</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.999999999999993</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>12.59230769230768</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-9.750000000000004</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-1.129120879120876</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-20.09999999999999</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>17.03846153846153</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-217</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>159.4672727272728</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.09523809523809534</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0.6000000000000014</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.244505494505493</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12.74565330824522</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-4.451858181271886</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.02420812002615851</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.0105951981835002</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.1456043956043956</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.010069444444444</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.03948412698412729</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.2731710812980168</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-3820.494287560847</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.4038875598086122</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4.92857142857136</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.8827380952380963</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-17216.22023809523</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-6585714.285714287</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.3457341269841265</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.3142857142857145</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>-1.862847222222229</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.560293118665129</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-17428.57142857142</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1.457142857142857</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-1.676190476190474</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1.579924025254272</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>18.80000000000001</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-6721845.238095235</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>25.88571428571427</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-3.233375203705435</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>2325138.337277139</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>481</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.1200000000000002</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.14151098901099</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.638461538461538</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.935897435897436</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8.487179487179487</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.582051282051282</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.90656745215569</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>17.61946537238637</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>741.2996457022426</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>786.2610652659041</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>57.24404761904761</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>44.61904761904762</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>11.42564102564102</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>48.04102564102564</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>239.1666666666667</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1.583333333333333</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-6.666666666666666</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-8.253187599156162</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-2.890093071010179</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.01754297382483105</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.01294005594560308</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.2487179487179487</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-1.983238636363637</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-0.1934027777777778</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0.9744944831761124</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>372.3722041059518</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.1208626345752248</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.4690476190476147</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-1.576893939393941</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-104.4823232323251</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-29557142.85714285</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0.7081123737373503</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-2.571428571428572</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-3.258617424242431</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>-2.745085104953517</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-128714.2857142857</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-2.571428571428571</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-0.4119047619047613</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-1.07711345671872</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-192</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-4218774.463383839</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-207.5714285714286</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-2.521097779069919</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-2123322.052837274</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H7" t="n">
+        <v>481</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.5025</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.99978835978836</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.720306513409962</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.94125159642401</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>14.47254150702427</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.047254150702426</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.720306513409962</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>21.49810700994912</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>18.43164874217108</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>851.3181912767902</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>962.7208286487376</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>38.05076923076923</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>35.75384615384616</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>6.554278416347387</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>3.272030651340998</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>7.453846153846087</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-1.185185185185185</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1142857142857141</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4.037037037037035</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-4.955734357606179</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.5990821427615902</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.04130097037336451</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.0001073923237880012</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.3180076628352491</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.466806958473622</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.641849046015713</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.012852196561305</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>44446.4179684078</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.98638083379805</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-4.558333333333337</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>5.390319865319867</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>68947.75533108869</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>16916666.66666666</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.9636363636363683</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0.7333333333333334</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8.77608024691358</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.715870565426769</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-64666.66666666666</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>-8.558333333333334</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>2.767881593903766</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>-51.83333333333334</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>39534111.95286195</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>-48.90000000000001</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>3.097383437547421</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>24181974.71513396</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>48</v>
+      </c>
+      <c r="H8" t="n">
+        <v>481</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.4925000000000002</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.604616935483871</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4383301707779885</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.31404174573055</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.850000000000001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7.929791271347248</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.1537001897533206</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.3757115749525617</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>16.21770118770119</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>16.48025259798602</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>826.0726896287683</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>809.447173640694</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>11.83333333333333</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>7.275862068965509</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>26.65086206896552</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>4.032258064516128</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-2.299999999999997</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-8.166982922201129</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>173.6999999999999</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.4818181818181821</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.649999999999999</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.219165085388992</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-22.13720780681475</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-18.16196771013285</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.04828416574787624</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0.03219626947044651</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0.07969639468690703</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-1.064141414141414</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>-0.2912773569023566</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.3959888828825875</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-1630.222376474958</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.2259199878781926</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-6.623809523809541</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-0.1052960157126819</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1055.76950056116</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-3242857.142857143</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>2.544605780022437</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-1.493676346801365</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-1.694921638245944</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2.414285714285718</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>-1.733541608651265</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-1801114.267676767</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-7.571428571428584</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.6372100594624044</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-2045736.700138145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">molineux stadium
-  wolverhampton </t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>48</v>
+      </c>
+      <c r="H9" t="n">
+        <v>481</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3374999999999997</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.5955128205128204</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.4829059829059827</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-3.264957264957265</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-4.257834757834759</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-1.125356125356125</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-1.508547008547009</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23.46519544052439</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>23.52497122355394</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1138.326511762885</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1100.790940882064</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-46.46499999999999</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-24.02833333333334</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-9.914529914529915</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-37.60113960113959</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-473.25</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-376.44</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.0322061191626406</v>
+      </c>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>4.910256410256412</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17.14331995550746</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10.20788198607952</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.009608280382732613</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.001471773567170154</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0.1937321937321937</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-1.023611111111109</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-2.100662878787879</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-1.208464455436204</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-90233.87781057094</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-1.45571243395837</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.309523809523824</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-6.617803030303037</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-133452.8409090909</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-65780952.38095239</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.2163825757575921</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0.5952380952380951</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-7.642897727272725</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-5.087123252564425</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-265261.9047619047</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-1.952380952380953</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.3650793650793638</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-4.44165973452931</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-54.02380952380952</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-47347440.02525252</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-64.21428571428572</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0.005607545511765011</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-29531666.41735672</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>48</v>
+      </c>
+      <c r="H10" t="n">
+        <v>481</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-0.07916666666666661</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6897230769230769</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.7777777777777777</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.703703703703705</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.150000000000002</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8.370370370370372</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5000000000000002</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.7407407407407409</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.2222222222222222</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.82360764235764</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>19.66676990525056</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>779.3238865720953</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>873.6579492058854</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.233974358974365</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>41.16666666666667</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>14.90705128205128</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.1851851851851833</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>8.450000000000003</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3.592592592592595</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>84.91666666666669</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>64.95833333333331</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-1.284900284900285</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.444444444444443</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>27.31279055742123</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.045110859288236</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.0828436072778812</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.022035248622157</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0.1111111111111111</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-1.368827160493822</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0.9660493827160495</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-3.076867413632119</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-23806.53983815747</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-0.8157939101566549</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-1.763888888888886</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-29043.20987654322</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.6712962962963047</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>-2.566358024691368</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-1.823410104782653</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>21750</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-1.00902972300031</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>-8683641.975308642</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>2.472766884531609</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-5984904.554414356</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45598.39583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.0475</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.5030769230769232</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.1292307692307699</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9061538461538472</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.007692307692307887</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.05538461538461537</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>16.93838494838495</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21.49150308953996</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>850.5780246862568</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>921.8527181012627</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-74.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-26.50757575757576</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-14.84469696969698</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>7.450000000000003</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.46153846153846</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>8.099999999999994</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-9.052307692307693</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-96.25</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-93.39130434782601</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.7533333333333334</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.9461538461538446</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.2516986662851277</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>3.092113132455507</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.03462043131160777</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.02014435442144367</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.01538461538461544</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.749337121212125</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0.8051136363636364</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.207396567551523</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-16577.33993743084</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.3900921356573057</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>7.042857142857116</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-3.46622474747474</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-38441.57196969702</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-117942857.1428571</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.185637626262604</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>-0.7142857142857144</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-2.894917929292944</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.05811118861235798</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-289142.8571428572</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-2.857142857142856</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0.764285714285716</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-2.812586605969017</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-73.57142857142861</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-25762383.20707072</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-62.57142857142856</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>4.039937774789422</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-8854322.626496501</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>EqY7Orsg</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">emirates stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4024999999999999</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.345370370370371</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.2999999999999998</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.585714285714286</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.950000000000001</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.778571428571428</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8.049999999999999</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8.661428571428573</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.7785714285714287</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.6342857142857143</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>18.68447693090684</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>19.78705383152251</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>888.5744039633655</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>936.9556303881934</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>12.16783216783216</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>-24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>39.04545454545454</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.599999999999998</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>3.69285714285714</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.200000000000003</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-0.462857142857132</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-24.49999999999989</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0.4404761904761907</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6.200000000000003</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.437142857142856</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-6.18243378254941</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0.9399569320134553</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.01013117059361546</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.03292252020111551</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0.08571428571428574</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-1.048074494949496</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0.09539141414141339</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.8626630722919302</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7477.433353974411</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.007938363362419931</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>6.623809523809541</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.4660984848484873</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>15746.11742424243</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>141557142.8571429</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-1.934122474747454</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>3.114285714285714</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.8125315656565562</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-2.708950640082634</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>511285.7142857143</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>8.114285714285714</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>2.821428571428573</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>-0.2967887816321735</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>255.1428571428572</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1889157.196969703</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-4.101489339464905</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-5967351.035930127</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EJlHkLuh</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrott s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">london stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.3880000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.03001436781609157</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.8000000000000007</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.3275862068965516</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.759946949602121</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0.02254641909814303</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.06763925729442954</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22.33531087270218</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>24.0179034719913</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>998.8140351609502</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>989.7971985991728</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-48.66666666666667</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-4.763888888888886</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.300925925925924</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.03580901856764</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-12.40000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-13.32360742705571</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-171.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-137.375</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.3485714285714288</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-5.388594164456233</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>13.93371910218216</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>9.854639460291327</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.0002690457239593533</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.003532523175472646</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0.103448275862069</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.748853615520279</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.1827601410934747</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.771054303131507</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-8854.416739986598</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0.001204716216971491</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.8095238095238244</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-2.64166666666668</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-13596.07583774249</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-32071428.57142857</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0.817724867724877</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-2</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0.7894620811287467</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0.0937068060842563</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-148642.8571428571</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-2.785714285714286</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.654761904761902</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-1.74980345770787</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-154.9285714285714</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-10215911.59611993</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-164.0714285714286</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-2.838416686118904</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-5238032.335085034</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>zD1kyMQb</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">selhurst park
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.5525</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3108333333333333</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-5.599999999999998</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.639999999999999</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.2000000000000002</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3599999999999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25.00537185037185</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>20.41103568000627</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1033.321240211614</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1075.367774456912</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-31.33333333333333</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-36.08695652173913</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-23</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-6.260869565217384</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>-36.80000000000001</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-33.84</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-335.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-331.9891304347826</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.4166666666666665</v>
+      </c>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-0.7999999999999972</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>37.87571471156625</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12.63068276658319</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.002605212041826475</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.008865481970736701</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.1907242063492056</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-1.310912698412699</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.059057950563371</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-17653.40441722021</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-0.8484971577270339</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.980952380952431</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-3.78710317460316</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-39270.28769841272</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-32071428.57142857</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-1.816369047619048</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-3.5923115079365</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-3.635294510700845</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-3.028571428571429</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.438095238095237</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>-5.929309448291647</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>11.62857142857141</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>-20064702.38095239</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>10.25714285714287</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-1.030773320246993</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-14349115.34565366</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EcDtwrdn</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stamford bridge
+  london </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.0175</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.163960292580982</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.211764705882353</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.713725490196079</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.199999999999998</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7.664705882352941</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.080392156862745</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.523529411764706</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>22.14322677322677</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>19.03242812225172</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>972.5757180759391</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>866.3645645242561</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>24.66666666666669</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>35.69642857142857</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-4.333333333333329</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>19.62053571428572</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.927450980392159</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>16.61960784313726</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-123.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>125.5925925925926</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.1941176470588233</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="n">
+        <v>9.999999999999996</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.654901960784315</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.955327394041593</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-4.453829242797788</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.01896372510622004</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.002678222792586921</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.1803921568627451</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-4.251767676767678</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.5969696969696967</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-2.862983501038201</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10732.3786975361</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.06535335603318049</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-7.705555555555549</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.525252525252512</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-10538.63636363634</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-58614285.71428572</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>-2.842929292929313</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>-0.3332070707070613</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.273205757138939</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-235309.5238095238</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-5.857142857142858</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-3.290476190476188</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>3.160892107596169</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-125.0714285714286</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>5724015.151515156</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-117.7619047619048</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>-1.601105665108463</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>8303158.739372946</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rw5cZaeB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goodison park
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.6600000000000001</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.9923076923076926</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.791871921182266</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.1666666666666665</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.476600985221674</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.9999999999999982</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.873152709359607</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5652709359605912</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.5357142857142856</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>20.37657227032227</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>19.79920745666209</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>967.3161358240334</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>946.9180953062432</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>18.76780626780626</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>17.3974358974359</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-2.532019704433495</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>-23.33333333333333</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-12.71428571428571</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-184.75</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-113.2481884057971</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-2.220446049250313e-16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.4572158365261816</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-2.333333333333332</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-0.6108374384236477</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>18.97414562307254</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8.054312790331013</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.02016699316966819</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.006572878005234178</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2426108374384237</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.8196969696969667</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0.03749999999999942</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0.5078407182946805</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-22676.14823053868</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0.02244780061276264</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-2.480952380952374</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0.3866161616161463</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-20026.76767676767</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>31453571.42857143</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-1.676262626262627</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>3.314285714285715</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-0.07992424242424079</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-0.4932910081141131</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>97771.42857142858</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3.457142857142857</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-4.638095238095239</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-0.438922406963755</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>241.4571428571428</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>67133.83838383853</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>270.7428571428571</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.01627725783734491</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-1188360.583079893</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ABRGMMB5</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villa park
+  birmingham </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.7050000000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4776000000000002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3646153846153846</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.047692307692308</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.450000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.903076923076924</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.258461538461539</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.421538461538461</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>21.31273254437341</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>21.07765582559797</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>759.8132481914106</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>760.1530146480472</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13.33333333333334</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>9.880434782608702</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>-12.16666666666666</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>12.47463768115943</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>8.950000000000003</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>13.44307692307693</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>9.299999999999997</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>17.59538461538462</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>159.3333333333334</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-4.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>-8.040000000000003</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-1.605363188515366</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-1.056890473441834</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.01016051987874508</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>-0.006779066752411793</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.1184615384615385</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0.6616161616161591</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.085006313131313</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-0.7134440615751174</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>34828.00433965105</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0.4455430131191924</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>10.27380952380952</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>2.591666666666654</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>53262.18434343436</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>47598809.52380952</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>2.689551767676761</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1.452380952380952</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>3.173327020202024</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1.293315098602022</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>225261.9047619047</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>2.80952380952381</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>2.13492063492064</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>2.223692717586999</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>120.7380952380952</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>13946114.26767677</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>121.6428571428572</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>2.299188454636123</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8303020.845184945</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zypxSHmo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">etihad stadium
+  manchester </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.666</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.9676728110599082</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.335294117647059</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.825490196078432</v>
+      </c>
+      <c r="V18" t="n">
+        <v>15</v>
+      </c>
+      <c r="W18" t="n">
+        <v>11.04117647058824</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.864705882352941</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.823529411764706</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.18328792854655</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>15.90964696220469</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>874.3284842510021</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>883.6829551541744</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>37.6875</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>33</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>47.36607142857143</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>17.16666666666667</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>10.27843137254902</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.6666666666666643</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>6.121568627450984</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>195.9814814814815</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-1.167342799188641</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-1.80392156862745</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-6.330616609370114</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-9.285136481148323</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.002033505977885097</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0.02046109724968038</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0.207843137254902</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0.23715277777778</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.976357323232323</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-0.2573657965653595</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>97738.11561591813</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>1.425023325070087</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-9.892857142857167</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.102525252525268</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>136676.452020202</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>78517857.14285715</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-1.070549242424278</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>10.68942550505051</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8.711044916746673</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>305571.4285714286</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>1.273809523809522</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>7.505565202794955</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>41</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>52238837.59469697</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>41.14285714285714</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-1.01394424915614</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>35001667.75822622</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>viJXIvBU</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>j3Azpf5d</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Wtn9Stg0</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="G19" t="n">
         <v>48</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H19" t="n">
         <v>481</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>20242025</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>va62Pxqi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>GxXzVQFQ</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1.273333333333334</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-1.3048</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="S4" t="n">
-        <v>-1.524444444444445</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-3.833333333333333</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-4.527407407407407</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-4.666666666666668</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-9.482962962962963</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.333333333333333</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-1.474074074074074</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>20.79411764705882</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>25.59308002766895</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1089.059424324118</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1086.681684463652</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-47.83333333333333</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-60.24038461538461</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-43.83333333333334</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-36.51602564102565</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>-11.80888888888889</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>-29.33333333333333</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>-24.52444444444444</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>-328.3333333333334</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>-276.9583333333334</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>-0.416666666666667</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.4966329966329965</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10.83333333333333</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.457455920078463</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.619433638041372</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0.01821357536242923</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>-0.0144675204521035</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>-0.08333333333333331</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>-0.1288888888888889</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>-7.182293169793169</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>-80658.3962026106</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>-4.009731299279636</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>-1.756180856180856</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>-1.184121048124808</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-45073483.04473305</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>-5.264901071457899</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.412902837902863</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.183990869688586</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.924357449089321</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>-28024573.71891831</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-83700000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-127710.7864357864</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>-6.062674362674372</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.2456349206349131</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-2.583333333333332</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>8.666666666666657</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>-323000</v>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.865</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.103547826086957</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.617777777777778</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.933333333333334</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.456296296296296</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>10.16148148148148</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.566666666666666</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.02962962962963</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>15.83270419810668</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>16.26474635100402</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>761.0753869088082</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>806.6041772692249</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>41.08333333333333</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>53.96173913043478</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>45.47826086956522</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>7.866666666666664</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>10.49185185185185</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>14.26666666666667</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>24.14222222222223</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>257.6452173913044</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.319444444444444</v>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-4.133333333333336</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-4.717037037037038</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-4.016818342579656</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-7.191749720323251</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>-0.007411253523882881</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.03090808538764596</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0.3666666666666667</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>-1.380190796857459</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.001747635080968424</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>-4.384094657094053</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1152.436041795314</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-0.07492073592490867</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-12.23690476190473</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>0.2481000481000422</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>6721.653038319702</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>22669047.61904762</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.4674603174603078</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>-0.3809523809523809</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>-1.678479236812578</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>-2.310222852711178</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>67095.23809523808</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>7.434523809523807</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>2.651224286993454</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>-19.16666666666666</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>-2272014.18951419</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>-26.78571428571428</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-0.1678158794818785</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>-233880.0772641692</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>rPPOK0tI</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45591.45833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brentford community stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>481</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.6825</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4124999999999999</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4307692307692308</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.47948717948718</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2.200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.6871794871794865</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-0.09487179487179476</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-0.4846153846153847</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22.24215730112755</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>21.03816188433591</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>797.8221398001135</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>781.1515544524282</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>-1.69047619047619</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>37.66666666666666</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.672619047619051</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>2.200000000000006</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>3.551282051282058</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-6.189743589743586</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>162</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>-0.8262068965517237</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>-7.999999999999996</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-3.24871794871795</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>21.89691291640674</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-1.233390428659883</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>-0.06254635094023217</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.004239086635646191</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.1666666666666667</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.258080808080809</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0.09242774971941659</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>-3.096589581251607</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2733.653953784255</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0.02220474934613237</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-3.576190476190504</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>2.013348765432099</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>10395.63341750843</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>32771428.57142857</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0.8587051066217555</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.4285714285714284</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.391740319865349</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-0.5578257667589526</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>111142.8571428571</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0.2857142857142856</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-2.340476190476195</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>4.00913541342463</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>51.28571428571428</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>4250891.905162739</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>54.85714285714283</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>0.9192316985273692</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>2739792.765546765</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>v5b6XwQN</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45590.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kavanagh c 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">king power stadium
+  leicester </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KrrdAMyI</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>-0.4199999999999997</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8260999999999998</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.377931034482758</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.25655172413793</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7.082758620689656</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.721379310344828</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.928275862068966</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>20.53740981240981</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>17.43967652650897</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>716.299556048328</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>782.2101386212155</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>60.66666666666667</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>86.0402576489533</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>11.16666666666666</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>53.33977455716587</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>10.59999999999999</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>11.48551724137931</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>44.77517241379311</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>178.44</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-1.411034482758621</v>
+      </c>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-4.699999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-6.026206896551722</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-13.13343632678281</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-3.139659475584724</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0.009805502769564663</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0.02541180898762269</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.3903448275862069</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-0.08518518518518903</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0.03518518518518521</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.387452222604445</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-10372.27498211761</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>0.03574786639802108</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-2.190476190476176</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-0.9774691358024654</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>-14503.08641975308</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-9814285.714285715</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>-2.08456790123455</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1.107142857142857</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>-1.532407407407391</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-2.151239413894217</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>321.4285714285652</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-0.8928571428571428</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>-2.321428571428573</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-2.032185515531737</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>66.32142857142858</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>-4193680.555555556</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>74.57142857142858</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-3.886774534375178</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>-4069485.669511469</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,112 +695,112 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_start</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_rep_player_start</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
     </row>
@@ -983,70 +983,70 @@
         <v>0.04120879120879123</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.977777777777781</v>
+        <v>-1.885714285714286</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2969977553310887</v>
+        <v>12651.6835016835</v>
       </c>
       <c r="BD2" t="n">
         <v>3.38421814399122</v>
       </c>
       <c r="BE2" t="n">
+        <v>1.977777777777781</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>643682.7096929122</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>-155.4571428571428</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>363902.9180695843</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.1910637604478183</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.1368125701459064</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>2.948807959915897</v>
+      </c>
+      <c r="BL2" t="n">
         <v>17448.06183130934</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.1910637604478183</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>11.09047619047621</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>-1.663916947250272</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>12651.6835016835</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-32414285.71428572</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.1368125701459064</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>-1.885714285714286</v>
       </c>
       <c r="BM2" t="n">
         <v>1.15286195286194</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.948807959915897</v>
+        <v>-1.663916947250272</v>
       </c>
       <c r="BO2" t="n">
+        <v>-148.4571428571429</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-32414285.71428572</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>-108914.2857142857</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-1.885714285714286</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>3.547619047619051</v>
       </c>
       <c r="BR2" t="n">
         <v>-1.638545740357344</v>
       </c>
       <c r="BS2" t="n">
-        <v>-148.4571428571429</v>
+        <v>3.547619047619051</v>
       </c>
       <c r="BT2" t="n">
-        <v>363902.9180695843</v>
+        <v>0.2969977553310887</v>
       </c>
       <c r="BU2" t="n">
-        <v>-155.4571428571428</v>
+        <v>11.09047619047621</v>
       </c>
       <c r="BV2" t="n">
         <v>1.649782971922576</v>
       </c>
       <c r="BW2" t="n">
-        <v>643682.7096929122</v>
+        <v>-1.885714285714286</v>
       </c>
     </row>
     <row r="3">
@@ -1228,70 +1228,70 @@
         <v>0.03846153846153846</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.107936507936508</v>
+        <v>0.3333333333333335</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.6515873015873015</v>
+        <v>2725.39682539682</v>
       </c>
       <c r="BD3" t="n">
         <v>2.812969258446234</v>
       </c>
       <c r="BE3" t="n">
+        <v>3.107936507936508</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>-6718122.031477295</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>32.90476190476193</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>-1224404.761904765</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0.148175526958422</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>-0.503571428571405</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>-1.096318666713401</v>
+      </c>
+      <c r="BL3" t="n">
         <v>-16829.46929715024</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0.148175526958422</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>-0.6706349206349387</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>-0.9416666666666487</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2725.39682539682</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>20571428.57142857</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>-0.503571428571405</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.3333333333333335</v>
       </c>
       <c r="BM3" t="n">
         <v>0.5498015873015873</v>
       </c>
       <c r="BN3" t="n">
-        <v>-1.096318666713401</v>
+        <v>-0.9416666666666487</v>
       </c>
       <c r="BO3" t="n">
+        <v>45.92857142857142</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>20571428.57142857</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>104309.5238095238</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>2.285714285714286</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>3.178571428571431</v>
       </c>
       <c r="BR3" t="n">
         <v>-2.078729950604952</v>
       </c>
       <c r="BS3" t="n">
-        <v>45.92857142857142</v>
+        <v>3.178571428571431</v>
       </c>
       <c r="BT3" t="n">
-        <v>-1224404.761904765</v>
+        <v>0.6515873015873015</v>
       </c>
       <c r="BU3" t="n">
-        <v>32.90476190476193</v>
+        <v>-0.6706349206349387</v>
       </c>
       <c r="BV3" t="n">
         <v>2.627179098313945</v>
       </c>
       <c r="BW3" t="n">
-        <v>-6718122.031477295</v>
+        <v>2.285714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -1475,70 +1475,70 @@
         <v>0.04000000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.5068542568542576</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4936147186147184</v>
+        <v>8010.533910533908</v>
       </c>
       <c r="BD4" t="n">
         <v>0.4169434625009885</v>
       </c>
       <c r="BE4" t="n">
+        <v>-0.5068542568542576</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4805863.558809757</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>-88.00000000000003</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>14491747.83549784</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.3099442692063252</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.3743867243867385</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.836741160498349</v>
+      </c>
+      <c r="BL4" t="n">
         <v>-4474.686089273979</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.3099442692063252</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>-4.154761904761898</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.632936507936506</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>8010.533910533908</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-8960714.285714276</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.3743867243867385</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>-1.142857142857143</v>
       </c>
       <c r="BM4" t="n">
         <v>2.804401154401148</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.836741160498349</v>
+        <v>2.632936507936506</v>
       </c>
       <c r="BO4" t="n">
+        <v>-90.99999999999997</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-8960714.285714276</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>-96428.57142857142</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>-1.714285714285714</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>-2.761904761904763</v>
       </c>
       <c r="BR4" t="n">
         <v>1.339901082403856</v>
       </c>
       <c r="BS4" t="n">
-        <v>-90.99999999999997</v>
+        <v>-2.761904761904763</v>
       </c>
       <c r="BT4" t="n">
-        <v>14491747.83549784</v>
+        <v>0.4936147186147184</v>
       </c>
       <c r="BU4" t="n">
-        <v>-88.00000000000003</v>
+        <v>-4.154761904761898</v>
       </c>
       <c r="BV4" t="n">
         <v>2.641442564671365</v>
       </c>
       <c r="BW4" t="n">
-        <v>4805863.558809757</v>
+        <v>-1.714285714285714</v>
       </c>
     </row>
     <row r="5">
@@ -1720,70 +1720,70 @@
         <v>0.1456043956043956</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.010069444444444</v>
+        <v>0.3142857142857145</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.03948412698412729</v>
+        <v>-17216.22023809523</v>
       </c>
       <c r="BD5" t="n">
         <v>0.2731710812980168</v>
       </c>
       <c r="BE5" t="n">
+        <v>1.010069444444444</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2325138.337277139</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>25.88571428571427</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-6721845.238095235</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.4038875598086122</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.3457341269841265</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.560293118665129</v>
+      </c>
+      <c r="BL5" t="n">
         <v>-3820.494287560847</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0.4038875598086122</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.92857142857136</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>-0.8827380952380963</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>-17216.22023809523</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-6585714.285714287</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.3457341269841265</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.3142857142857145</v>
       </c>
       <c r="BM5" t="n">
         <v>-1.862847222222229</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.560293118665129</v>
+        <v>-0.8827380952380963</v>
       </c>
       <c r="BO5" t="n">
+        <v>18.80000000000001</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>-6585714.285714287</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>-17428.57142857142</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1.457142857142857</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>-1.676190476190474</v>
       </c>
       <c r="BR5" t="n">
         <v>1.579924025254272</v>
       </c>
       <c r="BS5" t="n">
-        <v>18.80000000000001</v>
+        <v>-1.676190476190474</v>
       </c>
       <c r="BT5" t="n">
-        <v>-6721845.238095235</v>
+        <v>0.03948412698412729</v>
       </c>
       <c r="BU5" t="n">
-        <v>25.88571428571427</v>
+        <v>4.92857142857136</v>
       </c>
       <c r="BV5" t="n">
         <v>-3.233375203705435</v>
       </c>
       <c r="BW5" t="n">
-        <v>2325138.337277139</v>
+        <v>1.457142857142857</v>
       </c>
     </row>
     <row r="6">
@@ -1965,70 +1965,70 @@
         <v>0.2487179487179487</v>
       </c>
       <c r="BB6" t="n">
-        <v>-1.983238636363637</v>
+        <v>-2.571428571428572</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.1934027777777778</v>
+        <v>-104.4823232323251</v>
       </c>
       <c r="BD6" t="n">
         <v>-0.9744944831761124</v>
       </c>
       <c r="BE6" t="n">
+        <v>-1.983238636363637</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-2123322.052837274</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-207.5714285714286</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-4218774.463383839</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>-0.1208626345752248</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0.7081123737373503</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-2.745085104953517</v>
+      </c>
+      <c r="BL6" t="n">
         <v>372.3722041059518</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>-0.1208626345752248</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>-0.4690476190476147</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>-1.576893939393941</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>-104.4823232323251</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>-29557142.85714285</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>-0.7081123737373503</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>-2.571428571428572</v>
       </c>
       <c r="BM6" t="n">
         <v>-3.258617424242431</v>
       </c>
       <c r="BN6" t="n">
-        <v>-2.745085104953517</v>
+        <v>-1.576893939393941</v>
       </c>
       <c r="BO6" t="n">
+        <v>-192</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-29557142.85714285</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>-128714.2857142857</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>-2.571428571428571</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>-0.4119047619047613</v>
       </c>
       <c r="BR6" t="n">
         <v>-1.07711345671872</v>
       </c>
       <c r="BS6" t="n">
-        <v>-192</v>
+        <v>-0.4119047619047613</v>
       </c>
       <c r="BT6" t="n">
-        <v>-4218774.463383839</v>
+        <v>-0.1934027777777778</v>
       </c>
       <c r="BU6" t="n">
-        <v>-207.5714285714286</v>
+        <v>-0.4690476190476147</v>
       </c>
       <c r="BV6" t="n">
         <v>-2.521097779069919</v>
       </c>
       <c r="BW6" t="n">
-        <v>-2123322.052837274</v>
+        <v>-2.571428571428571</v>
       </c>
     </row>
     <row r="7">
@@ -2212,70 +2212,70 @@
         <v>0.3180076628352491</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.466806958473622</v>
+        <v>-0.7333333333333334</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.641849046015713</v>
+        <v>68947.75533108869</v>
       </c>
       <c r="BD7" t="n">
         <v>2.012852196561305</v>
       </c>
       <c r="BE7" t="n">
+        <v>1.466806958473622</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>24181974.71513396</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-48.90000000000001</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>39534111.95286195</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.98638083379805</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.9636363636363683</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.715870565426769</v>
+      </c>
+      <c r="BL7" t="n">
         <v>44446.4179684078</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.98638083379805</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>-4.558333333333337</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>5.390319865319867</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>68947.75533108869</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>16916666.66666666</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.9636363636363683</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>-0.7333333333333334</v>
       </c>
       <c r="BM7" t="n">
         <v>8.77608024691358</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.715870565426769</v>
+        <v>5.390319865319867</v>
       </c>
       <c r="BO7" t="n">
+        <v>-51.83333333333334</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>16916666.66666666</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>-64666.66666666666</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>-8.558333333333334</v>
       </c>
       <c r="BR7" t="n">
         <v>2.767881593903766</v>
       </c>
       <c r="BS7" t="n">
-        <v>-51.83333333333334</v>
+        <v>-8.558333333333334</v>
       </c>
       <c r="BT7" t="n">
-        <v>39534111.95286195</v>
+        <v>1.641849046015713</v>
       </c>
       <c r="BU7" t="n">
-        <v>-48.90000000000001</v>
+        <v>-4.558333333333337</v>
       </c>
       <c r="BV7" t="n">
         <v>3.097383437547421</v>
       </c>
       <c r="BW7" t="n">
-        <v>24181974.71513396</v>
+        <v>-0.8999999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2457,70 +2457,70 @@
         <v>-0.07969639468690703</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.064141414141414</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.2912773569023566</v>
+        <v>1055.76950056116</v>
       </c>
       <c r="BD8" t="n">
         <v>-0.3959888828825875</v>
       </c>
       <c r="BE8" t="n">
+        <v>-1.064141414141414</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-2045736.700138145</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-7.571428571428584</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>-1801114.267676767</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0.2259199878781926</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.544605780022437</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-1.694921638245944</v>
+      </c>
+      <c r="BL8" t="n">
         <v>-1630.222376474958</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>-0.2259199878781926</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>-6.623809523809541</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>-0.1052960157126819</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1055.76950056116</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>-3242857.142857143</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>2.544605780022437</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0</v>
       </c>
       <c r="BM8" t="n">
         <v>-1.493676346801365</v>
       </c>
       <c r="BN8" t="n">
-        <v>-1.694921638245944</v>
+        <v>-0.1052960157126819</v>
       </c>
       <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-3242857.142857143</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>-10000</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>2.414285714285718</v>
       </c>
       <c r="BR8" t="n">
         <v>-1.733541608651265</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>2.414285714285718</v>
       </c>
       <c r="BT8" t="n">
-        <v>-1801114.267676767</v>
+        <v>-0.2912773569023566</v>
       </c>
       <c r="BU8" t="n">
-        <v>-7.571428571428584</v>
+        <v>-6.623809523809541</v>
       </c>
       <c r="BV8" t="n">
         <v>0.6372100594624044</v>
       </c>
       <c r="BW8" t="n">
-        <v>-2045736.700138145</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="9">
@@ -2702,70 +2702,70 @@
         <v>-0.1937321937321937</v>
       </c>
       <c r="BB9" t="n">
-        <v>-1.023611111111109</v>
+        <v>-0.5952380952380951</v>
       </c>
       <c r="BC9" t="n">
-        <v>-2.100662878787879</v>
+        <v>-133452.8409090909</v>
       </c>
       <c r="BD9" t="n">
         <v>-1.208464455436204</v>
       </c>
       <c r="BE9" t="n">
+        <v>-1.023611111111109</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-29531666.41735672</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-64.21428571428572</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-47347440.02525252</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-1.45571243395837</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.2163825757575921</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>-5.087123252564425</v>
+      </c>
+      <c r="BL9" t="n">
         <v>-90233.87781057094</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>-1.45571243395837</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.309523809523824</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>-6.617803030303037</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>-133452.8409090909</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>-65780952.38095239</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.2163825757575921</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>-0.5952380952380951</v>
       </c>
       <c r="BM9" t="n">
         <v>-7.642897727272725</v>
       </c>
       <c r="BN9" t="n">
-        <v>-5.087123252564425</v>
+        <v>-6.617803030303037</v>
       </c>
       <c r="BO9" t="n">
+        <v>-54.02380952380952</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-65780952.38095239</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>-265261.9047619047</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>-1.952380952380953</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.3650793650793638</v>
       </c>
       <c r="BR9" t="n">
         <v>-4.44165973452931</v>
       </c>
       <c r="BS9" t="n">
-        <v>-54.02380952380952</v>
+        <v>0.3650793650793638</v>
       </c>
       <c r="BT9" t="n">
-        <v>-47347440.02525252</v>
+        <v>-2.100662878787879</v>
       </c>
       <c r="BU9" t="n">
-        <v>-64.21428571428572</v>
+        <v>1.309523809523824</v>
       </c>
       <c r="BV9" t="n">
         <v>-0.005607545511765011</v>
       </c>
       <c r="BW9" t="n">
-        <v>-29531666.41735672</v>
+        <v>-1.952380952380953</v>
       </c>
     </row>
     <row r="10">
@@ -2947,70 +2947,70 @@
         <v>-0.1111111111111111</v>
       </c>
       <c r="BB10" t="n">
-        <v>-1.368827160493822</v>
+        <v>0.75</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0.9660493827160495</v>
+        <v>-29043.20987654322</v>
       </c>
       <c r="BD10" t="n">
         <v>-3.076867413632119</v>
       </c>
       <c r="BE10" t="n">
+        <v>-1.368827160493822</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>-5984904.554414356</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-8683641.975308642</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0.8157939101566549</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.6712962962963047</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-1.823410104782653</v>
+      </c>
+      <c r="BL10" t="n">
         <v>-23806.53983815747</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>-0.8157939101566549</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>-1.763888888888886</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>-29043.20987654322</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.6712962962963047</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
         <v>-2.566358024691368</v>
       </c>
       <c r="BN10" t="n">
-        <v>-1.823410104782653</v>
+        <v>-1.763888888888886</v>
       </c>
       <c r="BO10" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>21750</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>-2.5</v>
       </c>
       <c r="BR10" t="n">
         <v>-1.00902972300031</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.75</v>
+        <v>-2.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>-8683641.975308642</v>
+        <v>-0.9660493827160495</v>
       </c>
       <c r="BU10" t="n">
-        <v>59.5</v>
+        <v>9.5</v>
       </c>
       <c r="BV10" t="n">
         <v>2.472766884531609</v>
       </c>
       <c r="BW10" t="n">
-        <v>-5984904.554414356</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -3194,70 +3194,70 @@
         <v>0.01538461538461544</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.749337121212125</v>
+        <v>-0.7142857142857144</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.8051136363636364</v>
+        <v>-38441.57196969702</v>
       </c>
       <c r="BD11" t="n">
         <v>2.207396567551523</v>
       </c>
       <c r="BE11" t="n">
+        <v>1.749337121212125</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-8854322.626496501</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-62.57142857142856</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-25762383.20707072</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0.3900921356573057</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>4.185637626262604</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.05811118861235798</v>
+      </c>
+      <c r="BL11" t="n">
         <v>-16577.33993743084</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-0.3900921356573057</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>7.042857142857116</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-3.46622474747474</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>-38441.57196969702</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>-117942857.1428571</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>4.185637626262604</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>-0.7142857142857144</v>
       </c>
       <c r="BM11" t="n">
         <v>-2.894917929292944</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.05811118861235798</v>
+        <v>-3.46622474747474</v>
       </c>
       <c r="BO11" t="n">
+        <v>-73.57142857142861</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>-117942857.1428571</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>-289142.8571428572</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-2.857142857142856</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>-0.764285714285716</v>
       </c>
       <c r="BR11" t="n">
         <v>-2.812586605969017</v>
       </c>
       <c r="BS11" t="n">
-        <v>-73.57142857142861</v>
+        <v>-0.764285714285716</v>
       </c>
       <c r="BT11" t="n">
-        <v>-25762383.20707072</v>
+        <v>-0.8051136363636364</v>
       </c>
       <c r="BU11" t="n">
-        <v>-62.57142857142856</v>
+        <v>7.042857142857116</v>
       </c>
       <c r="BV11" t="n">
         <v>4.039937774789422</v>
       </c>
       <c r="BW11" t="n">
-        <v>-8854322.626496501</v>
+        <v>-2.857142857142856</v>
       </c>
     </row>
     <row r="12">
@@ -3439,70 +3439,70 @@
         <v>-0.08571428571428574</v>
       </c>
       <c r="BB12" t="n">
-        <v>-1.048074494949496</v>
+        <v>3.114285714285714</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.09539141414141339</v>
+        <v>15746.11742424243</v>
       </c>
       <c r="BD12" t="n">
         <v>-0.8626630722919302</v>
       </c>
       <c r="BE12" t="n">
+        <v>-1.048074494949496</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-5967351.035930127</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>251.4</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1889157.196969703</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.007938363362419931</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1.934122474747454</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>-2.708950640082634</v>
+      </c>
+      <c r="BL12" t="n">
         <v>7477.433353974411</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0.007938363362419931</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>6.623809523809541</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>-0.4660984848484873</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>15746.11742424243</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>141557142.8571429</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>-1.934122474747454</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>3.114285714285714</v>
       </c>
       <c r="BM12" t="n">
         <v>-0.8125315656565562</v>
       </c>
       <c r="BN12" t="n">
-        <v>-2.708950640082634</v>
+        <v>-0.4660984848484873</v>
       </c>
       <c r="BO12" t="n">
+        <v>255.1428571428572</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>141557142.8571429</v>
+      </c>
+      <c r="BQ12" t="n">
         <v>511285.7142857143</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>8.114285714285714</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>2.821428571428573</v>
       </c>
       <c r="BR12" t="n">
         <v>-0.2967887816321735</v>
       </c>
       <c r="BS12" t="n">
-        <v>255.1428571428572</v>
+        <v>2.821428571428573</v>
       </c>
       <c r="BT12" t="n">
-        <v>1889157.196969703</v>
+        <v>0.09539141414141339</v>
       </c>
       <c r="BU12" t="n">
-        <v>251.4</v>
+        <v>6.623809523809541</v>
       </c>
       <c r="BV12" t="n">
         <v>-4.101489339464905</v>
       </c>
       <c r="BW12" t="n">
-        <v>-5967351.035930127</v>
+        <v>8.114285714285714</v>
       </c>
     </row>
     <row r="13">
@@ -3684,70 +3684,70 @@
         <v>-0.103448275862069</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.748853615520279</v>
+        <v>-2</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0.1827601410934747</v>
+        <v>-13596.07583774249</v>
       </c>
       <c r="BD13" t="n">
         <v>1.771054303131507</v>
       </c>
       <c r="BE13" t="n">
+        <v>1.748853615520279</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-5238032.335085034</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-164.0714285714286</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-10215911.59611993</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0.001204716216971491</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0.817724867724877</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0.0937068060842563</v>
+      </c>
+      <c r="BL13" t="n">
         <v>-8854.416739986598</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>-0.001204716216971491</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0.8095238095238244</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>-2.64166666666668</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>-13596.07583774249</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-32071428.57142857</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>-0.817724867724877</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-2</v>
       </c>
       <c r="BM13" t="n">
         <v>-0.7894620811287467</v>
       </c>
       <c r="BN13" t="n">
-        <v>-0.0937068060842563</v>
+        <v>-2.64166666666668</v>
       </c>
       <c r="BO13" t="n">
+        <v>-154.9285714285714</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-32071428.57142857</v>
+      </c>
+      <c r="BQ13" t="n">
         <v>-148642.8571428571</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>-2.785714285714286</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.654761904761902</v>
       </c>
       <c r="BR13" t="n">
         <v>-1.74980345770787</v>
       </c>
       <c r="BS13" t="n">
-        <v>-154.9285714285714</v>
+        <v>4.654761904761902</v>
       </c>
       <c r="BT13" t="n">
-        <v>-10215911.59611993</v>
+        <v>-0.1827601410934747</v>
       </c>
       <c r="BU13" t="n">
-        <v>-164.0714285714286</v>
+        <v>0.8095238095238244</v>
       </c>
       <c r="BV13" t="n">
         <v>-2.838416686118904</v>
       </c>
       <c r="BW13" t="n">
-        <v>-5238032.335085034</v>
+        <v>-2.785714285714286</v>
       </c>
     </row>
     <row r="14">
@@ -3929,70 +3929,70 @@
         <v>-0.08000000000000002</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.1907242063492056</v>
+        <v>0.2571428571428571</v>
       </c>
       <c r="BC14" t="n">
-        <v>-1.310912698412699</v>
+        <v>-39270.28769841272</v>
       </c>
       <c r="BD14" t="n">
         <v>3.059057950563371</v>
       </c>
       <c r="BE14" t="n">
+        <v>0.1907242063492056</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-14349115.34565366</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>10.25714285714287</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-20064702.38095239</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0.8484971577270339</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-1.816369047619048</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-3.635294510700845</v>
+      </c>
+      <c r="BL14" t="n">
         <v>-17653.40441722021</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>-0.8484971577270339</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.980952380952431</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>-3.78710317460316</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>-39270.28769841272</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>-32071428.57142857</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>-1.816369047619048</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.2571428571428571</v>
       </c>
       <c r="BM14" t="n">
         <v>-3.5923115079365</v>
       </c>
       <c r="BN14" t="n">
-        <v>-3.635294510700845</v>
+        <v>-3.78710317460316</v>
       </c>
       <c r="BO14" t="n">
+        <v>11.62857142857141</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-32071428.57142857</v>
+      </c>
+      <c r="BQ14" t="n">
         <v>-80000</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>-3.028571428571429</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.438095238095237</v>
       </c>
       <c r="BR14" t="n">
         <v>-5.929309448291647</v>
       </c>
       <c r="BS14" t="n">
-        <v>11.62857142857141</v>
+        <v>1.438095238095237</v>
       </c>
       <c r="BT14" t="n">
-        <v>-20064702.38095239</v>
+        <v>-1.310912698412699</v>
       </c>
       <c r="BU14" t="n">
-        <v>10.25714285714287</v>
+        <v>2.980952380952431</v>
       </c>
       <c r="BV14" t="n">
         <v>-1.030773320246993</v>
       </c>
       <c r="BW14" t="n">
-        <v>-14349115.34565366</v>
+        <v>-3.028571428571429</v>
       </c>
     </row>
     <row r="15">
@@ -4172,70 +4172,70 @@
         <v>0.1803921568627451</v>
       </c>
       <c r="BB15" t="n">
-        <v>-4.251767676767678</v>
+        <v>-1.333333333333333</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0.5969696969696967</v>
+        <v>-10538.63636363634</v>
       </c>
       <c r="BD15" t="n">
         <v>-2.862983501038201</v>
       </c>
       <c r="BE15" t="n">
+        <v>-4.251767676767678</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8303158.739372946</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-117.7619047619048</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>5724015.151515156</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0.06535335603318049</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-2.842929292929313</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.273205757138939</v>
+      </c>
+      <c r="BL15" t="n">
         <v>10732.3786975361</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>-0.06535335603318049</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>-7.705555555555549</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.525252525252512</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>-10538.63636363634</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>-58614285.71428572</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>-2.842929292929313</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>-1.333333333333333</v>
       </c>
       <c r="BM15" t="n">
         <v>-0.3332070707070613</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.273205757138939</v>
+        <v>2.525252525252512</v>
       </c>
       <c r="BO15" t="n">
+        <v>-125.0714285714286</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-58614285.71428572</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>-235309.5238095238</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>-5.857142857142858</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>-3.290476190476188</v>
       </c>
       <c r="BR15" t="n">
         <v>3.160892107596169</v>
       </c>
       <c r="BS15" t="n">
-        <v>-125.0714285714286</v>
+        <v>-3.290476190476188</v>
       </c>
       <c r="BT15" t="n">
-        <v>5724015.151515156</v>
+        <v>-0.5969696969696967</v>
       </c>
       <c r="BU15" t="n">
-        <v>-117.7619047619048</v>
+        <v>-7.705555555555549</v>
       </c>
       <c r="BV15" t="n">
         <v>-1.601105665108463</v>
       </c>
       <c r="BW15" t="n">
-        <v>8303158.739372946</v>
+        <v>-5.857142857142858</v>
       </c>
     </row>
     <row r="16">
@@ -4417,70 +4417,70 @@
         <v>0.2426108374384237</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.8196969696969667</v>
+        <v>3.314285714285715</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.03749999999999942</v>
+        <v>-20026.76767676767</v>
       </c>
       <c r="BD16" t="n">
         <v>0.5078407182946805</v>
       </c>
       <c r="BE16" t="n">
+        <v>0.8196969696969667</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-1188360.583079893</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>270.7428571428571</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>67133.83838383853</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.02244780061276264</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-1.676262626262627</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0.4932910081141131</v>
+      </c>
+      <c r="BL16" t="n">
         <v>-22676.14823053868</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0.02244780061276264</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>-2.480952380952374</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.3866161616161463</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>-20026.76767676767</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>31453571.42857143</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>-1.676262626262627</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>3.314285714285715</v>
       </c>
       <c r="BM16" t="n">
         <v>-0.07992424242424079</v>
       </c>
       <c r="BN16" t="n">
-        <v>-0.4932910081141131</v>
+        <v>0.3866161616161463</v>
       </c>
       <c r="BO16" t="n">
+        <v>241.4571428571428</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>31453571.42857143</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>97771.42857142858</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>3.457142857142857</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>-4.638095238095239</v>
       </c>
       <c r="BR16" t="n">
         <v>-0.438922406963755</v>
       </c>
       <c r="BS16" t="n">
-        <v>241.4571428571428</v>
+        <v>-4.638095238095239</v>
       </c>
       <c r="BT16" t="n">
-        <v>67133.83838383853</v>
+        <v>0.03749999999999942</v>
       </c>
       <c r="BU16" t="n">
-        <v>270.7428571428571</v>
+        <v>-2.480952380952374</v>
       </c>
       <c r="BV16" t="n">
         <v>0.01627725783734491</v>
       </c>
       <c r="BW16" t="n">
-        <v>-1188360.583079893</v>
+        <v>3.457142857142857</v>
       </c>
     </row>
     <row r="17">
@@ -4662,70 +4662,70 @@
         <v>0.1184615384615385</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.6616161616161591</v>
+        <v>1.452380952380952</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.085006313131313</v>
+        <v>53262.18434343436</v>
       </c>
       <c r="BD17" t="n">
         <v>-0.7134440615751174</v>
       </c>
       <c r="BE17" t="n">
+        <v>0.6616161616161591</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8303020.845184945</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>121.6428571428572</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>13946114.26767677</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.4455430131191924</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2.689551767676761</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1.293315098602022</v>
+      </c>
+      <c r="BL17" t="n">
         <v>34828.00433965105</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0.4455430131191924</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>10.27380952380952</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>2.591666666666654</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>53262.18434343436</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>47598809.52380952</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>2.689551767676761</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1.452380952380952</v>
       </c>
       <c r="BM17" t="n">
         <v>3.173327020202024</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.293315098602022</v>
+        <v>2.591666666666654</v>
       </c>
       <c r="BO17" t="n">
+        <v>120.7380952380952</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>47598809.52380952</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>225261.9047619047</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>2.80952380952381</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>2.13492063492064</v>
       </c>
       <c r="BR17" t="n">
         <v>2.223692717586999</v>
       </c>
       <c r="BS17" t="n">
-        <v>120.7380952380952</v>
+        <v>2.13492063492064</v>
       </c>
       <c r="BT17" t="n">
-        <v>13946114.26767677</v>
+        <v>1.085006313131313</v>
       </c>
       <c r="BU17" t="n">
-        <v>121.6428571428572</v>
+        <v>10.27380952380952</v>
       </c>
       <c r="BV17" t="n">
         <v>2.299188454636123</v>
       </c>
       <c r="BW17" t="n">
-        <v>8303020.845184945</v>
+        <v>2.80952380952381</v>
       </c>
     </row>
     <row r="18">
@@ -4909,70 +4909,70 @@
         <v>0.207843137254902</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.23715277777778</v>
+        <v>0.2857142857142856</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.976357323232323</v>
+        <v>136676.452020202</v>
       </c>
       <c r="BD18" t="n">
         <v>-0.2573657965653595</v>
       </c>
       <c r="BE18" t="n">
+        <v>0.23715277777778</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>35001667.75822622</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>41.14285714285714</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>52238837.59469697</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1.425023325070087</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-1.070549242424278</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>8.711044916746673</v>
+      </c>
+      <c r="BL18" t="n">
         <v>97738.11561591813</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.425023325070087</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>-9.892857142857167</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.102525252525268</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>136676.452020202</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>78517857.14285715</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>-1.070549242424278</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.2857142857142856</v>
       </c>
       <c r="BM18" t="n">
         <v>10.68942550505051</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.711044916746673</v>
+        <v>9.102525252525268</v>
       </c>
       <c r="BO18" t="n">
+        <v>41</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>78517857.14285715</v>
+      </c>
+      <c r="BQ18" t="n">
         <v>305571.4285714286</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>1.273809523809522</v>
       </c>
       <c r="BR18" t="n">
         <v>7.505565202794955</v>
       </c>
       <c r="BS18" t="n">
-        <v>41</v>
+        <v>1.273809523809522</v>
       </c>
       <c r="BT18" t="n">
-        <v>52238837.59469697</v>
+        <v>1.976357323232323</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.14285714285714</v>
+        <v>-9.892857142857167</v>
       </c>
       <c r="BV18" t="n">
         <v>-1.01394424915614</v>
       </c>
       <c r="BW18" t="n">
-        <v>35001667.75822622</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -5154,70 +5154,70 @@
         <v>0.1481481481481481</v>
       </c>
       <c r="BB19" t="n">
-        <v>-1.380190796857459</v>
+        <v>-0.3809523809523809</v>
       </c>
       <c r="BC19" t="n">
-        <v>0.001747635080968424</v>
+        <v>6721.653038319702</v>
       </c>
       <c r="BD19" t="n">
         <v>-4.384094657094053</v>
       </c>
       <c r="BE19" t="n">
+        <v>-1.380190796857459</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-233880.0772641692</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>-26.78571428571428</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>-2272014.18951419</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-0.07492073592490867</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.4674603174603078</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-2.310222852711178</v>
+      </c>
+      <c r="BL19" t="n">
         <v>1152.436041795314</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>-0.07492073592490867</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>-12.23690476190473</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>0.2481000481000422</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>6721.653038319702</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>22669047.61904762</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.4674603174603078</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>-0.3809523809523809</v>
       </c>
       <c r="BM19" t="n">
         <v>-1.678479236812578</v>
       </c>
       <c r="BN19" t="n">
-        <v>-2.310222852711178</v>
+        <v>0.2481000481000422</v>
       </c>
       <c r="BO19" t="n">
+        <v>-19.16666666666666</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>22669047.61904762</v>
+      </c>
+      <c r="BQ19" t="n">
         <v>67095.23809523808</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>0.6428571428571428</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>7.434523809523807</v>
       </c>
       <c r="BR19" t="n">
         <v>2.651224286993454</v>
       </c>
       <c r="BS19" t="n">
-        <v>-19.16666666666666</v>
+        <v>7.434523809523807</v>
       </c>
       <c r="BT19" t="n">
-        <v>-2272014.18951419</v>
+        <v>0.001747635080968424</v>
       </c>
       <c r="BU19" t="n">
-        <v>-26.78571428571428</v>
+        <v>-12.23690476190473</v>
       </c>
       <c r="BV19" t="n">
         <v>-0.1678158794818785</v>
       </c>
       <c r="BW19" t="n">
-        <v>-233880.0772641692</v>
+        <v>0.6428571428571428</v>
       </c>
     </row>
     <row r="20">
@@ -5399,70 +5399,70 @@
         <v>-0.1666666666666667</v>
       </c>
       <c r="BB20" t="n">
-        <v>-0.258080808080809</v>
+        <v>0.4285714285714284</v>
       </c>
       <c r="BC20" t="n">
-        <v>0.09242774971941659</v>
+        <v>10395.63341750843</v>
       </c>
       <c r="BD20" t="n">
         <v>-3.096589581251607</v>
       </c>
       <c r="BE20" t="n">
+        <v>-0.258080808080809</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2739792.765546765</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>54.85714285714283</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4250891.905162739</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0.02220474934613237</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0.8587051066217555</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-0.5578257667589526</v>
+      </c>
+      <c r="BL20" t="n">
         <v>2733.653953784255</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0.02220474934613237</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>-3.576190476190504</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>2.013348765432099</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>10395.63341750843</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>32771428.57142857</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.8587051066217555</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.4285714285714284</v>
       </c>
       <c r="BM20" t="n">
         <v>1.391740319865349</v>
       </c>
       <c r="BN20" t="n">
-        <v>-0.5578257667589526</v>
+        <v>2.013348765432099</v>
       </c>
       <c r="BO20" t="n">
+        <v>51.28571428571428</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>32771428.57142857</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>111142.8571428571</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>0.2857142857142856</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>-2.340476190476195</v>
       </c>
       <c r="BR20" t="n">
         <v>4.00913541342463</v>
       </c>
       <c r="BS20" t="n">
-        <v>51.28571428571428</v>
+        <v>-2.340476190476195</v>
       </c>
       <c r="BT20" t="n">
-        <v>4250891.905162739</v>
+        <v>0.09242774971941659</v>
       </c>
       <c r="BU20" t="n">
-        <v>54.85714285714283</v>
+        <v>-3.576190476190504</v>
       </c>
       <c r="BV20" t="n">
         <v>0.9192316985273692</v>
       </c>
       <c r="BW20" t="n">
-        <v>2739792.765546765</v>
+        <v>0.2857142857142856</v>
       </c>
     </row>
     <row r="21">
@@ -5644,70 +5644,70 @@
         <v>0.3903448275862069</v>
       </c>
       <c r="BB21" t="n">
-        <v>-0.08518518518518903</v>
+        <v>1.107142857142857</v>
       </c>
       <c r="BC21" t="n">
-        <v>0.03518518518518521</v>
+        <v>-14503.08641975308</v>
       </c>
       <c r="BD21" t="n">
         <v>1.387452222604445</v>
       </c>
       <c r="BE21" t="n">
+        <v>-0.08518518518518903</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-4069485.669511469</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>74.57142857142858</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-4193680.555555556</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0.03574786639802108</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-2.08456790123455</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>-2.151239413894217</v>
+      </c>
+      <c r="BL21" t="n">
         <v>-10372.27498211761</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0.03574786639802108</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>-2.190476190476176</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>-0.9774691358024654</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>-14503.08641975308</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>-9814285.714285715</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>-2.08456790123455</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1.107142857142857</v>
       </c>
       <c r="BM21" t="n">
         <v>-1.532407407407391</v>
       </c>
       <c r="BN21" t="n">
-        <v>-2.151239413894217</v>
+        <v>-0.9774691358024654</v>
       </c>
       <c r="BO21" t="n">
+        <v>66.32142857142858</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>-9814285.714285715</v>
+      </c>
+      <c r="BQ21" t="n">
         <v>321.4285714285652</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>-0.8928571428571428</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>-2.321428571428573</v>
       </c>
       <c r="BR21" t="n">
         <v>-2.032185515531737</v>
       </c>
       <c r="BS21" t="n">
-        <v>66.32142857142858</v>
+        <v>-2.321428571428573</v>
       </c>
       <c r="BT21" t="n">
-        <v>-4193680.555555556</v>
+        <v>0.03518518518518521</v>
       </c>
       <c r="BU21" t="n">
-        <v>74.57142857142858</v>
+        <v>-2.190476190476176</v>
       </c>
       <c r="BV21" t="n">
         <v>-3.886774534375178</v>
       </c>
       <c r="BW21" t="n">
-        <v>-4069485.669511469</v>
+        <v>-0.8928571428571428</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW11"/>
+  <dimension ref="A1:BW21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,123 +695,123 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_value_player_sub</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_value_player_miss</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_rat_player_miss</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EqY7Orsg</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45606.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -821,18 +821,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">emirates stadium
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>hA1Zm19f</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,204 +859,206 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>xpALVpwq</t>
+          <t>nJsvYDRG</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>nJsvYDRG</t>
+          <t>lnG1OUjk</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4024999999999999</v>
+        <v>1.9375</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.345370370370371</v>
+        <v>0.3887745098039218</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.2999999999999998</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
-        <v>1.585714285714286</v>
+        <v>0.815873015873016</v>
       </c>
       <c r="T2" t="n">
-        <v>4.950000000000001</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>3.778571428571428</v>
+        <v>0.9164835164835163</v>
       </c>
       <c r="V2" t="n">
-        <v>8.049999999999999</v>
+        <v>16</v>
       </c>
       <c r="W2" t="n">
-        <v>8.661428571428573</v>
+        <v>1.66043956043956</v>
       </c>
       <c r="X2" t="n">
+        <v>0.7499999999999998</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-0.04945054945054927</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.3999999999999998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.03809523809523818</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>14.22652576181988</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>20.90152338106236</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>781.3712693670561</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>887.7228525799995</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>29.83333333333334</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-6.541666666666671</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-12.55208333333334</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7.833333333333336</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.147089947089945</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6.193406593406593</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>52.02639751552795</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.5833333333333335</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-0.03428571428571425</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.766666666666669</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0.707936507936509</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>-9.258778860077031</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>-1.813176008109926</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.00851834744329831</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>-0.02192850920755056</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-0.2275132275132275</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-1.424305555555555</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.44548611111108</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-49984.37499999999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>-574857.1428571428</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.4235978992879694</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>-3413.883545659133</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-212.7142857142857</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>-1.013194444444451</v>
+      </c>
+      <c r="BK2" t="n">
         <v>0.25</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.7785714285714287</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.6342857142857143</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>18.68447693090684</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>19.78705383152251</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>888.5744039633655</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>936.9556303881934</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.16783216783216</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>39.04545454545454</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.599999999999998</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.69285714285714</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>3.200000000000003</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-0.462857142857132</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-50</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-24.49999999999989</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-0.4404761904761907</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.200000000000003</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.437142857142856</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>-6.18243378254941</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>-0.9399569320134553</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0.01013117059361546</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.03292252020111551</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-0.08571428571428574</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-0.01983914935451381</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-0.5153679653679575</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-0.8861111111111128</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.1104617604617597</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>15745.92352092353</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>-0.8492424242424192</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>998142.1356421486</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>-0.5833333333333321</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-6108605.265552796</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>2.666666666666657</v>
-      </c>
       <c r="BL2" t="n">
-        <v>167</v>
+        <v>-19005381.94444444</v>
       </c>
       <c r="BM2" t="n">
-        <v>-2.913120459414188</v>
+        <v>-2.602430555555554</v>
       </c>
       <c r="BN2" t="n">
-        <v>220000000</v>
+        <v>-3.379513888888894</v>
       </c>
       <c r="BO2" t="n">
-        <v>6642.576894338068</v>
+        <v>-0.3919534281984227</v>
       </c>
       <c r="BP2" t="n">
-        <v>-4.079423190680956</v>
+        <v>-4.459523809523809</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-2.159920634920667</v>
+        <v>1.944098900638508</v>
       </c>
       <c r="BR2" t="n">
-        <v>2</v>
+        <v>451989.8305038437</v>
       </c>
       <c r="BS2" t="n">
-        <v>172</v>
+        <v>-206128571.4285714</v>
       </c>
       <c r="BT2" t="n">
-        <v>-1.01651289894588</v>
+        <v>2.135365108845519</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.2082347980558268</v>
+        <v>-9.714285714285715</v>
       </c>
       <c r="BV2" t="n">
-        <v>497000</v>
+        <v>-229.8571428571428</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>-0.4851608683237707</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcDtwrdn</t>
+          <t>hY71igYg</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1066,13 +1068,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stamford bridge
-  london </t>
+          <t xml:space="preserve">city ground
+  nottingham </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4fGZN2oK</t>
+          <t>UsushcZr</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1104,223 +1106,223 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lnG1OUjk</t>
+          <t>GlJdeJqp</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>hbOpz9hE</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0175</v>
+        <v>-0.2815000000000003</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.163960292580982</v>
+        <v>0.1179743589743589</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.211764705882353</v>
+        <v>-0.296996662958843</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>0.4666666666666659</v>
       </c>
       <c r="U3" t="n">
-        <v>3.713725490196079</v>
+        <v>1.089861751152074</v>
       </c>
       <c r="V3" t="n">
-        <v>4.199999999999998</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="W3" t="n">
-        <v>7.664705882352941</v>
+        <v>4.305299539170507</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>-0.03333333333333344</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.080392156862745</v>
+        <v>-0.2108294930875576</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.523529411764706</v>
+        <v>-0.3303670745272524</v>
       </c>
       <c r="AB3" t="n">
-        <v>22.14322677322677</v>
+        <v>25.27732274261686</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.03242812225172</v>
+        <v>19.64695073054424</v>
       </c>
       <c r="AD3" t="n">
-        <v>972.5757180759391</v>
+        <v>942.8825525186382</v>
       </c>
       <c r="AE3" t="n">
-        <v>866.3645645242561</v>
+        <v>978.1624780016411</v>
       </c>
       <c r="AF3" t="n">
-        <v>24.66666666666669</v>
+        <v>2.666666666666671</v>
       </c>
       <c r="AG3" t="n">
-        <v>35.69642857142857</v>
+        <v>-4.986263736263737</v>
       </c>
       <c r="AH3" t="n">
-        <v>-4.333333333333329</v>
+        <v>13.00000000000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>19.62053571428572</v>
+        <v>0.5796703296703285</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-10.2</v>
+        <v>-6.166666666666664</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.927450980392159</v>
+        <v>-2.659621802002221</v>
       </c>
       <c r="AL3" t="n">
-        <v>-4</v>
+        <v>-22.06666666666667</v>
       </c>
       <c r="AM3" t="n">
-        <v>16.61960784313726</v>
+        <v>-14.29147465437787</v>
       </c>
       <c r="AN3" t="n">
-        <v>-123.5</v>
+        <v>-178.4499999999999</v>
       </c>
       <c r="AO3" t="n">
-        <v>125.5925925925926</v>
+        <v>-156.48</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.6</v>
+        <v>1.233333333333333</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.1941176470588233</v>
+        <v>-0.2198327359617682</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>9.999999999999996</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.654901960784315</v>
+        <v>8.877641824249164</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.955327394041593</v>
+        <v>4.452388756821236</v>
       </c>
       <c r="AW3" t="n">
-        <v>-4.453829242797788</v>
+        <v>1.798028018302668</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.01896372510622004</v>
+        <v>0.0330214027381326</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.002678222792586921</v>
+        <v>0.0153342333929286</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1803921568627451</v>
+        <v>-0.1056729699666296</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.1082920199579034</v>
+        <v>-1.207751623376623</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.346117424242422</v>
+        <v>-3.482918470418497</v>
       </c>
       <c r="BD3" t="n">
-        <v>-4.226939033189034</v>
+        <v>-51476.94805194804</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.6210452741702741</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="BF3" t="n">
-        <v>-10959.28932178931</v>
+        <v>-217190.4761904762</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.4544462481962483</v>
+        <v>-1.361427508679839</v>
       </c>
       <c r="BH3" t="n">
-        <v>5501373.444264073</v>
+        <v>-34207.27740182076</v>
       </c>
       <c r="BI3" t="n">
-        <v>-8.25</v>
+        <v>-154.8809523809524</v>
       </c>
       <c r="BJ3" t="n">
-        <v>6972089.001868691</v>
+        <v>-3.259438131313132</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.25</v>
+        <v>-0.3095238095238244</v>
       </c>
       <c r="BL3" t="n">
-        <v>-249</v>
+        <v>-15666563.06367243</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.9921558246504389</v>
+        <v>-0.5912247474747474</v>
       </c>
       <c r="BN3" t="n">
-        <v>-65100000</v>
+        <v>-3.430041486291486</v>
       </c>
       <c r="BO3" t="n">
-        <v>8736.709515345225</v>
+        <v>-0.7178653035560929</v>
       </c>
       <c r="BP3" t="n">
-        <v>-1.643541963236629</v>
+        <v>0.7317460317460309</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-2.590259740259739</v>
+        <v>-1.294558882165319</v>
       </c>
       <c r="BR3" t="n">
-        <v>-3</v>
+        <v>-8451468.419915352</v>
       </c>
       <c r="BS3" t="n">
-        <v>-250</v>
+        <v>-47303571.42857143</v>
       </c>
       <c r="BT3" t="n">
-        <v>-2.888502539173569</v>
+        <v>-0.3151740996361525</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.087435632147589</v>
+        <v>-4.261904761904762</v>
       </c>
       <c r="BV3" t="n">
-        <v>-325000</v>
+        <v>-144.8095238095238</v>
       </c>
       <c r="BW3" t="n">
-        <v>-8</v>
+        <v>-1.171777118864973</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zD1kyMQb</t>
+          <t>KK9ggF3s</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bond d 
+          <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">selhurst park
-  london </t>
+          <t xml:space="preserve">old trafford
+  manchester </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AovF1Mia</t>
+          <t>ppjDR086</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UDg08Ohm</t>
+          <t>KrrdAMyI</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1347,225 +1349,227 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>MeAQUqrN</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>joAFj9hO</t>
+          <t>IoJ2QpOs</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5525</v>
+        <v>0.7425000000000002</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3108333333333333</v>
+        <v>-0.05432500000000018</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.08</v>
+        <v>0.02142857142857146</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.8</v>
+        <v>6.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3599999999999999</v>
+        <v>1.42156862745098</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.599999999999998</v>
+        <v>13.8</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639999999999999</v>
+        <v>3.725490196078429</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3599999999999999</v>
+        <v>-0.3289760348583879</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0.6000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0.2142857142857144</v>
       </c>
       <c r="AB4" t="n">
-        <v>25.00537185037185</v>
+        <v>16.52668025211504</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.41103568000627</v>
+        <v>21.29356477256028</v>
       </c>
       <c r="AD4" t="n">
-        <v>1033.321240211614</v>
+        <v>831.8244013741178</v>
       </c>
       <c r="AE4" t="n">
-        <v>1075.367774456912</v>
+        <v>830.1229313467695</v>
       </c>
       <c r="AF4" t="n">
-        <v>-31.33333333333333</v>
+        <v>48.33333333333333</v>
       </c>
       <c r="AG4" t="n">
-        <v>-36.08695652173913</v>
+        <v>14.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>-23</v>
+        <v>41</v>
       </c>
       <c r="AI4" t="n">
-        <v>-6.260869565217384</v>
+        <v>21.095</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-11.8</v>
+        <v>6</v>
       </c>
       <c r="AK4" t="n">
-        <v>-3</v>
+        <v>2.407142857142858</v>
       </c>
       <c r="AL4" t="n">
-        <v>-36.80000000000001</v>
+        <v>10.40000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>-33.84</v>
+        <v>-5.385620915032675</v>
       </c>
       <c r="AN4" t="n">
-        <v>-335.5</v>
+        <v>147.25</v>
       </c>
       <c r="AO4" t="n">
-        <v>-331.9891304347826</v>
+        <v>181.2499999999999</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.65</v>
+        <v>-0.1999999999999997</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.4166666666666665</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>0.07070707070707138</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
       <c r="AS4" t="n">
-        <v>-0.5</v>
+        <v>0.5333333333333332</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.7999999999999972</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.399999999999999</v>
+        <v>5.514285714285714</v>
       </c>
       <c r="AV4" t="n">
-        <v>37.87571471156625</v>
+        <v>-23.75585603617756</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.63068276658319</v>
+        <v>-17.41765975561781</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.002605212041826475</v>
+        <v>0.03136790969224593</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.008865481970736701</v>
+        <v>0.03504319374300962</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.4</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.08000000000000002</v>
+        <v>-0.1714285714285714</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.8787516313113393</v>
+        <v>1.08640873015873</v>
       </c>
       <c r="BC4" t="n">
-        <v>-3.820254629629616</v>
+        <v>2.357242063492066</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.2276620370370352</v>
+        <v>57634.623015873</v>
       </c>
       <c r="BE4" t="n">
-        <v>-1.325925925925926</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-39412.38425925928</v>
+        <v>126857.1428571428</v>
       </c>
       <c r="BG4" t="n">
-        <v>-3.650231481481498</v>
+        <v>4.817373526671133</v>
       </c>
       <c r="BH4" t="n">
-        <v>-20280451.3888889</v>
+        <v>39827.1238345203</v>
       </c>
       <c r="BI4" t="n">
-        <v>-1.666666666666668</v>
+        <v>19.71428571428572</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-14547461.41485057</v>
+        <v>5.1750496031746</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.166666666666657</v>
+        <v>-8.214285714285722</v>
       </c>
       <c r="BL4" t="n">
-        <v>72</v>
+        <v>23653287.45039683</v>
       </c>
       <c r="BM4" t="n">
-        <v>-3.788739286046905</v>
+        <v>-0.1579365079365047</v>
       </c>
       <c r="BN4" t="n">
-        <v>-34400000</v>
+        <v>4.828918650793653</v>
       </c>
       <c r="BO4" t="n">
-        <v>-17823.67970682323</v>
+        <v>0.7158929209335549</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.8874618931120608</v>
+        <v>0.3404761904761884</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-1.967361111111074</v>
+        <v>3.495978279975958</v>
       </c>
       <c r="BR4" t="n">
-        <v>1</v>
+        <v>13634576.98852146</v>
       </c>
       <c r="BS4" t="n">
-        <v>69</v>
+        <v>36914285.71428572</v>
       </c>
       <c r="BT4" t="n">
-        <v>2.943821535484513</v>
+        <v>3.650348066858356</v>
       </c>
       <c r="BU4" t="n">
-        <v>-5.977021545951203</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BV4" t="n">
-        <v>-72000</v>
+        <v>20.85714285714286</v>
       </c>
       <c r="BW4" t="n">
-        <v>-2</v>
+        <v>-0.3775773509471279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EJlHkLuh</t>
+          <t>CzO2kX26</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">coote d 
+          <t xml:space="preserve">smith l 
   eng </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">london stadium
+          <t xml:space="preserve">tottenham hotspur stadium
   london </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cxq57r8g</t>
+          <t>UDg08Ohm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ppjDR086</t>
+          <t>thqhB2MB</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1592,225 +1596,227 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0K79iBXL</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>va62Pxqi</t>
+          <t>pdaUMZYd</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3880000000000001</v>
+        <v>3.1445</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03001436781609157</v>
+        <v>0.7490999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.2</v>
+        <v>3.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.103448275862069</v>
+        <v>1.098014888337469</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8000000000000007</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3275862068965516</v>
+        <v>1.516129032258064</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="W5" t="n">
-        <v>1.759946949602121</v>
+        <v>5.014193548387095</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6000000000000001</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.02254641909814303</v>
+        <v>0.663225806451613</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.06763925729442954</v>
+        <v>0.554590570719603</v>
       </c>
       <c r="AB5" t="n">
-        <v>22.33531087270218</v>
+        <v>15.72211218732958</v>
       </c>
       <c r="AC5" t="n">
-        <v>24.0179034719913</v>
+        <v>18.73980090001609</v>
       </c>
       <c r="AD5" t="n">
-        <v>998.8140351609502</v>
+        <v>650.9736961307113</v>
       </c>
       <c r="AE5" t="n">
-        <v>989.7971985991728</v>
+        <v>673.8247849275517</v>
       </c>
       <c r="AF5" t="n">
-        <v>-48.66666666666667</v>
+        <v>68.33333333333333</v>
       </c>
       <c r="AG5" t="n">
-        <v>-4.763888888888886</v>
+        <v>35.39285714285714</v>
       </c>
       <c r="AH5" t="n">
-        <v>-28</v>
+        <v>64.33333333333333</v>
       </c>
       <c r="AI5" t="n">
-        <v>4.300925925925924</v>
+        <v>32.93167701863354</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-11.8</v>
+        <v>8.433333333333326</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.03580901856764</v>
+        <v>11.84367245657568</v>
       </c>
       <c r="AL5" t="n">
-        <v>-12.40000000000001</v>
+        <v>33</v>
       </c>
       <c r="AM5" t="n">
-        <v>-13.32360742705571</v>
+        <v>19.24645161290323</v>
       </c>
       <c r="AN5" t="n">
-        <v>-171.25</v>
+        <v>405.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>-137.375</v>
+        <v>455.76</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.5999999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.3485714285714288</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>-1.541666666666667</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-2</v>
+      </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.8000000000000007</v>
+        <v>-1.566666666666666</v>
       </c>
       <c r="AU5" t="n">
-        <v>-5.388594164456233</v>
+        <v>-4.44044665012407</v>
       </c>
       <c r="AV5" t="n">
-        <v>13.93371910218216</v>
+        <v>-17.9521779219404</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.854639460291327</v>
+        <v>-14.62832228947592</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0002690457239593533</v>
+        <v>-0.04725862853084527</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.003532523175472646</v>
+        <v>0.01635686092761426</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.103448275862069</v>
+        <v>-0.1228287841191067</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01601542860734018</v>
+        <v>1.688311688311688</v>
       </c>
       <c r="BC5" t="n">
-        <v>-2.544791666666683</v>
+        <v>1.027417027417016</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.680208333333336</v>
+        <v>66185.4256854257</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.1506944444444445</v>
+        <v>-0.5714285714285716</v>
       </c>
       <c r="BF5" t="n">
-        <v>-12998.61111111111</v>
+        <v>157857.1428571429</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.6934027777777629</v>
+        <v>7.42672774575415</v>
       </c>
       <c r="BH5" t="n">
-        <v>-10166493.05555555</v>
+        <v>37064.21181833059</v>
       </c>
       <c r="BI5" t="n">
-        <v>-3.199999999999999</v>
+        <v>-16.85714285714286</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-4841698.302718531</v>
+        <v>6.506493506493527</v>
       </c>
       <c r="BK5" t="n">
-        <v>-4.800000000000011</v>
+        <v>1.214285714285694</v>
       </c>
       <c r="BL5" t="n">
-        <v>-326</v>
+        <v>33434487.73448773</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.1910609917043757</v>
+        <v>0.02409812409812773</v>
       </c>
       <c r="BN5" t="n">
-        <v>-49000000</v>
+        <v>7.972005772005787</v>
       </c>
       <c r="BO5" t="n">
-        <v>-9174.718765711397</v>
+        <v>0.9208650362979205</v>
       </c>
       <c r="BP5" t="n">
-        <v>-2.709491713352008</v>
+        <v>-2.738095238095237</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.9010416666666856</v>
+        <v>6.014267032724007</v>
       </c>
       <c r="BR5" t="n">
-        <v>-4</v>
+        <v>19601847.48595795</v>
       </c>
       <c r="BS5" t="n">
-        <v>-313</v>
+        <v>55700000</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.519334127881923</v>
+        <v>3.87731580486448</v>
       </c>
       <c r="BU5" t="n">
-        <v>-1.710215111685699</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="BV5" t="n">
-        <v>-344000</v>
+        <v>-21.28571428571428</v>
       </c>
       <c r="BW5" t="n">
-        <v>-8</v>
+        <v>-1.912271963441249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rw5cZaeB</t>
+          <t>0zTMbytK</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brooks j 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">goodison park
+          <t xml:space="preserve">anfield
   liverpool </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KluSTr9s</t>
+          <t>lId4TMwf</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>W00wmLO0</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1837,225 +1843,227 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>pdaUMZYd</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8QQVnKh9</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6600000000000001</v>
+        <v>0.8700000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9923076923076926</v>
+        <v>1.963314285714286</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.4999999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.791871921182266</v>
+        <v>2.644444444444445</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1666666666666665</v>
+        <v>5.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.476600985221674</v>
+        <v>6.446949602122015</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9999999999999982</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>4.873152709359607</v>
+        <v>14.96684350132626</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.7999999999999996</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5652709359605912</v>
+        <v>1.823607427055703</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5357142857142856</v>
+        <v>1.533333333333333</v>
       </c>
       <c r="AB6" t="n">
-        <v>20.37657227032227</v>
+        <v>18.2134216952638</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.79920745666209</v>
+        <v>16.86452346966026</v>
       </c>
       <c r="AD6" t="n">
-        <v>967.3161358240334</v>
+        <v>796.3087177333479</v>
       </c>
       <c r="AE6" t="n">
-        <v>946.9180953062432</v>
+        <v>806.8729193950549</v>
       </c>
       <c r="AF6" t="n">
-        <v>-6.5</v>
+        <v>48.66666666666667</v>
       </c>
       <c r="AG6" t="n">
-        <v>18.76780626780626</v>
+        <v>55.60576923076924</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.75</v>
+        <v>31.83333333333334</v>
       </c>
       <c r="AI6" t="n">
-        <v>17.3974358974359</v>
+        <v>46.4871794871795</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.5</v>
+        <v>4.166666666666668</v>
       </c>
       <c r="AK6" t="n">
-        <v>-2.532019704433495</v>
+        <v>-0.7740740740740684</v>
       </c>
       <c r="AL6" t="n">
-        <v>-23.33333333333333</v>
+        <v>10.8</v>
       </c>
       <c r="AM6" t="n">
-        <v>-12.71428571428571</v>
+        <v>18.82758620689656</v>
       </c>
       <c r="AN6" t="n">
-        <v>-184.75</v>
+        <v>169.75</v>
       </c>
       <c r="AO6" t="n">
-        <v>-113.2481884057971</v>
+        <v>205.76</v>
       </c>
       <c r="AP6" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-0.8000000000000003</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.4572158365261816</v>
-      </c>
-      <c r="AR6" t="inlineStr"/>
+        <v>-1.527065527065527</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-1</v>
+      </c>
       <c r="AS6" t="n">
-        <v>-1</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>-2.333333333333332</v>
+        <v>-0.1666666666666643</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.6108374384236477</v>
+        <v>6.640740740740739</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.97414562307254</v>
+        <v>-4.829177338061779</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.054312790331013</v>
+        <v>-10.47725408096047</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.02016699316966819</v>
+        <v>0.04233854540675239</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.006572878005234178</v>
+        <v>0.02353612610593558</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2426108374384237</v>
+        <v>0.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0359680614036435</v>
+        <v>0.8441919191919189</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.5134740259739914</v>
+        <v>0.3359848484848555</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.7352092352092292</v>
+        <v>26747.9797979798</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01547619047619042</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="BF6" t="n">
-        <v>-20209.16305916306</v>
+        <v>-128880.9523809524</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01534992784992539</v>
+        <v>2.139234635501793</v>
       </c>
       <c r="BH6" t="n">
-        <v>222081.52958153</v>
+        <v>17865.00135900523</v>
       </c>
       <c r="BI6" t="n">
-        <v>-5.857142857142858</v>
+        <v>-81.88095238095238</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-1501727.084536308</v>
+        <v>3.507196969696977</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.9285714285714164</v>
+        <v>-10.61904761904762</v>
       </c>
       <c r="BL6" t="n">
-        <v>258</v>
+        <v>24574684.34343434</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.5031666698426562</v>
+        <v>0.7669191919191931</v>
       </c>
       <c r="BN6" t="n">
-        <v>31200000</v>
+        <v>4.354797979797979</v>
       </c>
       <c r="BO6" t="n">
-        <v>-23382.98818792745</v>
+        <v>0.7308126263039023</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.2700809420758503</v>
+        <v>-3.113095238095241</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-1.76473665223665</v>
+        <v>3.819619624035397</v>
       </c>
       <c r="BR6" t="n">
-        <v>3</v>
+        <v>15705371.81330302</v>
       </c>
       <c r="BS6" t="n">
-        <v>209</v>
+        <v>12801190.47619047</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.8525708080815164</v>
+        <v>1.400313979736836</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.5625377078342098</v>
+        <v>-1.904761904761904</v>
       </c>
       <c r="BV6" t="n">
-        <v>3000</v>
+        <v>-86.45238095238093</v>
       </c>
       <c r="BW6" t="n">
-        <v>2</v>
+        <v>1.354566938591532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ABRGMMB5</t>
+          <t>6HqKvGll</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">madley a 
+          <t xml:space="preserve">harrington t 
   eng </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">villa park
-  birmingham </t>
+          <t xml:space="preserve">amex stadium
+  brighton </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>W00wmLO0</t>
+          <t>2XrRecc3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OtpNdwrc</t>
+          <t>Wtn9Stg0</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2082,208 +2090,208 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>GxXzVQFQ</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>lAbHYaQM</t>
+          <t>Aotm1TVI</t>
         </is>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7050000000000001</v>
+        <v>-0.02150000000000007</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4776000000000002</v>
+        <v>-0.5430128205128204</v>
       </c>
       <c r="R7" t="n">
-        <v>0.75</v>
+        <v>-0.1714285714285712</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3646153846153846</v>
+        <v>-0.1923076923076924</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7</v>
+        <v>-1.892857142857143</v>
       </c>
       <c r="U7" t="n">
-        <v>2.047692307692308</v>
+        <v>-2.115384615384615</v>
       </c>
       <c r="V7" t="n">
-        <v>1.450000000000001</v>
+        <v>-3.892857142857142</v>
       </c>
       <c r="W7" t="n">
-        <v>3.903076923076924</v>
+        <v>-2.307692307692307</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>-0.2500000000000002</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.258461538461539</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>-0.08571428571428608</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.421538461538461</v>
+        <v>-0.8589743589743588</v>
       </c>
       <c r="AB7" t="n">
-        <v>21.31273254437341</v>
+        <v>22.6710203220044</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.07765582559797</v>
+        <v>21.97785004481574</v>
       </c>
       <c r="AD7" t="n">
-        <v>759.8132481914106</v>
+        <v>1009.061664772888</v>
       </c>
       <c r="AE7" t="n">
-        <v>760.1530146480472</v>
+        <v>1022.420830005881</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.33333333333334</v>
+        <v>-13.75</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.880434782608702</v>
+        <v>-26.10326086956522</v>
       </c>
       <c r="AH7" t="n">
-        <v>-12.16666666666666</v>
+        <v>-21</v>
       </c>
       <c r="AI7" t="n">
-        <v>12.47463768115943</v>
+        <v>-11.23007246376812</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.950000000000003</v>
+        <v>-5.857142857142858</v>
       </c>
       <c r="AK7" t="n">
-        <v>13.44307692307693</v>
+        <v>-5.794871794871792</v>
       </c>
       <c r="AL7" t="n">
-        <v>9.299999999999997</v>
+        <v>-20.57142857142857</v>
       </c>
       <c r="AM7" t="n">
-        <v>17.59538461538462</v>
+        <v>-9.92307692307692</v>
       </c>
       <c r="AN7" t="n">
-        <v>124.75</v>
+        <v>-208.75</v>
       </c>
       <c r="AO7" t="n">
-        <v>159.3333333333334</v>
+        <v>-93.90333333333336</v>
       </c>
       <c r="AP7" t="n">
-        <v>-3</v>
+        <v>0.8333333333333335</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-1.12</v>
+        <v>0.2626086956521738</v>
       </c>
       <c r="AR7" t="inlineStr"/>
       <c r="AS7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>-4.199999999999999</v>
+        <v>0.428571428571427</v>
       </c>
       <c r="AU7" t="n">
-        <v>-8.040000000000003</v>
+        <v>1.984330484330485</v>
       </c>
       <c r="AV7" t="n">
-        <v>-1.605363188515366</v>
+        <v>10.20314503620335</v>
       </c>
       <c r="AW7" t="n">
-        <v>-1.056890473441834</v>
+        <v>1.711966276908386</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.01016051987874508</v>
+        <v>0.003349221906793383</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.006779066752411793</v>
+        <v>0.006937907919860375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.35</v>
+        <v>-0.05714285714285716</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.1184615384615385</v>
+        <v>-0.2222222222222222</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.4343620830205739</v>
+        <v>-1.717297979797979</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.537662337662326</v>
+        <v>2.711868686868684</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.6334776334776286</v>
+        <v>-120782.4494949495</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.050974025974026</v>
+        <v>-0.6666666666666665</v>
       </c>
       <c r="BF7" t="n">
-        <v>51873.95382395383</v>
+        <v>-234357.1428571428</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.039357864357882</v>
+        <v>-1.784367913685443</v>
       </c>
       <c r="BH7" t="n">
-        <v>13527016.5945166</v>
+        <v>-73333.96948530337</v>
       </c>
       <c r="BI7" t="n">
-        <v>-3</v>
+        <v>-71.71428571428572</v>
       </c>
       <c r="BJ7" t="n">
-        <v>7727942.190415444</v>
+        <v>-5.476388888888906</v>
       </c>
       <c r="BK7" t="n">
-        <v>4</v>
+        <v>2.342460317460365</v>
       </c>
       <c r="BL7" t="n">
-        <v>4</v>
+        <v>-48064507.57575758</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.7841968473819065</v>
+        <v>-1.081186868686871</v>
       </c>
       <c r="BN7" t="n">
-        <v>500000</v>
+        <v>-8.447853535353516</v>
       </c>
       <c r="BO7" t="n">
-        <v>33061.93693239033</v>
+        <v>-1.18176331635453</v>
       </c>
       <c r="BP7" t="n">
-        <v>2.21267796176096</v>
+        <v>7.74404761904762</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.676948051948045</v>
+        <v>-4.904651756407546</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>-26519029.58215059</v>
       </c>
       <c r="BS7" t="n">
-        <v>-2</v>
+        <v>-62342857.14285715</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.9038000159497983</v>
+        <v>0.5869959379193119</v>
       </c>
       <c r="BU7" t="n">
-        <v>2.078778071800087</v>
+        <v>-3.333333333333333</v>
       </c>
       <c r="BV7" t="n">
-        <v>14000</v>
+        <v>-59</v>
       </c>
       <c r="BW7" t="n">
-        <v>-2</v>
+        <v>-2.507968130814199</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rPPOK0tI</t>
+          <t>nX2mpxRQ</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">smith l 
+          <t xml:space="preserve">kavanagh c 
   eng </t>
         </is>
       </c>
@@ -2300,7 +2308,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>thqhB2MB</t>
+          <t>OtpNdwrc</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2327,225 +2335,225 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>dpjHQ7zJ</t>
+          <t>va62Pxqi</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>xpALVpwq</t>
         </is>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6825</v>
+        <v>1.482</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4124999999999999</v>
+        <v>0.3624769230769236</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4307692307692308</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="T8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.47948717948718</v>
+        <v>1.25925925925926</v>
       </c>
       <c r="V8" t="n">
-        <v>2.200000000000001</v>
+        <v>-0.3333333333333339</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6871794871794865</v>
+        <v>0.8518518518518512</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.09487179487179476</v>
+        <v>0.5925925925925923</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.4846153846153847</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="AB8" t="n">
-        <v>22.24215730112755</v>
+        <v>26.12577383630015</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.03816188433591</v>
+        <v>24.06910878727365</v>
       </c>
       <c r="AD8" t="n">
-        <v>797.8221398001135</v>
+        <v>807.8754815592688</v>
       </c>
       <c r="AE8" t="n">
-        <v>781.1515544524282</v>
+        <v>811.3516750090439</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>6.000000000000014</v>
       </c>
       <c r="AG8" t="n">
-        <v>-1.69047619047619</v>
+        <v>1.666666666666671</v>
       </c>
       <c r="AH8" t="n">
-        <v>37.66666666666666</v>
+        <v>-0.3333333333333286</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.672619047619051</v>
+        <v>3.041666666666671</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.200000000000006</v>
+        <v>10</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.551282051282058</v>
+        <v>6.111111111111107</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>5.833333333333336</v>
       </c>
       <c r="AM8" t="n">
-        <v>-6.189743589743586</v>
+        <v>7.592592592592581</v>
       </c>
       <c r="AN8" t="n">
-        <v>162</v>
+        <v>40.80000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>203.75</v>
+        <v>71.20000000000005</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.8262068965517237</v>
+        <v>-0.8076923076923077</v>
       </c>
       <c r="AR8" t="inlineStr"/>
       <c r="AS8" t="n">
-        <v>0.25</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="AT8" t="n">
-        <v>-7.999999999999996</v>
+        <v>-9.000000000000004</v>
       </c>
       <c r="AU8" t="n">
-        <v>-3.24871794871795</v>
+        <v>-3.703703703703706</v>
       </c>
       <c r="AV8" t="n">
-        <v>21.89691291640674</v>
+        <v>21.81573724080199</v>
       </c>
       <c r="AW8" t="n">
-        <v>-1.233390428659883</v>
+        <v>3.792585224753777</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.06254635094023217</v>
+        <v>-0.02819839692237198</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.004239086635646191</v>
+        <v>0.0007021775392603916</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.01652465810885784</v>
+        <v>-0.006096681096680934</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.173980880230886</v>
+        <v>3.448647186147213</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.4453823953823957</v>
+        <v>4143.163780663774</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.07987463924963945</v>
+        <v>1.619047619047619</v>
       </c>
       <c r="BF8" t="n">
-        <v>9034.406565656565</v>
+        <v>112380.9523809524</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.238888888888908</v>
+        <v>0.4012342815914138</v>
       </c>
       <c r="BH8" t="n">
-        <v>4069530.573593073</v>
+        <v>-4478.090611244494</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0.8500000000000014</v>
+        <v>126.8571428571428</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2487392.714212879</v>
+        <v>0.2506493506493683</v>
       </c>
       <c r="BK8" t="n">
-        <v>-6.050000000000011</v>
+        <v>1.220634920634893</v>
       </c>
       <c r="BL8" t="n">
-        <v>-51</v>
+        <v>-1358390.151515152</v>
       </c>
       <c r="BM8" t="n">
-        <v>-1.042797568588853</v>
+        <v>0.2389971139971152</v>
       </c>
       <c r="BN8" t="n">
-        <v>38200000</v>
+        <v>-0.8338383838383692</v>
       </c>
       <c r="BO8" t="n">
-        <v>1587.051410476481</v>
+        <v>-0.1301536144760933</v>
       </c>
       <c r="BP8" t="n">
-        <v>1.407540582022278</v>
+        <v>0.4468253968253961</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.7646464646464608</v>
+        <v>-3.834635388246213</v>
       </c>
       <c r="BR8" t="n">
-        <v>-1</v>
+        <v>-3146267.237008438</v>
       </c>
       <c r="BS8" t="n">
-        <v>-45</v>
+        <v>19630952.38095238</v>
       </c>
       <c r="BT8" t="n">
-        <v>-3.190745815870208</v>
+        <v>1.729129265342465</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.663467053488077</v>
+        <v>-0.3809523809523809</v>
       </c>
       <c r="BV8" t="n">
-        <v>97000</v>
+        <v>125.0238095238095</v>
       </c>
       <c r="BW8" t="n">
-        <v>-1</v>
+        <v>-1.910018022360465</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>viJXIvBU</t>
+          <t>YTzyyYmD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">oliver m 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">amex stadium
-  brighton </t>
+          <t xml:space="preserve">selhurst park
+  london </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2XrRecc3</t>
+          <t>AovF1Mia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>j3Azpf5d</t>
+          <t>69ZiU2Om</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2572,225 +2580,225 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>hbOpz9hE</t>
+          <t>CznGurCt</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>hxNijWrJ</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.865</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.103547826086957</v>
+        <v>0.8384296296296294</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="S9" t="n">
-        <v>1.617777777777778</v>
+        <v>1.623342175066313</v>
       </c>
       <c r="T9" t="n">
-        <v>4.933333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>4.456296296296296</v>
+        <v>2.169761273209549</v>
       </c>
       <c r="V9" t="n">
-        <v>9.4</v>
+        <v>1.333333333333332</v>
       </c>
       <c r="W9" t="n">
-        <v>10.16148148148148</v>
+        <v>4.372679045092839</v>
       </c>
       <c r="X9" t="n">
-        <v>2.566666666666666</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.02962962962963</v>
+        <v>0.8793103448275863</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.84</v>
+        <v>0.6326259946949602</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.83270419810668</v>
+        <v>20.91994757887615</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.26474635100402</v>
+        <v>19.10447280745366</v>
       </c>
       <c r="AD9" t="n">
-        <v>761.0753869088082</v>
+        <v>935.2695353246698</v>
       </c>
       <c r="AE9" t="n">
-        <v>806.6041772692249</v>
+        <v>944.5259277725452</v>
       </c>
       <c r="AF9" t="n">
-        <v>41.08333333333333</v>
+        <v>33.08333333333333</v>
       </c>
       <c r="AG9" t="n">
-        <v>53.96173913043478</v>
+        <v>15.03511705685618</v>
       </c>
       <c r="AH9" t="n">
-        <v>37.5</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="AI9" t="n">
-        <v>45.47826086956522</v>
+        <v>19.68729096989967</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.866666666666664</v>
+        <v>-2.880952380952383</v>
       </c>
       <c r="AK9" t="n">
-        <v>10.49185185185185</v>
+        <v>-0.5901856763925792</v>
       </c>
       <c r="AL9" t="n">
-        <v>14.26666666666667</v>
+        <v>-16.38095238095238</v>
       </c>
       <c r="AM9" t="n">
-        <v>24.14222222222223</v>
+        <v>-6.824933687002655</v>
       </c>
       <c r="AN9" t="n">
-        <v>100</v>
+        <v>-116</v>
       </c>
       <c r="AO9" t="n">
-        <v>257.6452173913044</v>
+        <v>-47.065</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-0.2380952380952379</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-1.319444444444444</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>-4.133333333333336</v>
+        <v>-2.61904761904762</v>
       </c>
       <c r="AU9" t="n">
-        <v>-4.717037037037038</v>
+        <v>-3.179045092838194</v>
       </c>
       <c r="AV9" t="n">
-        <v>-4.016818342579656</v>
+        <v>30.86974997601108</v>
       </c>
       <c r="AW9" t="n">
-        <v>-7.191749720323251</v>
+        <v>9.742233575746498</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.007411253523882881</v>
+        <v>0.05990044240317996</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.03090808538764596</v>
+        <v>0.006714700780004017</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.3666666666666667</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.1481481481481481</v>
+        <v>0.1114058355437666</v>
       </c>
       <c r="BB9" t="n">
-        <v>-0.03984848776206995</v>
+        <v>-0.05138888888888915</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.3390993265993245</v>
+        <v>-1.970138888888869</v>
       </c>
       <c r="BD9" t="n">
-        <v>-1.845075757575763</v>
+        <v>4378.819444444438</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.05193602693602717</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="BF9" t="n">
-        <v>4950.252525252523</v>
+        <v>55333.33333333333</v>
       </c>
       <c r="BG9" t="n">
-        <v>-1.908543771043767</v>
+        <v>-1.313947325688474</v>
       </c>
       <c r="BH9" t="n">
-        <v>-2562310.606060605</v>
+        <v>-2751.735169659019</v>
       </c>
       <c r="BI9" t="n">
-        <v>6</v>
+        <v>97.83333333333334</v>
       </c>
       <c r="BJ9" t="n">
-        <v>-129195.6495820358</v>
+        <v>2.627430555555563</v>
       </c>
       <c r="BK9" t="n">
-        <v>-5.533333333333331</v>
+        <v>-1.999999999999943</v>
       </c>
       <c r="BL9" t="n">
-        <v>-156</v>
+        <v>8815798.611111112</v>
       </c>
       <c r="BM9" t="n">
-        <v>-2.246698919018755</v>
+        <v>-1.784375000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>26000000</v>
+        <v>1.82430555555554</v>
       </c>
       <c r="BO9" t="n">
-        <v>2017.718168503103</v>
+        <v>-0.2204730576441105</v>
       </c>
       <c r="BP9" t="n">
-        <v>-0.06091562656544625</v>
+        <v>-3.027777777777782</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.4754629629629505</v>
+        <v>-0.4206856789245137</v>
       </c>
       <c r="BR9" t="n">
-        <v>-2</v>
+        <v>513161.8935713116</v>
       </c>
       <c r="BS9" t="n">
-        <v>-137</v>
+        <v>23116666.66666666</v>
       </c>
       <c r="BT9" t="n">
-        <v>-4.218871195113163</v>
+        <v>0.5025854077328518</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.607627322867629</v>
+        <v>1</v>
       </c>
       <c r="BV9" t="n">
-        <v>71000</v>
+        <v>89.83333333333334</v>
       </c>
       <c r="BW9" t="n">
-        <v>-1</v>
+        <v>1.195670428735948</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zypxSHmo</t>
+          <t>K0RAmBXI</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45591.45833333334</v>
+        <v>45605.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">harrington t 
+          <t xml:space="preserve">brooks j 
   eng </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">etihad stadium
-  manchester </t>
+          <t xml:space="preserve">london stadium
+  london </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wtn9Stg0</t>
+          <t>Cxq57r8g</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WdKOwxDM</t>
+          <t>KluSTr9s</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2817,441 +2825,2895 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4rSZHs2M</t>
+          <t>joAFj9hO</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GlJdeJqp</t>
+          <t>GxXzVQFQ</t>
         </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.666</v>
+        <v>0.8714999999999998</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9676728110599082</v>
+        <v>0.408953846153846</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>0.7000000000000002</v>
       </c>
       <c r="S10" t="n">
-        <v>1.335294117647059</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.666666666666667</v>
+        <v>1.583333333333333</v>
       </c>
       <c r="U10" t="n">
-        <v>2.825490196078432</v>
+        <v>0.7136752136752142</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>2.833333333333334</v>
       </c>
       <c r="W10" t="n">
-        <v>11.04117647058824</v>
+        <v>2.33903133903134</v>
       </c>
       <c r="X10" t="n">
-        <v>1.833333333333333</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.864705882352941</v>
+        <v>0.7635327635327633</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.823529411764706</v>
+        <v>0.7777777777777779</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.18328792854655</v>
+        <v>21.21758288599721</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.90964696220469</v>
+        <v>21.87048200306344</v>
       </c>
       <c r="AD10" t="n">
-        <v>874.3284842510021</v>
+        <v>783.5634443229901</v>
       </c>
       <c r="AE10" t="n">
-        <v>883.6829551541744</v>
+        <v>868.0834747821843</v>
       </c>
       <c r="AF10" t="n">
-        <v>-1</v>
+        <v>27.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>37.6875</v>
+        <v>-11.41666666666667</v>
       </c>
       <c r="AH10" t="n">
-        <v>33</v>
+        <v>-9.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>47.36607142857143</v>
+        <v>-2.291666666666664</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.16666666666667</v>
+        <v>-1.599999999999998</v>
       </c>
       <c r="AK10" t="n">
-        <v>10.27843137254902</v>
+        <v>4.074074074074076</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.6666666666666643</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="AM10" t="n">
-        <v>6.121568627450984</v>
+        <v>7.826210826210826</v>
       </c>
       <c r="AN10" t="n">
-        <v>122.25</v>
+        <v>168.35</v>
       </c>
       <c r="AO10" t="n">
-        <v>195.9814814814815</v>
+        <v>79.97666666666669</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>-0.1666666666666667</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-1.167342799188641</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
+        <v>-0.609230769230769</v>
+      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>2.566666666666663</v>
       </c>
       <c r="AU10" t="n">
-        <v>-1.80392156862745</v>
+        <v>-7.074074074074073</v>
       </c>
       <c r="AV10" t="n">
-        <v>-6.330616609370114</v>
+        <v>-9.6287491564122</v>
       </c>
       <c r="AW10" t="n">
-        <v>-9.285136481148323</v>
+        <v>1.819151873733935</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.002033505977885097</v>
+        <v>-0.02905034857886928</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.02046109724968038</v>
+        <v>-0.02664756283244316</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.207843137254902</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.409863657768346</v>
+        <v>0.8056096681096683</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.915584415584433</v>
+        <v>0.05853625541121232</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.4186507936507944</v>
+        <v>39123.62914862914</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.919011544011544</v>
+        <v>-3.428571428571429</v>
       </c>
       <c r="BF10" t="n">
-        <v>135661.9769119769</v>
+        <v>-99000</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.74188311688312</v>
+        <v>2.144605272178808</v>
       </c>
       <c r="BH10" t="n">
-        <v>51229703.28282828</v>
+        <v>36551.32690022395</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0.3333333333333321</v>
+        <v>-272.5714285714286</v>
       </c>
       <c r="BJ10" t="n">
-        <v>35413575.56427368</v>
+        <v>2.230424783549779</v>
       </c>
       <c r="BK10" t="n">
-        <v>-3.800000000000011</v>
+        <v>-7.480952380952374</v>
       </c>
       <c r="BL10" t="n">
-        <v>196</v>
+        <v>10190963.65440116</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.313379149966948</v>
+        <v>-0.3931682900432811</v>
       </c>
       <c r="BN10" t="n">
-        <v>152200000</v>
+        <v>3.036305014430027</v>
       </c>
       <c r="BO10" t="n">
-        <v>94353.94629665141</v>
+        <v>0.6786005558983501</v>
       </c>
       <c r="BP10" t="n">
-        <v>-1.238839723105542</v>
+        <v>4.242857142857147</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0.8028499278499623</v>
+        <v>3.193652374994286</v>
       </c>
       <c r="BR10" t="n">
-        <v>2</v>
+        <v>7586589.457927693</v>
       </c>
       <c r="BS10" t="n">
-        <v>186</v>
+        <v>-10142857.14285714</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0.7488032281984083</v>
+        <v>-2.551085658622412</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.634948264976458</v>
+        <v>-1.904761904761905</v>
       </c>
       <c r="BV10" t="n">
-        <v>605000</v>
+        <v>-244.7142857142857</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>1.873358014534482</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v5b6XwQN</t>
+          <t>0d4cBEPP</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45605.5</v>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1845000000000001</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.4911057692307688</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.5852216748768474</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.5428571428571427</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-1.314285714285715</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.085714285714285</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.2857142857142858</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.2142857142857144</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0.1891625615763548</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>19.34570665256698</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>23.42294224015464</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1065.42055136325</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1008.733456185842</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-67.33333333333333</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-44.67788461538461</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-32.58333333333334</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-20.87019230769231</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-6.214285714285715</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-6.832512315270936</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-41.02857142857142</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-27.64285714285714</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-334</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-167.6171428571428</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0.157142857142857</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>11.76190476190476</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.895566502463057</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3.556402517810991</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-1.039956244277963</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.03653527780558282</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.03447107723128854</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.4523809523809523</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.07487684729064041</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.1481481481481488</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.74636243386243</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7032.738095238099</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>88285.71428571429</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.661335002501801</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>12772.27929449291</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>80.28571428571428</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>3.215608465608454</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>3.445238095238096</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>6739533.73015873</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.2321428571428612</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>3.392526455026442</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.273284411451981</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.6666666666666714</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>3.733822552146862</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>6322563.092222534</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>15100000</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0.7694761078275292</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>76.85714285714286</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.8964366966882444</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ratYowuH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">craven cottage
+  london </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>69ZiU2Om</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>xYe7DwID</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>481</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vBIoDoo1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>pdaUMZYd</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2155555555555551</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5521978021978023</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.392857142857142</v>
+      </c>
+      <c r="V12" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7.192307692307692</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6675824175824174</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.582417582417582</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>16.32671258184988</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18.28475840710841</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>864.0890708403604</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>811.631631034975</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>48.81730769230769</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>63.16666666666666</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>36.28205128205128</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>9.598901098901099</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>-3.599999999999994</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>16.57692307692308</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>194.8765217391305</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.06552706552706566</v>
+      </c>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>-2.052197802197803</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-13.0655034637207</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-7.510588563964713</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.04529053688436585</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.01766887663929214</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.04120879120879123</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.3372474747474747</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0.2006313131313107</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>13468.93939393941</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>-1.452380952380952</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-76380.95238095238</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-1.568228088336781</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>18976.80404589372</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-121.6904761904762</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-1.572474747474757</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>10.80714285714288</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>426862.3737373743</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>2.027272727272727</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.243560606060612</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0.1676091269841269</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>3.414285714285718</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>3.351241157694972</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1102060.310990337</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-27014285.71428572</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1.876669254658395</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>-114.8571428571429</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>3.300534851621812</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zil0kCo9</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">old trafford
+  manchester </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ppjDR086</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4fGZN2oK</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>48</v>
+      </c>
+      <c r="H13" t="n">
+        <v>481</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>joAFj9hO</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>hbOpz9hE</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.2749999999999997</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3222615384615386</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.132478632478632</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.449999999999999</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.756410256410255</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.699999999999999</v>
+      </c>
+      <c r="W13" t="n">
+        <v>5.012820512820511</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.1438746438746437</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.5512820512820513</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.39545322621696</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>21.70090009706729</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>981.3238883712061</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>978.6748829013491</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.984999999999999</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-2.899999999999999</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>3.019943019943014</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-11.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-10.13675213675214</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-164.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-118.01</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.4500000000000002</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.6495726495726495</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.809116809116809</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0.2241021413151074</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.562009169250826</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.03052719013781589</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.01219290129318897</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.6968253968253968</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.3281746031746025</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5331.150793650784</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.7142857142857144</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>127857.1428571428</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-2.186071220446209</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-18349.64473574673</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>63.57142857142858</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0.702380952380949</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-2.309523809523824</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>154910.7142857127</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>3.13373015873016</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.9091269841269991</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.08289774918064396</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>3.785714285714285</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-1.402145734382572</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-8258270.579931758</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>26142857.14285714</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>2.425664896141853</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>3.142857142857142</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>2.932768757193099</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>drzevnw8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">pawson c 
   eng </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">king power stadium
-  leicester </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tottenham hotspur stadium
+  london </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UDg08Ohm</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>W00wmLO0</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>48</v>
+      </c>
+      <c r="H14" t="n">
+        <v>481</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>CznGurCt</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>xpALVpwq</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.1725</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7392000000000003</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.301538461538461</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.653846153846153</v>
+      </c>
+      <c r="V14" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.586153846153845</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.9999999999999998</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.7215384615384615</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0.8999999999999999</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.3876923076923078</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>15.59690205929336</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>19.13295051146706</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>752.3199405888154</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>804.5429237101957</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>40.66666666666667</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>31.875</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>31.33333333333334</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>33.55072463768116</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.253846153846155</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>169</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>181.72</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.8666666666666663</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-1.105769230769231</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>-3.300000000000001</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.044615384615387</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-7.877571899982385</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-7.88353577106491</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.0170650536814863</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.02022457865906983</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.5258658008658004</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0.4453102453102531</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8288.311688311689</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>-73857.14285714287</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.289203720125599</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-3594.594469292657</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-76.42857142857144</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>2.569444444444457</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-3.083333333333343</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>14579283.91053391</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>-0.4553030303030283</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>2.894300144300146</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.3344686622968949</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>-1.904761904761905</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.009214316427403</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>5267957.615182303</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-2460714.285714284</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>2.510037919479998</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-1.285714285714286</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>-79.14285714285714</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.5765052038642011</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EJ4unbdE</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">taylor a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">molineux stadium
+  wolverhampton </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>j3Azpf5d</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AovF1Mia</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
+      </c>
+      <c r="H15" t="n">
+        <v>481</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0K79iBXL</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.08750000000000024</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1429692307692314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2380952380952382</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0582010582010577</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-4.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.4232804232804224</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4854497354497354</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.5999999999999999</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.5595238095238095</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>21.36106334841629</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>21.26802696082636</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>973.808294259961</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>838.5311605466284</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-12.66666666666666</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>14.34461538461538</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.999999999999993</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>12.59230769230768</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>-7.800000000000008</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0.8955026455026385</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>-19.59999999999999</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>16.38888888888889</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-215</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>151.24</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.04857142857142893</v>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.600000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.636243386243383</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9.50598087183365</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-4.497247069964455</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.02420812002615851</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.0105951981835002</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0.1812169312169312</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.08981481481481524</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.019675925925895</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-16178.81944444444</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-26952.38095238095</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.923702289927135</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>-4735.807963536296</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>12.14285714285714</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.4237268518518533</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>2.921428571428521</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-5834131.944444446</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.095486111111114</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-1.378009259259258</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.4162297315257844</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>-1.293650793650787</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.642052295399822</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>2584610.159255089</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-10788095.23809524</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-3.14559214435377</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>4.452380952380935</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0.02486689651937368</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OGMmt88e</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley a 
+  eng </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  mary s stadium
+  southampton </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>WdKOwxDM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KluSTr9s</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>48</v>
+      </c>
+      <c r="H16" t="n">
+        <v>481</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>hxNijWrJ</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GxXzVQFQ</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.1200000000000002</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.14151098901099</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.638461538461538</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.935897435897436</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8.487179487179487</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.582051282051282</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.346153846153846</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>23.90656745215569</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>17.61946537238637</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>741.2996457022426</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>786.2610652659041</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>57.24404761904761</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44.61904761904762</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>11.42564102564102</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>48.04102564102564</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>275.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>239.1666666666667</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1.583333333333333</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-6.666666666666666</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-8.253187599156162</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-2.890093071010179</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0.01754297382483105</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0.01294005594560308</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.2487179487179487</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>-0.1180014430014431</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0.6247474747474939</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2014.502164502155</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-117571.4285714286</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-1.934341509883311</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3087.605612266991</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-185.7142857142857</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-1.120021645021623</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0.7547619047618923</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>-3342493.686868687</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>-2.019408369408364</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>-2.641522366522352</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0.1251103632779327</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.2547619047619065</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-2.144263500087803</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>-2858854.928858122</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-24714285.71428571</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>-2.841790403439006</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>-168.2857142857143</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0.03911958730553877</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>21YvrUwq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">city ground
+  nottingham </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UsushcZr</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Cxq57r8g</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>481</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>GlJdeJqp</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>dpjHQ7zJ</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1099999999999999</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7092307692307691</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7817460317460319</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.199999999999999</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.66931216931217</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="W17" t="n">
+        <v>8.33994708994709</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8000000000000003</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7843915343915344</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-0.08730158730158721</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.31797702297702</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>19.97856079720724</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>778.3265701806803</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>870.2499485837517</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5.233974358974365</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>41.16666666666667</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>14.90705128205128</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.5846560846560891</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>9.800000000000004</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>4.062169312169324</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>70.01999999999998</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-1.296296296296296</v>
+      </c>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>-0.8333333333333333</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.62037037037037</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>24.96323444277492</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.7109104519695695</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.0828436072778812</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.022035248622157</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>-0.06878306878306878</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-1.040674603174603</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0.4476686507936734</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>-28906.74603174604</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>37666.66666666667</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.7382442720678171</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-20610.40566867772</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>77.83333333333334</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>-1.935763888888872</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>8.333333333333343</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>-9363467.261904761</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>-1.241319444444446</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-2.675843253968253</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>-0.8048232914960856</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0.7777777777777821</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>-1.371616771708688</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>-4638916.058410544</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1.915783460820222</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-3.158506719995692</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>MqhPmaA4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oliver m 
+  eng </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vitality stadium
+  bournemouth </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OtpNdwrc</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Wtn9Stg0</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
+      </c>
+      <c r="H18" t="n">
+        <v>481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>8QQVnKh9</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Aotm1TVI</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.3374999999999997</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.5955128205128204</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.4829059829059827</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-3.264957264957265</v>
+      </c>
+      <c r="V18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-4.257834757834759</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-1.125356125356125</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-1.508547008547009</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>23.46519544052439</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>23.52497122355394</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1138.326511762885</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1100.790940882064</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>-46.46499999999999</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-48</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-24.02833333333334</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>-9.914529914529915</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-50</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-37.60113960113959</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>-473.25</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-376.44</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.0322061191626406</v>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.910256410256412</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>17.14331995550746</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>10.20788198607952</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.009608280382732613</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>-0.001471773567170154</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.1937321937321937</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-2.068272005772005</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0.3013528138528159</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>-131707.3051948052</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>-371523.8095238095</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>-4.471320614032621</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-84971.85133331336</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>-123.7142857142857</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>-6.351533189033205</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.2174603174603362</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>-47028169.19191919</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>-1.150992063492062</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>-7.353661616161617</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-1.348469915738961</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-1.075396825396826</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-4.418395231052784</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-27966344.75081132</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>-90059523.80952382</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>-0.3721261984273951</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>-4.333333333333334</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-114.1666666666667</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0.895351937701836</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rc1ER8g2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anfield
+  liverpool </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>lId4TMwf</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2XrRecc3</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>48</v>
+      </c>
+      <c r="H19" t="n">
+        <v>481</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lAbHYaQM</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4rSZHs2M</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.5025</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.99978835978836</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.720306513409962</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5.94125159642401</v>
+      </c>
+      <c r="V19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>14.47254150702427</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.047254150702426</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.720306513409962</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>21.49810700994912</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>18.43164874217108</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>851.3181912767902</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>962.7208286487376</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>38.05076923076923</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>35.75384615384616</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>5.149999999999999</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>6.554278416347387</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3.272030651340998</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>7.453846153846087</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-1.185185185185185</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.1142857142857141</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.037037037037035</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>-4.955734357606179</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.5990821427615902</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.04130097037336451</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0.0001073923237880012</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0.3180076628352491</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.560606060606061</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0.5527777777778056</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>67902.27272727274</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>-0.3333333333333335</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>-47666.66666666666</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.973939103673501</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>40778.36523053159</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>-12.16666666666666</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>5.032449494949503</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>-3.263888888888914</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>38728207.07070707</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>1.527020202020207</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>8.337626262626259</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.9879719980097308</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>5.508439416956719</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>22940990.19828183</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>29533333.33333333</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>3.076988236656177</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>-20.16666666666666</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>1.901489647632502</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>lb85TUOk</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45598.5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">robinson t 
+  eng </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">portman road
+  ipswich </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>thqhB2MB</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>KrrdAMyI</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>UsushcZr</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="G20" t="n">
         <v>48</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H20" t="n">
         <v>481</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>20242025</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>england</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>premier league</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Aotm1TVI</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>CznGurCt</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>-0.4199999999999997</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.8260999999999998</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.377931034482758</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>va62Pxqi</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>IoJ2QpOs</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4925000000000002</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.604616935483871</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-0.1499999999999999</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4383301707779885</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.31404174573055</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.850000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7.929791271347248</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.1537001897533206</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-1.5</v>
       </c>
-      <c r="U11" t="n">
-        <v>2.25655172413793</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>7.082758620689656</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.721379310344828</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.8999999999999999</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.928275862068966</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>20.53740981240981</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>17.43967652650897</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>716.299556048328</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>782.2101386212155</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>60.66666666666667</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>86.0402576489533</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>11.16666666666666</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>53.33977455716587</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>10.59999999999999</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>11.48551724137931</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>44.77517241379311</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>251.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>178.44</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>-1.411034482758621</v>
-      </c>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="n">
+      <c r="AA20" t="n">
+        <v>0.3757115749525617</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>16.21770118770119</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>16.48025259798602</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>826.0726896287683</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>809.447173640694</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11.83333333333333</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>7.275862068965509</v>
+      </c>
+      <c r="AH20" t="n">
         <v>-1</v>
       </c>
-      <c r="AT11" t="n">
-        <v>-4.699999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>-6.026206896551722</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>-13.13343632678281</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>-3.139659475584724</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0.009805502769564663</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0.02541180898762269</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>-0.09999999999999998</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.3903448275862069</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0.03756067204209623</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>-0.8709490740740762</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.3009259259259238</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0.08078703703703716</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>-15305.78703703703</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>-1.538310185185182</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>-3819094.328703703</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>-4189025.31592934</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>137</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>-2.16227460619875</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>-21300000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>-10176.65619554165</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>-3.44534342076912</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>-2.090046296296293</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>130</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1.606196250429999</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>-2.217464428416449</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>29000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>0</v>
+      <c r="AI20" t="n">
+        <v>26.65086206896552</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>4.032258064516128</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>-2.299999999999997</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>-8.166982922201129</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>173.6999999999999</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.4818181818181821</v>
+      </c>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.649999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>5.219165085388992</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-22.13720780681475</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-18.16196771013285</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.04828416574787624</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.03219626947044651</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-0.07969639468690703</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-0.3046807359307357</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.432602813852839</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1784.514790764784</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>-0.4285714285714284</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>-35285.71428571429</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>-1.626219522896875</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>-2337.186629037598</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>-39.85714285714286</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>-0.02906295093796984</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>-6.142857142857139</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>-1625198.299963925</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>-1.060209235209236</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>-1.347055375180389</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>-0.2561511446683944</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>2.554761904761904</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>-1.773640508835101</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>-2312913.812454806</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>-5714285.714285714</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0.4951688570165231</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>-0.4285714285714284</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>-31.42857142857144</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>-0.5166578034722633</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>WIs9mjGL</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45598.39583333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brooks j 
+  eng </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  james  park
+  newcastle </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>p6ahwuwJ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>hA1Zm19f</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>481</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>premier league</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>nJsvYDRG</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.0475</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3291666666666667</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.5030769230769232</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1292307692307699</v>
+      </c>
+      <c r="V21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.9061538461538472</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.007692307692307887</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.05538461538461537</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>16.93838494838495</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>21.49150308953996</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>850.5780246862568</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>921.8527181012627</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-74.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>-26.50757575757576</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>-14.84469696969698</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>7.450000000000003</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.46153846153846</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>8.099999999999994</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>-9.052307692307693</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-96.25</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>-93.39130434782601</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>-1.35</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>-0.7533333333333334</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0.9461538461538446</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0.2516986662851277</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.092113132455507</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.03462043131160777</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>-0.02014435442144367</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.04999999999999999</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0.01538461538461544</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>-0.7113952020202023</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.31253156565657</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-36226.67297979798</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>-0.9999999999999996</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>-346285.7142857143</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>-3.106643339950949</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>-16520.79414881587</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>-90.14285714285711</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>-3.042645202020196</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>-23243779.19823232</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.599905303030305</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>-2.561773989898981</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>-0.4418886355349456</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0.1261904761904731</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0.3398316454908468</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>-9113816.450391687</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>-153682142.8571429</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>4.391262483744413</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>-98.42857142857139</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>2.397836243998036</v>
       </c>
     </row>
   </sheetData>

--- a/data/england/p6_deployment/data_preparation/df_constructed.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_constructed.xlsx
@@ -695,144 +695,144 @@
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_start</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_wage_player_miss</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>dif_sum_pot_player_miss</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_start</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_start</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_start</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_value_player_miss</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_start</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_value_player_miss</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_wage_player_miss</t>
-        </is>
-      </c>
-      <c r="BN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="BO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="BU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="BV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ratYowuH</t>
+          <t>CEnSxfJ0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">attwell s 
+          <t xml:space="preserve">oliver m 
   eng </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">craven cottage
+          <t xml:space="preserve">stamford bridge
   london </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69ZiU2Om</t>
+          <t>4fGZN2oK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>xYe7DwID</t>
+          <t>hA1Zm19f</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -859,208 +859,210 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>vBIoDoo1</t>
+          <t>4fYy95jc</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Y39YvFx6</t>
+          <t>lAbHYaQM</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2155555555555551</v>
+        <v>0.3993411764705882</v>
       </c>
       <c r="R2" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5521978021978023</v>
+        <v>0.8357142857142859</v>
       </c>
       <c r="T2" t="n">
-        <v>6.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.392857142857142</v>
+        <v>0.8285714285714287</v>
       </c>
       <c r="V2" t="n">
-        <v>15.05</v>
+        <v>9.999999